--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5896,10 +5896,10 @@
         <v>447.350006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1237</v>
+        <v>5.1259</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9496</v>
+        <v>5.9594</v>
       </c>
       <c r="H62" t="n">
         <v>7718.600098</v>
@@ -5920,10 +5920,10 @@
         <v>96.279999</v>
       </c>
       <c r="N62" t="n">
-        <v>1309.75</v>
+        <v>1293.75</v>
       </c>
       <c r="O62" t="n">
-        <v>536.75</v>
+        <v>512</v>
       </c>
       <c r="P62" t="n">
         <v>4.355791</v>
@@ -5938,10 +5938,10 @@
         <v>-0.445087</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.30027</v>
+        <v>-1.257898</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.998645</v>
+        <v>-0.835574</v>
       </c>
       <c r="V62" t="n">
         <v>0.422318</v>
@@ -5962,10 +5962,10 @@
         <v>6.398498</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.705352</v>
+        <v>1.450696</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.223301</v>
+        <v>-0.582524</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5899,7 +5899,7 @@
         <v>5.1259</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9594</v>
+        <v>5.9606</v>
       </c>
       <c r="H62" t="n">
         <v>7718.600098</v>
@@ -5941,7 +5941,7 @@
         <v>-1.257898</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.835574</v>
+        <v>-0.8156099999999999</v>
       </c>
       <c r="V62" t="n">
         <v>0.422318</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185147</v>
+        <v>188913.453125</v>
       </c>
       <c r="C62" t="n">
-        <v>181.940002</v>
+        <v>186.029999</v>
       </c>
       <c r="D62" t="n">
-        <v>110.989998</v>
+        <v>112.760002</v>
       </c>
       <c r="E62" t="n">
-        <v>447.350006</v>
+        <v>439.269989</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1259</v>
+        <v>5.0806</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9606</v>
+        <v>5.9044</v>
       </c>
       <c r="H62" t="n">
-        <v>7718.600098</v>
+        <v>7684.339844</v>
       </c>
       <c r="I62" t="n">
-        <v>26506.990234</v>
+        <v>26390.132812</v>
       </c>
       <c r="J62" t="n">
-        <v>53414.25</v>
+        <v>52819.558594</v>
       </c>
       <c r="K62" t="n">
-        <v>4476.600098</v>
+        <v>4442</v>
       </c>
       <c r="L62" t="n">
-        <v>91.480003</v>
+        <v>93.269997</v>
       </c>
       <c r="M62" t="n">
-        <v>96.279999</v>
+        <v>98.08000199999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1293.75</v>
+        <v>1307.25</v>
       </c>
       <c r="O62" t="n">
-        <v>512</v>
+        <v>535.5</v>
       </c>
       <c r="P62" t="n">
-        <v>4.355791</v>
+        <v>6.478705</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.096581</v>
+        <v>6.436663</v>
       </c>
       <c r="R62" t="n">
-        <v>4.57929</v>
+        <v>6.24706</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.445087</v>
+        <v>-2.243244</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.257898</v>
+        <v>-2.130529</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.8156099999999999</v>
+        <v>-1.750779</v>
       </c>
       <c r="V62" t="n">
-        <v>0.422318</v>
+        <v>-0.023423</v>
       </c>
       <c r="W62" t="n">
-        <v>0.5160979999999999</v>
+        <v>0.07296800000000001</v>
       </c>
       <c r="X62" t="n">
-        <v>0.429346</v>
+        <v>-0.688791</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.026833</v>
+        <v>0.245986</v>
       </c>
       <c r="Z62" t="n">
-        <v>6.669777</v>
+        <v>8.75699</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.398498</v>
+        <v>8.387672</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.450696</v>
+        <v>2.509312</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.582524</v>
+        <v>3.980583</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>188913.453125</v>
+        <v>187042.90625</v>
       </c>
       <c r="C62" t="n">
-        <v>186.029999</v>
+        <v>184.070007</v>
       </c>
       <c r="D62" t="n">
-        <v>112.760002</v>
+        <v>111.110001</v>
       </c>
       <c r="E62" t="n">
-        <v>439.269989</v>
+        <v>440.329987</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0806</v>
+        <v>5.0937</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9044</v>
+        <v>5.9353</v>
       </c>
       <c r="H62" t="n">
-        <v>7684.339844</v>
+        <v>7653.459961</v>
       </c>
       <c r="I62" t="n">
-        <v>26390.132812</v>
+        <v>26360.449219</v>
       </c>
       <c r="J62" t="n">
-        <v>52819.558594</v>
+        <v>52381.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4442</v>
+        <v>4456.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>93.269997</v>
+        <v>95.75</v>
       </c>
       <c r="M62" t="n">
-        <v>98.08000199999999</v>
+        <v>100.669998</v>
       </c>
       <c r="N62" t="n">
-        <v>1307.25</v>
+        <v>1308.75</v>
       </c>
       <c r="O62" t="n">
-        <v>535.5</v>
+        <v>527.25</v>
       </c>
       <c r="P62" t="n">
-        <v>6.478705</v>
+        <v>5.424394</v>
       </c>
       <c r="Q62" t="n">
-        <v>6.436663</v>
+        <v>5.315258</v>
       </c>
       <c r="R62" t="n">
-        <v>6.24706</v>
+        <v>4.692362</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.243244</v>
+        <v>-2.007348</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.130529</v>
+        <v>-1.878176</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.750779</v>
+        <v>-1.236603</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.023423</v>
+        <v>-0.425183</v>
       </c>
       <c r="W62" t="n">
-        <v>0.07296800000000001</v>
+        <v>-0.039594</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.688791</v>
+        <v>-1.512164</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.245986</v>
+        <v>0.575478</v>
       </c>
       <c r="Z62" t="n">
-        <v>8.75699</v>
+        <v>11.648785</v>
       </c>
       <c r="AA62" t="n">
-        <v>8.387672</v>
+        <v>11.249862</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.509312</v>
+        <v>2.626936</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.980583</v>
+        <v>2.378641</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>187042.90625</v>
+        <v>185144.859375</v>
       </c>
       <c r="C62" t="n">
-        <v>184.070007</v>
+        <v>182.330002</v>
       </c>
       <c r="D62" t="n">
-        <v>111.110001</v>
+        <v>109.870003</v>
       </c>
       <c r="E62" t="n">
-        <v>440.329987</v>
+        <v>440.929993</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0937</v>
+        <v>5.1422</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9353</v>
+        <v>5.9703</v>
       </c>
       <c r="H62" t="n">
-        <v>7653.459961</v>
+        <v>7583.859863</v>
       </c>
       <c r="I62" t="n">
-        <v>26360.449219</v>
+        <v>26037.785156</v>
       </c>
       <c r="J62" t="n">
-        <v>52381.640625</v>
+        <v>52079.46875</v>
       </c>
       <c r="K62" t="n">
-        <v>4456.600098</v>
+        <v>4409.5</v>
       </c>
       <c r="L62" t="n">
-        <v>95.75</v>
+        <v>99.300003</v>
       </c>
       <c r="M62" t="n">
-        <v>100.669998</v>
+        <v>104.540001</v>
       </c>
       <c r="N62" t="n">
-        <v>1308.75</v>
+        <v>1316</v>
       </c>
       <c r="O62" t="n">
-        <v>527.25</v>
+        <v>528</v>
       </c>
       <c r="P62" t="n">
-        <v>5.424394</v>
+        <v>4.354584</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.315258</v>
+        <v>4.319718</v>
       </c>
       <c r="R62" t="n">
-        <v>4.692362</v>
+        <v>3.523985</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.007348</v>
+        <v>-1.873821</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.878176</v>
+        <v>-0.943901</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.236603</v>
+        <v>-0.654197</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.425183</v>
+        <v>-1.33071</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.039594</v>
+        <v>-1.263156</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.512164</v>
+        <v>-2.080306</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.575478</v>
+        <v>-0.487466</v>
       </c>
       <c r="Z62" t="n">
-        <v>11.648785</v>
+        <v>15.788247</v>
       </c>
       <c r="AA62" t="n">
-        <v>11.249862</v>
+        <v>15.526581</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.626936</v>
+        <v>3.195452</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.378641</v>
+        <v>2.524272</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185144.859375</v>
+        <v>187021.609375</v>
       </c>
       <c r="C62" t="n">
-        <v>182.330002</v>
+        <v>184.119995</v>
       </c>
       <c r="D62" t="n">
-        <v>109.870003</v>
+        <v>111.400002</v>
       </c>
       <c r="E62" t="n">
-        <v>440.929993</v>
+        <v>440.160004</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1422</v>
+        <v>5.083</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9703</v>
+        <v>5.9061</v>
       </c>
       <c r="H62" t="n">
-        <v>7583.859863</v>
+        <v>7675.77002</v>
       </c>
       <c r="I62" t="n">
-        <v>26037.785156</v>
+        <v>26405.673828</v>
       </c>
       <c r="J62" t="n">
-        <v>52079.46875</v>
+        <v>52662.679688</v>
       </c>
       <c r="K62" t="n">
-        <v>4409.5</v>
+        <v>4432.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>99.300003</v>
+        <v>98.75</v>
       </c>
       <c r="M62" t="n">
-        <v>104.540001</v>
+        <v>104.110001</v>
       </c>
       <c r="N62" t="n">
-        <v>1316</v>
+        <v>1311.5</v>
       </c>
       <c r="O62" t="n">
-        <v>528</v>
+        <v>525.5</v>
       </c>
       <c r="P62" t="n">
-        <v>4.354584</v>
+        <v>5.412391</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.319718</v>
+        <v>5.343859</v>
       </c>
       <c r="R62" t="n">
-        <v>3.523985</v>
+        <v>4.965612</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.873821</v>
+        <v>-2.045177</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.943901</v>
+        <v>-2.084289</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.654197</v>
+        <v>-1.722492</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.33071</v>
+        <v>-0.13492</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.263156</v>
+        <v>0.1319</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.080306</v>
+        <v>-0.983755</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.487466</v>
+        <v>0.029334</v>
       </c>
       <c r="Z62" t="n">
-        <v>15.788247</v>
+        <v>15.146919</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.526581</v>
+        <v>15.05139</v>
       </c>
       <c r="AB62" t="n">
-        <v>3.195452</v>
+        <v>2.84258</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.524272</v>
+        <v>2.038835</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>187021.609375</v>
+        <v>187039.734375</v>
       </c>
       <c r="C62" t="n">
-        <v>184.119995</v>
+        <v>184.139999</v>
       </c>
       <c r="D62" t="n">
-        <v>111.400002</v>
+        <v>111.370003</v>
       </c>
       <c r="E62" t="n">
-        <v>440.160004</v>
+        <v>440.209991</v>
       </c>
       <c r="F62" t="n">
-        <v>5.083</v>
+        <v>5.0901</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9061</v>
+        <v>5.9107</v>
       </c>
       <c r="H62" t="n">
-        <v>7675.77002</v>
+        <v>7664.779785</v>
       </c>
       <c r="I62" t="n">
-        <v>26405.673828</v>
+        <v>26356.910156</v>
       </c>
       <c r="J62" t="n">
-        <v>52662.679688</v>
+        <v>52650.328125</v>
       </c>
       <c r="K62" t="n">
-        <v>4432.399902</v>
+        <v>4430.5</v>
       </c>
       <c r="L62" t="n">
-        <v>98.75</v>
+        <v>99.050003</v>
       </c>
       <c r="M62" t="n">
-        <v>104.110001</v>
+        <v>104.43</v>
       </c>
       <c r="N62" t="n">
-        <v>1311.5</v>
+        <v>1310.75</v>
       </c>
       <c r="O62" t="n">
-        <v>525.5</v>
+        <v>525.25</v>
       </c>
       <c r="P62" t="n">
-        <v>5.412391</v>
+        <v>5.422607</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.343859</v>
+        <v>5.355304</v>
       </c>
       <c r="R62" t="n">
-        <v>4.965612</v>
+        <v>4.937346</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.045177</v>
+        <v>-2.034052</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.084289</v>
+        <v>-1.947526</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.722492</v>
+        <v>-1.645947</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.13492</v>
+        <v>-0.277907</v>
       </c>
       <c r="W62" t="n">
-        <v>0.1319</v>
+        <v>-0.053015</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.983755</v>
+        <v>-1.006978</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.029334</v>
+        <v>-0.013543</v>
       </c>
       <c r="Z62" t="n">
-        <v>15.146919</v>
+        <v>15.496736</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.05139</v>
+        <v>15.40502</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.84258</v>
+        <v>2.783768</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.038835</v>
+        <v>1.990291</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>187039.734375</v>
+        <v>187207</v>
       </c>
       <c r="C62" t="n">
-        <v>184.139999</v>
+        <v>185.210007</v>
       </c>
       <c r="D62" t="n">
-        <v>111.370003</v>
+        <v>112.300003</v>
       </c>
       <c r="E62" t="n">
-        <v>440.209991</v>
+        <v>437.649994</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0901</v>
+        <v>5.1262</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9107</v>
+        <v>5.9463</v>
       </c>
       <c r="H62" t="n">
-        <v>7664.779785</v>
+        <v>7656.97998</v>
       </c>
       <c r="I62" t="n">
-        <v>26356.910156</v>
+        <v>26333.039062</v>
       </c>
       <c r="J62" t="n">
-        <v>52650.328125</v>
+        <v>52573.289062</v>
       </c>
       <c r="K62" t="n">
-        <v>4430.5</v>
+        <v>4366.200195</v>
       </c>
       <c r="L62" t="n">
-        <v>99.050003</v>
+        <v>100.050003</v>
       </c>
       <c r="M62" t="n">
-        <v>104.43</v>
+        <v>104.610001</v>
       </c>
       <c r="N62" t="n">
-        <v>1310.75</v>
+        <v>1280.25</v>
       </c>
       <c r="O62" t="n">
-        <v>525.25</v>
+        <v>510.25</v>
       </c>
       <c r="P62" t="n">
-        <v>5.422607</v>
+        <v>5.516884</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.355304</v>
+        <v>5.967507</v>
       </c>
       <c r="R62" t="n">
-        <v>4.937346</v>
+        <v>5.81363</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.034052</v>
+        <v>-2.603764</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.947526</v>
+        <v>-1.252111</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.645947</v>
+        <v>-1.05356</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.277907</v>
+        <v>-0.379386</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.053015</v>
+        <v>-0.143535</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.006978</v>
+        <v>-1.151827</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.013543</v>
+        <v>-1.464645</v>
       </c>
       <c r="Z62" t="n">
-        <v>15.496736</v>
+        <v>16.662781</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.40502</v>
+        <v>15.603938</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.783768</v>
+        <v>0.39208</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.990291</v>
+        <v>-0.92233</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5887,13 +5887,13 @@
         <v>187207</v>
       </c>
       <c r="C62" t="n">
-        <v>185.210007</v>
+        <v>183.850006</v>
       </c>
       <c r="D62" t="n">
-        <v>112.300003</v>
+        <v>110.830002</v>
       </c>
       <c r="E62" t="n">
-        <v>437.649994</v>
+        <v>443.149994</v>
       </c>
       <c r="F62" t="n">
         <v>5.1262</v>
@@ -5911,7 +5911,7 @@
         <v>52573.289062</v>
       </c>
       <c r="K62" t="n">
-        <v>4366.200195</v>
+        <v>4408.899902</v>
       </c>
       <c r="L62" t="n">
         <v>100.050003</v>
@@ -5920,22 +5920,22 @@
         <v>104.610001</v>
       </c>
       <c r="N62" t="n">
-        <v>1280.25</v>
+        <v>1299</v>
       </c>
       <c r="O62" t="n">
-        <v>510.25</v>
+        <v>532</v>
       </c>
       <c r="P62" t="n">
         <v>5.516884</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.967507</v>
+        <v>5.189385</v>
       </c>
       <c r="R62" t="n">
-        <v>5.81363</v>
+        <v>4.428535</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.603764</v>
+        <v>-1.379773</v>
       </c>
       <c r="T62" t="n">
         <v>-1.252111</v>
@@ -5953,7 +5953,7 @@
         <v>-1.151827</v>
       </c>
       <c r="Y62" t="n">
-        <v>-1.464645</v>
+        <v>-0.501009</v>
       </c>
       <c r="Z62" t="n">
         <v>16.662781</v>
@@ -5962,10 +5962,10 @@
         <v>15.603938</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.39208</v>
+        <v>1.86238</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.92233</v>
+        <v>3.300971</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>187207</v>
+        <v>185371.140625</v>
       </c>
       <c r="C62" t="n">
-        <v>183.850006</v>
+        <v>182.369995</v>
       </c>
       <c r="D62" t="n">
-        <v>110.830002</v>
+        <v>109.68</v>
       </c>
       <c r="E62" t="n">
-        <v>443.149994</v>
+        <v>443.630005</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1262</v>
+        <v>5.1539</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9463</v>
+        <v>5.9512</v>
       </c>
       <c r="H62" t="n">
-        <v>7656.97998</v>
+        <v>7626.77002</v>
       </c>
       <c r="I62" t="n">
-        <v>26333.039062</v>
+        <v>26209.451172</v>
       </c>
       <c r="J62" t="n">
-        <v>52573.289062</v>
+        <v>52482.101562</v>
       </c>
       <c r="K62" t="n">
-        <v>4408.899902</v>
+        <v>4331.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>100.050003</v>
+        <v>102.970001</v>
       </c>
       <c r="M62" t="n">
-        <v>104.610001</v>
+        <v>107.419998</v>
       </c>
       <c r="N62" t="n">
-        <v>1299</v>
+        <v>1306.5</v>
       </c>
       <c r="O62" t="n">
-        <v>532</v>
+        <v>530.5</v>
       </c>
       <c r="P62" t="n">
-        <v>5.516884</v>
+        <v>4.482125</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.189385</v>
+        <v>4.3426</v>
       </c>
       <c r="R62" t="n">
-        <v>4.428535</v>
+        <v>3.344957</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.379773</v>
+        <v>-1.27295</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.252111</v>
+        <v>-0.718517</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.05356</v>
+        <v>-0.972025</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.379386</v>
+        <v>-0.772431</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.143535</v>
+        <v>-0.612188</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.151827</v>
+        <v>-1.323277</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.501009</v>
+        <v>-2.245492</v>
       </c>
       <c r="Z62" t="n">
-        <v>16.662781</v>
+        <v>20.067629</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.603938</v>
+        <v>18.70925</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.86238</v>
+        <v>2.4505</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.300971</v>
+        <v>3.009709</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -599,7 +599,7 @@
         <v>33843.921875</v>
       </c>
       <c r="K2" t="n">
-        <v>1755.300049</v>
+        <v>1757</v>
       </c>
       <c r="L2" t="n">
         <v>75.029999</v>
@@ -660,7 +660,7 @@
         <v>35819.558594</v>
       </c>
       <c r="K3" t="n">
-        <v>1783</v>
+        <v>1783.900024</v>
       </c>
       <c r="L3" t="n">
         <v>83.56999999999999</v>
@@ -702,7 +702,7 @@
         <v>5.837493</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.578075</v>
+        <v>1.53102</v>
       </c>
       <c r="Z3" t="n">
         <v>11.382115</v>
@@ -791,7 +791,7 @@
         <v>-3.729359</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.527203</v>
+        <v>-0.577389</v>
       </c>
       <c r="Z4" t="n">
         <v>-20.808902</v>
@@ -838,7 +838,7 @@
         <v>36338.300781</v>
       </c>
       <c r="K5" t="n">
-        <v>1827.5</v>
+        <v>1828.599976</v>
       </c>
       <c r="L5" t="n">
         <v>75.209999</v>
@@ -880,7 +880,7 @@
         <v>5.378138</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.039018</v>
+        <v>3.101037</v>
       </c>
       <c r="Z5" t="n">
         <v>13.644604</v>
@@ -969,7 +969,7 @@
         <v>-3.320027</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.778386</v>
+        <v>-1.83747</v>
       </c>
       <c r="Z6" t="n">
         <v>17.205162</v>
@@ -1016,7 +1016,7 @@
         <v>33892.601562</v>
       </c>
       <c r="K7" t="n">
-        <v>1899.400024</v>
+        <v>1900.699951</v>
       </c>
       <c r="L7" t="n">
         <v>95.720001</v>
@@ -1058,7 +1058,7 @@
         <v>-3.527447</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.816157</v>
+        <v>5.888577</v>
       </c>
       <c r="Z7" t="n">
         <v>8.587634</v>
@@ -1147,7 +1147,7 @@
         <v>2.318353</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.621877</v>
+        <v>2.551692</v>
       </c>
       <c r="Z8" t="n">
         <v>4.763892</v>
@@ -1194,7 +1194,7 @@
         <v>32977.210938</v>
       </c>
       <c r="K9" t="n">
-        <v>1909.300049</v>
+        <v>1911.699951</v>
       </c>
       <c r="L9" t="n">
         <v>104.690002</v>
@@ -1236,7 +1236,7 @@
         <v>-4.905483</v>
       </c>
       <c r="Y9" t="n">
-        <v>-2.046989</v>
+        <v>-1.923866</v>
       </c>
       <c r="Z9" t="n">
         <v>4.39769</v>
@@ -1325,7 +1325,7 @@
         <v>0.039149</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.488194</v>
+        <v>-3.609353</v>
       </c>
       <c r="Z10" t="n">
         <v>9.532902</v>
@@ -1372,7 +1372,7 @@
         <v>30775.429688</v>
       </c>
       <c r="K11" t="n">
-        <v>1804.099976</v>
+        <v>1807.300049</v>
       </c>
       <c r="L11" t="n">
         <v>105.760002</v>
@@ -1414,7 +1414,7 @@
         <v>-6.713196</v>
       </c>
       <c r="Y11" t="n">
-        <v>-2.094751</v>
+        <v>-1.921089</v>
       </c>
       <c r="Z11" t="n">
         <v>-7.77012</v>
@@ -1503,7 +1503,7 @@
         <v>6.725168</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.283684</v>
+        <v>-2.456705</v>
       </c>
       <c r="Z12" t="n">
         <v>-6.751134</v>
@@ -1550,7 +1550,7 @@
         <v>31510.429688</v>
       </c>
       <c r="K13" t="n">
-        <v>1712.800049</v>
+        <v>1726.199951</v>
       </c>
       <c r="L13" t="n">
         <v>89.550003</v>
@@ -1592,7 +1592,7 @@
         <v>-4.063614</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.841907</v>
+        <v>-2.081801</v>
       </c>
       <c r="Z13" t="n">
         <v>-9.196916999999999</v>
@@ -1639,7 +1639,7 @@
         <v>28725.509766</v>
       </c>
       <c r="K14" t="n">
-        <v>1662.400024</v>
+        <v>1672</v>
       </c>
       <c r="L14" t="n">
         <v>79.489998</v>
@@ -1681,7 +1681,7 @@
         <v>-8.838089</v>
       </c>
       <c r="Y14" t="n">
-        <v>-2.942552</v>
+        <v>-3.139842</v>
       </c>
       <c r="Z14" t="n">
         <v>-11.233953</v>
@@ -1728,7 +1728,7 @@
         <v>32732.949219</v>
       </c>
       <c r="K15" t="n">
-        <v>1635.900024</v>
+        <v>1640.699951</v>
       </c>
       <c r="L15" t="n">
         <v>86.529999</v>
@@ -1770,7 +1770,7 @@
         <v>13.950804</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1.594081</v>
+        <v>-1.872012</v>
       </c>
       <c r="Z15" t="n">
         <v>8.856460999999999</v>
@@ -1859,7 +1859,7 @@
         <v>5.672634</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.730239</v>
+        <v>6.417995</v>
       </c>
       <c r="Z16" t="n">
         <v>-6.910893</v>
@@ -1906,7 +1906,7 @@
         <v>33147.25</v>
       </c>
       <c r="K17" t="n">
-        <v>1819.699951</v>
+        <v>1826.199951</v>
       </c>
       <c r="L17" t="n">
         <v>80.260002</v>
@@ -1948,7 +1948,7 @@
         <v>-4.170365</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.221074</v>
+        <v>4.593353</v>
       </c>
       <c r="Z17" t="n">
         <v>-0.360026</v>
@@ -2037,7 +2037,7 @@
         <v>2.832178</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.033964</v>
+        <v>5.656557</v>
       </c>
       <c r="Z18" t="n">
         <v>-1.731871</v>
@@ -2084,7 +2084,7 @@
         <v>32656.699219</v>
       </c>
       <c r="K19" t="n">
-        <v>1828.900024</v>
+        <v>1836.699951</v>
       </c>
       <c r="L19" t="n">
         <v>77.050003</v>
@@ -2126,7 +2126,7 @@
         <v>-4.193329</v>
       </c>
       <c r="Y19" t="n">
-        <v>-5.213785</v>
+        <v>-4.809539</v>
       </c>
       <c r="Z19" t="n">
         <v>-2.307594</v>
@@ -2215,7 +2215,7 @@
         <v>1.890728</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.660341</v>
+        <v>7.203139</v>
       </c>
       <c r="Z20" t="n">
         <v>-1.791051</v>
@@ -2262,7 +2262,7 @@
         <v>34098.160156</v>
       </c>
       <c r="K21" t="n">
-        <v>1990.099976</v>
+        <v>1999.099976</v>
       </c>
       <c r="L21" t="n">
         <v>76.779999</v>
@@ -2304,7 +2304,7 @@
         <v>2.476432</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.071609</v>
+        <v>1.528694</v>
       </c>
       <c r="Z21" t="n">
         <v>1.466897</v>
@@ -2393,7 +2393,7 @@
         <v>-3.489604</v>
       </c>
       <c r="Y22" t="n">
-        <v>-1.316514</v>
+        <v>-1.76079</v>
       </c>
       <c r="Z22" t="n">
         <v>-11.318055</v>
@@ -2440,7 +2440,7 @@
         <v>34407.601562</v>
       </c>
       <c r="K23" t="n">
-        <v>1921.099976</v>
+        <v>1929.400024</v>
       </c>
       <c r="L23" t="n">
         <v>70.639999</v>
@@ -2482,7 +2482,7 @@
         <v>4.556095</v>
       </c>
       <c r="Y23" t="n">
-        <v>-2.179339</v>
+        <v>-1.756709</v>
       </c>
       <c r="Z23" t="n">
         <v>3.745048</v>
@@ -2571,7 +2571,7 @@
         <v>3.347893</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.571445</v>
+        <v>2.130195</v>
       </c>
       <c r="Z24" t="n">
         <v>15.79842</v>
@@ -2618,7 +2618,7 @@
         <v>34721.910156</v>
       </c>
       <c r="K25" t="n">
-        <v>1938.199951</v>
+        <v>1965.900024</v>
       </c>
       <c r="L25" t="n">
         <v>83.629997</v>
@@ -2660,7 +2660,7 @@
         <v>-2.355546</v>
       </c>
       <c r="Y25" t="n">
-        <v>-1.63918</v>
+        <v>-0.233442</v>
       </c>
       <c r="Z25" t="n">
         <v>2.237157</v>
@@ -2707,7 +2707,7 @@
         <v>33507.5</v>
       </c>
       <c r="K26" t="n">
-        <v>1848.099976</v>
+        <v>1866.099976</v>
       </c>
       <c r="L26" t="n">
         <v>90.790001</v>
@@ -2749,7 +2749,7 @@
         <v>-3.497533</v>
       </c>
       <c r="Y26" t="n">
-        <v>-4.648642</v>
+        <v>-5.076558</v>
       </c>
       <c r="Z26" t="n">
         <v>8.561526000000001</v>
@@ -2796,7 +2796,7 @@
         <v>33052.871094</v>
       </c>
       <c r="K27" t="n">
-        <v>1985.199951</v>
+        <v>1994.300049</v>
       </c>
       <c r="L27" t="n">
         <v>81.019997</v>
@@ -2838,7 +2838,7 @@
         <v>-1.356797</v>
       </c>
       <c r="Y27" t="n">
-        <v>7.418429</v>
+        <v>6.869947</v>
       </c>
       <c r="Z27" t="n">
         <v>-10.761102</v>
@@ -2927,7 +2927,7 @@
         <v>8.76783</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.66472</v>
+        <v>2.196256</v>
       </c>
       <c r="Z28" t="n">
         <v>-6.245369</v>
@@ -2974,7 +2974,7 @@
         <v>37689.539062</v>
       </c>
       <c r="K29" t="n">
-        <v>2062.399902</v>
+        <v>2071.800049</v>
       </c>
       <c r="L29" t="n">
         <v>71.650002</v>
@@ -3016,7 +3016,7 @@
         <v>4.836176</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.192283</v>
+        <v>1.653504</v>
       </c>
       <c r="Z29" t="n">
         <v>-5.674036</v>
@@ -3105,7 +3105,7 @@
         <v>1.222519</v>
       </c>
       <c r="Y30" t="n">
-        <v>-0.678821</v>
+        <v>-1.12946</v>
       </c>
       <c r="Z30" t="n">
         <v>5.861824</v>
@@ -3152,7 +3152,7 @@
         <v>38996.390625</v>
       </c>
       <c r="K31" t="n">
-        <v>2045.699951</v>
+        <v>2054.699951</v>
       </c>
       <c r="L31" t="n">
         <v>78.260002</v>
@@ -3194,7 +3194,7 @@
         <v>2.21778</v>
       </c>
       <c r="Y31" t="n">
-        <v>-0.131808</v>
+        <v>0.30756</v>
       </c>
       <c r="Z31" t="n">
         <v>3.177329</v>
@@ -3283,7 +3283,7 @@
         <v>2.07963</v>
       </c>
       <c r="Y32" t="n">
-        <v>8.393212999999999</v>
+        <v>7.918429</v>
       </c>
       <c r="Z32" t="n">
         <v>6.273953</v>
@@ -3330,7 +3330,7 @@
         <v>37815.921875</v>
       </c>
       <c r="K33" t="n">
-        <v>2291.399902</v>
+        <v>2302.899902</v>
       </c>
       <c r="L33" t="n">
         <v>81.93000000000001</v>
@@ -3372,7 +3372,7 @@
         <v>-5.002715</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.337242</v>
+        <v>3.855867</v>
       </c>
       <c r="Z33" t="n">
         <v>-1.49092</v>
@@ -3461,7 +3461,7 @@
         <v>2.301672</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.374705</v>
+        <v>0.86847</v>
       </c>
       <c r="Z34" t="n">
         <v>-6.02954</v>
@@ -3508,7 +3508,7 @@
         <v>39118.859375</v>
       </c>
       <c r="K35" t="n">
-        <v>2327.699951</v>
+        <v>2339.600098</v>
       </c>
       <c r="L35" t="n">
         <v>81.540001</v>
@@ -3550,7 +3550,7 @@
         <v>1.118067</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.20664</v>
+        <v>0.718937</v>
       </c>
       <c r="Z35" t="n">
         <v>5.909863</v>
@@ -3639,7 +3639,7 @@
         <v>4.406902</v>
       </c>
       <c r="Y36" t="n">
-        <v>4.244535</v>
+        <v>3.714306</v>
       </c>
       <c r="Z36" t="n">
         <v>-4.451799</v>
@@ -3686,7 +3686,7 @@
         <v>41563.078125</v>
       </c>
       <c r="K37" t="n">
-        <v>2493.800049</v>
+        <v>2527.600098</v>
       </c>
       <c r="L37" t="n">
         <v>73.550003</v>
@@ -3728,7 +3728,7 @@
         <v>1.763565</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.773544</v>
+        <v>4.166499</v>
       </c>
       <c r="Z37" t="n">
         <v>-5.596201</v>
@@ -3775,7 +3775,7 @@
         <v>42330.148438</v>
       </c>
       <c r="K38" t="n">
-        <v>2636.100098</v>
+        <v>2659.399902</v>
       </c>
       <c r="L38" t="n">
         <v>68.16999800000001</v>
@@ -3817,7 +3817,7 @@
         <v>1.845557</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.706153</v>
+        <v>5.214425</v>
       </c>
       <c r="Z38" t="n">
         <v>-7.314758</v>
@@ -3864,7 +3864,7 @@
         <v>41763.460938</v>
       </c>
       <c r="K39" t="n">
-        <v>2738.300049</v>
+        <v>2749.300049</v>
       </c>
       <c r="L39" t="n">
         <v>69.260002</v>
@@ -3906,7 +3906,7 @@
         <v>-1.338733</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.876937</v>
+        <v>3.380467</v>
       </c>
       <c r="Z39" t="n">
         <v>1.59895</v>
@@ -3995,7 +3995,7 @@
         <v>7.535744</v>
       </c>
       <c r="Y40" t="n">
-        <v>-2.968997</v>
+        <v>-3.35722</v>
       </c>
       <c r="Z40" t="n">
         <v>-1.819235</v>
@@ -4042,7 +4042,7 @@
         <v>42544.21875</v>
       </c>
       <c r="K41" t="n">
-        <v>2629.199951</v>
+        <v>2641</v>
       </c>
       <c r="L41" t="n">
         <v>71.720001</v>
@@ -4084,7 +4084,7 @@
         <v>-5.269195</v>
       </c>
       <c r="Y41" t="n">
-        <v>-1.046295</v>
+        <v>-0.602183</v>
       </c>
       <c r="Z41" t="n">
         <v>5.47059</v>
@@ -4173,7 +4173,7 @@
         <v>4.702029</v>
       </c>
       <c r="Y42" t="n">
-        <v>6.971704</v>
+        <v>6.493752</v>
       </c>
       <c r="Z42" t="n">
         <v>1.129389</v>
@@ -4220,7 +4220,7 @@
         <v>43840.910156</v>
       </c>
       <c r="K43" t="n">
-        <v>2836.800049</v>
+        <v>2848.5</v>
       </c>
       <c r="L43" t="n">
         <v>69.760002</v>
@@ -4262,7 +4262,7 @@
         <v>-1.579875</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.864002</v>
+        <v>1.28</v>
       </c>
       <c r="Z43" t="n">
         <v>-3.819105</v>
@@ -4351,7 +4351,7 @@
         <v>-4.195051</v>
       </c>
       <c r="Y44" t="n">
-        <v>10.081782</v>
+        <v>9.629631</v>
       </c>
       <c r="Z44" t="n">
         <v>2.465598</v>
@@ -4398,7 +4398,7 @@
         <v>40669.359375</v>
       </c>
       <c r="K45" t="n">
-        <v>3305</v>
+        <v>3319.100098</v>
       </c>
       <c r="L45" t="n">
         <v>58.209999</v>
@@ -4440,7 +4440,7 @@
         <v>-3.172253</v>
       </c>
       <c r="Y45" t="n">
-        <v>5.834506</v>
+        <v>6.286027</v>
       </c>
       <c r="Z45" t="n">
         <v>-18.564639</v>
@@ -4529,7 +4529,7 @@
         <v>3.935914</v>
       </c>
       <c r="Y46" t="n">
-        <v>-0.487144</v>
+        <v>-0.909891</v>
       </c>
       <c r="Z46" t="n">
         <v>4.432231</v>
@@ -4576,7 +4576,7 @@
         <v>44094.769531</v>
       </c>
       <c r="K47" t="n">
-        <v>3294.399902</v>
+        <v>3307.699951</v>
       </c>
       <c r="L47" t="n">
         <v>65.110001</v>
@@ -4618,7 +4618,7 @@
         <v>4.316764</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.167229</v>
+        <v>0.571621</v>
       </c>
       <c r="Z47" t="n">
         <v>7.106431</v>
@@ -4707,7 +4707,7 @@
         <v>0.082121</v>
       </c>
       <c r="Y48" t="n">
-        <v>-0.036424</v>
+        <v>-0.438371</v>
       </c>
       <c r="Z48" t="n">
         <v>6.373831</v>
@@ -4754,7 +4754,7 @@
         <v>45544.878906</v>
       </c>
       <c r="K49" t="n">
-        <v>3473.699951</v>
+        <v>3516.100098</v>
       </c>
       <c r="L49" t="n">
         <v>64.010002</v>
@@ -4796,7 +4796,7 @@
         <v>3.203868</v>
       </c>
       <c r="Y49" t="n">
-        <v>5.480991</v>
+        <v>6.768497</v>
       </c>
       <c r="Z49" t="n">
         <v>-7.580133</v>
@@ -4843,7 +4843,7 @@
         <v>46397.890625</v>
       </c>
       <c r="K50" t="n">
-        <v>3840.800049</v>
+        <v>3873.199951</v>
       </c>
       <c r="L50" t="n">
         <v>62.369999</v>
@@ -4885,7 +4885,7 @@
         <v>1.872904</v>
       </c>
       <c r="Y50" t="n">
-        <v>10.567985</v>
+        <v>10.156134</v>
       </c>
       <c r="Z50" t="n">
         <v>-2.562105</v>
@@ -4932,7 +4932,7 @@
         <v>47562.871094</v>
       </c>
       <c r="K51" t="n">
-        <v>3982.199951</v>
+        <v>3996.5</v>
       </c>
       <c r="L51" t="n">
         <v>60.98</v>
@@ -4974,7 +4974,7 @@
         <v>2.510848</v>
       </c>
       <c r="Y51" t="n">
-        <v>3.681522</v>
+        <v>3.183416</v>
       </c>
       <c r="Z51" t="n">
         <v>-2.228635</v>
@@ -5021,7 +5021,7 @@
         <v>47716.421875</v>
       </c>
       <c r="K52" t="n">
-        <v>4218.299805</v>
+        <v>4254.899902</v>
       </c>
       <c r="L52" t="n">
         <v>58.549999</v>
@@ -5063,7 +5063,7 @@
         <v>0.322837</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.92888</v>
+        <v>6.465655</v>
       </c>
       <c r="Z52" t="n">
         <v>-3.984914</v>
@@ -5110,7 +5110,7 @@
         <v>48063.289062</v>
       </c>
       <c r="K53" t="n">
-        <v>4325.600098</v>
+        <v>4341.100098</v>
       </c>
       <c r="L53" t="n">
         <v>57.419998</v>
@@ -5152,7 +5152,7 @@
         <v>0.726935</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.543686</v>
+        <v>2.025904</v>
       </c>
       <c r="Z53" t="n">
         <v>-1.929976</v>
@@ -5199,7 +5199,7 @@
         <v>48892.46875</v>
       </c>
       <c r="K54" t="n">
-        <v>4713.899902</v>
+        <v>4745.100098</v>
       </c>
       <c r="L54" t="n">
         <v>65.209999</v>
@@ -5241,7 +5241,7 @@
         <v>1.725183</v>
       </c>
       <c r="Y54" t="n">
-        <v>8.976785</v>
+        <v>9.306397</v>
       </c>
       <c r="Z54" t="n">
         <v>13.566704</v>
@@ -5288,7 +5288,7 @@
         <v>48977.921875</v>
       </c>
       <c r="K55" t="n">
-        <v>5230.5</v>
+        <v>5247.899902</v>
       </c>
       <c r="L55" t="n">
         <v>67.019997</v>
@@ -5330,7 +5330,7 @@
         <v>0.174778</v>
       </c>
       <c r="Y55" t="n">
-        <v>10.959081</v>
+        <v>10.59619</v>
       </c>
       <c r="Z55" t="n">
         <v>2.775644</v>
@@ -5419,7 +5419,7 @@
         <v>-5.382854</v>
       </c>
       <c r="Y56" t="n">
-        <v>-11.144248</v>
+        <v>-11.438858</v>
       </c>
       <c r="Z56" t="n">
         <v>51.268282</v>
@@ -5466,7 +5466,7 @@
         <v>49652.140625</v>
       </c>
       <c r="K57" t="n">
-        <v>4614.700195</v>
+        <v>4629.600098</v>
       </c>
       <c r="L57" t="n">
         <v>105.07</v>
@@ -5508,7 +5508,7 @@
         <v>7.143981</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.70789</v>
+        <v>-0.387297</v>
       </c>
       <c r="Z57" t="n">
         <v>3.639774</v>
@@ -5555,7 +5555,7 @@
         <v>51032.460938</v>
       </c>
       <c r="K58" t="n">
-        <v>4560.5</v>
+        <v>4593</v>
       </c>
       <c r="L58" t="n">
         <v>87.360001</v>
@@ -5597,7 +5597,7 @@
         <v>2.779981</v>
       </c>
       <c r="Y58" t="n">
-        <v>-1.174512</v>
+        <v>-0.790567</v>
       </c>
       <c r="Z58" t="n">
         <v>-16.855429</v>
@@ -5644,7 +5644,7 @@
         <v>52319.199219</v>
       </c>
       <c r="K59" t="n">
-        <v>4022.899902</v>
+        <v>4038.5</v>
       </c>
       <c r="L59" t="n">
         <v>69.5</v>
@@ -5686,7 +5686,7 @@
         <v>2.521411</v>
       </c>
       <c r="Y59" t="n">
-        <v>-11.788183</v>
+        <v>-12.072719</v>
       </c>
       <c r="Z59" t="n">
         <v>-20.44414</v>
@@ -5733,7 +5733,7 @@
         <v>52485.03125</v>
       </c>
       <c r="K60" t="n">
-        <v>4049.100098</v>
+        <v>4107</v>
       </c>
       <c r="L60" t="n">
         <v>84.66999800000001</v>
@@ -5775,7 +5775,7 @@
         <v>0.316962</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.651276</v>
+        <v>1.696174</v>
       </c>
       <c r="Z60" t="n">
         <v>21.827335</v>
@@ -5822,7 +5822,7 @@
         <v>53185.898438</v>
       </c>
       <c r="K61" t="n">
-        <v>4431.100098</v>
+        <v>4481.5</v>
       </c>
       <c r="L61" t="n">
         <v>85.760002</v>
@@ -5864,7 +5864,7 @@
         <v>1.335366</v>
       </c>
       <c r="Y61" t="n">
-        <v>9.434195000000001</v>
+        <v>9.118577999999999</v>
       </c>
       <c r="Z61" t="n">
         <v>1.287356</v>
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185371.140625</v>
+        <v>185959.625</v>
       </c>
       <c r="C62" t="n">
-        <v>182.369995</v>
+        <v>183.039993</v>
       </c>
       <c r="D62" t="n">
-        <v>109.68</v>
+        <v>109.540001</v>
       </c>
       <c r="E62" t="n">
-        <v>443.630005</v>
+        <v>440.839996</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1539</v>
+        <v>5.1456</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9512</v>
+        <v>5.9456</v>
       </c>
       <c r="H62" t="n">
-        <v>7626.77002</v>
+        <v>7585.890137</v>
       </c>
       <c r="I62" t="n">
-        <v>26209.451172</v>
+        <v>26026.601562</v>
       </c>
       <c r="J62" t="n">
-        <v>52482.101562</v>
+        <v>51923.578125</v>
       </c>
       <c r="K62" t="n">
-        <v>4331.600098</v>
+        <v>4329.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>102.970001</v>
+        <v>103.730003</v>
       </c>
       <c r="M62" t="n">
-        <v>107.419998</v>
+        <v>102.610001</v>
       </c>
       <c r="N62" t="n">
         <v>1306.5</v>
       </c>
       <c r="O62" t="n">
-        <v>530.5</v>
+        <v>531.25</v>
       </c>
       <c r="P62" t="n">
-        <v>4.482125</v>
+        <v>4.813816</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.3426</v>
+        <v>4.725938</v>
       </c>
       <c r="R62" t="n">
-        <v>3.344957</v>
+        <v>3.213044</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.27295</v>
+        <v>-1.893849</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.718517</v>
+        <v>-0.878408</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.972025</v>
+        <v>-1.065208</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.772431</v>
+        <v>-1.304296</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.612188</v>
+        <v>-1.305565</v>
       </c>
       <c r="X62" t="n">
-        <v>-1.323277</v>
+        <v>-2.373412</v>
       </c>
       <c r="Y62" t="n">
-        <v>-2.245492</v>
+        <v>-3.396189</v>
       </c>
       <c r="Z62" t="n">
-        <v>20.067629</v>
+        <v>20.953826</v>
       </c>
       <c r="AA62" t="n">
-        <v>18.70925</v>
+        <v>13.393749</v>
       </c>
       <c r="AB62" t="n">
         <v>2.4505</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.009709</v>
+        <v>3.15534</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185959.625</v>
+        <v>185399.484375</v>
       </c>
       <c r="C62" t="n">
-        <v>183.039993</v>
+        <v>182.539993</v>
       </c>
       <c r="D62" t="n">
         <v>109.540001</v>
       </c>
       <c r="E62" t="n">
-        <v>440.839996</v>
+        <v>442.51001</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1456</v>
+        <v>5.1546</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9456</v>
+        <v>5.9476</v>
       </c>
       <c r="H62" t="n">
-        <v>7585.890137</v>
+        <v>7600.680176</v>
       </c>
       <c r="I62" t="n">
-        <v>26026.601562</v>
+        <v>26133.207031</v>
       </c>
       <c r="J62" t="n">
-        <v>51923.578125</v>
+        <v>51940.390625</v>
       </c>
       <c r="K62" t="n">
-        <v>4329.299805</v>
+        <v>4376.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>103.730003</v>
+        <v>103.169998</v>
       </c>
       <c r="M62" t="n">
-        <v>102.610001</v>
+        <v>106.949997</v>
       </c>
       <c r="N62" t="n">
-        <v>1306.5</v>
+        <v>1320.25</v>
       </c>
       <c r="O62" t="n">
-        <v>531.25</v>
+        <v>535</v>
       </c>
       <c r="P62" t="n">
-        <v>4.813816</v>
+        <v>4.4981</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.725938</v>
+        <v>4.439864</v>
       </c>
       <c r="R62" t="n">
         <v>3.213044</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.893849</v>
+        <v>-1.522198</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.878408</v>
+        <v>-0.705032</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.065208</v>
+        <v>-1.031931</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.304296</v>
+        <v>-1.111871</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.305565</v>
+        <v>-0.9013099999999999</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.373412</v>
+        <v>-2.341801</v>
       </c>
       <c r="Y62" t="n">
-        <v>-3.396189</v>
+        <v>-2.334042</v>
       </c>
       <c r="Z62" t="n">
-        <v>20.953826</v>
+        <v>20.300834</v>
       </c>
       <c r="AA62" t="n">
-        <v>13.393749</v>
+        <v>18.189855</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.4505</v>
+        <v>3.52872</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.15534</v>
+        <v>3.883495</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185399.484375</v>
+        <v>184544.75</v>
       </c>
       <c r="C62" t="n">
-        <v>182.539993</v>
+        <v>181.610001</v>
       </c>
       <c r="D62" t="n">
-        <v>109.540001</v>
+        <v>109.209999</v>
       </c>
       <c r="E62" t="n">
-        <v>442.51001</v>
+        <v>444.839996</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1546</v>
+        <v>5.1599</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9476</v>
+        <v>5.9317</v>
       </c>
       <c r="H62" t="n">
-        <v>7600.680176</v>
+        <v>7630.069824</v>
       </c>
       <c r="I62" t="n">
-        <v>26133.207031</v>
+        <v>26407.919922</v>
       </c>
       <c r="J62" t="n">
-        <v>51940.390625</v>
+        <v>51741.929688</v>
       </c>
       <c r="K62" t="n">
-        <v>4376.899902</v>
+        <v>4410.5</v>
       </c>
       <c r="L62" t="n">
-        <v>103.169998</v>
+        <v>100.389999</v>
       </c>
       <c r="M62" t="n">
-        <v>106.949997</v>
+        <v>102.959999</v>
       </c>
       <c r="N62" t="n">
-        <v>1320.25</v>
+        <v>1312.5</v>
       </c>
       <c r="O62" t="n">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="P62" t="n">
-        <v>4.4981</v>
+        <v>4.01634</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.439864</v>
+        <v>3.907771</v>
       </c>
       <c r="R62" t="n">
-        <v>3.213044</v>
+        <v>2.902103</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.522198</v>
+        <v>-1.003674</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.705032</v>
+        <v>-0.602936</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.031931</v>
+        <v>-1.296501</v>
       </c>
       <c r="V62" t="n">
-        <v>-1.111871</v>
+        <v>-0.729499</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.9013099999999999</v>
+        <v>0.140417</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.341801</v>
+        <v>-2.714947</v>
       </c>
       <c r="Y62" t="n">
-        <v>-2.334042</v>
+        <v>-1.584291</v>
       </c>
       <c r="Z62" t="n">
-        <v>20.300834</v>
+        <v>17.059231</v>
       </c>
       <c r="AA62" t="n">
-        <v>18.189855</v>
+        <v>13.78053</v>
       </c>
       <c r="AB62" t="n">
-        <v>3.52872</v>
+        <v>2.920996</v>
       </c>
       <c r="AC62" t="n">
-        <v>3.883495</v>
+        <v>2.524272</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -607,9 +607,7 @@
       <c r="M2" t="n">
         <v>78.519997</v>
       </c>
-      <c r="N2" t="n">
-        <v>1256</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>536.75</v>
       </c>
@@ -668,9 +666,7 @@
       <c r="M3" t="n">
         <v>84.379997</v>
       </c>
-      <c r="N3" t="n">
-        <v>1235.75</v>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>568.25</v>
       </c>
@@ -710,9 +706,7 @@
       <c r="AA3" t="n">
         <v>7.463068</v>
       </c>
-      <c r="AB3" t="n">
-        <v>-1.612261</v>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
         <v>5.868654</v>
       </c>
@@ -757,9 +751,7 @@
       <c r="M4" t="n">
         <v>70.56999999999999</v>
       </c>
-      <c r="N4" t="n">
-        <v>1217.25</v>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>567</v>
       </c>
@@ -799,9 +791,7 @@
       <c r="AA4" t="n">
         <v>-16.366435</v>
       </c>
-      <c r="AB4" t="n">
-        <v>-1.497067</v>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
         <v>-0.219974</v>
       </c>
@@ -846,9 +836,7 @@
       <c r="M5" t="n">
         <v>77.779999</v>
       </c>
-      <c r="N5" t="n">
-        <v>1328.75</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>593.25</v>
       </c>
@@ -888,9 +876,7 @@
       <c r="AA5" t="n">
         <v>10.216805</v>
       </c>
-      <c r="AB5" t="n">
-        <v>9.159992000000001</v>
-      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
         <v>4.62963</v>
       </c>
@@ -935,9 +921,7 @@
       <c r="M6" t="n">
         <v>91.209999</v>
       </c>
-      <c r="N6" t="n">
-        <v>1490.5</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
         <v>626</v>
       </c>
@@ -977,9 +961,7 @@
       <c r="AA6" t="n">
         <v>17.26665</v>
       </c>
-      <c r="AB6" t="n">
-        <v>12.173095</v>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="n">
         <v>5.520438</v>
       </c>
@@ -1024,9 +1006,7 @@
       <c r="M7" t="n">
         <v>100.989998</v>
       </c>
-      <c r="N7" t="n">
-        <v>1644.25</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
         <v>697.5</v>
       </c>
@@ -1066,9 +1046,7 @@
       <c r="AA7" t="n">
         <v>10.722507</v>
       </c>
-      <c r="AB7" t="n">
-        <v>10.31533</v>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="n">
         <v>11.421725</v>
       </c>
@@ -1113,9 +1091,7 @@
       <c r="M8" t="n">
         <v>107.910004</v>
       </c>
-      <c r="N8" t="n">
-        <v>1618.25</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
         <v>748.75</v>
       </c>
@@ -1155,9 +1131,7 @@
       <c r="AA8" t="n">
         <v>6.852169</v>
       </c>
-      <c r="AB8" t="n">
-        <v>-1.581268</v>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="n">
         <v>7.34767</v>
       </c>
@@ -1202,9 +1176,7 @@
       <c r="M9" t="n">
         <v>109.339996</v>
       </c>
-      <c r="N9" t="n">
-        <v>1708.25</v>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
         <v>818.25</v>
       </c>
@@ -1244,9 +1216,7 @@
       <c r="AA9" t="n">
         <v>1.325172</v>
       </c>
-      <c r="AB9" t="n">
-        <v>5.561563</v>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="n">
         <v>9.282137000000001</v>
       </c>
@@ -1291,9 +1261,7 @@
       <c r="M10" t="n">
         <v>122.839996</v>
       </c>
-      <c r="N10" t="n">
-        <v>1683.25</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
         <v>753.5</v>
       </c>
@@ -1333,9 +1301,7 @@
       <c r="AA10" t="n">
         <v>12.346809</v>
       </c>
-      <c r="AB10" t="n">
-        <v>-1.463486</v>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="n">
         <v>-7.913229</v>
       </c>
@@ -1380,9 +1346,7 @@
       <c r="M11" t="n">
         <v>114.809998</v>
       </c>
-      <c r="N11" t="n">
-        <v>1675</v>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
         <v>743.75</v>
       </c>
@@ -1422,9 +1386,7 @@
       <c r="AA11" t="n">
         <v>-6.536958</v>
       </c>
-      <c r="AB11" t="n">
-        <v>-0.490123</v>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="n">
         <v>-1.293962</v>
       </c>
@@ -1469,9 +1431,7 @@
       <c r="M12" t="n">
         <v>110.010002</v>
       </c>
-      <c r="N12" t="n">
-        <v>1637</v>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
         <v>616.25</v>
       </c>
@@ -1511,9 +1471,7 @@
       <c r="AA12" t="n">
         <v>-4.180817</v>
       </c>
-      <c r="AB12" t="n">
-        <v>-2.268657</v>
-      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="n">
         <v>-17.142857</v>
       </c>
@@ -1558,9 +1516,7 @@
       <c r="M13" t="n">
         <v>96.489998</v>
       </c>
-      <c r="N13" t="n">
-        <v>1507.5</v>
-      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
         <v>673.75</v>
       </c>
@@ -1600,9 +1556,7 @@
       <c r="AA13" t="n">
         <v>-12.289795</v>
       </c>
-      <c r="AB13" t="n">
-        <v>-7.910812</v>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="n">
         <v>9.330629</v>
       </c>
@@ -1647,9 +1601,7 @@
       <c r="M14" t="n">
         <v>87.959999</v>
       </c>
-      <c r="N14" t="n">
-        <v>1364.75</v>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
         <v>677.5</v>
       </c>
@@ -1689,9 +1641,7 @@
       <c r="AA14" t="n">
         <v>-8.840293000000001</v>
       </c>
-      <c r="AB14" t="n">
-        <v>-9.46932</v>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="n">
         <v>0.556586</v>
       </c>
@@ -1736,9 +1686,7 @@
       <c r="M15" t="n">
         <v>94.83000199999999</v>
       </c>
-      <c r="N15" t="n">
-        <v>1407</v>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
         <v>691.5</v>
       </c>
@@ -1778,9 +1726,7 @@
       <c r="AA15" t="n">
         <v>7.810372</v>
       </c>
-      <c r="AB15" t="n">
-        <v>3.095805</v>
-      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="n">
         <v>2.066421</v>
       </c>
@@ -1825,9 +1771,7 @@
       <c r="M16" t="n">
         <v>85.43000000000001</v>
       </c>
-      <c r="N16" t="n">
-        <v>1469.5</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>662</v>
       </c>
@@ -1867,9 +1811,7 @@
       <c r="AA16" t="n">
         <v>-9.912476</v>
       </c>
-      <c r="AB16" t="n">
-        <v>4.442075</v>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="n">
         <v>-4.266088</v>
       </c>
@@ -1914,9 +1856,7 @@
       <c r="M17" t="n">
         <v>85.910004</v>
       </c>
-      <c r="N17" t="n">
-        <v>1519.25</v>
-      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
         <v>678.5</v>
       </c>
@@ -1956,9 +1896,7 @@
       <c r="AA17" t="n">
         <v>0.561867</v>
       </c>
-      <c r="AB17" t="n">
-        <v>3.385505</v>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="n">
         <v>2.492447</v>
       </c>
@@ -2003,9 +1941,7 @@
       <c r="M18" t="n">
         <v>84.489998</v>
       </c>
-      <c r="N18" t="n">
-        <v>1538</v>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
         <v>679.75</v>
       </c>
@@ -2045,9 +1981,7 @@
       <c r="AA18" t="n">
         <v>-1.652899</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.234162</v>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="n">
         <v>0.18423</v>
       </c>
@@ -2092,9 +2026,7 @@
       <c r="M19" t="n">
         <v>83.889999</v>
       </c>
-      <c r="N19" t="n">
-        <v>1490.5</v>
-      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
         <v>629.5</v>
       </c>
@@ -2134,9 +2066,7 @@
       <c r="AA19" t="n">
         <v>-0.710141</v>
       </c>
-      <c r="AB19" t="n">
-        <v>-3.088427</v>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="n">
         <v>-7.392424</v>
       </c>
@@ -2181,9 +2111,7 @@
       <c r="M20" t="n">
         <v>79.769997</v>
       </c>
-      <c r="N20" t="n">
-        <v>1505.5</v>
-      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
         <v>660.5</v>
       </c>
@@ -2223,9 +2151,7 @@
       <c r="AA20" t="n">
         <v>-4.911197</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.006374</v>
-      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="n">
         <v>4.924543</v>
       </c>
@@ -2270,9 +2196,7 @@
       <c r="M21" t="n">
         <v>79.540001</v>
       </c>
-      <c r="N21" t="n">
-        <v>1444.25</v>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
         <v>636</v>
       </c>
@@ -2312,9 +2236,7 @@
       <c r="AA21" t="n">
         <v>-0.288324</v>
       </c>
-      <c r="AB21" t="n">
-        <v>-4.068416</v>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="n">
         <v>-3.709311</v>
       </c>
@@ -2359,9 +2281,7 @@
       <c r="M22" t="n">
         <v>72.660004</v>
       </c>
-      <c r="N22" t="n">
-        <v>1299.75</v>
-      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
         <v>594</v>
       </c>
@@ -2401,9 +2321,7 @@
       <c r="AA22" t="n">
         <v>-8.649732</v>
       </c>
-      <c r="AB22" t="n">
-        <v>-10.005193</v>
-      </c>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="n">
         <v>-6.603774</v>
       </c>
@@ -2448,9 +2366,7 @@
       <c r="M23" t="n">
         <v>74.900002</v>
       </c>
-      <c r="N23" t="n">
-        <v>1557.25</v>
-      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
         <v>554.5</v>
       </c>
@@ -2490,9 +2406,7 @@
       <c r="AA23" t="n">
         <v>3.082849</v>
       </c>
-      <c r="AB23" t="n">
-        <v>19.811502</v>
-      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="n">
         <v>-6.649832</v>
       </c>
@@ -2537,9 +2451,7 @@
       <c r="M24" t="n">
         <v>85.55999799999999</v>
       </c>
-      <c r="N24" t="n">
-        <v>1445.75</v>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
         <v>504</v>
       </c>
@@ -2579,9 +2491,7 @@
       <c r="AA24" t="n">
         <v>14.232304</v>
       </c>
-      <c r="AB24" t="n">
-        <v>-7.160058</v>
-      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="n">
         <v>-9.107303999999999</v>
       </c>
@@ -2626,9 +2536,7 @@
       <c r="M25" t="n">
         <v>86.860001</v>
       </c>
-      <c r="N25" t="n">
-        <v>1360</v>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
         <v>461</v>
       </c>
@@ -2668,9 +2576,7 @@
       <c r="AA25" t="n">
         <v>1.519405</v>
       </c>
-      <c r="AB25" t="n">
-        <v>-5.931178</v>
-      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="n">
         <v>-8.531746</v>
       </c>
@@ -2715,9 +2621,7 @@
       <c r="M26" t="n">
         <v>95.30999799999999</v>
       </c>
-      <c r="N26" t="n">
-        <v>1275</v>
-      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
         <v>476.75</v>
       </c>
@@ -2757,9 +2661,7 @@
       <c r="AA26" t="n">
         <v>9.728294999999999</v>
       </c>
-      <c r="AB26" t="n">
-        <v>-6.25</v>
-      </c>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="n">
         <v>3.416486</v>
       </c>
@@ -2804,9 +2706,7 @@
       <c r="M27" t="n">
         <v>87.410004</v>
       </c>
-      <c r="N27" t="n">
-        <v>1287</v>
-      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
         <v>478.75</v>
       </c>
@@ -2846,9 +2746,7 @@
       <c r="AA27" t="n">
         <v>-8.288736</v>
       </c>
-      <c r="AB27" t="n">
-        <v>0.941176</v>
-      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="n">
         <v>0.419507</v>
       </c>
@@ -2893,9 +2791,7 @@
       <c r="M28" t="n">
         <v>82.83000199999999</v>
       </c>
-      <c r="N28" t="n">
-        <v>1342.75</v>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
         <v>461.75</v>
       </c>
@@ -2935,9 +2831,7 @@
       <c r="AA28" t="n">
         <v>-5.239677</v>
       </c>
-      <c r="AB28" t="n">
-        <v>4.331779</v>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="n">
         <v>-3.550914</v>
       </c>
@@ -2982,9 +2876,7 @@
       <c r="M29" t="n">
         <v>77.040001</v>
       </c>
-      <c r="N29" t="n">
-        <v>1293.5</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
         <v>471.25</v>
       </c>
@@ -3024,9 +2916,7 @@
       <c r="AA29" t="n">
         <v>-6.990222</v>
       </c>
-      <c r="AB29" t="n">
-        <v>-3.667846</v>
-      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="n">
         <v>2.05739</v>
       </c>
@@ -3071,9 +2961,7 @@
       <c r="M30" t="n">
         <v>81.709999</v>
       </c>
-      <c r="N30" t="n">
-        <v>1222.25</v>
-      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
         <v>448.25</v>
       </c>
@@ -3113,9 +3001,7 @@
       <c r="AA30" t="n">
         <v>6.061784</v>
       </c>
-      <c r="AB30" t="n">
-        <v>-5.508311</v>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
         <v>-4.880637</v>
       </c>
@@ -3160,9 +3046,7 @@
       <c r="M31" t="n">
         <v>83.620003</v>
       </c>
-      <c r="N31" t="n">
-        <v>1128.25</v>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
         <v>415.75</v>
       </c>
@@ -3202,9 +3086,7 @@
       <c r="AA31" t="n">
         <v>2.33754</v>
       </c>
-      <c r="AB31" t="n">
-        <v>-7.690734</v>
-      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="n">
         <v>-7.250418</v>
       </c>
@@ -3249,9 +3131,7 @@
       <c r="M32" t="n">
         <v>87.480003</v>
       </c>
-      <c r="N32" t="n">
-        <v>1191.5</v>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
         <v>442</v>
       </c>
@@ -3291,9 +3171,7 @@
       <c r="AA32" t="n">
         <v>4.616121</v>
       </c>
-      <c r="AB32" t="n">
-        <v>5.606027</v>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="n">
         <v>6.313891</v>
       </c>
@@ -3338,9 +3216,7 @@
       <c r="M33" t="n">
         <v>87.860001</v>
       </c>
-      <c r="N33" t="n">
-        <v>1145.5</v>
-      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
         <v>439.5</v>
       </c>
@@ -3380,9 +3256,7 @@
       <c r="AA33" t="n">
         <v>0.434382</v>
       </c>
-      <c r="AB33" t="n">
-        <v>-3.86068</v>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
         <v>-0.565611</v>
       </c>
@@ -3427,9 +3301,7 @@
       <c r="M34" t="n">
         <v>81.620003</v>
       </c>
-      <c r="N34" t="n">
-        <v>1205</v>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
         <v>446.25</v>
       </c>
@@ -3469,9 +3341,7 @@
       <c r="AA34" t="n">
         <v>-7.102206</v>
       </c>
-      <c r="AB34" t="n">
-        <v>5.194238</v>
-      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="n">
         <v>1.535836</v>
       </c>
@@ -3516,9 +3386,7 @@
       <c r="M35" t="n">
         <v>86.410004</v>
       </c>
-      <c r="N35" t="n">
-        <v>1150.5</v>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
         <v>397.25</v>
       </c>
@@ -3558,9 +3426,7 @@
       <c r="AA35" t="n">
         <v>5.868661</v>
       </c>
-      <c r="AB35" t="n">
-        <v>-4.522822</v>
-      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="n">
         <v>-10.980392</v>
       </c>
@@ -3605,9 +3471,7 @@
       <c r="M36" t="n">
         <v>80.720001</v>
       </c>
-      <c r="N36" t="n">
-        <v>1028.5</v>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="n">
         <v>382.75</v>
       </c>
@@ -3647,9 +3511,7 @@
       <c r="AA36" t="n">
         <v>-6.584889</v>
       </c>
-      <c r="AB36" t="n">
-        <v>-10.604085</v>
-      </c>
+      <c r="AB36" t="inlineStr"/>
       <c r="AC36" t="n">
         <v>-3.650094</v>
       </c>
@@ -3694,9 +3556,7 @@
       <c r="M37" t="n">
         <v>78.800003</v>
       </c>
-      <c r="N37" t="n">
-        <v>982</v>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
         <v>378</v>
       </c>
@@ -3736,9 +3596,7 @@
       <c r="AA37" t="n">
         <v>-2.37859</v>
       </c>
-      <c r="AB37" t="n">
-        <v>-4.521147</v>
-      </c>
+      <c r="AB37" t="inlineStr"/>
       <c r="AC37" t="n">
         <v>-1.241019</v>
       </c>
@@ -3783,9 +3641,7 @@
       <c r="M38" t="n">
         <v>71.769997</v>
       </c>
-      <c r="N38" t="n">
-        <v>1057</v>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
         <v>424.75</v>
       </c>
@@ -3825,9 +3681,7 @@
       <c r="AA38" t="n">
         <v>-8.921328000000001</v>
       </c>
-      <c r="AB38" t="n">
-        <v>7.637475</v>
-      </c>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
         <v>12.367725</v>
       </c>
@@ -3872,9 +3726,7 @@
       <c r="M39" t="n">
         <v>73.160004</v>
       </c>
-      <c r="N39" t="n">
-        <v>982.5</v>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
         <v>410.75</v>
       </c>
@@ -3914,9 +3766,7 @@
       <c r="AA39" t="n">
         <v>1.936752</v>
       </c>
-      <c r="AB39" t="n">
-        <v>-7.04825</v>
-      </c>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="n">
         <v>-3.296057</v>
       </c>
@@ -3961,9 +3811,7 @@
       <c r="M40" t="n">
         <v>72.94000200000001</v>
       </c>
-      <c r="N40" t="n">
-        <v>989.5</v>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
         <v>423</v>
       </c>
@@ -4003,9 +3851,7 @@
       <c r="AA40" t="n">
         <v>-0.300712</v>
       </c>
-      <c r="AB40" t="n">
-        <v>0.712468</v>
-      </c>
+      <c r="AB40" t="inlineStr"/>
       <c r="AC40" t="n">
         <v>2.982349</v>
       </c>
@@ -4050,9 +3896,7 @@
       <c r="M41" t="n">
         <v>74.639999</v>
       </c>
-      <c r="N41" t="n">
-        <v>998.25</v>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
         <v>458.5</v>
       </c>
@@ -4092,9 +3936,7 @@
       <c r="AA41" t="n">
         <v>2.330678</v>
       </c>
-      <c r="AB41" t="n">
-        <v>0.884285</v>
-      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="n">
         <v>8.392435000000001</v>
       </c>
@@ -4139,9 +3981,7 @@
       <c r="M42" t="n">
         <v>76.760002</v>
       </c>
-      <c r="N42" t="n">
-        <v>1042</v>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
         <v>482</v>
       </c>
@@ -4181,9 +4021,7 @@
       <c r="AA42" t="n">
         <v>2.840304</v>
       </c>
-      <c r="AB42" t="n">
-        <v>4.38267</v>
-      </c>
+      <c r="AB42" t="inlineStr"/>
       <c r="AC42" t="n">
         <v>5.125409</v>
       </c>
@@ -4228,9 +4066,7 @@
       <c r="M43" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="N43" t="n">
-        <v>1011.5</v>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
         <v>453.5</v>
       </c>
@@ -4270,9 +4106,7 @@
       <c r="AA43" t="n">
         <v>-4.66389</v>
       </c>
-      <c r="AB43" t="n">
-        <v>-2.927063</v>
-      </c>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="n">
         <v>-5.912863</v>
       </c>
@@ -4317,9 +4151,7 @@
       <c r="M44" t="n">
         <v>74.739998</v>
       </c>
-      <c r="N44" t="n">
-        <v>1014.75</v>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
         <v>457.25</v>
       </c>
@@ -4359,9 +4191,7 @@
       <c r="AA44" t="n">
         <v>2.131727</v>
       </c>
-      <c r="AB44" t="n">
-        <v>0.321305</v>
-      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="n">
         <v>0.826902</v>
       </c>
@@ -4406,9 +4236,7 @@
       <c r="M45" t="n">
         <v>63.119999</v>
       </c>
-      <c r="N45" t="n">
-        <v>1034.75</v>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
         <v>467.25</v>
       </c>
@@ -4448,9 +4276,7 @@
       <c r="AA45" t="n">
         <v>-15.547229</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.970929</v>
-      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="n">
         <v>2.186987</v>
       </c>
@@ -4495,9 +4321,7 @@
       <c r="M46" t="n">
         <v>63.900002</v>
       </c>
-      <c r="N46" t="n">
-        <v>1041.75</v>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
         <v>444</v>
       </c>
@@ -4537,9 +4361,7 @@
       <c r="AA46" t="n">
         <v>1.235746</v>
       </c>
-      <c r="AB46" t="n">
-        <v>0.676492</v>
-      </c>
+      <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="n">
         <v>-4.975923</v>
       </c>
@@ -4584,9 +4406,7 @@
       <c r="M47" t="n">
         <v>67.610001</v>
       </c>
-      <c r="N47" t="n">
-        <v>1024.25</v>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
         <v>420.5</v>
       </c>
@@ -4626,9 +4446,7 @@
       <c r="AA47" t="n">
         <v>5.805945</v>
       </c>
-      <c r="AB47" t="n">
-        <v>-1.679866</v>
-      </c>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="n">
         <v>-5.292793</v>
       </c>
@@ -4673,9 +4491,7 @@
       <c r="M48" t="n">
         <v>72.529999</v>
       </c>
-      <c r="N48" t="n">
-        <v>961.75</v>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="n">
         <v>394</v>
       </c>
@@ -4715,9 +4531,7 @@
       <c r="AA48" t="n">
         <v>7.277027</v>
       </c>
-      <c r="AB48" t="n">
-        <v>-6.102026</v>
-      </c>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="n">
         <v>-6.302021</v>
       </c>
@@ -4762,9 +4576,7 @@
       <c r="M49" t="n">
         <v>68.120003</v>
       </c>
-      <c r="N49" t="n">
-        <v>1036.75</v>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
         <v>398</v>
       </c>
@@ -4804,9 +4616,7 @@
       <c r="AA49" t="n">
         <v>-6.080237</v>
       </c>
-      <c r="AB49" t="n">
-        <v>7.798284</v>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="n">
         <v>1.015228</v>
       </c>
@@ -4851,9 +4661,7 @@
       <c r="M50" t="n">
         <v>67.019997</v>
       </c>
-      <c r="N50" t="n">
-        <v>1001.75</v>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
         <v>415.5</v>
       </c>
@@ -4893,9 +4701,7 @@
       <c r="AA50" t="n">
         <v>-1.614806</v>
       </c>
-      <c r="AB50" t="n">
-        <v>-3.375934</v>
-      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="n">
         <v>4.396985</v>
       </c>
@@ -4940,9 +4746,7 @@
       <c r="M51" t="n">
         <v>65.06999999999999</v>
       </c>
-      <c r="N51" t="n">
-        <v>1099.75</v>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
         <v>431.5</v>
       </c>
@@ -4982,9 +4786,7 @@
       <c r="AA51" t="n">
         <v>-2.909575</v>
       </c>
-      <c r="AB51" t="n">
-        <v>9.78288</v>
-      </c>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="n">
         <v>3.850782</v>
       </c>
@@ -5029,9 +4831,7 @@
       <c r="M52" t="n">
         <v>63.200001</v>
       </c>
-      <c r="N52" t="n">
-        <v>1137.75</v>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
         <v>435.5</v>
       </c>
@@ -5071,9 +4871,7 @@
       <c r="AA52" t="n">
         <v>-2.873827</v>
       </c>
-      <c r="AB52" t="n">
-        <v>3.455331</v>
-      </c>
+      <c r="AB52" t="inlineStr"/>
       <c r="AC52" t="n">
         <v>0.926999</v>
       </c>
@@ -5118,9 +4916,7 @@
       <c r="M53" t="n">
         <v>60.849998</v>
       </c>
-      <c r="N53" t="n">
-        <v>1030.5</v>
-      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="n">
         <v>440.25</v>
       </c>
@@ -5160,9 +4956,7 @@
       <c r="AA53" t="n">
         <v>-3.718358</v>
       </c>
-      <c r="AB53" t="n">
-        <v>-9.426500000000001</v>
-      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="n">
         <v>1.0907</v>
       </c>
@@ -5207,9 +5001,7 @@
       <c r="M54" t="n">
         <v>70.69000200000001</v>
       </c>
-      <c r="N54" t="n">
-        <v>1064.25</v>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
         <v>428.25</v>
       </c>
@@ -5249,9 +5041,7 @@
       <c r="AA54" t="n">
         <v>16.170919</v>
       </c>
-      <c r="AB54" t="n">
-        <v>3.275109</v>
-      </c>
+      <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="n">
         <v>-2.725724</v>
       </c>
@@ -5296,9 +5086,7 @@
       <c r="M55" t="n">
         <v>72.480003</v>
       </c>
-      <c r="N55" t="n">
-        <v>1157.25</v>
-      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
         <v>438.75</v>
       </c>
@@ -5338,9 +5126,7 @@
       <c r="AA55" t="n">
         <v>2.532184</v>
       </c>
-      <c r="AB55" t="n">
-        <v>8.738548</v>
-      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="n">
         <v>2.451839</v>
       </c>
@@ -5385,9 +5171,7 @@
       <c r="M56" t="n">
         <v>118.349998</v>
       </c>
-      <c r="N56" t="n">
-        <v>1171</v>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="n">
         <v>457.75</v>
       </c>
@@ -5427,9 +5211,7 @@
       <c r="AA56" t="n">
         <v>63.286414</v>
       </c>
-      <c r="AB56" t="n">
-        <v>1.188162</v>
-      </c>
+      <c r="AB56" t="inlineStr"/>
       <c r="AC56" t="n">
         <v>4.330484</v>
       </c>
@@ -5474,9 +5256,7 @@
       <c r="M57" t="n">
         <v>114.010002</v>
       </c>
-      <c r="N57" t="n">
-        <v>1182</v>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="n">
         <v>464.75</v>
       </c>
@@ -5516,9 +5296,7 @@
       <c r="AA57" t="n">
         <v>-3.667086</v>
       </c>
-      <c r="AB57" t="n">
-        <v>0.939368</v>
-      </c>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="n">
         <v>1.529219</v>
       </c>
@@ -5563,9 +5341,7 @@
       <c r="M58" t="n">
         <v>92.050003</v>
       </c>
-      <c r="N58" t="n">
-        <v>1186.75</v>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="n">
         <v>446.75</v>
       </c>
@@ -5605,9 +5381,7 @@
       <c r="AA58" t="n">
         <v>-19.261467</v>
       </c>
-      <c r="AB58" t="n">
-        <v>0.401861</v>
-      </c>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="n">
         <v>-3.87305</v>
       </c>
@@ -5652,9 +5426,7 @@
       <c r="M59" t="n">
         <v>72.91999800000001</v>
       </c>
-      <c r="N59" t="n">
-        <v>1116.75</v>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="n">
         <v>412.75</v>
       </c>
@@ -5694,9 +5466,7 @@
       <c r="AA59" t="n">
         <v>-20.782188</v>
       </c>
-      <c r="AB59" t="n">
-        <v>-5.898462</v>
-      </c>
+      <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="n">
         <v>-7.61052</v>
       </c>
@@ -5741,9 +5511,7 @@
       <c r="M60" t="n">
         <v>90.120003</v>
       </c>
-      <c r="N60" t="n">
-        <v>1172</v>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="n">
         <v>440.75</v>
       </c>
@@ -5783,9 +5551,7 @@
       <c r="AA60" t="n">
         <v>23.5875</v>
       </c>
-      <c r="AB60" t="n">
-        <v>4.947392</v>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="n">
         <v>6.783767</v>
       </c>
@@ -5830,9 +5596,7 @@
       <c r="M61" t="n">
         <v>90.489998</v>
       </c>
-      <c r="N61" t="n">
-        <v>1275.25</v>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="n">
         <v>515</v>
       </c>
@@ -5872,9 +5636,7 @@
       <c r="AA61" t="n">
         <v>0.410558</v>
       </c>
-      <c r="AB61" t="n">
-        <v>8.809727000000001</v>
-      </c>
+      <c r="AB61" t="inlineStr"/>
       <c r="AC61" t="n">
         <v>16.846285</v>
       </c>
@@ -5884,88 +5646,84 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>184544.75</v>
+        <v>184955.578125</v>
       </c>
       <c r="C62" t="n">
-        <v>181.610001</v>
+        <v>182.089996</v>
       </c>
       <c r="D62" t="n">
-        <v>109.209999</v>
+        <v>108.889999</v>
       </c>
       <c r="E62" t="n">
-        <v>444.839996</v>
+        <v>444.149994</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1599</v>
+        <v>5.1563</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9317</v>
+        <v>5.9081</v>
       </c>
       <c r="H62" t="n">
-        <v>7630.069824</v>
+        <v>7623.669922</v>
       </c>
       <c r="I62" t="n">
-        <v>26407.919922</v>
+        <v>26423.677734</v>
       </c>
       <c r="J62" t="n">
-        <v>51741.929688</v>
+        <v>51562.378906</v>
       </c>
       <c r="K62" t="n">
-        <v>4410.5</v>
+        <v>4391</v>
       </c>
       <c r="L62" t="n">
-        <v>100.389999</v>
+        <v>97.860001</v>
       </c>
       <c r="M62" t="n">
-        <v>102.959999</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1312.5</v>
-      </c>
+        <v>100.040001</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="n">
-        <v>528</v>
+        <v>526.75</v>
       </c>
       <c r="P62" t="n">
-        <v>4.01634</v>
+        <v>4.247898</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.907771</v>
+        <v>4.182399</v>
       </c>
       <c r="R62" t="n">
-        <v>2.902103</v>
+        <v>2.600586</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.003674</v>
+        <v>-1.15723</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.602936</v>
+        <v>-0.6722860000000001</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.296501</v>
+        <v>-1.689207</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.729499</v>
+        <v>-0.812764</v>
       </c>
       <c r="W62" t="n">
-        <v>0.140417</v>
+        <v>0.200172</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.714947</v>
+        <v>-3.052538</v>
       </c>
       <c r="Y62" t="n">
-        <v>-1.584291</v>
+        <v>-2.019413</v>
       </c>
       <c r="Z62" t="n">
-        <v>17.059231</v>
+        <v>14.10914</v>
       </c>
       <c r="AA62" t="n">
-        <v>13.78053</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>2.920996</v>
-      </c>
+        <v>10.553656</v>
+      </c>
+      <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="n">
-        <v>2.524272</v>
+        <v>2.281553</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -607,7 +607,9 @@
       <c r="M2" t="n">
         <v>78.519997</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>1256</v>
+      </c>
       <c r="O2" t="n">
         <v>536.75</v>
       </c>
@@ -666,7 +668,9 @@
       <c r="M3" t="n">
         <v>84.379997</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>1235.75</v>
+      </c>
       <c r="O3" t="n">
         <v>568.25</v>
       </c>
@@ -706,7 +710,9 @@
       <c r="AA3" t="n">
         <v>7.463068</v>
       </c>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>-1.612261</v>
+      </c>
       <c r="AC3" t="n">
         <v>5.868654</v>
       </c>
@@ -751,7 +757,9 @@
       <c r="M4" t="n">
         <v>70.56999999999999</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>1217.25</v>
+      </c>
       <c r="O4" t="n">
         <v>567</v>
       </c>
@@ -791,7 +799,9 @@
       <c r="AA4" t="n">
         <v>-16.366435</v>
       </c>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>-1.497067</v>
+      </c>
       <c r="AC4" t="n">
         <v>-0.219974</v>
       </c>
@@ -836,7 +846,9 @@
       <c r="M5" t="n">
         <v>77.779999</v>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>1328.75</v>
+      </c>
       <c r="O5" t="n">
         <v>593.25</v>
       </c>
@@ -876,7 +888,9 @@
       <c r="AA5" t="n">
         <v>10.216805</v>
       </c>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>9.159992000000001</v>
+      </c>
       <c r="AC5" t="n">
         <v>4.62963</v>
       </c>
@@ -921,7 +935,9 @@
       <c r="M6" t="n">
         <v>91.209999</v>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>1490.5</v>
+      </c>
       <c r="O6" t="n">
         <v>626</v>
       </c>
@@ -961,7 +977,9 @@
       <c r="AA6" t="n">
         <v>17.26665</v>
       </c>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>12.173095</v>
+      </c>
       <c r="AC6" t="n">
         <v>5.520438</v>
       </c>
@@ -1006,7 +1024,9 @@
       <c r="M7" t="n">
         <v>100.989998</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>1644.25</v>
+      </c>
       <c r="O7" t="n">
         <v>697.5</v>
       </c>
@@ -1046,7 +1066,9 @@
       <c r="AA7" t="n">
         <v>10.722507</v>
       </c>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>10.31533</v>
+      </c>
       <c r="AC7" t="n">
         <v>11.421725</v>
       </c>
@@ -1091,7 +1113,9 @@
       <c r="M8" t="n">
         <v>107.910004</v>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>1618.25</v>
+      </c>
       <c r="O8" t="n">
         <v>748.75</v>
       </c>
@@ -1131,7 +1155,9 @@
       <c r="AA8" t="n">
         <v>6.852169</v>
       </c>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>-1.581268</v>
+      </c>
       <c r="AC8" t="n">
         <v>7.34767</v>
       </c>
@@ -1176,7 +1202,9 @@
       <c r="M9" t="n">
         <v>109.339996</v>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>1708.25</v>
+      </c>
       <c r="O9" t="n">
         <v>818.25</v>
       </c>
@@ -1216,7 +1244,9 @@
       <c r="AA9" t="n">
         <v>1.325172</v>
       </c>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>5.561563</v>
+      </c>
       <c r="AC9" t="n">
         <v>9.282137000000001</v>
       </c>
@@ -1261,7 +1291,9 @@
       <c r="M10" t="n">
         <v>122.839996</v>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>1683.25</v>
+      </c>
       <c r="O10" t="n">
         <v>753.5</v>
       </c>
@@ -1301,7 +1333,9 @@
       <c r="AA10" t="n">
         <v>12.346809</v>
       </c>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>-1.463486</v>
+      </c>
       <c r="AC10" t="n">
         <v>-7.913229</v>
       </c>
@@ -1346,7 +1380,9 @@
       <c r="M11" t="n">
         <v>114.809998</v>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>1675</v>
+      </c>
       <c r="O11" t="n">
         <v>743.75</v>
       </c>
@@ -1386,7 +1422,9 @@
       <c r="AA11" t="n">
         <v>-6.536958</v>
       </c>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>-0.490123</v>
+      </c>
       <c r="AC11" t="n">
         <v>-1.293962</v>
       </c>
@@ -1431,7 +1469,9 @@
       <c r="M12" t="n">
         <v>110.010002</v>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>1637</v>
+      </c>
       <c r="O12" t="n">
         <v>616.25</v>
       </c>
@@ -1471,7 +1511,9 @@
       <c r="AA12" t="n">
         <v>-4.180817</v>
       </c>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>-2.268657</v>
+      </c>
       <c r="AC12" t="n">
         <v>-17.142857</v>
       </c>
@@ -1516,7 +1558,9 @@
       <c r="M13" t="n">
         <v>96.489998</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>1507.5</v>
+      </c>
       <c r="O13" t="n">
         <v>673.75</v>
       </c>
@@ -1556,7 +1600,9 @@
       <c r="AA13" t="n">
         <v>-12.289795</v>
       </c>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>-7.910812</v>
+      </c>
       <c r="AC13" t="n">
         <v>9.330629</v>
       </c>
@@ -1601,7 +1647,9 @@
       <c r="M14" t="n">
         <v>87.959999</v>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>1364.75</v>
+      </c>
       <c r="O14" t="n">
         <v>677.5</v>
       </c>
@@ -1641,7 +1689,9 @@
       <c r="AA14" t="n">
         <v>-8.840293000000001</v>
       </c>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>-9.46932</v>
+      </c>
       <c r="AC14" t="n">
         <v>0.556586</v>
       </c>
@@ -1686,7 +1736,9 @@
       <c r="M15" t="n">
         <v>94.83000199999999</v>
       </c>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="n">
+        <v>1407</v>
+      </c>
       <c r="O15" t="n">
         <v>691.5</v>
       </c>
@@ -1726,7 +1778,9 @@
       <c r="AA15" t="n">
         <v>7.810372</v>
       </c>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>3.095805</v>
+      </c>
       <c r="AC15" t="n">
         <v>2.066421</v>
       </c>
@@ -1771,7 +1825,9 @@
       <c r="M16" t="n">
         <v>85.43000000000001</v>
       </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>1469.5</v>
+      </c>
       <c r="O16" t="n">
         <v>662</v>
       </c>
@@ -1811,7 +1867,9 @@
       <c r="AA16" t="n">
         <v>-9.912476</v>
       </c>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AB16" t="n">
+        <v>4.442075</v>
+      </c>
       <c r="AC16" t="n">
         <v>-4.266088</v>
       </c>
@@ -1856,7 +1914,9 @@
       <c r="M17" t="n">
         <v>85.910004</v>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>1519.25</v>
+      </c>
       <c r="O17" t="n">
         <v>678.5</v>
       </c>
@@ -1896,7 +1956,9 @@
       <c r="AA17" t="n">
         <v>0.561867</v>
       </c>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>3.385505</v>
+      </c>
       <c r="AC17" t="n">
         <v>2.492447</v>
       </c>
@@ -1941,7 +2003,9 @@
       <c r="M18" t="n">
         <v>84.489998</v>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>1538</v>
+      </c>
       <c r="O18" t="n">
         <v>679.75</v>
       </c>
@@ -1981,7 +2045,9 @@
       <c r="AA18" t="n">
         <v>-1.652899</v>
       </c>
-      <c r="AB18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>1.234162</v>
+      </c>
       <c r="AC18" t="n">
         <v>0.18423</v>
       </c>
@@ -2026,7 +2092,9 @@
       <c r="M19" t="n">
         <v>83.889999</v>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>1490.5</v>
+      </c>
       <c r="O19" t="n">
         <v>629.5</v>
       </c>
@@ -2066,7 +2134,9 @@
       <c r="AA19" t="n">
         <v>-0.710141</v>
       </c>
-      <c r="AB19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>-3.088427</v>
+      </c>
       <c r="AC19" t="n">
         <v>-7.392424</v>
       </c>
@@ -2111,7 +2181,9 @@
       <c r="M20" t="n">
         <v>79.769997</v>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="n">
+        <v>1505.5</v>
+      </c>
       <c r="O20" t="n">
         <v>660.5</v>
       </c>
@@ -2151,7 +2223,9 @@
       <c r="AA20" t="n">
         <v>-4.911197</v>
       </c>
-      <c r="AB20" t="inlineStr"/>
+      <c r="AB20" t="n">
+        <v>1.006374</v>
+      </c>
       <c r="AC20" t="n">
         <v>4.924543</v>
       </c>
@@ -2196,7 +2270,9 @@
       <c r="M21" t="n">
         <v>79.540001</v>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>1444.25</v>
+      </c>
       <c r="O21" t="n">
         <v>636</v>
       </c>
@@ -2236,7 +2312,9 @@
       <c r="AA21" t="n">
         <v>-0.288324</v>
       </c>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AB21" t="n">
+        <v>-4.068416</v>
+      </c>
       <c r="AC21" t="n">
         <v>-3.709311</v>
       </c>
@@ -2281,7 +2359,9 @@
       <c r="M22" t="n">
         <v>72.660004</v>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>1299.75</v>
+      </c>
       <c r="O22" t="n">
         <v>594</v>
       </c>
@@ -2321,7 +2401,9 @@
       <c r="AA22" t="n">
         <v>-8.649732</v>
       </c>
-      <c r="AB22" t="inlineStr"/>
+      <c r="AB22" t="n">
+        <v>-10.005193</v>
+      </c>
       <c r="AC22" t="n">
         <v>-6.603774</v>
       </c>
@@ -2366,7 +2448,9 @@
       <c r="M23" t="n">
         <v>74.900002</v>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>1557.25</v>
+      </c>
       <c r="O23" t="n">
         <v>554.5</v>
       </c>
@@ -2406,7 +2490,9 @@
       <c r="AA23" t="n">
         <v>3.082849</v>
       </c>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="n">
+        <v>19.811502</v>
+      </c>
       <c r="AC23" t="n">
         <v>-6.649832</v>
       </c>
@@ -2451,7 +2537,9 @@
       <c r="M24" t="n">
         <v>85.55999799999999</v>
       </c>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>1445.75</v>
+      </c>
       <c r="O24" t="n">
         <v>504</v>
       </c>
@@ -2491,7 +2579,9 @@
       <c r="AA24" t="n">
         <v>14.232304</v>
       </c>
-      <c r="AB24" t="inlineStr"/>
+      <c r="AB24" t="n">
+        <v>-7.160058</v>
+      </c>
       <c r="AC24" t="n">
         <v>-9.107303999999999</v>
       </c>
@@ -2536,7 +2626,9 @@
       <c r="M25" t="n">
         <v>86.860001</v>
       </c>
-      <c r="N25" t="inlineStr"/>
+      <c r="N25" t="n">
+        <v>1360</v>
+      </c>
       <c r="O25" t="n">
         <v>461</v>
       </c>
@@ -2576,7 +2668,9 @@
       <c r="AA25" t="n">
         <v>1.519405</v>
       </c>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>-5.931178</v>
+      </c>
       <c r="AC25" t="n">
         <v>-8.531746</v>
       </c>
@@ -2621,7 +2715,9 @@
       <c r="M26" t="n">
         <v>95.30999799999999</v>
       </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="N26" t="n">
+        <v>1275</v>
+      </c>
       <c r="O26" t="n">
         <v>476.75</v>
       </c>
@@ -2661,7 +2757,9 @@
       <c r="AA26" t="n">
         <v>9.728294999999999</v>
       </c>
-      <c r="AB26" t="inlineStr"/>
+      <c r="AB26" t="n">
+        <v>-6.25</v>
+      </c>
       <c r="AC26" t="n">
         <v>3.416486</v>
       </c>
@@ -2706,7 +2804,9 @@
       <c r="M27" t="n">
         <v>87.410004</v>
       </c>
-      <c r="N27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>1287</v>
+      </c>
       <c r="O27" t="n">
         <v>478.75</v>
       </c>
@@ -2746,7 +2846,9 @@
       <c r="AA27" t="n">
         <v>-8.288736</v>
       </c>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>0.941176</v>
+      </c>
       <c r="AC27" t="n">
         <v>0.419507</v>
       </c>
@@ -2791,7 +2893,9 @@
       <c r="M28" t="n">
         <v>82.83000199999999</v>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="n">
+        <v>1342.75</v>
+      </c>
       <c r="O28" t="n">
         <v>461.75</v>
       </c>
@@ -2831,7 +2935,9 @@
       <c r="AA28" t="n">
         <v>-5.239677</v>
       </c>
-      <c r="AB28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>4.331779</v>
+      </c>
       <c r="AC28" t="n">
         <v>-3.550914</v>
       </c>
@@ -2876,7 +2982,9 @@
       <c r="M29" t="n">
         <v>77.040001</v>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>1293.5</v>
+      </c>
       <c r="O29" t="n">
         <v>471.25</v>
       </c>
@@ -2916,7 +3024,9 @@
       <c r="AA29" t="n">
         <v>-6.990222</v>
       </c>
-      <c r="AB29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>-3.667846</v>
+      </c>
       <c r="AC29" t="n">
         <v>2.05739</v>
       </c>
@@ -2961,7 +3071,9 @@
       <c r="M30" t="n">
         <v>81.709999</v>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>1222.25</v>
+      </c>
       <c r="O30" t="n">
         <v>448.25</v>
       </c>
@@ -3001,7 +3113,9 @@
       <c r="AA30" t="n">
         <v>6.061784</v>
       </c>
-      <c r="AB30" t="inlineStr"/>
+      <c r="AB30" t="n">
+        <v>-5.508311</v>
+      </c>
       <c r="AC30" t="n">
         <v>-4.880637</v>
       </c>
@@ -3046,7 +3160,9 @@
       <c r="M31" t="n">
         <v>83.620003</v>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="N31" t="n">
+        <v>1128.25</v>
+      </c>
       <c r="O31" t="n">
         <v>415.75</v>
       </c>
@@ -3086,7 +3202,9 @@
       <c r="AA31" t="n">
         <v>2.33754</v>
       </c>
-      <c r="AB31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>-7.690734</v>
+      </c>
       <c r="AC31" t="n">
         <v>-7.250418</v>
       </c>
@@ -3131,7 +3249,9 @@
       <c r="M32" t="n">
         <v>87.480003</v>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>1191.5</v>
+      </c>
       <c r="O32" t="n">
         <v>442</v>
       </c>
@@ -3171,7 +3291,9 @@
       <c r="AA32" t="n">
         <v>4.616121</v>
       </c>
-      <c r="AB32" t="inlineStr"/>
+      <c r="AB32" t="n">
+        <v>5.606027</v>
+      </c>
       <c r="AC32" t="n">
         <v>6.313891</v>
       </c>
@@ -3216,7 +3338,9 @@
       <c r="M33" t="n">
         <v>87.860001</v>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="N33" t="n">
+        <v>1145.5</v>
+      </c>
       <c r="O33" t="n">
         <v>439.5</v>
       </c>
@@ -3256,7 +3380,9 @@
       <c r="AA33" t="n">
         <v>0.434382</v>
       </c>
-      <c r="AB33" t="inlineStr"/>
+      <c r="AB33" t="n">
+        <v>-3.86068</v>
+      </c>
       <c r="AC33" t="n">
         <v>-0.565611</v>
       </c>
@@ -3301,7 +3427,9 @@
       <c r="M34" t="n">
         <v>81.620003</v>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>1205</v>
+      </c>
       <c r="O34" t="n">
         <v>446.25</v>
       </c>
@@ -3341,7 +3469,9 @@
       <c r="AA34" t="n">
         <v>-7.102206</v>
       </c>
-      <c r="AB34" t="inlineStr"/>
+      <c r="AB34" t="n">
+        <v>5.194238</v>
+      </c>
       <c r="AC34" t="n">
         <v>1.535836</v>
       </c>
@@ -3386,7 +3516,9 @@
       <c r="M35" t="n">
         <v>86.410004</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>1150.5</v>
+      </c>
       <c r="O35" t="n">
         <v>397.25</v>
       </c>
@@ -3426,7 +3558,9 @@
       <c r="AA35" t="n">
         <v>5.868661</v>
       </c>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="n">
+        <v>-4.522822</v>
+      </c>
       <c r="AC35" t="n">
         <v>-10.980392</v>
       </c>
@@ -3471,7 +3605,9 @@
       <c r="M36" t="n">
         <v>80.720001</v>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>1028.5</v>
+      </c>
       <c r="O36" t="n">
         <v>382.75</v>
       </c>
@@ -3511,7 +3647,9 @@
       <c r="AA36" t="n">
         <v>-6.584889</v>
       </c>
-      <c r="AB36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>-10.604085</v>
+      </c>
       <c r="AC36" t="n">
         <v>-3.650094</v>
       </c>
@@ -3556,7 +3694,9 @@
       <c r="M37" t="n">
         <v>78.800003</v>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>982</v>
+      </c>
       <c r="O37" t="n">
         <v>378</v>
       </c>
@@ -3596,7 +3736,9 @@
       <c r="AA37" t="n">
         <v>-2.37859</v>
       </c>
-      <c r="AB37" t="inlineStr"/>
+      <c r="AB37" t="n">
+        <v>-4.521147</v>
+      </c>
       <c r="AC37" t="n">
         <v>-1.241019</v>
       </c>
@@ -3641,7 +3783,9 @@
       <c r="M38" t="n">
         <v>71.769997</v>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>1057</v>
+      </c>
       <c r="O38" t="n">
         <v>424.75</v>
       </c>
@@ -3681,7 +3825,9 @@
       <c r="AA38" t="n">
         <v>-8.921328000000001</v>
       </c>
-      <c r="AB38" t="inlineStr"/>
+      <c r="AB38" t="n">
+        <v>7.637475</v>
+      </c>
       <c r="AC38" t="n">
         <v>12.367725</v>
       </c>
@@ -3726,7 +3872,9 @@
       <c r="M39" t="n">
         <v>73.160004</v>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>982.5</v>
+      </c>
       <c r="O39" t="n">
         <v>410.75</v>
       </c>
@@ -3766,7 +3914,9 @@
       <c r="AA39" t="n">
         <v>1.936752</v>
       </c>
-      <c r="AB39" t="inlineStr"/>
+      <c r="AB39" t="n">
+        <v>-7.04825</v>
+      </c>
       <c r="AC39" t="n">
         <v>-3.296057</v>
       </c>
@@ -3811,7 +3961,9 @@
       <c r="M40" t="n">
         <v>72.94000200000001</v>
       </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>989.5</v>
+      </c>
       <c r="O40" t="n">
         <v>423</v>
       </c>
@@ -3851,7 +4003,9 @@
       <c r="AA40" t="n">
         <v>-0.300712</v>
       </c>
-      <c r="AB40" t="inlineStr"/>
+      <c r="AB40" t="n">
+        <v>0.712468</v>
+      </c>
       <c r="AC40" t="n">
         <v>2.982349</v>
       </c>
@@ -3896,7 +4050,9 @@
       <c r="M41" t="n">
         <v>74.639999</v>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>998.25</v>
+      </c>
       <c r="O41" t="n">
         <v>458.5</v>
       </c>
@@ -3936,7 +4092,9 @@
       <c r="AA41" t="n">
         <v>2.330678</v>
       </c>
-      <c r="AB41" t="inlineStr"/>
+      <c r="AB41" t="n">
+        <v>0.884285</v>
+      </c>
       <c r="AC41" t="n">
         <v>8.392435000000001</v>
       </c>
@@ -3981,7 +4139,9 @@
       <c r="M42" t="n">
         <v>76.760002</v>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>1042</v>
+      </c>
       <c r="O42" t="n">
         <v>482</v>
       </c>
@@ -4021,7 +4181,9 @@
       <c r="AA42" t="n">
         <v>2.840304</v>
       </c>
-      <c r="AB42" t="inlineStr"/>
+      <c r="AB42" t="n">
+        <v>4.38267</v>
+      </c>
       <c r="AC42" t="n">
         <v>5.125409</v>
       </c>
@@ -4066,7 +4228,9 @@
       <c r="M43" t="n">
         <v>73.18000000000001</v>
       </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>1011.5</v>
+      </c>
       <c r="O43" t="n">
         <v>453.5</v>
       </c>
@@ -4106,7 +4270,9 @@
       <c r="AA43" t="n">
         <v>-4.66389</v>
       </c>
-      <c r="AB43" t="inlineStr"/>
+      <c r="AB43" t="n">
+        <v>-2.927063</v>
+      </c>
       <c r="AC43" t="n">
         <v>-5.912863</v>
       </c>
@@ -4151,7 +4317,9 @@
       <c r="M44" t="n">
         <v>74.739998</v>
       </c>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="n">
+        <v>1014.75</v>
+      </c>
       <c r="O44" t="n">
         <v>457.25</v>
       </c>
@@ -4191,7 +4359,9 @@
       <c r="AA44" t="n">
         <v>2.131727</v>
       </c>
-      <c r="AB44" t="inlineStr"/>
+      <c r="AB44" t="n">
+        <v>0.321305</v>
+      </c>
       <c r="AC44" t="n">
         <v>0.826902</v>
       </c>
@@ -4236,7 +4406,9 @@
       <c r="M45" t="n">
         <v>63.119999</v>
       </c>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="n">
+        <v>1034.75</v>
+      </c>
       <c r="O45" t="n">
         <v>467.25</v>
       </c>
@@ -4276,7 +4448,9 @@
       <c r="AA45" t="n">
         <v>-15.547229</v>
       </c>
-      <c r="AB45" t="inlineStr"/>
+      <c r="AB45" t="n">
+        <v>1.970929</v>
+      </c>
       <c r="AC45" t="n">
         <v>2.186987</v>
       </c>
@@ -4321,7 +4495,9 @@
       <c r="M46" t="n">
         <v>63.900002</v>
       </c>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>1041.75</v>
+      </c>
       <c r="O46" t="n">
         <v>444</v>
       </c>
@@ -4361,7 +4537,9 @@
       <c r="AA46" t="n">
         <v>1.235746</v>
       </c>
-      <c r="AB46" t="inlineStr"/>
+      <c r="AB46" t="n">
+        <v>0.676492</v>
+      </c>
       <c r="AC46" t="n">
         <v>-4.975923</v>
       </c>
@@ -4406,7 +4584,9 @@
       <c r="M47" t="n">
         <v>67.610001</v>
       </c>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>1024.25</v>
+      </c>
       <c r="O47" t="n">
         <v>420.5</v>
       </c>
@@ -4446,7 +4626,9 @@
       <c r="AA47" t="n">
         <v>5.805945</v>
       </c>
-      <c r="AB47" t="inlineStr"/>
+      <c r="AB47" t="n">
+        <v>-1.679866</v>
+      </c>
       <c r="AC47" t="n">
         <v>-5.292793</v>
       </c>
@@ -4491,7 +4673,9 @@
       <c r="M48" t="n">
         <v>72.529999</v>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>961.75</v>
+      </c>
       <c r="O48" t="n">
         <v>394</v>
       </c>
@@ -4531,7 +4715,9 @@
       <c r="AA48" t="n">
         <v>7.277027</v>
       </c>
-      <c r="AB48" t="inlineStr"/>
+      <c r="AB48" t="n">
+        <v>-6.102026</v>
+      </c>
       <c r="AC48" t="n">
         <v>-6.302021</v>
       </c>
@@ -4576,7 +4762,9 @@
       <c r="M49" t="n">
         <v>68.120003</v>
       </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>1036.75</v>
+      </c>
       <c r="O49" t="n">
         <v>398</v>
       </c>
@@ -4616,7 +4804,9 @@
       <c r="AA49" t="n">
         <v>-6.080237</v>
       </c>
-      <c r="AB49" t="inlineStr"/>
+      <c r="AB49" t="n">
+        <v>7.798284</v>
+      </c>
       <c r="AC49" t="n">
         <v>1.015228</v>
       </c>
@@ -4661,7 +4851,9 @@
       <c r="M50" t="n">
         <v>67.019997</v>
       </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="n">
+        <v>1001.75</v>
+      </c>
       <c r="O50" t="n">
         <v>415.5</v>
       </c>
@@ -4701,7 +4893,9 @@
       <c r="AA50" t="n">
         <v>-1.614806</v>
       </c>
-      <c r="AB50" t="inlineStr"/>
+      <c r="AB50" t="n">
+        <v>-3.375934</v>
+      </c>
       <c r="AC50" t="n">
         <v>4.396985</v>
       </c>
@@ -4746,7 +4940,9 @@
       <c r="M51" t="n">
         <v>65.06999999999999</v>
       </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>1099.75</v>
+      </c>
       <c r="O51" t="n">
         <v>431.5</v>
       </c>
@@ -4786,7 +4982,9 @@
       <c r="AA51" t="n">
         <v>-2.909575</v>
       </c>
-      <c r="AB51" t="inlineStr"/>
+      <c r="AB51" t="n">
+        <v>9.78288</v>
+      </c>
       <c r="AC51" t="n">
         <v>3.850782</v>
       </c>
@@ -4831,7 +5029,9 @@
       <c r="M52" t="n">
         <v>63.200001</v>
       </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="n">
+        <v>1137.75</v>
+      </c>
       <c r="O52" t="n">
         <v>435.5</v>
       </c>
@@ -4871,7 +5071,9 @@
       <c r="AA52" t="n">
         <v>-2.873827</v>
       </c>
-      <c r="AB52" t="inlineStr"/>
+      <c r="AB52" t="n">
+        <v>3.455331</v>
+      </c>
       <c r="AC52" t="n">
         <v>0.926999</v>
       </c>
@@ -4916,7 +5118,9 @@
       <c r="M53" t="n">
         <v>60.849998</v>
       </c>
-      <c r="N53" t="inlineStr"/>
+      <c r="N53" t="n">
+        <v>1030.5</v>
+      </c>
       <c r="O53" t="n">
         <v>440.25</v>
       </c>
@@ -4956,7 +5160,9 @@
       <c r="AA53" t="n">
         <v>-3.718358</v>
       </c>
-      <c r="AB53" t="inlineStr"/>
+      <c r="AB53" t="n">
+        <v>-9.426500000000001</v>
+      </c>
       <c r="AC53" t="n">
         <v>1.0907</v>
       </c>
@@ -5001,7 +5207,9 @@
       <c r="M54" t="n">
         <v>70.69000200000001</v>
       </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="n">
+        <v>1064.25</v>
+      </c>
       <c r="O54" t="n">
         <v>428.25</v>
       </c>
@@ -5041,7 +5249,9 @@
       <c r="AA54" t="n">
         <v>16.170919</v>
       </c>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AB54" t="n">
+        <v>3.275109</v>
+      </c>
       <c r="AC54" t="n">
         <v>-2.725724</v>
       </c>
@@ -5086,7 +5296,9 @@
       <c r="M55" t="n">
         <v>72.480003</v>
       </c>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="n">
+        <v>1157.25</v>
+      </c>
       <c r="O55" t="n">
         <v>438.75</v>
       </c>
@@ -5126,7 +5338,9 @@
       <c r="AA55" t="n">
         <v>2.532184</v>
       </c>
-      <c r="AB55" t="inlineStr"/>
+      <c r="AB55" t="n">
+        <v>8.738548</v>
+      </c>
       <c r="AC55" t="n">
         <v>2.451839</v>
       </c>
@@ -5171,7 +5385,9 @@
       <c r="M56" t="n">
         <v>118.349998</v>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>1171</v>
+      </c>
       <c r="O56" t="n">
         <v>457.75</v>
       </c>
@@ -5211,7 +5427,9 @@
       <c r="AA56" t="n">
         <v>63.286414</v>
       </c>
-      <c r="AB56" t="inlineStr"/>
+      <c r="AB56" t="n">
+        <v>1.188162</v>
+      </c>
       <c r="AC56" t="n">
         <v>4.330484</v>
       </c>
@@ -5256,7 +5474,9 @@
       <c r="M57" t="n">
         <v>114.010002</v>
       </c>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="n">
+        <v>1182</v>
+      </c>
       <c r="O57" t="n">
         <v>464.75</v>
       </c>
@@ -5296,7 +5516,9 @@
       <c r="AA57" t="n">
         <v>-3.667086</v>
       </c>
-      <c r="AB57" t="inlineStr"/>
+      <c r="AB57" t="n">
+        <v>0.939368</v>
+      </c>
       <c r="AC57" t="n">
         <v>1.529219</v>
       </c>
@@ -5341,7 +5563,9 @@
       <c r="M58" t="n">
         <v>92.050003</v>
       </c>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="n">
+        <v>1186.75</v>
+      </c>
       <c r="O58" t="n">
         <v>446.75</v>
       </c>
@@ -5381,7 +5605,9 @@
       <c r="AA58" t="n">
         <v>-19.261467</v>
       </c>
-      <c r="AB58" t="inlineStr"/>
+      <c r="AB58" t="n">
+        <v>0.401861</v>
+      </c>
       <c r="AC58" t="n">
         <v>-3.87305</v>
       </c>
@@ -5426,7 +5652,9 @@
       <c r="M59" t="n">
         <v>72.91999800000001</v>
       </c>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="n">
+        <v>1116.75</v>
+      </c>
       <c r="O59" t="n">
         <v>412.75</v>
       </c>
@@ -5466,7 +5694,9 @@
       <c r="AA59" t="n">
         <v>-20.782188</v>
       </c>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AB59" t="n">
+        <v>-5.898462</v>
+      </c>
       <c r="AC59" t="n">
         <v>-7.61052</v>
       </c>
@@ -5511,7 +5741,9 @@
       <c r="M60" t="n">
         <v>90.120003</v>
       </c>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>1172</v>
+      </c>
       <c r="O60" t="n">
         <v>440.75</v>
       </c>
@@ -5551,7 +5783,9 @@
       <c r="AA60" t="n">
         <v>23.5875</v>
       </c>
-      <c r="AB60" t="inlineStr"/>
+      <c r="AB60" t="n">
+        <v>4.947392</v>
+      </c>
       <c r="AC60" t="n">
         <v>6.783767</v>
       </c>
@@ -5596,7 +5830,9 @@
       <c r="M61" t="n">
         <v>90.489998</v>
       </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>1275.25</v>
+      </c>
       <c r="O61" t="n">
         <v>515</v>
       </c>
@@ -5636,7 +5872,9 @@
       <c r="AA61" t="n">
         <v>0.410558</v>
       </c>
-      <c r="AB61" t="inlineStr"/>
+      <c r="AB61" t="n">
+        <v>8.809727000000001</v>
+      </c>
       <c r="AC61" t="n">
         <v>16.846285</v>
       </c>
@@ -5646,84 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>184955.578125</v>
+        <v>185229</v>
       </c>
       <c r="C62" t="n">
-        <v>182.089996</v>
+        <v>183.279999</v>
       </c>
       <c r="D62" t="n">
-        <v>108.889999</v>
+        <v>109.690002</v>
       </c>
       <c r="E62" t="n">
-        <v>444.149994</v>
+        <v>442.600006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1563</v>
+        <v>5.1421</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9081</v>
+        <v>5.9057</v>
       </c>
       <c r="H62" t="n">
-        <v>7623.669922</v>
+        <v>7650.5</v>
       </c>
       <c r="I62" t="n">
-        <v>26423.677734</v>
+        <v>26522.539062</v>
       </c>
       <c r="J62" t="n">
-        <v>51562.378906</v>
+        <v>51682.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4391</v>
+        <v>4424.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>97.860001</v>
+        <v>100.300003</v>
       </c>
       <c r="M62" t="n">
-        <v>100.040001</v>
-      </c>
-      <c r="N62" t="inlineStr"/>
+        <v>103.870003</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1303.5</v>
+      </c>
       <c r="O62" t="n">
-        <v>526.75</v>
+        <v>527.5</v>
       </c>
       <c r="P62" t="n">
-        <v>4.247898</v>
+        <v>4.402009</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.182399</v>
+        <v>4.863257</v>
       </c>
       <c r="R62" t="n">
-        <v>2.600586</v>
+        <v>3.354382</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.15723</v>
+        <v>-1.50217</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.6722860000000001</v>
+        <v>-0.9458299999999999</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.689207</v>
+        <v>-1.729141</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.812764</v>
+        <v>-0.463694</v>
       </c>
       <c r="W62" t="n">
-        <v>0.200172</v>
+        <v>0.57506</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.052538</v>
+        <v>-2.826422</v>
       </c>
       <c r="Y62" t="n">
-        <v>-2.019413</v>
+        <v>-1.262972</v>
       </c>
       <c r="Z62" t="n">
-        <v>14.10914</v>
+        <v>16.954292</v>
       </c>
       <c r="AA62" t="n">
-        <v>10.553656</v>
-      </c>
-      <c r="AB62" t="inlineStr"/>
+        <v>14.78617</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>2.215252</v>
+      </c>
       <c r="AC62" t="n">
-        <v>2.281553</v>
+        <v>2.427184</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5887,16 +5887,16 @@
         <v>185229</v>
       </c>
       <c r="C62" t="n">
-        <v>183.279999</v>
+        <v>182.470001</v>
       </c>
       <c r="D62" t="n">
         <v>109.690002</v>
       </c>
       <c r="E62" t="n">
-        <v>442.600006</v>
+        <v>443.5</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1421</v>
+        <v>5.1442</v>
       </c>
       <c r="G62" t="n">
         <v>5.9057</v>
@@ -5914,10 +5914,10 @@
         <v>4424.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>100.300003</v>
+        <v>96.08000199999999</v>
       </c>
       <c r="M62" t="n">
-        <v>103.870003</v>
+        <v>99.290001</v>
       </c>
       <c r="N62" t="n">
         <v>1303.5</v>
@@ -5929,16 +5929,16 @@
         <v>4.402009</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.863257</v>
+        <v>4.399818</v>
       </c>
       <c r="R62" t="n">
         <v>3.354382</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.50217</v>
+        <v>-1.301882</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.9458299999999999</v>
+        <v>-0.905377</v>
       </c>
       <c r="U62" t="n">
         <v>-1.729141</v>
@@ -5956,10 +5956,10 @@
         <v>-1.262972</v>
       </c>
       <c r="Z62" t="n">
-        <v>16.954292</v>
+        <v>12.033581</v>
       </c>
       <c r="AA62" t="n">
-        <v>14.78617</v>
+        <v>9.724835000000001</v>
       </c>
       <c r="AB62" t="n">
         <v>2.215252</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185229</v>
+        <v>186247.09375</v>
       </c>
       <c r="C62" t="n">
-        <v>182.470001</v>
+        <v>183.380005</v>
       </c>
       <c r="D62" t="n">
-        <v>109.690002</v>
+        <v>111.540001</v>
       </c>
       <c r="E62" t="n">
-        <v>443.5</v>
+        <v>446.429993</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1442</v>
+        <v>5.1019</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9057</v>
+        <v>5.8593</v>
       </c>
       <c r="H62" t="n">
-        <v>7650.5</v>
+        <v>7743.27002</v>
       </c>
       <c r="I62" t="n">
-        <v>26522.539062</v>
+        <v>27005.107422</v>
       </c>
       <c r="J62" t="n">
-        <v>51682.640625</v>
+        <v>51959.019531</v>
       </c>
       <c r="K62" t="n">
-        <v>4424.899902</v>
+        <v>4386.200195</v>
       </c>
       <c r="L62" t="n">
-        <v>96.08000199999999</v>
+        <v>92.339996</v>
       </c>
       <c r="M62" t="n">
-        <v>99.290001</v>
+        <v>96.199997</v>
       </c>
       <c r="N62" t="n">
-        <v>1303.5</v>
+        <v>1325.25</v>
       </c>
       <c r="O62" t="n">
-        <v>527.5</v>
+        <v>542.5</v>
       </c>
       <c r="P62" t="n">
-        <v>4.402009</v>
+        <v>4.975845</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.399818</v>
+        <v>4.920475</v>
       </c>
       <c r="R62" t="n">
-        <v>3.354382</v>
+        <v>5.097525</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.301882</v>
+        <v>-0.649831</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.905377</v>
+        <v>-1.720213</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.729141</v>
+        <v>-2.501239</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.463694</v>
+        <v>0.7432839999999999</v>
       </c>
       <c r="W62" t="n">
-        <v>0.57506</v>
+        <v>2.404988</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.826422</v>
+        <v>-2.306775</v>
       </c>
       <c r="Y62" t="n">
-        <v>-1.262972</v>
+        <v>-2.126516</v>
       </c>
       <c r="Z62" t="n">
-        <v>12.033581</v>
+        <v>7.672568</v>
       </c>
       <c r="AA62" t="n">
-        <v>9.724835000000001</v>
+        <v>6.310089</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.215252</v>
+        <v>3.9208</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.427184</v>
+        <v>5.339806</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>186247.09375</v>
+        <v>185986.109375</v>
       </c>
       <c r="C62" t="n">
-        <v>183.380005</v>
+        <v>183.190002</v>
       </c>
       <c r="D62" t="n">
-        <v>111.540001</v>
+        <v>111.32</v>
       </c>
       <c r="E62" t="n">
-        <v>446.429993</v>
+        <v>449.369995</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1019</v>
+        <v>5.1202</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8593</v>
+        <v>5.8591</v>
       </c>
       <c r="H62" t="n">
-        <v>7743.27002</v>
+        <v>7770.220215</v>
       </c>
       <c r="I62" t="n">
-        <v>27005.107422</v>
+        <v>27251.701172</v>
       </c>
       <c r="J62" t="n">
-        <v>51959.019531</v>
+        <v>51857.640625</v>
       </c>
       <c r="K62" t="n">
-        <v>4386.200195</v>
+        <v>4367.5</v>
       </c>
       <c r="L62" t="n">
-        <v>92.339996</v>
+        <v>90.910004</v>
       </c>
       <c r="M62" t="n">
-        <v>96.199997</v>
+        <v>99.470001</v>
       </c>
       <c r="N62" t="n">
-        <v>1325.25</v>
+        <v>1327.25</v>
       </c>
       <c r="O62" t="n">
-        <v>542.5</v>
+        <v>538.25</v>
       </c>
       <c r="P62" t="n">
-        <v>4.975845</v>
+        <v>4.828744</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.920475</v>
+        <v>4.811765</v>
       </c>
       <c r="R62" t="n">
-        <v>5.097525</v>
+        <v>4.890231</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.649831</v>
+        <v>0.004448</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.720213</v>
+        <v>-1.367692</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.501239</v>
+        <v>-2.504571</v>
       </c>
       <c r="V62" t="n">
-        <v>0.7432839999999999</v>
+        <v>1.093918</v>
       </c>
       <c r="W62" t="n">
-        <v>2.404988</v>
+        <v>3.340086</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.306775</v>
+        <v>-2.497387</v>
       </c>
       <c r="Y62" t="n">
-        <v>-2.126516</v>
+        <v>-2.543791</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.672568</v>
+        <v>6.005132</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.310089</v>
+        <v>9.923752</v>
       </c>
       <c r="AB62" t="n">
-        <v>3.9208</v>
+        <v>4.077632</v>
       </c>
       <c r="AC62" t="n">
-        <v>5.339806</v>
+        <v>4.514563</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185986.109375</v>
+        <v>185576.765625</v>
       </c>
       <c r="C62" t="n">
-        <v>183.190002</v>
+        <v>182.740005</v>
       </c>
       <c r="D62" t="n">
-        <v>111.32</v>
+        <v>111.169998</v>
       </c>
       <c r="E62" t="n">
-        <v>449.369995</v>
+        <v>449.450012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1202</v>
+        <v>5.1167</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8591</v>
+        <v>5.858</v>
       </c>
       <c r="H62" t="n">
-        <v>7770.220215</v>
+        <v>7768.72998</v>
       </c>
       <c r="I62" t="n">
-        <v>27251.701172</v>
+        <v>27249.957031</v>
       </c>
       <c r="J62" t="n">
-        <v>51857.640625</v>
+        <v>51828.691406</v>
       </c>
       <c r="K62" t="n">
-        <v>4367.5</v>
+        <v>4366</v>
       </c>
       <c r="L62" t="n">
-        <v>90.910004</v>
+        <v>90.699997</v>
       </c>
       <c r="M62" t="n">
-        <v>99.470001</v>
+        <v>99.25</v>
       </c>
       <c r="N62" t="n">
-        <v>1327.25</v>
+        <v>1327.5</v>
       </c>
       <c r="O62" t="n">
-        <v>538.25</v>
+        <v>538</v>
       </c>
       <c r="P62" t="n">
-        <v>4.828744</v>
+        <v>4.598023</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.811765</v>
+        <v>4.554301</v>
       </c>
       <c r="R62" t="n">
-        <v>4.890231</v>
+        <v>4.748894</v>
       </c>
       <c r="S62" t="n">
-        <v>0.004448</v>
+        <v>0.022256</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.367692</v>
+        <v>-1.435113</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.504571</v>
+        <v>-2.522876</v>
       </c>
       <c r="V62" t="n">
-        <v>1.093918</v>
+        <v>1.07453</v>
       </c>
       <c r="W62" t="n">
-        <v>3.340086</v>
+        <v>3.333473</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.497387</v>
+        <v>-2.551817</v>
       </c>
       <c r="Y62" t="n">
-        <v>-2.543791</v>
+        <v>-2.577262</v>
       </c>
       <c r="Z62" t="n">
-        <v>6.005132</v>
+        <v>5.760255</v>
       </c>
       <c r="AA62" t="n">
-        <v>9.923752</v>
+        <v>9.680630000000001</v>
       </c>
       <c r="AB62" t="n">
-        <v>4.077632</v>
+        <v>4.097236</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.514563</v>
+        <v>4.466019</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185576.765625</v>
+        <v>187575.046875</v>
       </c>
       <c r="C62" t="n">
-        <v>182.740005</v>
+        <v>184.679993</v>
       </c>
       <c r="D62" t="n">
-        <v>111.169998</v>
+        <v>111.980003</v>
       </c>
       <c r="E62" t="n">
-        <v>449.450012</v>
+        <v>448.869995</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1167</v>
+        <v>5.1471</v>
       </c>
       <c r="G62" t="n">
-        <v>5.858</v>
+        <v>5.8651</v>
       </c>
       <c r="H62" t="n">
-        <v>7768.72998</v>
+        <v>7725.299805</v>
       </c>
       <c r="I62" t="n">
-        <v>27249.957031</v>
+        <v>26969.003906</v>
       </c>
       <c r="J62" t="n">
-        <v>51828.691406</v>
+        <v>51787.929688</v>
       </c>
       <c r="K62" t="n">
-        <v>4366</v>
+        <v>4315.5</v>
       </c>
       <c r="L62" t="n">
-        <v>90.699997</v>
+        <v>92.099998</v>
       </c>
       <c r="M62" t="n">
-        <v>99.25</v>
+        <v>97.620003</v>
       </c>
       <c r="N62" t="n">
-        <v>1327.5</v>
+        <v>1315.75</v>
       </c>
       <c r="O62" t="n">
-        <v>538</v>
+        <v>528.75</v>
       </c>
       <c r="P62" t="n">
-        <v>4.598023</v>
+        <v>5.724329</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.554301</v>
+        <v>5.66426</v>
       </c>
       <c r="R62" t="n">
-        <v>4.748894</v>
+        <v>5.512114</v>
       </c>
       <c r="S62" t="n">
-        <v>0.022256</v>
+        <v>-0.106823</v>
       </c>
       <c r="T62" t="n">
-        <v>-1.435113</v>
+        <v>-0.849511</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.522876</v>
+        <v>-2.40473</v>
       </c>
       <c r="V62" t="n">
-        <v>1.07453</v>
+        <v>0.509484</v>
       </c>
       <c r="W62" t="n">
-        <v>3.333473</v>
+        <v>2.268081</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.551817</v>
+        <v>-2.628458</v>
       </c>
       <c r="Y62" t="n">
-        <v>-2.577262</v>
+        <v>-3.704117</v>
       </c>
       <c r="Z62" t="n">
-        <v>5.760255</v>
+        <v>7.392719</v>
       </c>
       <c r="AA62" t="n">
-        <v>9.680630000000001</v>
+        <v>7.879329</v>
       </c>
       <c r="AB62" t="n">
-        <v>4.097236</v>
+        <v>3.175848</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.466019</v>
+        <v>2.669903</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>187575.046875</v>
+        <v>185430.703125</v>
       </c>
       <c r="C62" t="n">
-        <v>184.679993</v>
+        <v>182.5</v>
       </c>
       <c r="D62" t="n">
-        <v>111.980003</v>
+        <v>110.760002</v>
       </c>
       <c r="E62" t="n">
-        <v>448.869995</v>
+        <v>449.720001</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1471</v>
+        <v>5.1764</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8651</v>
+        <v>5.8909</v>
       </c>
       <c r="H62" t="n">
-        <v>7725.299805</v>
+        <v>7687.310059</v>
       </c>
       <c r="I62" t="n">
-        <v>26969.003906</v>
+        <v>26805.265625</v>
       </c>
       <c r="J62" t="n">
-        <v>51787.929688</v>
+        <v>51308.679688</v>
       </c>
       <c r="K62" t="n">
-        <v>4315.5</v>
+        <v>4298.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>92.099998</v>
+        <v>94.66999800000001</v>
       </c>
       <c r="M62" t="n">
-        <v>97.620003</v>
+        <v>100.309998</v>
       </c>
       <c r="N62" t="n">
-        <v>1315.75</v>
+        <v>1316</v>
       </c>
       <c r="O62" t="n">
-        <v>528.75</v>
+        <v>527.75</v>
       </c>
       <c r="P62" t="n">
-        <v>5.724329</v>
+        <v>4.515696</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.66426</v>
+        <v>4.416982</v>
       </c>
       <c r="R62" t="n">
-        <v>5.512114</v>
+        <v>4.362579</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.106823</v>
+        <v>0.08234</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.849511</v>
+        <v>-0.28509</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.40473</v>
+        <v>-1.975415</v>
       </c>
       <c r="V62" t="n">
-        <v>0.509484</v>
+        <v>0.015221</v>
       </c>
       <c r="W62" t="n">
-        <v>2.268081</v>
+        <v>1.647176</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.628458</v>
+        <v>-3.529542</v>
       </c>
       <c r="Y62" t="n">
-        <v>-3.704117</v>
+        <v>-4.074531</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.392719</v>
+        <v>10.389454</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.879329</v>
+        <v>10.852028</v>
       </c>
       <c r="AB62" t="n">
-        <v>3.175848</v>
+        <v>3.195452</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.669903</v>
+        <v>2.475728</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185430.703125</v>
+        <v>185707.59375</v>
       </c>
       <c r="C62" t="n">
-        <v>182.5</v>
+        <v>182.770004</v>
       </c>
       <c r="D62" t="n">
-        <v>110.760002</v>
+        <v>110.959999</v>
       </c>
       <c r="E62" t="n">
-        <v>449.720001</v>
+        <v>449.549988</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1764</v>
+        <v>5.1808</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8909</v>
+        <v>5.8912</v>
       </c>
       <c r="H62" t="n">
-        <v>7687.310059</v>
+        <v>7687.410156</v>
       </c>
       <c r="I62" t="n">
-        <v>26805.265625</v>
+        <v>26794.8125</v>
       </c>
       <c r="J62" t="n">
-        <v>51308.679688</v>
+        <v>51309.371094</v>
       </c>
       <c r="K62" t="n">
-        <v>4298.899902</v>
+        <v>4296.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>94.66999800000001</v>
+        <v>94.720001</v>
       </c>
       <c r="M62" t="n">
-        <v>100.309998</v>
+        <v>100.32</v>
       </c>
       <c r="N62" t="n">
-        <v>1316</v>
+        <v>1317.5</v>
       </c>
       <c r="O62" t="n">
-        <v>527.75</v>
+        <v>530</v>
       </c>
       <c r="P62" t="n">
-        <v>4.515696</v>
+        <v>4.671762</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.416982</v>
+        <v>4.571464</v>
       </c>
       <c r="R62" t="n">
-        <v>4.362579</v>
+        <v>4.551024</v>
       </c>
       <c r="S62" t="n">
-        <v>0.08234</v>
+        <v>0.044505</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.28509</v>
+        <v>-0.200336</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.975415</v>
+        <v>-1.970424</v>
       </c>
       <c r="V62" t="n">
-        <v>0.015221</v>
+        <v>0.016524</v>
       </c>
       <c r="W62" t="n">
-        <v>1.647176</v>
+        <v>1.607537</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.529542</v>
+        <v>-3.528242</v>
       </c>
       <c r="Y62" t="n">
-        <v>-4.074531</v>
+        <v>-4.132549</v>
       </c>
       <c r="Z62" t="n">
-        <v>10.389454</v>
+        <v>10.44776</v>
       </c>
       <c r="AA62" t="n">
-        <v>10.852028</v>
+        <v>10.863081</v>
       </c>
       <c r="AB62" t="n">
-        <v>3.195452</v>
+        <v>3.313076</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.475728</v>
+        <v>2.912621</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185707.59375</v>
+        <v>182428.5</v>
       </c>
       <c r="C62" t="n">
-        <v>182.770004</v>
+        <v>179.610001</v>
       </c>
       <c r="D62" t="n">
-        <v>110.959999</v>
+        <v>109.449997</v>
       </c>
       <c r="E62" t="n">
-        <v>449.549988</v>
+        <v>453.279999</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1808</v>
+        <v>5.204</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8912</v>
+        <v>5.9357</v>
       </c>
       <c r="H62" t="n">
-        <v>7687.410156</v>
+        <v>7712.609863</v>
       </c>
       <c r="I62" t="n">
-        <v>26794.8125</v>
+        <v>26965.560547</v>
       </c>
       <c r="J62" t="n">
-        <v>51309.371094</v>
+        <v>51492.351562</v>
       </c>
       <c r="K62" t="n">
-        <v>4296.299805</v>
+        <v>4306.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>94.720001</v>
+        <v>94.099998</v>
       </c>
       <c r="M62" t="n">
-        <v>100.32</v>
+        <v>99.589996</v>
       </c>
       <c r="N62" t="n">
-        <v>1317.5</v>
+        <v>1305</v>
       </c>
       <c r="O62" t="n">
-        <v>530</v>
+        <v>521.25</v>
       </c>
       <c r="P62" t="n">
-        <v>4.671762</v>
+        <v>2.823542</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.571464</v>
+        <v>2.763475</v>
       </c>
       <c r="R62" t="n">
-        <v>4.551024</v>
+        <v>3.128239</v>
       </c>
       <c r="S62" t="n">
-        <v>0.044505</v>
+        <v>0.874595</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.200336</v>
+        <v>0.246575</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.970424</v>
+        <v>-1.229946</v>
       </c>
       <c r="V62" t="n">
-        <v>0.016524</v>
+        <v>0.344383</v>
       </c>
       <c r="W62" t="n">
-        <v>1.607537</v>
+        <v>2.255024</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.528242</v>
+        <v>-3.184203</v>
       </c>
       <c r="Y62" t="n">
-        <v>-4.132549</v>
+        <v>-3.896019</v>
       </c>
       <c r="Z62" t="n">
-        <v>10.44776</v>
+        <v>9.724809</v>
       </c>
       <c r="AA62" t="n">
-        <v>10.863081</v>
+        <v>10.056358</v>
       </c>
       <c r="AB62" t="n">
-        <v>3.313076</v>
+        <v>2.332876</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.912621</v>
+        <v>1.213592</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>182428.5</v>
+        <v>183477</v>
       </c>
       <c r="C62" t="n">
-        <v>179.610001</v>
+        <v>180.869995</v>
       </c>
       <c r="D62" t="n">
-        <v>109.449997</v>
+        <v>109.949997</v>
       </c>
       <c r="E62" t="n">
-        <v>453.279999</v>
+        <v>451.149994</v>
       </c>
       <c r="F62" t="n">
-        <v>5.204</v>
+        <v>5.1866</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9357</v>
+        <v>5.9081</v>
       </c>
       <c r="H62" t="n">
-        <v>7712.609863</v>
+        <v>7743.410156</v>
       </c>
       <c r="I62" t="n">
-        <v>26965.560547</v>
+        <v>27068.720703</v>
       </c>
       <c r="J62" t="n">
-        <v>51492.351562</v>
+        <v>51828.621094</v>
       </c>
       <c r="K62" t="n">
-        <v>4306.899902</v>
+        <v>4321.200195</v>
       </c>
       <c r="L62" t="n">
-        <v>94.099998</v>
+        <v>92.410004</v>
       </c>
       <c r="M62" t="n">
-        <v>99.589996</v>
+        <v>104.32</v>
       </c>
       <c r="N62" t="n">
-        <v>1305</v>
+        <v>1319</v>
       </c>
       <c r="O62" t="n">
-        <v>521.25</v>
+        <v>528.25</v>
       </c>
       <c r="P62" t="n">
-        <v>2.823542</v>
+        <v>3.414516</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.763475</v>
+        <v>3.484378</v>
       </c>
       <c r="R62" t="n">
-        <v>3.128239</v>
+        <v>3.599359</v>
       </c>
       <c r="S62" t="n">
-        <v>0.874595</v>
+        <v>0.400576</v>
       </c>
       <c r="T62" t="n">
-        <v>0.246575</v>
+        <v>-0.088603</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.229946</v>
+        <v>-1.689207</v>
       </c>
       <c r="V62" t="n">
-        <v>0.344383</v>
+        <v>0.745108</v>
       </c>
       <c r="W62" t="n">
-        <v>2.255024</v>
+        <v>2.646214</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.184203</v>
+        <v>-2.55195</v>
       </c>
       <c r="Y62" t="n">
-        <v>-3.896019</v>
+        <v>-3.576923</v>
       </c>
       <c r="Z62" t="n">
-        <v>9.724809</v>
+        <v>7.754199</v>
       </c>
       <c r="AA62" t="n">
-        <v>10.056358</v>
+        <v>15.283459</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.332876</v>
+        <v>3.4307</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.213592</v>
+        <v>2.572816</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5887,13 +5887,13 @@
         <v>183477</v>
       </c>
       <c r="C62" t="n">
-        <v>180.869995</v>
+        <v>180.820007</v>
       </c>
       <c r="D62" t="n">
-        <v>109.949997</v>
+        <v>110.449997</v>
       </c>
       <c r="E62" t="n">
-        <v>451.149994</v>
+        <v>453</v>
       </c>
       <c r="F62" t="n">
         <v>5.1866</v>
@@ -5917,7 +5917,7 @@
         <v>92.410004</v>
       </c>
       <c r="M62" t="n">
-        <v>104.32</v>
+        <v>97.44000200000001</v>
       </c>
       <c r="N62" t="n">
         <v>1319</v>
@@ -5929,13 +5929,13 @@
         <v>3.414516</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.484378</v>
+        <v>3.455778</v>
       </c>
       <c r="R62" t="n">
-        <v>3.599359</v>
+        <v>4.070479</v>
       </c>
       <c r="S62" t="n">
-        <v>0.400576</v>
+        <v>0.812283</v>
       </c>
       <c r="T62" t="n">
         <v>-0.088603</v>
@@ -5959,7 +5959,7 @@
         <v>7.754199</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.283459</v>
+        <v>7.680412</v>
       </c>
       <c r="AB62" t="n">
         <v>3.4307</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>183477</v>
+        <v>183439.546875</v>
       </c>
       <c r="C62" t="n">
-        <v>180.820007</v>
+        <v>180.580002</v>
       </c>
       <c r="D62" t="n">
-        <v>110.449997</v>
+        <v>109.720001</v>
       </c>
       <c r="E62" t="n">
-        <v>453</v>
+        <v>453.25</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1866</v>
+        <v>5.2176</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9081</v>
+        <v>5.9337</v>
       </c>
       <c r="H62" t="n">
-        <v>7743.410156</v>
+        <v>7702.799805</v>
       </c>
       <c r="I62" t="n">
-        <v>27068.720703</v>
+        <v>26903.330078</v>
       </c>
       <c r="J62" t="n">
-        <v>51828.621094</v>
+        <v>51612.378906</v>
       </c>
       <c r="K62" t="n">
-        <v>4321.200195</v>
+        <v>4170.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>92.410004</v>
+        <v>92.589996</v>
       </c>
       <c r="M62" t="n">
-        <v>97.44000200000001</v>
+        <v>97.69000200000001</v>
       </c>
       <c r="N62" t="n">
-        <v>1319</v>
+        <v>1287</v>
       </c>
       <c r="O62" t="n">
-        <v>528.25</v>
+        <v>522</v>
       </c>
       <c r="P62" t="n">
-        <v>3.414516</v>
+        <v>3.393406</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.455778</v>
+        <v>3.318459</v>
       </c>
       <c r="R62" t="n">
-        <v>4.070479</v>
+        <v>3.382648</v>
       </c>
       <c r="S62" t="n">
-        <v>0.812283</v>
+        <v>0.867919</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.088603</v>
+        <v>0.508555</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.689207</v>
+        <v>-1.263223</v>
       </c>
       <c r="V62" t="n">
-        <v>0.745108</v>
+        <v>0.216749</v>
       </c>
       <c r="W62" t="n">
-        <v>2.646214</v>
+        <v>2.019042</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.55195</v>
+        <v>-2.958528</v>
       </c>
       <c r="Y62" t="n">
-        <v>-3.576923</v>
+        <v>-6.932951</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.754199</v>
+        <v>7.964079</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.680412</v>
+        <v>7.956686</v>
       </c>
       <c r="AB62" t="n">
-        <v>3.4307</v>
+        <v>0.921388</v>
       </c>
       <c r="AC62" t="n">
-        <v>2.572816</v>
+        <v>1.359223</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>183439.546875</v>
+        <v>183466.265625</v>
       </c>
       <c r="C62" t="n">
-        <v>180.580002</v>
+        <v>180.649994</v>
       </c>
       <c r="D62" t="n">
-        <v>109.720001</v>
+        <v>109.889999</v>
       </c>
       <c r="E62" t="n">
-        <v>453.25</v>
+        <v>452.769989</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2176</v>
+        <v>5.2163</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9337</v>
+        <v>5.9327</v>
       </c>
       <c r="H62" t="n">
-        <v>7702.799805</v>
+        <v>7702.350098</v>
       </c>
       <c r="I62" t="n">
-        <v>26903.330078</v>
+        <v>26899.5</v>
       </c>
       <c r="J62" t="n">
-        <v>51612.378906</v>
+        <v>51614.789062</v>
       </c>
       <c r="K62" t="n">
-        <v>4170.799805</v>
+        <v>4170.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>92.589996</v>
+        <v>92.55999799999999</v>
       </c>
       <c r="M62" t="n">
-        <v>97.69000200000001</v>
+        <v>97.769997</v>
       </c>
       <c r="N62" t="n">
-        <v>1287</v>
+        <v>1288.25</v>
       </c>
       <c r="O62" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P62" t="n">
-        <v>3.393406</v>
+        <v>3.408466</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.318459</v>
+        <v>3.358505</v>
       </c>
       <c r="R62" t="n">
-        <v>3.382648</v>
+        <v>3.542827</v>
       </c>
       <c r="S62" t="n">
-        <v>0.867919</v>
+        <v>0.761096</v>
       </c>
       <c r="T62" t="n">
-        <v>0.508555</v>
+        <v>0.483515</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.263223</v>
+        <v>-1.279862</v>
       </c>
       <c r="V62" t="n">
-        <v>0.216749</v>
+        <v>0.210899</v>
       </c>
       <c r="W62" t="n">
-        <v>2.019042</v>
+        <v>2.004518</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.958528</v>
+        <v>-2.953996</v>
       </c>
       <c r="Y62" t="n">
-        <v>-6.932951</v>
+        <v>-6.941874</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.964079</v>
+        <v>7.929099</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.956686</v>
+        <v>8.045087000000001</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.921388</v>
+        <v>1.019408</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.359223</v>
+        <v>1.553398</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>183466.265625</v>
+        <v>182477.703125</v>
       </c>
       <c r="C62" t="n">
-        <v>180.649994</v>
+        <v>179.699997</v>
       </c>
       <c r="D62" t="n">
-        <v>109.889999</v>
+        <v>108.629997</v>
       </c>
       <c r="E62" t="n">
-        <v>452.769989</v>
+        <v>452.440002</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2163</v>
+        <v>5.2304</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9327</v>
+        <v>5.9299</v>
       </c>
       <c r="H62" t="n">
-        <v>7702.350098</v>
+        <v>7660.640137</v>
       </c>
       <c r="I62" t="n">
-        <v>26899.5</v>
+        <v>26774.152344</v>
       </c>
       <c r="J62" t="n">
-        <v>51614.789062</v>
+        <v>51159.171875</v>
       </c>
       <c r="K62" t="n">
-        <v>4170.399902</v>
+        <v>4183.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>92.55999799999999</v>
+        <v>90.720001</v>
       </c>
       <c r="M62" t="n">
-        <v>97.769997</v>
+        <v>96.80999799999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1288.25</v>
+        <v>1297</v>
       </c>
       <c r="O62" t="n">
-        <v>523</v>
+        <v>521.25</v>
       </c>
       <c r="P62" t="n">
-        <v>3.408466</v>
+        <v>2.851275</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.358505</v>
+        <v>2.814966</v>
       </c>
       <c r="R62" t="n">
-        <v>3.542827</v>
+        <v>2.355602</v>
       </c>
       <c r="S62" t="n">
-        <v>0.761096</v>
+        <v>0.687659</v>
       </c>
       <c r="T62" t="n">
-        <v>0.483515</v>
+        <v>0.75513</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.279862</v>
+        <v>-1.326454</v>
       </c>
       <c r="V62" t="n">
-        <v>0.210899</v>
+        <v>-0.331766</v>
       </c>
       <c r="W62" t="n">
-        <v>2.004518</v>
+        <v>1.529193</v>
       </c>
       <c r="X62" t="n">
-        <v>-2.953996</v>
+        <v>-3.810646</v>
       </c>
       <c r="Y62" t="n">
-        <v>-6.941874</v>
+        <v>-6.647326</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.929099</v>
+        <v>5.783581</v>
       </c>
       <c r="AA62" t="n">
-        <v>8.045087000000001</v>
+        <v>6.984197</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.019408</v>
+        <v>1.705548</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.553398</v>
+        <v>1.213592</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>182477.703125</v>
+        <v>182503.359375</v>
       </c>
       <c r="C62" t="n">
-        <v>179.699997</v>
+        <v>179.679993</v>
       </c>
       <c r="D62" t="n">
-        <v>108.629997</v>
+        <v>108.690002</v>
       </c>
       <c r="E62" t="n">
-        <v>452.440002</v>
+        <v>452.390015</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2304</v>
+        <v>5.2357</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9299</v>
+        <v>5.9313</v>
       </c>
       <c r="H62" t="n">
-        <v>7660.640137</v>
+        <v>7660.899902</v>
       </c>
       <c r="I62" t="n">
-        <v>26774.152344</v>
+        <v>26779.210938</v>
       </c>
       <c r="J62" t="n">
-        <v>51159.171875</v>
+        <v>51162.320312</v>
       </c>
       <c r="K62" t="n">
-        <v>4183.600098</v>
+        <v>4185.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>90.720001</v>
+        <v>90.44000200000001</v>
       </c>
       <c r="M62" t="n">
-        <v>96.80999799999999</v>
+        <v>96.769997</v>
       </c>
       <c r="N62" t="n">
-        <v>1297</v>
+        <v>1298.75</v>
       </c>
       <c r="O62" t="n">
-        <v>521.25</v>
+        <v>522</v>
       </c>
       <c r="P62" t="n">
-        <v>2.851275</v>
+        <v>2.865736</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.814966</v>
+        <v>2.803521</v>
       </c>
       <c r="R62" t="n">
-        <v>2.355602</v>
+        <v>2.412141</v>
       </c>
       <c r="S62" t="n">
-        <v>0.687659</v>
+        <v>0.676535</v>
       </c>
       <c r="T62" t="n">
-        <v>0.75513</v>
+        <v>0.857227</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.326454</v>
+        <v>-1.303158</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.331766</v>
+        <v>-0.328386</v>
       </c>
       <c r="W62" t="n">
-        <v>1.529193</v>
+        <v>1.548375</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.810646</v>
+        <v>-3.804727</v>
       </c>
       <c r="Y62" t="n">
-        <v>-6.647326</v>
+        <v>-6.607165</v>
       </c>
       <c r="Z62" t="n">
-        <v>5.783581</v>
+        <v>5.45709</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.984197</v>
+        <v>6.939992</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.705548</v>
+        <v>1.842776</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.213592</v>
+        <v>1.359223</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>182503.359375</v>
+        <v>185742.0625</v>
       </c>
       <c r="C62" t="n">
-        <v>179.679993</v>
+        <v>182.880005</v>
       </c>
       <c r="D62" t="n">
-        <v>108.690002</v>
+        <v>110.900002</v>
       </c>
       <c r="E62" t="n">
-        <v>452.390015</v>
+        <v>450.890015</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2357</v>
+        <v>5.1848</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9313</v>
+        <v>5.8759</v>
       </c>
       <c r="H62" t="n">
-        <v>7660.899902</v>
+        <v>7715.97998</v>
       </c>
       <c r="I62" t="n">
-        <v>26779.210938</v>
+        <v>27077.017578</v>
       </c>
       <c r="J62" t="n">
-        <v>51162.320312</v>
+        <v>51323.691406</v>
       </c>
       <c r="K62" t="n">
-        <v>4185.399902</v>
+        <v>4191.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>90.44000200000001</v>
+        <v>91.379997</v>
       </c>
       <c r="M62" t="n">
-        <v>96.769997</v>
+        <v>98.83000199999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1298.75</v>
+        <v>1309.75</v>
       </c>
       <c r="O62" t="n">
-        <v>522</v>
+        <v>513.5</v>
       </c>
       <c r="P62" t="n">
-        <v>2.865736</v>
+        <v>4.69119</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.803521</v>
+        <v>4.634401</v>
       </c>
       <c r="R62" t="n">
-        <v>2.412141</v>
+        <v>4.494492</v>
       </c>
       <c r="S62" t="n">
-        <v>0.676535</v>
+        <v>0.342719</v>
       </c>
       <c r="T62" t="n">
-        <v>0.857227</v>
+        <v>-0.123278</v>
       </c>
       <c r="U62" t="n">
-        <v>-1.303158</v>
+        <v>-2.22502</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.328386</v>
+        <v>0.388229</v>
       </c>
       <c r="W62" t="n">
-        <v>1.548375</v>
+        <v>2.677676</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.804727</v>
+        <v>-3.501317</v>
       </c>
       <c r="Y62" t="n">
-        <v>-6.607165</v>
+        <v>-6.475515</v>
       </c>
       <c r="Z62" t="n">
-        <v>5.45709</v>
+        <v>6.553166</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.939992</v>
+        <v>9.216493</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.842776</v>
+        <v>2.705352</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.359223</v>
+        <v>-0.291262</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,34 +5884,34 @@
         <v>46295</v>
       </c>
       <c r="B62" t="n">
-        <v>185742.0625</v>
+        <v>185892.640625</v>
       </c>
       <c r="C62" t="n">
-        <v>182.880005</v>
+        <v>183.020004</v>
       </c>
       <c r="D62" t="n">
-        <v>110.900002</v>
+        <v>110.860001</v>
       </c>
       <c r="E62" t="n">
-        <v>450.890015</v>
+        <v>451.519989</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1848</v>
+        <v>5.1838</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8759</v>
+        <v>5.8751</v>
       </c>
       <c r="H62" t="n">
-        <v>7715.97998</v>
+        <v>7711.649902</v>
       </c>
       <c r="I62" t="n">
-        <v>27077.017578</v>
+        <v>27062.792969</v>
       </c>
       <c r="J62" t="n">
-        <v>51323.691406</v>
+        <v>51319.070312</v>
       </c>
       <c r="K62" t="n">
-        <v>4191.299805</v>
+        <v>4189.299805</v>
       </c>
       <c r="L62" t="n">
         <v>91.379997</v>
@@ -5920,40 +5920,40 @@
         <v>98.83000199999999</v>
       </c>
       <c r="N62" t="n">
-        <v>1309.75</v>
+        <v>1306.5</v>
       </c>
       <c r="O62" t="n">
-        <v>513.5</v>
+        <v>507.5</v>
       </c>
       <c r="P62" t="n">
-        <v>4.69119</v>
+        <v>4.776062</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.634401</v>
+        <v>4.714501</v>
       </c>
       <c r="R62" t="n">
-        <v>4.494492</v>
+        <v>4.456802</v>
       </c>
       <c r="S62" t="n">
-        <v>0.342719</v>
+        <v>0.482916</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.123278</v>
+        <v>-0.14254</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.22502</v>
+        <v>-2.238327</v>
       </c>
       <c r="V62" t="n">
-        <v>0.388229</v>
+        <v>0.331893</v>
       </c>
       <c r="W62" t="n">
-        <v>2.677676</v>
+        <v>2.623735</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.501317</v>
+        <v>-3.510006</v>
       </c>
       <c r="Y62" t="n">
-        <v>-6.475515</v>
+        <v>-6.520143</v>
       </c>
       <c r="Z62" t="n">
         <v>6.553166</v>
@@ -5962,10 +5962,10 @@
         <v>9.216493</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.705352</v>
+        <v>2.4505</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.291262</v>
+        <v>-1.456311</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -569,49 +569,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44469</v>
+        <v>44500</v>
       </c>
       <c r="B2" t="n">
-        <v>110979</v>
+        <v>103501</v>
       </c>
       <c r="C2" t="n">
-        <v>106.489998</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>127.400002</v>
+        <v>111.199997</v>
       </c>
       <c r="E2" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
       <c r="F2" t="n">
-        <v>5.4143</v>
+        <v>5.6449</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2785</v>
+        <v>6.593</v>
       </c>
       <c r="H2" t="n">
-        <v>4307.540039</v>
+        <v>4605.379883</v>
       </c>
       <c r="I2" t="n">
-        <v>14448.580078</v>
+        <v>15498.389648</v>
       </c>
       <c r="J2" t="n">
-        <v>33843.921875</v>
+        <v>35819.558594</v>
       </c>
       <c r="K2" t="n">
-        <v>1757</v>
+        <v>1783.900024</v>
       </c>
       <c r="L2" t="n">
-        <v>75.029999</v>
+        <v>83.56999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>78.519997</v>
+        <v>84.379997</v>
       </c>
       <c r="N2" t="n">
-        <v>1256</v>
+        <v>1235.75</v>
       </c>
       <c r="O2" t="n">
-        <v>536.75</v>
+        <v>568.25</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -630,5342 +630,5342 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B3" t="n">
-        <v>103501</v>
+        <v>101915</v>
       </c>
       <c r="C3" t="n">
-        <v>99.68000000000001</v>
+        <v>98.349998</v>
       </c>
       <c r="D3" t="n">
-        <v>111.199997</v>
+        <v>108.800003</v>
       </c>
       <c r="E3" t="n">
-        <v>283</v>
+        <v>280.549988</v>
       </c>
       <c r="F3" t="n">
-        <v>5.6449</v>
+        <v>5.6007</v>
       </c>
       <c r="G3" t="n">
-        <v>6.593</v>
+        <v>6.3223</v>
       </c>
       <c r="H3" t="n">
-        <v>4605.379883</v>
+        <v>4567</v>
       </c>
       <c r="I3" t="n">
-        <v>15498.389648</v>
+        <v>15537.69043</v>
       </c>
       <c r="J3" t="n">
-        <v>35819.558594</v>
+        <v>34483.71875</v>
       </c>
       <c r="K3" t="n">
-        <v>1783.900024</v>
+        <v>1773.599976</v>
       </c>
       <c r="L3" t="n">
-        <v>83.56999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>84.379997</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>1235.75</v>
+        <v>1217.25</v>
       </c>
       <c r="O3" t="n">
-        <v>568.25</v>
+        <v>567</v>
       </c>
       <c r="P3" t="n">
-        <v>-6.738212</v>
+        <v>-1.532352</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.394964</v>
+        <v>-1.334271</v>
       </c>
       <c r="R3" t="n">
-        <v>-12.715859</v>
+        <v>-2.158268</v>
       </c>
       <c r="S3" t="n">
-        <v>10.980392</v>
+        <v>-0.865729</v>
       </c>
       <c r="T3" t="n">
-        <v>4.259089</v>
+        <v>-0.783007</v>
       </c>
       <c r="U3" t="n">
-        <v>5.009156</v>
+        <v>-4.10587</v>
       </c>
       <c r="V3" t="n">
-        <v>6.914384</v>
+        <v>-0.833371</v>
       </c>
       <c r="W3" t="n">
-        <v>7.265832</v>
+        <v>0.25358</v>
       </c>
       <c r="X3" t="n">
-        <v>5.837493</v>
+        <v>-3.729359</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.53102</v>
+        <v>-0.577389</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.382115</v>
+        <v>-20.808902</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.463068</v>
+        <v>-16.366435</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.612261</v>
+        <v>-1.497067</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.868654</v>
+        <v>-0.219974</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B4" t="n">
-        <v>101915</v>
+        <v>104822</v>
       </c>
       <c r="C4" t="n">
-        <v>98.349998</v>
+        <v>100.800003</v>
       </c>
       <c r="D4" t="n">
-        <v>108.800003</v>
+        <v>113.300003</v>
       </c>
       <c r="E4" t="n">
-        <v>280.549988</v>
+        <v>293.559998</v>
       </c>
       <c r="F4" t="n">
-        <v>5.6007</v>
+        <v>5.5702</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3223</v>
+        <v>6.3049</v>
       </c>
       <c r="H4" t="n">
-        <v>4567</v>
+        <v>4766.180176</v>
       </c>
       <c r="I4" t="n">
-        <v>15537.69043</v>
+        <v>15644.969727</v>
       </c>
       <c r="J4" t="n">
-        <v>34483.71875</v>
+        <v>36338.300781</v>
       </c>
       <c r="K4" t="n">
-        <v>1773.599976</v>
+        <v>1828.599976</v>
       </c>
       <c r="L4" t="n">
-        <v>66.18000000000001</v>
+        <v>75.209999</v>
       </c>
       <c r="M4" t="n">
-        <v>70.56999999999999</v>
+        <v>77.779999</v>
       </c>
       <c r="N4" t="n">
-        <v>1217.25</v>
+        <v>1328.75</v>
       </c>
       <c r="O4" t="n">
-        <v>567</v>
+        <v>593.25</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.532352</v>
+        <v>2.852377</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.334271</v>
+        <v>2.491108</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.158268</v>
+        <v>4.136029</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.865729</v>
+        <v>4.637323</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.783007</v>
+        <v>-0.544574</v>
       </c>
       <c r="U4" t="n">
-        <v>-4.10587</v>
+        <v>-0.275213</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.833371</v>
+        <v>4.361291</v>
       </c>
       <c r="W4" t="n">
-        <v>0.25358</v>
+        <v>0.690446</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.729359</v>
+        <v>5.378138</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.577389</v>
+        <v>3.101037</v>
       </c>
       <c r="Z4" t="n">
-        <v>-20.808902</v>
+        <v>13.644604</v>
       </c>
       <c r="AA4" t="n">
-        <v>-16.366435</v>
+        <v>10.216805</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1.497067</v>
+        <v>9.159992000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.219974</v>
+        <v>4.62963</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B5" t="n">
-        <v>104822</v>
+        <v>112388</v>
       </c>
       <c r="C5" t="n">
-        <v>100.800003</v>
+        <v>107.980003</v>
       </c>
       <c r="D5" t="n">
-        <v>113.300003</v>
+        <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>293.559998</v>
+        <v>260.399994</v>
       </c>
       <c r="F5" t="n">
-        <v>5.5702</v>
+        <v>5.3626</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3049</v>
+        <v>5.9782</v>
       </c>
       <c r="H5" t="n">
-        <v>4766.180176</v>
+        <v>4515.549805</v>
       </c>
       <c r="I5" t="n">
-        <v>15644.969727</v>
+        <v>14239.879883</v>
       </c>
       <c r="J5" t="n">
-        <v>36338.300781</v>
+        <v>35131.859375</v>
       </c>
       <c r="K5" t="n">
-        <v>1828.599976</v>
+        <v>1795</v>
       </c>
       <c r="L5" t="n">
-        <v>75.209999</v>
+        <v>88.150002</v>
       </c>
       <c r="M5" t="n">
-        <v>77.779999</v>
+        <v>91.209999</v>
       </c>
       <c r="N5" t="n">
-        <v>1328.75</v>
+        <v>1490.5</v>
       </c>
       <c r="O5" t="n">
-        <v>593.25</v>
+        <v>626</v>
       </c>
       <c r="P5" t="n">
-        <v>2.852377</v>
+        <v>7.21795</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.491108</v>
+        <v>7.123016</v>
       </c>
       <c r="R5" t="n">
-        <v>4.136029</v>
+        <v>3.265664</v>
       </c>
       <c r="S5" t="n">
-        <v>4.637323</v>
+        <v>-11.295818</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.544574</v>
+        <v>-3.726978</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.275213</v>
+        <v>-5.181687</v>
       </c>
       <c r="V5" t="n">
-        <v>4.361291</v>
+        <v>-5.258517</v>
       </c>
       <c r="W5" t="n">
-        <v>0.690446</v>
+        <v>-8.981097</v>
       </c>
       <c r="X5" t="n">
-        <v>5.378138</v>
+        <v>-3.320027</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.101037</v>
+        <v>-1.83747</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.644604</v>
+        <v>17.205162</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.216805</v>
+        <v>17.26665</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.159992000000001</v>
+        <v>12.173095</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.62963</v>
+        <v>5.520438</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B6" t="n">
-        <v>112388</v>
+        <v>113142</v>
       </c>
       <c r="C6" t="n">
-        <v>107.980003</v>
+        <v>108.900002</v>
       </c>
       <c r="D6" t="n">
-        <v>117</v>
+        <v>111.040001</v>
       </c>
       <c r="E6" t="n">
-        <v>260.399994</v>
+        <v>245.5</v>
       </c>
       <c r="F6" t="n">
-        <v>5.3626</v>
+        <v>5.1594</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9782</v>
+        <v>5.814</v>
       </c>
       <c r="H6" t="n">
-        <v>4515.549805</v>
+        <v>4373.939941</v>
       </c>
       <c r="I6" t="n">
-        <v>14239.879883</v>
+        <v>13751.400391</v>
       </c>
       <c r="J6" t="n">
-        <v>35131.859375</v>
+        <v>33892.601562</v>
       </c>
       <c r="K6" t="n">
-        <v>1795</v>
+        <v>1900.699951</v>
       </c>
       <c r="L6" t="n">
-        <v>88.150002</v>
+        <v>95.720001</v>
       </c>
       <c r="M6" t="n">
-        <v>91.209999</v>
+        <v>100.989998</v>
       </c>
       <c r="N6" t="n">
-        <v>1490.5</v>
+        <v>1644.25</v>
       </c>
       <c r="O6" t="n">
-        <v>626</v>
+        <v>697.5</v>
       </c>
       <c r="P6" t="n">
-        <v>7.21795</v>
+        <v>0.67089</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.123016</v>
+        <v>0.852008</v>
       </c>
       <c r="R6" t="n">
-        <v>3.265664</v>
+        <v>-5.094016</v>
       </c>
       <c r="S6" t="n">
-        <v>-11.295818</v>
+        <v>-5.721964</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.726978</v>
+        <v>-3.789204</v>
       </c>
       <c r="U6" t="n">
-        <v>-5.181687</v>
+        <v>-2.746643</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.258517</v>
+        <v>-3.136049</v>
       </c>
       <c r="W6" t="n">
-        <v>-8.981097</v>
+        <v>-3.430362</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.320027</v>
+        <v>-3.527447</v>
       </c>
       <c r="Y6" t="n">
-        <v>-1.83747</v>
+        <v>5.888577</v>
       </c>
       <c r="Z6" t="n">
-        <v>17.205162</v>
+        <v>8.587634</v>
       </c>
       <c r="AA6" t="n">
-        <v>17.26665</v>
+        <v>10.722507</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.173095</v>
+        <v>10.31533</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.520438</v>
+        <v>11.421725</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B7" t="n">
-        <v>113142</v>
+        <v>119999</v>
       </c>
       <c r="C7" t="n">
-        <v>108.900002</v>
+        <v>115.599998</v>
       </c>
       <c r="D7" t="n">
-        <v>111.040001</v>
+        <v>120.940002</v>
       </c>
       <c r="E7" t="n">
-        <v>245.5</v>
+        <v>235.649994</v>
       </c>
       <c r="F7" t="n">
-        <v>5.1594</v>
+        <v>4.7697</v>
       </c>
       <c r="G7" t="n">
-        <v>5.814</v>
+        <v>5.3198</v>
       </c>
       <c r="H7" t="n">
-        <v>4373.939941</v>
+        <v>4530.410156</v>
       </c>
       <c r="I7" t="n">
-        <v>13751.400391</v>
+        <v>14220.519531</v>
       </c>
       <c r="J7" t="n">
-        <v>33892.601562</v>
+        <v>34678.351562</v>
       </c>
       <c r="K7" t="n">
-        <v>1900.699951</v>
+        <v>1949.199951</v>
       </c>
       <c r="L7" t="n">
-        <v>95.720001</v>
+        <v>100.279999</v>
       </c>
       <c r="M7" t="n">
-        <v>100.989998</v>
+        <v>107.910004</v>
       </c>
       <c r="N7" t="n">
-        <v>1644.25</v>
+        <v>1618.25</v>
       </c>
       <c r="O7" t="n">
-        <v>697.5</v>
+        <v>748.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0.67089</v>
+        <v>6.060526</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.852008</v>
+        <v>6.152431</v>
       </c>
       <c r="R7" t="n">
-        <v>-5.094016</v>
+        <v>8.915706999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.721964</v>
+        <v>-4.012222</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.789204</v>
+        <v>-7.553203</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.746643</v>
+        <v>-8.500176</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.136049</v>
+        <v>3.577329</v>
       </c>
       <c r="W7" t="n">
-        <v>-3.430362</v>
+        <v>3.411428</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.527447</v>
+        <v>2.318353</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.888577</v>
+        <v>2.551692</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.587634</v>
+        <v>4.763892</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.722507</v>
+        <v>6.852169</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.31533</v>
+        <v>-1.581268</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.421725</v>
+        <v>7.34767</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B8" t="n">
-        <v>119999</v>
+        <v>107876</v>
       </c>
       <c r="C8" t="n">
-        <v>115.599998</v>
+        <v>103.400002</v>
       </c>
       <c r="D8" t="n">
-        <v>120.940002</v>
+        <v>110.599998</v>
       </c>
       <c r="E8" t="n">
-        <v>235.649994</v>
+        <v>224.100006</v>
       </c>
       <c r="F8" t="n">
-        <v>4.7697</v>
+        <v>4.9378</v>
       </c>
       <c r="G8" t="n">
-        <v>5.3198</v>
+        <v>5.1837</v>
       </c>
       <c r="H8" t="n">
-        <v>4530.410156</v>
+        <v>4131.930176</v>
       </c>
       <c r="I8" t="n">
-        <v>14220.519531</v>
+        <v>12334.639648</v>
       </c>
       <c r="J8" t="n">
-        <v>34678.351562</v>
+        <v>32977.210938</v>
       </c>
       <c r="K8" t="n">
-        <v>1949.199951</v>
+        <v>1911.699951</v>
       </c>
       <c r="L8" t="n">
-        <v>100.279999</v>
+        <v>104.690002</v>
       </c>
       <c r="M8" t="n">
-        <v>107.910004</v>
+        <v>109.339996</v>
       </c>
       <c r="N8" t="n">
-        <v>1618.25</v>
+        <v>1708.25</v>
       </c>
       <c r="O8" t="n">
-        <v>748.75</v>
+        <v>818.25</v>
       </c>
       <c r="P8" t="n">
-        <v>6.060526</v>
+        <v>-10.102584</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.152431</v>
+        <v>-10.553631</v>
       </c>
       <c r="R8" t="n">
-        <v>8.915706999999999</v>
+        <v>-8.549697</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.012222</v>
+        <v>-4.901332</v>
       </c>
       <c r="T8" t="n">
-        <v>-7.553203</v>
+        <v>3.524328</v>
       </c>
       <c r="U8" t="n">
-        <v>-8.500176</v>
+        <v>-2.558363</v>
       </c>
       <c r="V8" t="n">
-        <v>3.577329</v>
+        <v>-8.795671</v>
       </c>
       <c r="W8" t="n">
-        <v>3.411428</v>
+        <v>-13.261681</v>
       </c>
       <c r="X8" t="n">
-        <v>2.318353</v>
+        <v>-4.905483</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.551692</v>
+        <v>-1.923866</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.763892</v>
+        <v>4.39769</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.852169</v>
+        <v>1.325172</v>
       </c>
       <c r="AB8" t="n">
-        <v>-1.581268</v>
+        <v>5.561563</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.34767</v>
+        <v>9.282137000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B9" t="n">
-        <v>107876</v>
+        <v>111351</v>
       </c>
       <c r="C9" t="n">
-        <v>103.400002</v>
+        <v>107.18</v>
       </c>
       <c r="D9" t="n">
-        <v>110.599998</v>
+        <v>109.300003</v>
       </c>
       <c r="E9" t="n">
-        <v>224.100006</v>
+        <v>214.5</v>
       </c>
       <c r="F9" t="n">
-        <v>4.9378</v>
+        <v>4.7524</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1837</v>
+        <v>5.1176</v>
       </c>
       <c r="H9" t="n">
-        <v>4131.930176</v>
+        <v>4132.149902</v>
       </c>
       <c r="I9" t="n">
-        <v>12334.639648</v>
+        <v>12081.389648</v>
       </c>
       <c r="J9" t="n">
-        <v>32977.210938</v>
+        <v>32990.121094</v>
       </c>
       <c r="K9" t="n">
-        <v>1911.699951</v>
+        <v>1842.699951</v>
       </c>
       <c r="L9" t="n">
-        <v>104.690002</v>
+        <v>114.669998</v>
       </c>
       <c r="M9" t="n">
-        <v>109.339996</v>
+        <v>122.839996</v>
       </c>
       <c r="N9" t="n">
-        <v>1708.25</v>
+        <v>1683.25</v>
       </c>
       <c r="O9" t="n">
-        <v>818.25</v>
+        <v>753.5</v>
       </c>
       <c r="P9" t="n">
-        <v>-10.102584</v>
+        <v>3.221291</v>
       </c>
       <c r="Q9" t="n">
-        <v>-10.553631</v>
+        <v>3.655705</v>
       </c>
       <c r="R9" t="n">
-        <v>-8.549697</v>
+        <v>-1.175403</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.901332</v>
+        <v>-4.283804</v>
       </c>
       <c r="T9" t="n">
-        <v>3.524328</v>
+        <v>-3.754709</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.558363</v>
+        <v>-1.275153</v>
       </c>
       <c r="V9" t="n">
-        <v>-8.795671</v>
+        <v>0.005318</v>
       </c>
       <c r="W9" t="n">
-        <v>-13.261681</v>
+        <v>-2.053161</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.905483</v>
+        <v>0.039149</v>
       </c>
       <c r="Y9" t="n">
-        <v>-1.923866</v>
+        <v>-3.609353</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.39769</v>
+        <v>9.532902</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.325172</v>
+        <v>12.346809</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.561563</v>
+        <v>-1.463486</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.282137000000001</v>
+        <v>-7.913229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B10" t="n">
-        <v>111351</v>
+        <v>98542</v>
       </c>
       <c r="C10" t="n">
-        <v>107.18</v>
+        <v>95</v>
       </c>
       <c r="D10" t="n">
-        <v>109.300003</v>
+        <v>91.33000199999999</v>
       </c>
       <c r="E10" t="n">
-        <v>214.5</v>
+        <v>216.699997</v>
       </c>
       <c r="F10" t="n">
-        <v>4.7524</v>
+        <v>5.1809</v>
       </c>
       <c r="G10" t="n">
-        <v>5.1176</v>
+        <v>5.4098</v>
       </c>
       <c r="H10" t="n">
-        <v>4132.149902</v>
+        <v>3785.379883</v>
       </c>
       <c r="I10" t="n">
-        <v>12081.389648</v>
+        <v>11028.740234</v>
       </c>
       <c r="J10" t="n">
-        <v>32990.121094</v>
+        <v>30775.429688</v>
       </c>
       <c r="K10" t="n">
-        <v>1842.699951</v>
+        <v>1807.300049</v>
       </c>
       <c r="L10" t="n">
-        <v>114.669998</v>
+        <v>105.760002</v>
       </c>
       <c r="M10" t="n">
-        <v>122.839996</v>
+        <v>114.809998</v>
       </c>
       <c r="N10" t="n">
-        <v>1683.25</v>
+        <v>1675</v>
       </c>
       <c r="O10" t="n">
-        <v>753.5</v>
+        <v>743.75</v>
       </c>
       <c r="P10" t="n">
-        <v>3.221291</v>
+        <v>-11.503264</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.655705</v>
+        <v>-11.364061</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.175403</v>
+        <v>-16.440989</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.283804</v>
+        <v>1.02564</v>
       </c>
       <c r="T10" t="n">
-        <v>-3.754709</v>
+        <v>9.016501</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.275153</v>
+        <v>5.709709</v>
       </c>
       <c r="V10" t="n">
-        <v>0.005318</v>
+        <v>-8.391999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-2.053161</v>
+        <v>-8.712982999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>0.039149</v>
+        <v>-6.713196</v>
       </c>
       <c r="Y10" t="n">
-        <v>-3.609353</v>
+        <v>-1.921089</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.532902</v>
+        <v>-7.77012</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.346809</v>
+        <v>-6.536958</v>
       </c>
       <c r="AB10" t="n">
-        <v>-1.463486</v>
+        <v>-0.490123</v>
       </c>
       <c r="AC10" t="n">
-        <v>-7.913229</v>
+        <v>-1.293962</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B11" t="n">
-        <v>98542</v>
+        <v>103165</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>99.300003</v>
       </c>
       <c r="D11" t="n">
-        <v>91.33000199999999</v>
+        <v>95.650002</v>
       </c>
       <c r="E11" t="n">
-        <v>216.699997</v>
+        <v>234.5</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1809</v>
+        <v>5.1827</v>
       </c>
       <c r="G11" t="n">
-        <v>5.4098</v>
+        <v>5.2797</v>
       </c>
       <c r="H11" t="n">
-        <v>3785.379883</v>
+        <v>4130.290039</v>
       </c>
       <c r="I11" t="n">
-        <v>11028.740234</v>
+        <v>12390.69043</v>
       </c>
       <c r="J11" t="n">
-        <v>30775.429688</v>
+        <v>32845.128906</v>
       </c>
       <c r="K11" t="n">
-        <v>1807.300049</v>
+        <v>1762.900024</v>
       </c>
       <c r="L11" t="n">
-        <v>105.760002</v>
+        <v>98.620003</v>
       </c>
       <c r="M11" t="n">
-        <v>114.809998</v>
+        <v>110.010002</v>
       </c>
       <c r="N11" t="n">
-        <v>1675</v>
+        <v>1637</v>
       </c>
       <c r="O11" t="n">
-        <v>743.75</v>
+        <v>616.25</v>
       </c>
       <c r="P11" t="n">
-        <v>-11.503264</v>
+        <v>4.691401</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11.364061</v>
+        <v>4.526319</v>
       </c>
       <c r="R11" t="n">
-        <v>-16.440989</v>
+        <v>4.730099</v>
       </c>
       <c r="S11" t="n">
-        <v>1.02564</v>
+        <v>8.214122</v>
       </c>
       <c r="T11" t="n">
-        <v>9.016501</v>
+        <v>0.034744</v>
       </c>
       <c r="U11" t="n">
-        <v>5.709709</v>
+        <v>-2.404899</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.391999999999999</v>
+        <v>9.111639</v>
       </c>
       <c r="W11" t="n">
-        <v>-8.712982999999999</v>
+        <v>12.3491</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.713196</v>
+        <v>6.725168</v>
       </c>
       <c r="Y11" t="n">
-        <v>-1.921089</v>
+        <v>-2.456705</v>
       </c>
       <c r="Z11" t="n">
-        <v>-7.77012</v>
+        <v>-6.751134</v>
       </c>
       <c r="AA11" t="n">
-        <v>-6.536958</v>
+        <v>-4.180817</v>
       </c>
       <c r="AB11" t="n">
-        <v>-0.490123</v>
+        <v>-2.268657</v>
       </c>
       <c r="AC11" t="n">
-        <v>-1.293962</v>
+        <v>-17.142857</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B12" t="n">
-        <v>103165</v>
+        <v>109523</v>
       </c>
       <c r="C12" t="n">
-        <v>99.300003</v>
+        <v>105.830002</v>
       </c>
       <c r="D12" t="n">
-        <v>95.650002</v>
+        <v>106.800003</v>
       </c>
       <c r="E12" t="n">
-        <v>234.5</v>
+        <v>226</v>
       </c>
       <c r="F12" t="n">
-        <v>5.1827</v>
+        <v>5.1219</v>
       </c>
       <c r="G12" t="n">
-        <v>5.2797</v>
+        <v>5.1318</v>
       </c>
       <c r="H12" t="n">
-        <v>4130.290039</v>
+        <v>3955</v>
       </c>
       <c r="I12" t="n">
-        <v>12390.69043</v>
+        <v>11816.200195</v>
       </c>
       <c r="J12" t="n">
-        <v>32845.128906</v>
+        <v>31510.429688</v>
       </c>
       <c r="K12" t="n">
-        <v>1762.900024</v>
+        <v>1726.199951</v>
       </c>
       <c r="L12" t="n">
-        <v>98.620003</v>
+        <v>89.550003</v>
       </c>
       <c r="M12" t="n">
-        <v>110.010002</v>
+        <v>96.489998</v>
       </c>
       <c r="N12" t="n">
-        <v>1637</v>
+        <v>1507.5</v>
       </c>
       <c r="O12" t="n">
-        <v>616.25</v>
+        <v>673.75</v>
       </c>
       <c r="P12" t="n">
-        <v>4.691401</v>
+        <v>6.162943</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.526319</v>
+        <v>6.576031</v>
       </c>
       <c r="R12" t="n">
-        <v>4.730099</v>
+        <v>11.657085</v>
       </c>
       <c r="S12" t="n">
-        <v>8.214122</v>
+        <v>-3.624733</v>
       </c>
       <c r="T12" t="n">
-        <v>0.034744</v>
+        <v>-1.173135</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.404899</v>
+        <v>-2.801289</v>
       </c>
       <c r="V12" t="n">
-        <v>9.111639</v>
+        <v>-4.244013</v>
       </c>
       <c r="W12" t="n">
-        <v>12.3491</v>
+        <v>-4.636467</v>
       </c>
       <c r="X12" t="n">
-        <v>6.725168</v>
+        <v>-4.063614</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.456705</v>
+        <v>-2.081801</v>
       </c>
       <c r="Z12" t="n">
-        <v>-6.751134</v>
+        <v>-9.196916999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>-4.180817</v>
+        <v>-12.289795</v>
       </c>
       <c r="AB12" t="n">
-        <v>-2.268657</v>
+        <v>-7.910812</v>
       </c>
       <c r="AC12" t="n">
-        <v>-17.142857</v>
+        <v>9.330629</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B13" t="n">
-        <v>109523</v>
+        <v>110037</v>
       </c>
       <c r="C13" t="n">
-        <v>105.830002</v>
+        <v>106.459999</v>
       </c>
       <c r="D13" t="n">
-        <v>106.800003</v>
+        <v>105.440002</v>
       </c>
       <c r="E13" t="n">
-        <v>226</v>
+        <v>213.5</v>
       </c>
       <c r="F13" t="n">
-        <v>5.1219</v>
+        <v>5.3962</v>
       </c>
       <c r="G13" t="n">
-        <v>5.1318</v>
+        <v>5.3031</v>
       </c>
       <c r="H13" t="n">
-        <v>3955</v>
+        <v>3585.620117</v>
       </c>
       <c r="I13" t="n">
-        <v>11816.200195</v>
+        <v>10575.620117</v>
       </c>
       <c r="J13" t="n">
-        <v>31510.429688</v>
+        <v>28725.509766</v>
       </c>
       <c r="K13" t="n">
-        <v>1726.199951</v>
+        <v>1672</v>
       </c>
       <c r="L13" t="n">
-        <v>89.550003</v>
+        <v>79.489998</v>
       </c>
       <c r="M13" t="n">
-        <v>96.489998</v>
+        <v>87.959999</v>
       </c>
       <c r="N13" t="n">
-        <v>1507.5</v>
+        <v>1364.75</v>
       </c>
       <c r="O13" t="n">
-        <v>673.75</v>
+        <v>677.5</v>
       </c>
       <c r="P13" t="n">
-        <v>6.162943</v>
+        <v>0.469308</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.576031</v>
+        <v>0.595292</v>
       </c>
       <c r="R13" t="n">
-        <v>11.657085</v>
+        <v>-1.273409</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.624733</v>
+        <v>-5.530973</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.173135</v>
+        <v>5.355436</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.801289</v>
+        <v>3.338009</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.244013</v>
+        <v>-9.339567000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-4.636467</v>
+        <v>-10.498976</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.063614</v>
+        <v>-8.838089</v>
       </c>
       <c r="Y13" t="n">
-        <v>-2.081801</v>
+        <v>-3.139842</v>
       </c>
       <c r="Z13" t="n">
-        <v>-9.196916999999999</v>
+        <v>-11.233953</v>
       </c>
       <c r="AA13" t="n">
-        <v>-12.289795</v>
+        <v>-8.840293000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>-7.910812</v>
+        <v>-9.46932</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.330629</v>
+        <v>0.556586</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B14" t="n">
-        <v>110037</v>
+        <v>116037</v>
       </c>
       <c r="C14" t="n">
-        <v>106.459999</v>
+        <v>112.150002</v>
       </c>
       <c r="D14" t="n">
-        <v>105.440002</v>
+        <v>112.5</v>
       </c>
       <c r="E14" t="n">
-        <v>213.5</v>
+        <v>220.240005</v>
       </c>
       <c r="F14" t="n">
-        <v>5.3962</v>
+        <v>5.2885</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3031</v>
+        <v>5.2737</v>
       </c>
       <c r="H14" t="n">
-        <v>3585.620117</v>
+        <v>3871.97998</v>
       </c>
       <c r="I14" t="n">
-        <v>10575.620117</v>
+        <v>10988.150391</v>
       </c>
       <c r="J14" t="n">
-        <v>28725.509766</v>
+        <v>32732.949219</v>
       </c>
       <c r="K14" t="n">
-        <v>1672</v>
+        <v>1640.699951</v>
       </c>
       <c r="L14" t="n">
-        <v>79.489998</v>
+        <v>86.529999</v>
       </c>
       <c r="M14" t="n">
-        <v>87.959999</v>
+        <v>94.83000199999999</v>
       </c>
       <c r="N14" t="n">
-        <v>1364.75</v>
+        <v>1407</v>
       </c>
       <c r="O14" t="n">
-        <v>677.5</v>
+        <v>691.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0.469308</v>
+        <v>5.452711</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.595292</v>
+        <v>5.344733</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.273409</v>
+        <v>6.695749</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.530973</v>
+        <v>3.156911</v>
       </c>
       <c r="T14" t="n">
-        <v>5.355436</v>
+        <v>-1.995855</v>
       </c>
       <c r="U14" t="n">
-        <v>3.338009</v>
+        <v>-0.55439</v>
       </c>
       <c r="V14" t="n">
-        <v>-9.339567000000001</v>
+        <v>7.986341</v>
       </c>
       <c r="W14" t="n">
-        <v>-10.498976</v>
+        <v>3.900767</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.838089</v>
+        <v>13.950804</v>
       </c>
       <c r="Y14" t="n">
-        <v>-3.139842</v>
+        <v>-1.872012</v>
       </c>
       <c r="Z14" t="n">
-        <v>-11.233953</v>
+        <v>8.856460999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>-8.840293000000001</v>
+        <v>7.810372</v>
       </c>
       <c r="AB14" t="n">
-        <v>-9.46932</v>
+        <v>3.095805</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.556586</v>
+        <v>2.066421</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B15" t="n">
-        <v>116037</v>
+        <v>112486</v>
       </c>
       <c r="C15" t="n">
-        <v>112.150002</v>
+        <v>108.580002</v>
       </c>
       <c r="D15" t="n">
-        <v>112.5</v>
+        <v>99.980003</v>
       </c>
       <c r="E15" t="n">
-        <v>220.240005</v>
+        <v>233.25</v>
       </c>
       <c r="F15" t="n">
-        <v>5.2885</v>
+        <v>5.2682</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2737</v>
+        <v>5.4362</v>
       </c>
       <c r="H15" t="n">
-        <v>3871.97998</v>
+        <v>4080.110107</v>
       </c>
       <c r="I15" t="n">
-        <v>10988.150391</v>
+        <v>11468</v>
       </c>
       <c r="J15" t="n">
-        <v>32732.949219</v>
+        <v>34589.769531</v>
       </c>
       <c r="K15" t="n">
-        <v>1640.699951</v>
+        <v>1746</v>
       </c>
       <c r="L15" t="n">
-        <v>86.529999</v>
+        <v>80.550003</v>
       </c>
       <c r="M15" t="n">
-        <v>94.83000199999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>1407</v>
+        <v>1469.5</v>
       </c>
       <c r="O15" t="n">
-        <v>691.5</v>
+        <v>662</v>
       </c>
       <c r="P15" t="n">
-        <v>5.452711</v>
+        <v>-3.060231</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.344733</v>
+        <v>-3.183236</v>
       </c>
       <c r="R15" t="n">
-        <v>6.695749</v>
+        <v>-11.128886</v>
       </c>
       <c r="S15" t="n">
-        <v>3.156911</v>
+        <v>5.90719</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.995855</v>
+        <v>-0.38385</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.55439</v>
+        <v>3.081326</v>
       </c>
       <c r="V15" t="n">
-        <v>7.986341</v>
+        <v>5.375289</v>
       </c>
       <c r="W15" t="n">
-        <v>3.900767</v>
+        <v>4.366973</v>
       </c>
       <c r="X15" t="n">
-        <v>13.950804</v>
+        <v>5.672634</v>
       </c>
       <c r="Y15" t="n">
-        <v>-1.872012</v>
+        <v>6.417995</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.856460999999999</v>
+        <v>-6.910893</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.810372</v>
+        <v>-9.912476</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.095805</v>
+        <v>4.442075</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.066421</v>
+        <v>-4.266088</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B16" t="n">
-        <v>112486</v>
+        <v>110031</v>
       </c>
       <c r="C16" t="n">
-        <v>108.580002</v>
+        <v>105.949997</v>
       </c>
       <c r="D16" t="n">
-        <v>99.980003</v>
+        <v>96.519997</v>
       </c>
       <c r="E16" t="n">
-        <v>233.25</v>
+        <v>225</v>
       </c>
       <c r="F16" t="n">
-        <v>5.2682</v>
+        <v>5.2846</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4362</v>
+        <v>5.633</v>
       </c>
       <c r="H16" t="n">
-        <v>4080.110107</v>
+        <v>3839.5</v>
       </c>
       <c r="I16" t="n">
-        <v>11468</v>
+        <v>10466.480469</v>
       </c>
       <c r="J16" t="n">
-        <v>34589.769531</v>
+        <v>33147.25</v>
       </c>
       <c r="K16" t="n">
-        <v>1746</v>
+        <v>1826.199951</v>
       </c>
       <c r="L16" t="n">
-        <v>80.550003</v>
+        <v>80.260002</v>
       </c>
       <c r="M16" t="n">
-        <v>85.43000000000001</v>
+        <v>85.910004</v>
       </c>
       <c r="N16" t="n">
-        <v>1469.5</v>
+        <v>1519.25</v>
       </c>
       <c r="O16" t="n">
-        <v>662</v>
+        <v>678.5</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.060231</v>
+        <v>-2.182494</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.183236</v>
+        <v>-2.422182</v>
       </c>
       <c r="R16" t="n">
-        <v>-11.128886</v>
+        <v>-3.460699</v>
       </c>
       <c r="S16" t="n">
-        <v>5.90719</v>
+        <v>-3.536977</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.38385</v>
+        <v>0.311299</v>
       </c>
       <c r="U16" t="n">
-        <v>3.081326</v>
+        <v>3.620171</v>
       </c>
       <c r="V16" t="n">
-        <v>5.375289</v>
+        <v>-5.897147</v>
       </c>
       <c r="W16" t="n">
-        <v>4.366973</v>
+        <v>-8.733166000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>5.672634</v>
+        <v>-4.170365</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.417995</v>
+        <v>4.593353</v>
       </c>
       <c r="Z16" t="n">
-        <v>-6.910893</v>
+        <v>-0.360026</v>
       </c>
       <c r="AA16" t="n">
-        <v>-9.912476</v>
+        <v>0.561867</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.442075</v>
+        <v>3.385505</v>
       </c>
       <c r="AC16" t="n">
-        <v>-4.266088</v>
+        <v>2.492447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B17" t="n">
-        <v>110031</v>
+        <v>113532</v>
       </c>
       <c r="C17" t="n">
-        <v>105.949997</v>
+        <v>109.839996</v>
       </c>
       <c r="D17" t="n">
-        <v>96.519997</v>
+        <v>99.44000200000001</v>
       </c>
       <c r="E17" t="n">
-        <v>225</v>
+        <v>228.199997</v>
       </c>
       <c r="F17" t="n">
-        <v>5.2846</v>
+        <v>5.1149</v>
       </c>
       <c r="G17" t="n">
-        <v>5.633</v>
+        <v>5.5471</v>
       </c>
       <c r="H17" t="n">
-        <v>3839.5</v>
+        <v>4076.600098</v>
       </c>
       <c r="I17" t="n">
-        <v>10466.480469</v>
+        <v>11584.549805</v>
       </c>
       <c r="J17" t="n">
-        <v>33147.25</v>
+        <v>34086.039062</v>
       </c>
       <c r="K17" t="n">
-        <v>1826.199951</v>
+        <v>1929.5</v>
       </c>
       <c r="L17" t="n">
-        <v>80.260002</v>
+        <v>78.870003</v>
       </c>
       <c r="M17" t="n">
-        <v>85.910004</v>
+        <v>84.489998</v>
       </c>
       <c r="N17" t="n">
-        <v>1519.25</v>
+        <v>1538</v>
       </c>
       <c r="O17" t="n">
-        <v>678.5</v>
+        <v>679.75</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.182494</v>
+        <v>3.181831</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.422182</v>
+        <v>3.671543</v>
       </c>
       <c r="R17" t="n">
-        <v>-3.460699</v>
+        <v>3.025286</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.536977</v>
+        <v>1.422221</v>
       </c>
       <c r="T17" t="n">
-        <v>0.311299</v>
+        <v>-3.211211</v>
       </c>
       <c r="U17" t="n">
-        <v>3.620171</v>
+        <v>-1.524939</v>
       </c>
       <c r="V17" t="n">
-        <v>-5.897147</v>
+        <v>6.175286</v>
       </c>
       <c r="W17" t="n">
-        <v>-8.733166000000001</v>
+        <v>10.682381</v>
       </c>
       <c r="X17" t="n">
-        <v>-4.170365</v>
+        <v>2.832178</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.593353</v>
+        <v>5.656557</v>
       </c>
       <c r="Z17" t="n">
-        <v>-0.360026</v>
+        <v>-1.731871</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.561867</v>
+        <v>-1.652899</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.385505</v>
+        <v>1.234162</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.492447</v>
+        <v>0.18423</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B18" t="n">
-        <v>113532</v>
+        <v>104932</v>
       </c>
       <c r="C18" t="n">
-        <v>109.839996</v>
+        <v>101.150002</v>
       </c>
       <c r="D18" t="n">
-        <v>99.44000200000001</v>
+        <v>88.360001</v>
       </c>
       <c r="E18" t="n">
-        <v>228.199997</v>
+        <v>229.300003</v>
       </c>
       <c r="F18" t="n">
-        <v>5.1149</v>
+        <v>5.1997</v>
       </c>
       <c r="G18" t="n">
-        <v>5.5471</v>
+        <v>5.514</v>
       </c>
       <c r="H18" t="n">
-        <v>4076.600098</v>
+        <v>3970.149902</v>
       </c>
       <c r="I18" t="n">
-        <v>11584.549805</v>
+        <v>11455.540039</v>
       </c>
       <c r="J18" t="n">
-        <v>34086.039062</v>
+        <v>32656.699219</v>
       </c>
       <c r="K18" t="n">
-        <v>1929.5</v>
+        <v>1836.699951</v>
       </c>
       <c r="L18" t="n">
-        <v>78.870003</v>
+        <v>77.050003</v>
       </c>
       <c r="M18" t="n">
-        <v>84.489998</v>
+        <v>83.889999</v>
       </c>
       <c r="N18" t="n">
-        <v>1538</v>
+        <v>1490.5</v>
       </c>
       <c r="O18" t="n">
-        <v>679.75</v>
+        <v>629.5</v>
       </c>
       <c r="P18" t="n">
-        <v>3.181831</v>
+        <v>-7.574957</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.671543</v>
+        <v>-7.911503</v>
       </c>
       <c r="R18" t="n">
-        <v>3.025286</v>
+        <v>-11.142399</v>
       </c>
       <c r="S18" t="n">
-        <v>1.422221</v>
+        <v>0.482036</v>
       </c>
       <c r="T18" t="n">
-        <v>-3.211211</v>
+        <v>1.657897</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.524939</v>
+        <v>-0.59671</v>
       </c>
       <c r="V18" t="n">
-        <v>6.175286</v>
+        <v>-2.611249</v>
       </c>
       <c r="W18" t="n">
-        <v>10.682381</v>
+        <v>-1.113636</v>
       </c>
       <c r="X18" t="n">
-        <v>2.832178</v>
+        <v>-4.193329</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.656557</v>
+        <v>-4.809539</v>
       </c>
       <c r="Z18" t="n">
-        <v>-1.731871</v>
+        <v>-2.307594</v>
       </c>
       <c r="AA18" t="n">
-        <v>-1.652899</v>
+        <v>-0.710141</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.234162</v>
+        <v>-3.088427</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.18423</v>
+        <v>-7.392424</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B19" t="n">
-        <v>104932</v>
+        <v>101882</v>
       </c>
       <c r="C19" t="n">
-        <v>101.150002</v>
+        <v>98.489998</v>
       </c>
       <c r="D19" t="n">
-        <v>88.360001</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>229.300003</v>
+        <v>229.75</v>
       </c>
       <c r="F19" t="n">
-        <v>5.1997</v>
+        <v>5.0927</v>
       </c>
       <c r="G19" t="n">
-        <v>5.514</v>
+        <v>5.5518</v>
       </c>
       <c r="H19" t="n">
-        <v>3970.149902</v>
+        <v>4109.310059</v>
       </c>
       <c r="I19" t="n">
-        <v>11455.540039</v>
+        <v>12221.910156</v>
       </c>
       <c r="J19" t="n">
-        <v>32656.699219</v>
+        <v>33274.148438</v>
       </c>
       <c r="K19" t="n">
-        <v>1836.699951</v>
+        <v>1969</v>
       </c>
       <c r="L19" t="n">
-        <v>77.050003</v>
+        <v>75.66999800000001</v>
       </c>
       <c r="M19" t="n">
-        <v>83.889999</v>
+        <v>79.769997</v>
       </c>
       <c r="N19" t="n">
-        <v>1490.5</v>
+        <v>1505.5</v>
       </c>
       <c r="O19" t="n">
-        <v>629.5</v>
+        <v>660.5</v>
       </c>
       <c r="P19" t="n">
-        <v>-7.574957</v>
+        <v>-2.906644</v>
       </c>
       <c r="Q19" t="n">
-        <v>-7.911503</v>
+        <v>-2.629761</v>
       </c>
       <c r="R19" t="n">
-        <v>-11.142399</v>
+        <v>-0.611137</v>
       </c>
       <c r="S19" t="n">
-        <v>0.482036</v>
+        <v>0.196248</v>
       </c>
       <c r="T19" t="n">
-        <v>1.657897</v>
+        <v>-2.057809</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.59671</v>
+        <v>0.6855250000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.611249</v>
+        <v>3.505161</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.113636</v>
+        <v>6.689952</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.193329</v>
+        <v>1.890728</v>
       </c>
       <c r="Y19" t="n">
-        <v>-4.809539</v>
+        <v>7.203139</v>
       </c>
       <c r="Z19" t="n">
-        <v>-2.307594</v>
+        <v>-1.791051</v>
       </c>
       <c r="AA19" t="n">
-        <v>-0.710141</v>
+        <v>-4.911197</v>
       </c>
       <c r="AB19" t="n">
-        <v>-3.088427</v>
+        <v>1.006374</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.392424</v>
+        <v>4.924543</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B20" t="n">
-        <v>101882</v>
+        <v>104432</v>
       </c>
       <c r="C20" t="n">
-        <v>98.489998</v>
+        <v>100.900002</v>
       </c>
       <c r="D20" t="n">
-        <v>87.81999999999999</v>
+        <v>89</v>
       </c>
       <c r="E20" t="n">
         <v>229.75</v>
       </c>
       <c r="F20" t="n">
-        <v>5.0927</v>
+        <v>4.9762</v>
       </c>
       <c r="G20" t="n">
-        <v>5.5518</v>
+        <v>5.4883</v>
       </c>
       <c r="H20" t="n">
-        <v>4109.310059</v>
+        <v>4169.47998</v>
       </c>
       <c r="I20" t="n">
-        <v>12221.910156</v>
+        <v>12226.580078</v>
       </c>
       <c r="J20" t="n">
-        <v>33274.148438</v>
+        <v>34098.160156</v>
       </c>
       <c r="K20" t="n">
-        <v>1969</v>
+        <v>1999.099976</v>
       </c>
       <c r="L20" t="n">
-        <v>75.66999800000001</v>
+        <v>76.779999</v>
       </c>
       <c r="M20" t="n">
-        <v>79.769997</v>
+        <v>79.540001</v>
       </c>
       <c r="N20" t="n">
-        <v>1505.5</v>
+        <v>1444.25</v>
       </c>
       <c r="O20" t="n">
-        <v>660.5</v>
+        <v>636</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.906644</v>
+        <v>2.502896</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.629761</v>
+        <v>2.446953</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.611137</v>
+        <v>1.343658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.196248</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.057809</v>
+        <v>-2.287586</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6855250000000001</v>
+        <v>-1.143772</v>
       </c>
       <c r="V20" t="n">
-        <v>3.505161</v>
+        <v>1.464234</v>
       </c>
       <c r="W20" t="n">
-        <v>6.689952</v>
+        <v>0.038209</v>
       </c>
       <c r="X20" t="n">
-        <v>1.890728</v>
+        <v>2.476432</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.203139</v>
+        <v>1.528694</v>
       </c>
       <c r="Z20" t="n">
-        <v>-1.791051</v>
+        <v>1.466897</v>
       </c>
       <c r="AA20" t="n">
-        <v>-4.911197</v>
+        <v>-0.288324</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.006374</v>
+        <v>-4.068416</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.924543</v>
+        <v>-3.709311</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B21" t="n">
-        <v>104432</v>
+        <v>108335</v>
       </c>
       <c r="C21" t="n">
-        <v>100.900002</v>
+        <v>104.839996</v>
       </c>
       <c r="D21" t="n">
-        <v>89</v>
+        <v>100.5</v>
       </c>
       <c r="E21" t="n">
-        <v>229.75</v>
+        <v>233.25</v>
       </c>
       <c r="F21" t="n">
-        <v>4.9762</v>
+        <v>5.0348</v>
       </c>
       <c r="G21" t="n">
-        <v>5.4883</v>
+        <v>5.4012</v>
       </c>
       <c r="H21" t="n">
-        <v>4169.47998</v>
+        <v>4179.830078</v>
       </c>
       <c r="I21" t="n">
-        <v>12226.580078</v>
+        <v>12935.290039</v>
       </c>
       <c r="J21" t="n">
-        <v>34098.160156</v>
+        <v>32908.269531</v>
       </c>
       <c r="K21" t="n">
-        <v>1999.099976</v>
+        <v>1963.900024</v>
       </c>
       <c r="L21" t="n">
-        <v>76.779999</v>
+        <v>68.089996</v>
       </c>
       <c r="M21" t="n">
-        <v>79.540001</v>
+        <v>72.660004</v>
       </c>
       <c r="N21" t="n">
-        <v>1444.25</v>
+        <v>1299.75</v>
       </c>
       <c r="O21" t="n">
-        <v>636</v>
+        <v>594</v>
       </c>
       <c r="P21" t="n">
-        <v>2.502896</v>
+        <v>3.73736</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.446953</v>
+        <v>3.904851</v>
       </c>
       <c r="R21" t="n">
-        <v>1.343658</v>
+        <v>12.921348</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.523395</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.287586</v>
+        <v>1.177604</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.143772</v>
+        <v>-1.587013</v>
       </c>
       <c r="V21" t="n">
-        <v>1.464234</v>
+        <v>0.248235</v>
       </c>
       <c r="W21" t="n">
-        <v>0.038209</v>
+        <v>5.796469</v>
       </c>
       <c r="X21" t="n">
-        <v>2.476432</v>
+        <v>-3.489604</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.528694</v>
+        <v>-1.76079</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.466897</v>
+        <v>-11.318055</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.288324</v>
+        <v>-8.649732</v>
       </c>
       <c r="AB21" t="n">
-        <v>-4.068416</v>
+        <v>-10.005193</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.709311</v>
+        <v>-6.603774</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B22" t="n">
-        <v>108335</v>
+        <v>118087</v>
       </c>
       <c r="C22" t="n">
-        <v>104.839996</v>
+        <v>114.169998</v>
       </c>
       <c r="D22" t="n">
-        <v>100.5</v>
+        <v>109.5</v>
       </c>
       <c r="E22" t="n">
-        <v>233.25</v>
+        <v>235.25</v>
       </c>
       <c r="F22" t="n">
-        <v>5.0348</v>
+        <v>4.8556</v>
       </c>
       <c r="G22" t="n">
-        <v>5.4012</v>
+        <v>5.2739</v>
       </c>
       <c r="H22" t="n">
-        <v>4179.830078</v>
+        <v>4450.379883</v>
       </c>
       <c r="I22" t="n">
-        <v>12935.290039</v>
+        <v>13787.919922</v>
       </c>
       <c r="J22" t="n">
-        <v>32908.269531</v>
+        <v>34407.601562</v>
       </c>
       <c r="K22" t="n">
-        <v>1963.900024</v>
+        <v>1929.400024</v>
       </c>
       <c r="L22" t="n">
-        <v>68.089996</v>
+        <v>70.639999</v>
       </c>
       <c r="M22" t="n">
-        <v>72.660004</v>
+        <v>74.900002</v>
       </c>
       <c r="N22" t="n">
-        <v>1299.75</v>
+        <v>1557.25</v>
       </c>
       <c r="O22" t="n">
-        <v>594</v>
+        <v>554.5</v>
       </c>
       <c r="P22" t="n">
-        <v>3.73736</v>
+        <v>9.001708000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.904851</v>
+        <v>8.899277</v>
       </c>
       <c r="R22" t="n">
-        <v>12.921348</v>
+        <v>8.955223999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>1.523395</v>
+        <v>0.857449</v>
       </c>
       <c r="T22" t="n">
-        <v>1.177604</v>
+        <v>-3.559231</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.587013</v>
+        <v>-2.35688</v>
       </c>
       <c r="V22" t="n">
-        <v>0.248235</v>
+        <v>6.472746</v>
       </c>
       <c r="W22" t="n">
-        <v>5.796469</v>
+        <v>6.591502</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.489604</v>
+        <v>4.556095</v>
       </c>
       <c r="Y22" t="n">
-        <v>-1.76079</v>
+        <v>-1.756709</v>
       </c>
       <c r="Z22" t="n">
-        <v>-11.318055</v>
+        <v>3.745048</v>
       </c>
       <c r="AA22" t="n">
-        <v>-8.649732</v>
+        <v>3.082849</v>
       </c>
       <c r="AB22" t="n">
-        <v>-10.005193</v>
+        <v>19.811502</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.603774</v>
+        <v>-6.649832</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B23" t="n">
-        <v>118087</v>
+        <v>121943</v>
       </c>
       <c r="C23" t="n">
-        <v>114.169998</v>
+        <v>117.949997</v>
       </c>
       <c r="D23" t="n">
-        <v>109.5</v>
+        <v>112.900002</v>
       </c>
       <c r="E23" t="n">
-        <v>235.25</v>
+        <v>239.820007</v>
       </c>
       <c r="F23" t="n">
-        <v>4.8556</v>
+        <v>4.7233</v>
       </c>
       <c r="G23" t="n">
-        <v>5.2739</v>
+        <v>5.1895</v>
       </c>
       <c r="H23" t="n">
-        <v>4450.379883</v>
+        <v>4588.959961</v>
       </c>
       <c r="I23" t="n">
-        <v>13787.919922</v>
+        <v>14346.019531</v>
       </c>
       <c r="J23" t="n">
-        <v>34407.601562</v>
+        <v>35559.53125</v>
       </c>
       <c r="K23" t="n">
-        <v>1929.400024</v>
+        <v>1970.5</v>
       </c>
       <c r="L23" t="n">
-        <v>70.639999</v>
+        <v>81.800003</v>
       </c>
       <c r="M23" t="n">
-        <v>74.900002</v>
+        <v>85.55999799999999</v>
       </c>
       <c r="N23" t="n">
-        <v>1557.25</v>
+        <v>1445.75</v>
       </c>
       <c r="O23" t="n">
-        <v>554.5</v>
+        <v>504</v>
       </c>
       <c r="P23" t="n">
-        <v>9.001708000000001</v>
+        <v>3.265389</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.899277</v>
+        <v>3.310851</v>
       </c>
       <c r="R23" t="n">
-        <v>8.955223999999999</v>
+        <v>3.105024</v>
       </c>
       <c r="S23" t="n">
-        <v>0.857449</v>
+        <v>1.942617</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.559231</v>
+        <v>-2.724687</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.35688</v>
+        <v>-1.600337</v>
       </c>
       <c r="V23" t="n">
-        <v>6.472746</v>
+        <v>3.113893</v>
       </c>
       <c r="W23" t="n">
-        <v>6.591502</v>
+        <v>4.047743</v>
       </c>
       <c r="X23" t="n">
-        <v>4.556095</v>
+        <v>3.347893</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.756709</v>
+        <v>2.130195</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.745048</v>
+        <v>15.79842</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.082849</v>
+        <v>14.232304</v>
       </c>
       <c r="AB23" t="n">
-        <v>19.811502</v>
+        <v>-7.160058</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.649832</v>
+        <v>-9.107303999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B24" t="n">
-        <v>121943</v>
+        <v>115742</v>
       </c>
       <c r="C24" t="n">
-        <v>117.949997</v>
+        <v>112.309998</v>
       </c>
       <c r="D24" t="n">
-        <v>112.900002</v>
+        <v>104.199997</v>
       </c>
       <c r="E24" t="n">
-        <v>239.820007</v>
+        <v>247.649994</v>
       </c>
       <c r="F24" t="n">
-        <v>4.7233</v>
+        <v>4.8884</v>
       </c>
       <c r="G24" t="n">
-        <v>5.1895</v>
+        <v>5.313</v>
       </c>
       <c r="H24" t="n">
-        <v>4588.959961</v>
+        <v>4507.660156</v>
       </c>
       <c r="I24" t="n">
-        <v>14346.019531</v>
+        <v>14034.969727</v>
       </c>
       <c r="J24" t="n">
-        <v>35559.53125</v>
+        <v>34721.910156</v>
       </c>
       <c r="K24" t="n">
-        <v>1970.5</v>
+        <v>1965.900024</v>
       </c>
       <c r="L24" t="n">
-        <v>81.800003</v>
+        <v>83.629997</v>
       </c>
       <c r="M24" t="n">
-        <v>85.55999799999999</v>
+        <v>86.860001</v>
       </c>
       <c r="N24" t="n">
-        <v>1445.75</v>
+        <v>1360</v>
       </c>
       <c r="O24" t="n">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="P24" t="n">
-        <v>3.265389</v>
+        <v>-5.085163</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.310851</v>
+        <v>-4.781687</v>
       </c>
       <c r="R24" t="n">
-        <v>3.105024</v>
+        <v>-7.705938</v>
       </c>
       <c r="S24" t="n">
-        <v>1.942617</v>
+        <v>3.264943</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.724687</v>
+        <v>3.49544</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.600337</v>
+        <v>2.379812</v>
       </c>
       <c r="V24" t="n">
-        <v>3.113893</v>
+        <v>-1.771639</v>
       </c>
       <c r="W24" t="n">
-        <v>4.047743</v>
+        <v>-2.168196</v>
       </c>
       <c r="X24" t="n">
-        <v>3.347893</v>
+        <v>-2.355546</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.130195</v>
+        <v>-0.233442</v>
       </c>
       <c r="Z24" t="n">
-        <v>15.79842</v>
+        <v>2.237157</v>
       </c>
       <c r="AA24" t="n">
-        <v>14.232304</v>
+        <v>1.519405</v>
       </c>
       <c r="AB24" t="n">
-        <v>-7.160058</v>
+        <v>-5.931178</v>
       </c>
       <c r="AC24" t="n">
-        <v>-9.107303999999999</v>
+        <v>-8.531746</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B25" t="n">
-        <v>115742</v>
+        <v>116565</v>
       </c>
       <c r="C25" t="n">
-        <v>112.309998</v>
+        <v>113.150002</v>
       </c>
       <c r="D25" t="n">
-        <v>104.199997</v>
+        <v>101.639999</v>
       </c>
       <c r="E25" t="n">
-        <v>247.649994</v>
+        <v>238.789993</v>
       </c>
       <c r="F25" t="n">
-        <v>4.8884</v>
+        <v>5.0328</v>
       </c>
       <c r="G25" t="n">
-        <v>5.313</v>
+        <v>5.3197</v>
       </c>
       <c r="H25" t="n">
-        <v>4507.660156</v>
+        <v>4288.049805</v>
       </c>
       <c r="I25" t="n">
-        <v>14034.969727</v>
+        <v>13219.320312</v>
       </c>
       <c r="J25" t="n">
-        <v>34721.910156</v>
+        <v>33507.5</v>
       </c>
       <c r="K25" t="n">
-        <v>1965.900024</v>
+        <v>1866.099976</v>
       </c>
       <c r="L25" t="n">
-        <v>83.629997</v>
+        <v>90.790001</v>
       </c>
       <c r="M25" t="n">
-        <v>86.860001</v>
+        <v>95.30999799999999</v>
       </c>
       <c r="N25" t="n">
-        <v>1360</v>
+        <v>1275</v>
       </c>
       <c r="O25" t="n">
-        <v>461</v>
+        <v>476.75</v>
       </c>
       <c r="P25" t="n">
-        <v>-5.085163</v>
+        <v>0.711064</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.781687</v>
+        <v>0.747933</v>
       </c>
       <c r="R25" t="n">
-        <v>-7.705938</v>
+        <v>-2.456812</v>
       </c>
       <c r="S25" t="n">
-        <v>3.264943</v>
+        <v>-3.57763</v>
       </c>
       <c r="T25" t="n">
-        <v>3.49544</v>
+        <v>2.953934</v>
       </c>
       <c r="U25" t="n">
-        <v>2.379812</v>
+        <v>0.126098</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.771639</v>
+        <v>-4.871937</v>
       </c>
       <c r="W25" t="n">
-        <v>-2.168196</v>
+        <v>-5.811551</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.355546</v>
+        <v>-3.497533</v>
       </c>
       <c r="Y25" t="n">
-        <v>-0.233442</v>
+        <v>-5.076558</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.237157</v>
+        <v>8.561526000000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.519405</v>
+        <v>9.728294999999999</v>
       </c>
       <c r="AB25" t="n">
-        <v>-5.931178</v>
+        <v>-6.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>-8.531746</v>
+        <v>3.416486</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B26" t="n">
-        <v>116565</v>
+        <v>113144</v>
       </c>
       <c r="C26" t="n">
-        <v>113.150002</v>
+        <v>109.620003</v>
       </c>
       <c r="D26" t="n">
-        <v>101.639999</v>
+        <v>94.199997</v>
       </c>
       <c r="E26" t="n">
-        <v>238.789993</v>
+        <v>234</v>
       </c>
       <c r="F26" t="n">
-        <v>5.0328</v>
+        <v>5.0461</v>
       </c>
       <c r="G26" t="n">
-        <v>5.3197</v>
+        <v>5.3537</v>
       </c>
       <c r="H26" t="n">
-        <v>4288.049805</v>
+        <v>4193.799805</v>
       </c>
       <c r="I26" t="n">
-        <v>13219.320312</v>
+        <v>12851.240234</v>
       </c>
       <c r="J26" t="n">
-        <v>33507.5</v>
+        <v>33052.871094</v>
       </c>
       <c r="K26" t="n">
-        <v>1866.099976</v>
+        <v>1994.300049</v>
       </c>
       <c r="L26" t="n">
-        <v>90.790001</v>
+        <v>81.019997</v>
       </c>
       <c r="M26" t="n">
-        <v>95.30999799999999</v>
+        <v>87.410004</v>
       </c>
       <c r="N26" t="n">
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="O26" t="n">
-        <v>476.75</v>
+        <v>478.75</v>
       </c>
       <c r="P26" t="n">
-        <v>0.711064</v>
+        <v>-2.934843</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.747933</v>
+        <v>-3.119751</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.456812</v>
+        <v>-7.319955</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.57763</v>
+        <v>-2.005944</v>
       </c>
       <c r="T26" t="n">
-        <v>2.953934</v>
+        <v>0.264265</v>
       </c>
       <c r="U26" t="n">
-        <v>0.126098</v>
+        <v>0.639141</v>
       </c>
       <c r="V26" t="n">
-        <v>-4.871937</v>
+        <v>-2.197969</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.811551</v>
+        <v>-2.78441</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.497533</v>
+        <v>-1.356797</v>
       </c>
       <c r="Y26" t="n">
-        <v>-5.076558</v>
+        <v>6.869947</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.561526000000001</v>
+        <v>-10.761102</v>
       </c>
       <c r="AA26" t="n">
-        <v>9.728294999999999</v>
+        <v>-8.288736</v>
       </c>
       <c r="AB26" t="n">
-        <v>-6.25</v>
+        <v>0.941176</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.416486</v>
+        <v>0.419507</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B27" t="n">
-        <v>113144</v>
+        <v>127331</v>
       </c>
       <c r="C27" t="n">
-        <v>109.620003</v>
+        <v>123.57</v>
       </c>
       <c r="D27" t="n">
-        <v>94.199997</v>
+        <v>106.349998</v>
       </c>
       <c r="E27" t="n">
-        <v>234</v>
+        <v>249.699997</v>
       </c>
       <c r="F27" t="n">
-        <v>5.0461</v>
+        <v>4.9041</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3537</v>
+        <v>5.3628</v>
       </c>
       <c r="H27" t="n">
-        <v>4193.799805</v>
+        <v>4567.799805</v>
       </c>
       <c r="I27" t="n">
-        <v>12851.240234</v>
+        <v>14226.219727</v>
       </c>
       <c r="J27" t="n">
-        <v>33052.871094</v>
+        <v>35950.890625</v>
       </c>
       <c r="K27" t="n">
-        <v>1994.300049</v>
+        <v>2038.099976</v>
       </c>
       <c r="L27" t="n">
-        <v>81.019997</v>
+        <v>75.959999</v>
       </c>
       <c r="M27" t="n">
-        <v>87.410004</v>
+        <v>82.83000199999999</v>
       </c>
       <c r="N27" t="n">
-        <v>1287</v>
+        <v>1342.75</v>
       </c>
       <c r="O27" t="n">
-        <v>478.75</v>
+        <v>461.75</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.934843</v>
+        <v>12.538888</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.119751</v>
+        <v>12.725777</v>
       </c>
       <c r="R27" t="n">
-        <v>-7.319955</v>
+        <v>12.898091</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.005944</v>
+        <v>6.7094</v>
       </c>
       <c r="T27" t="n">
-        <v>0.264265</v>
+        <v>-2.814058</v>
       </c>
       <c r="U27" t="n">
-        <v>0.639141</v>
+        <v>0.169975</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.197969</v>
+        <v>8.917927000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>-2.78441</v>
+        <v>10.699197</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.356797</v>
+        <v>8.76783</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.869947</v>
+        <v>2.196256</v>
       </c>
       <c r="Z27" t="n">
-        <v>-10.761102</v>
+        <v>-6.245369</v>
       </c>
       <c r="AA27" t="n">
-        <v>-8.288736</v>
+        <v>-5.239677</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.941176</v>
+        <v>4.331779</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.419507</v>
+        <v>-3.550914</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B28" t="n">
-        <v>127331</v>
+        <v>134185</v>
       </c>
       <c r="C28" t="n">
-        <v>123.57</v>
+        <v>130.389999</v>
       </c>
       <c r="D28" t="n">
-        <v>106.349998</v>
+        <v>113.199997</v>
       </c>
       <c r="E28" t="n">
-        <v>249.699997</v>
+        <v>257.609985</v>
       </c>
       <c r="F28" t="n">
-        <v>4.9041</v>
+        <v>4.8502</v>
       </c>
       <c r="G28" t="n">
-        <v>5.3628</v>
+        <v>5.343</v>
       </c>
       <c r="H28" t="n">
-        <v>4567.799805</v>
+        <v>4769.830078</v>
       </c>
       <c r="I28" t="n">
-        <v>14226.219727</v>
+        <v>15011.349609</v>
       </c>
       <c r="J28" t="n">
-        <v>35950.890625</v>
+        <v>37689.539062</v>
       </c>
       <c r="K28" t="n">
-        <v>2038.099976</v>
+        <v>2071.800049</v>
       </c>
       <c r="L28" t="n">
-        <v>75.959999</v>
+        <v>71.650002</v>
       </c>
       <c r="M28" t="n">
-        <v>82.83000199999999</v>
+        <v>77.040001</v>
       </c>
       <c r="N28" t="n">
-        <v>1342.75</v>
+        <v>1293.5</v>
       </c>
       <c r="O28" t="n">
-        <v>461.75</v>
+        <v>471.25</v>
       </c>
       <c r="P28" t="n">
-        <v>12.538888</v>
+        <v>5.382821</v>
       </c>
       <c r="Q28" t="n">
-        <v>12.725777</v>
+        <v>5.519139</v>
       </c>
       <c r="R28" t="n">
-        <v>12.898091</v>
+        <v>6.440995</v>
       </c>
       <c r="S28" t="n">
-        <v>6.7094</v>
+        <v>3.167797</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.814058</v>
+        <v>-1.099076</v>
       </c>
       <c r="U28" t="n">
-        <v>0.169975</v>
+        <v>-0.369214</v>
       </c>
       <c r="V28" t="n">
-        <v>8.917927000000001</v>
+        <v>4.422923</v>
       </c>
       <c r="W28" t="n">
-        <v>10.699197</v>
+        <v>5.518893</v>
       </c>
       <c r="X28" t="n">
-        <v>8.76783</v>
+        <v>4.836176</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.196256</v>
+        <v>1.653504</v>
       </c>
       <c r="Z28" t="n">
-        <v>-6.245369</v>
+        <v>-5.674036</v>
       </c>
       <c r="AA28" t="n">
-        <v>-5.239677</v>
+        <v>-6.990222</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.331779</v>
+        <v>-3.667846</v>
       </c>
       <c r="AC28" t="n">
-        <v>-3.550914</v>
+        <v>2.05739</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B29" t="n">
-        <v>134185</v>
+        <v>127752</v>
       </c>
       <c r="C29" t="n">
-        <v>130.389999</v>
+        <v>123.949997</v>
       </c>
       <c r="D29" t="n">
-        <v>113.199997</v>
+        <v>106.370003</v>
       </c>
       <c r="E29" t="n">
-        <v>257.609985</v>
+        <v>266.619995</v>
       </c>
       <c r="F29" t="n">
-        <v>4.8502</v>
+        <v>4.9503</v>
       </c>
       <c r="G29" t="n">
-        <v>5.343</v>
+        <v>5.3604</v>
       </c>
       <c r="H29" t="n">
-        <v>4769.830078</v>
+        <v>4845.649902</v>
       </c>
       <c r="I29" t="n">
-        <v>15011.349609</v>
+        <v>15164.009766</v>
       </c>
       <c r="J29" t="n">
-        <v>37689.539062</v>
+        <v>38150.300781</v>
       </c>
       <c r="K29" t="n">
-        <v>2071.800049</v>
+        <v>2048.399902</v>
       </c>
       <c r="L29" t="n">
-        <v>71.650002</v>
+        <v>75.849998</v>
       </c>
       <c r="M29" t="n">
-        <v>77.040001</v>
+        <v>81.709999</v>
       </c>
       <c r="N29" t="n">
-        <v>1293.5</v>
+        <v>1222.25</v>
       </c>
       <c r="O29" t="n">
-        <v>471.25</v>
+        <v>448.25</v>
       </c>
       <c r="P29" t="n">
-        <v>5.382821</v>
+        <v>-4.794128</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.519139</v>
+        <v>-4.939031</v>
       </c>
       <c r="R29" t="n">
-        <v>6.440995</v>
+        <v>-6.033564</v>
       </c>
       <c r="S29" t="n">
-        <v>3.167797</v>
+        <v>3.497539</v>
       </c>
       <c r="T29" t="n">
-        <v>-1.099076</v>
+        <v>2.063833</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.369214</v>
+        <v>0.325665</v>
       </c>
       <c r="V29" t="n">
-        <v>4.422923</v>
+        <v>1.589571</v>
       </c>
       <c r="W29" t="n">
-        <v>5.518893</v>
+        <v>1.016965</v>
       </c>
       <c r="X29" t="n">
-        <v>4.836176</v>
+        <v>1.222519</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.653504</v>
+        <v>-1.12946</v>
       </c>
       <c r="Z29" t="n">
-        <v>-5.674036</v>
+        <v>5.861824</v>
       </c>
       <c r="AA29" t="n">
-        <v>-6.990222</v>
+        <v>6.061784</v>
       </c>
       <c r="AB29" t="n">
-        <v>-3.667846</v>
+        <v>-5.508311</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.05739</v>
+        <v>-4.880637</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B30" t="n">
-        <v>127752</v>
+        <v>129020</v>
       </c>
       <c r="C30" t="n">
-        <v>123.949997</v>
+        <v>125.25</v>
       </c>
       <c r="D30" t="n">
-        <v>106.370003</v>
+        <v>106.5</v>
       </c>
       <c r="E30" t="n">
-        <v>266.619995</v>
+        <v>281.100006</v>
       </c>
       <c r="F30" t="n">
-        <v>4.9503</v>
+        <v>4.9673</v>
       </c>
       <c r="G30" t="n">
-        <v>5.3604</v>
+        <v>5.381</v>
       </c>
       <c r="H30" t="n">
-        <v>4845.649902</v>
+        <v>5096.27002</v>
       </c>
       <c r="I30" t="n">
-        <v>15164.009766</v>
+        <v>16091.919922</v>
       </c>
       <c r="J30" t="n">
-        <v>38150.300781</v>
+        <v>38996.390625</v>
       </c>
       <c r="K30" t="n">
-        <v>2048.399902</v>
+        <v>2054.699951</v>
       </c>
       <c r="L30" t="n">
-        <v>75.849998</v>
+        <v>78.260002</v>
       </c>
       <c r="M30" t="n">
-        <v>81.709999</v>
+        <v>83.620003</v>
       </c>
       <c r="N30" t="n">
-        <v>1222.25</v>
+        <v>1128.25</v>
       </c>
       <c r="O30" t="n">
-        <v>448.25</v>
+        <v>415.75</v>
       </c>
       <c r="P30" t="n">
-        <v>-4.794128</v>
+        <v>0.992548</v>
       </c>
       <c r="Q30" t="n">
-        <v>-4.939031</v>
+        <v>1.048812</v>
       </c>
       <c r="R30" t="n">
-        <v>-6.033564</v>
+        <v>0.122212</v>
       </c>
       <c r="S30" t="n">
-        <v>3.497539</v>
+        <v>5.430955</v>
       </c>
       <c r="T30" t="n">
-        <v>2.063833</v>
+        <v>0.343408</v>
       </c>
       <c r="U30" t="n">
-        <v>0.325665</v>
+        <v>0.384297</v>
       </c>
       <c r="V30" t="n">
-        <v>1.589571</v>
+        <v>5.172064</v>
       </c>
       <c r="W30" t="n">
-        <v>1.016965</v>
+        <v>6.119161</v>
       </c>
       <c r="X30" t="n">
-        <v>1.222519</v>
+        <v>2.21778</v>
       </c>
       <c r="Y30" t="n">
-        <v>-1.12946</v>
+        <v>0.30756</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.861824</v>
+        <v>3.177329</v>
       </c>
       <c r="AA30" t="n">
-        <v>6.061784</v>
+        <v>2.33754</v>
       </c>
       <c r="AB30" t="n">
-        <v>-5.508311</v>
+        <v>-7.690734</v>
       </c>
       <c r="AC30" t="n">
-        <v>-4.880637</v>
+        <v>-7.250418</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B31" t="n">
-        <v>129020</v>
+        <v>128106</v>
       </c>
       <c r="C31" t="n">
-        <v>125.25</v>
+        <v>124.330002</v>
       </c>
       <c r="D31" t="n">
-        <v>106.5</v>
+        <v>109</v>
       </c>
       <c r="E31" t="n">
-        <v>281.100006</v>
+        <v>292.600006</v>
       </c>
       <c r="F31" t="n">
-        <v>4.9673</v>
+        <v>5.0141</v>
       </c>
       <c r="G31" t="n">
-        <v>5.381</v>
+        <v>5.4065</v>
       </c>
       <c r="H31" t="n">
-        <v>5096.27002</v>
+        <v>5254.350098</v>
       </c>
       <c r="I31" t="n">
-        <v>16091.919922</v>
+        <v>16379.459961</v>
       </c>
       <c r="J31" t="n">
-        <v>38996.390625</v>
+        <v>39807.371094</v>
       </c>
       <c r="K31" t="n">
-        <v>2054.699951</v>
+        <v>2217.399902</v>
       </c>
       <c r="L31" t="n">
-        <v>78.260002</v>
+        <v>83.16999800000001</v>
       </c>
       <c r="M31" t="n">
-        <v>83.620003</v>
+        <v>87.480003</v>
       </c>
       <c r="N31" t="n">
-        <v>1128.25</v>
+        <v>1191.5</v>
       </c>
       <c r="O31" t="n">
-        <v>415.75</v>
+        <v>442</v>
       </c>
       <c r="P31" t="n">
-        <v>0.992548</v>
+        <v>-0.708417</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.048812</v>
+        <v>-0.734529</v>
       </c>
       <c r="R31" t="n">
-        <v>0.122212</v>
+        <v>2.347418</v>
       </c>
       <c r="S31" t="n">
-        <v>5.430955</v>
+        <v>4.091071</v>
       </c>
       <c r="T31" t="n">
-        <v>0.343408</v>
+        <v>0.942164</v>
       </c>
       <c r="U31" t="n">
-        <v>0.384297</v>
+        <v>0.473886</v>
       </c>
       <c r="V31" t="n">
-        <v>5.172064</v>
+        <v>3.101878</v>
       </c>
       <c r="W31" t="n">
-        <v>6.119161</v>
+        <v>1.78686</v>
       </c>
       <c r="X31" t="n">
-        <v>2.21778</v>
+        <v>2.07963</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.30756</v>
+        <v>7.918429</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.177329</v>
+        <v>6.273953</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.33754</v>
+        <v>4.616121</v>
       </c>
       <c r="AB31" t="n">
-        <v>-7.690734</v>
+        <v>5.606027</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.250418</v>
+        <v>6.313891</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B32" t="n">
-        <v>128106</v>
+        <v>125924</v>
       </c>
       <c r="C32" t="n">
-        <v>124.330002</v>
+        <v>122.379997</v>
       </c>
       <c r="D32" t="n">
-        <v>109</v>
+        <v>100.5</v>
       </c>
       <c r="E32" t="n">
-        <v>292.600006</v>
+        <v>291</v>
       </c>
       <c r="F32" t="n">
-        <v>5.0141</v>
+        <v>5.117</v>
       </c>
       <c r="G32" t="n">
-        <v>5.4065</v>
+        <v>5.4794</v>
       </c>
       <c r="H32" t="n">
-        <v>5254.350098</v>
+        <v>5035.689941</v>
       </c>
       <c r="I32" t="n">
-        <v>16379.459961</v>
+        <v>15657.820312</v>
       </c>
       <c r="J32" t="n">
-        <v>39807.371094</v>
+        <v>37815.921875</v>
       </c>
       <c r="K32" t="n">
-        <v>2217.399902</v>
+        <v>2302.899902</v>
       </c>
       <c r="L32" t="n">
-        <v>83.16999800000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>87.480003</v>
+        <v>87.860001</v>
       </c>
       <c r="N32" t="n">
-        <v>1191.5</v>
+        <v>1145.5</v>
       </c>
       <c r="O32" t="n">
-        <v>442</v>
+        <v>439.5</v>
       </c>
       <c r="P32" t="n">
-        <v>-0.708417</v>
+        <v>-1.703277</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.734529</v>
+        <v>-1.56841</v>
       </c>
       <c r="R32" t="n">
-        <v>2.347418</v>
+        <v>-7.798165</v>
       </c>
       <c r="S32" t="n">
-        <v>4.091071</v>
+        <v>-0.546824</v>
       </c>
       <c r="T32" t="n">
-        <v>0.942164</v>
+        <v>2.052213</v>
       </c>
       <c r="U32" t="n">
-        <v>0.473886</v>
+        <v>1.348382</v>
       </c>
       <c r="V32" t="n">
-        <v>3.101878</v>
+        <v>-4.161507</v>
       </c>
       <c r="W32" t="n">
-        <v>1.78686</v>
+        <v>-4.40576</v>
       </c>
       <c r="X32" t="n">
-        <v>2.07963</v>
+        <v>-5.002715</v>
       </c>
       <c r="Y32" t="n">
-        <v>7.918429</v>
+        <v>3.855867</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.273953</v>
+        <v>-1.49092</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.616121</v>
+        <v>0.434382</v>
       </c>
       <c r="AB32" t="n">
-        <v>5.606027</v>
+        <v>-3.86068</v>
       </c>
       <c r="AC32" t="n">
-        <v>6.313891</v>
+        <v>-0.565611</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B33" t="n">
-        <v>125924</v>
+        <v>122098</v>
       </c>
       <c r="C33" t="n">
-        <v>122.379997</v>
+        <v>118.660004</v>
       </c>
       <c r="D33" t="n">
-        <v>100.5</v>
+        <v>96.870003</v>
       </c>
       <c r="E33" t="n">
-        <v>291</v>
+        <v>308.200012</v>
       </c>
       <c r="F33" t="n">
-        <v>5.117</v>
+        <v>5.2021</v>
       </c>
       <c r="G33" t="n">
-        <v>5.4794</v>
+        <v>5.6311</v>
       </c>
       <c r="H33" t="n">
-        <v>5035.689941</v>
+        <v>5277.509766</v>
       </c>
       <c r="I33" t="n">
-        <v>15657.820312</v>
+        <v>16735.019531</v>
       </c>
       <c r="J33" t="n">
-        <v>37815.921875</v>
+        <v>38686.320312</v>
       </c>
       <c r="K33" t="n">
-        <v>2302.899902</v>
+        <v>2322.899902</v>
       </c>
       <c r="L33" t="n">
-        <v>81.93000000000001</v>
+        <v>76.989998</v>
       </c>
       <c r="M33" t="n">
-        <v>87.860001</v>
+        <v>81.620003</v>
       </c>
       <c r="N33" t="n">
-        <v>1145.5</v>
+        <v>1205</v>
       </c>
       <c r="O33" t="n">
-        <v>439.5</v>
+        <v>446.25</v>
       </c>
       <c r="P33" t="n">
-        <v>-1.703277</v>
+        <v>-3.038341</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.56841</v>
+        <v>-3.039707</v>
       </c>
       <c r="R33" t="n">
-        <v>-7.798165</v>
+        <v>-3.611938</v>
       </c>
       <c r="S33" t="n">
-        <v>-0.546824</v>
+        <v>5.910657</v>
       </c>
       <c r="T33" t="n">
-        <v>2.052213</v>
+        <v>1.663078</v>
       </c>
       <c r="U33" t="n">
-        <v>1.348382</v>
+        <v>2.768552</v>
       </c>
       <c r="V33" t="n">
-        <v>-4.161507</v>
+        <v>4.802119</v>
       </c>
       <c r="W33" t="n">
-        <v>-4.40576</v>
+        <v>6.879624</v>
       </c>
       <c r="X33" t="n">
-        <v>-5.002715</v>
+        <v>2.301672</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.855867</v>
+        <v>0.86847</v>
       </c>
       <c r="Z33" t="n">
-        <v>-1.49092</v>
+        <v>-6.02954</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.434382</v>
+        <v>-7.102206</v>
       </c>
       <c r="AB33" t="n">
-        <v>-3.86068</v>
+        <v>5.194238</v>
       </c>
       <c r="AC33" t="n">
-        <v>-0.565611</v>
+        <v>1.535836</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B34" t="n">
-        <v>122098</v>
+        <v>123907</v>
       </c>
       <c r="C34" t="n">
-        <v>118.660004</v>
+        <v>120.379997</v>
       </c>
       <c r="D34" t="n">
-        <v>96.870003</v>
+        <v>96.449997</v>
       </c>
       <c r="E34" t="n">
-        <v>308.200012</v>
+        <v>339.829987</v>
       </c>
       <c r="F34" t="n">
-        <v>5.2021</v>
+        <v>5.5005</v>
       </c>
       <c r="G34" t="n">
-        <v>5.6311</v>
+        <v>5.8909</v>
       </c>
       <c r="H34" t="n">
-        <v>5277.509766</v>
+        <v>5460.47998</v>
       </c>
       <c r="I34" t="n">
-        <v>16735.019531</v>
+        <v>17732.599609</v>
       </c>
       <c r="J34" t="n">
-        <v>38686.320312</v>
+        <v>39118.859375</v>
       </c>
       <c r="K34" t="n">
-        <v>2322.899902</v>
+        <v>2339.600098</v>
       </c>
       <c r="L34" t="n">
-        <v>76.989998</v>
+        <v>81.540001</v>
       </c>
       <c r="M34" t="n">
-        <v>81.620003</v>
+        <v>86.410004</v>
       </c>
       <c r="N34" t="n">
-        <v>1205</v>
+        <v>1150.5</v>
       </c>
       <c r="O34" t="n">
-        <v>446.25</v>
+        <v>397.25</v>
       </c>
       <c r="P34" t="n">
-        <v>-3.038341</v>
+        <v>1.481597</v>
       </c>
       <c r="Q34" t="n">
-        <v>-3.039707</v>
+        <v>1.449514</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.611938</v>
+        <v>-0.433577</v>
       </c>
       <c r="S34" t="n">
-        <v>5.910657</v>
+        <v>10.262808</v>
       </c>
       <c r="T34" t="n">
-        <v>1.663078</v>
+        <v>5.736153</v>
       </c>
       <c r="U34" t="n">
-        <v>2.768552</v>
+        <v>4.613663</v>
       </c>
       <c r="V34" t="n">
-        <v>4.802119</v>
+        <v>3.46698</v>
       </c>
       <c r="W34" t="n">
-        <v>6.879624</v>
+        <v>5.961033</v>
       </c>
       <c r="X34" t="n">
-        <v>2.301672</v>
+        <v>1.118067</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.86847</v>
+        <v>0.718937</v>
       </c>
       <c r="Z34" t="n">
-        <v>-6.02954</v>
+        <v>5.909863</v>
       </c>
       <c r="AA34" t="n">
-        <v>-7.102206</v>
+        <v>5.868661</v>
       </c>
       <c r="AB34" t="n">
-        <v>5.194238</v>
+        <v>-4.522822</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.535836</v>
+        <v>-10.980392</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B35" t="n">
-        <v>123907</v>
+        <v>127652</v>
       </c>
       <c r="C35" t="n">
-        <v>120.379997</v>
+        <v>124.040001</v>
       </c>
       <c r="D35" t="n">
-        <v>96.449997</v>
+        <v>98.5</v>
       </c>
       <c r="E35" t="n">
-        <v>339.829987</v>
+        <v>347.700012</v>
       </c>
       <c r="F35" t="n">
-        <v>5.5005</v>
+        <v>5.6111</v>
       </c>
       <c r="G35" t="n">
-        <v>5.8909</v>
+        <v>6.0695</v>
       </c>
       <c r="H35" t="n">
-        <v>5460.47998</v>
+        <v>5522.299805</v>
       </c>
       <c r="I35" t="n">
-        <v>17732.599609</v>
+        <v>17599.400391</v>
       </c>
       <c r="J35" t="n">
-        <v>39118.859375</v>
+        <v>40842.789062</v>
       </c>
       <c r="K35" t="n">
-        <v>2339.600098</v>
+        <v>2426.5</v>
       </c>
       <c r="L35" t="n">
-        <v>81.540001</v>
+        <v>77.910004</v>
       </c>
       <c r="M35" t="n">
-        <v>86.410004</v>
+        <v>80.720001</v>
       </c>
       <c r="N35" t="n">
-        <v>1150.5</v>
+        <v>1028.5</v>
       </c>
       <c r="O35" t="n">
-        <v>397.25</v>
+        <v>382.75</v>
       </c>
       <c r="P35" t="n">
-        <v>1.481597</v>
+        <v>3.022428</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.449514</v>
+        <v>3.040375</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.433577</v>
+        <v>2.125457</v>
       </c>
       <c r="S35" t="n">
-        <v>10.262808</v>
+        <v>2.315871</v>
       </c>
       <c r="T35" t="n">
-        <v>5.736153</v>
+        <v>2.010726</v>
       </c>
       <c r="U35" t="n">
-        <v>4.613663</v>
+        <v>3.031792</v>
       </c>
       <c r="V35" t="n">
-        <v>3.46698</v>
+        <v>1.132132</v>
       </c>
       <c r="W35" t="n">
-        <v>5.961033</v>
+        <v>-0.751154</v>
       </c>
       <c r="X35" t="n">
-        <v>1.118067</v>
+        <v>4.406902</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.718937</v>
+        <v>3.714306</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.909863</v>
+        <v>-4.451799</v>
       </c>
       <c r="AA35" t="n">
-        <v>5.868661</v>
+        <v>-6.584889</v>
       </c>
       <c r="AB35" t="n">
-        <v>-4.522822</v>
+        <v>-10.604085</v>
       </c>
       <c r="AC35" t="n">
-        <v>-10.980392</v>
+        <v>-3.650094</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B36" t="n">
-        <v>127652</v>
+        <v>136004</v>
       </c>
       <c r="C36" t="n">
-        <v>124.040001</v>
+        <v>132.600006</v>
       </c>
       <c r="D36" t="n">
-        <v>98.5</v>
+        <v>102.769997</v>
       </c>
       <c r="E36" t="n">
-        <v>347.700012</v>
+        <v>354.850006</v>
       </c>
       <c r="F36" t="n">
-        <v>5.6111</v>
+        <v>5.6277</v>
       </c>
       <c r="G36" t="n">
-        <v>6.0695</v>
+        <v>6.2224</v>
       </c>
       <c r="H36" t="n">
-        <v>5522.299805</v>
+        <v>5648.399902</v>
       </c>
       <c r="I36" t="n">
-        <v>17599.400391</v>
+        <v>17713.619141</v>
       </c>
       <c r="J36" t="n">
-        <v>40842.789062</v>
+        <v>41563.078125</v>
       </c>
       <c r="K36" t="n">
-        <v>2426.5</v>
+        <v>2527.600098</v>
       </c>
       <c r="L36" t="n">
-        <v>77.910004</v>
+        <v>73.550003</v>
       </c>
       <c r="M36" t="n">
-        <v>80.720001</v>
+        <v>78.800003</v>
       </c>
       <c r="N36" t="n">
-        <v>1028.5</v>
+        <v>982</v>
       </c>
       <c r="O36" t="n">
-        <v>382.75</v>
+        <v>378</v>
       </c>
       <c r="P36" t="n">
-        <v>3.022428</v>
+        <v>6.542788</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.040375</v>
+        <v>6.901004</v>
       </c>
       <c r="R36" t="n">
-        <v>2.125457</v>
+        <v>4.335022</v>
       </c>
       <c r="S36" t="n">
-        <v>2.315871</v>
+        <v>2.056369</v>
       </c>
       <c r="T36" t="n">
-        <v>2.010726</v>
+        <v>0.295836</v>
       </c>
       <c r="U36" t="n">
-        <v>3.031792</v>
+        <v>2.519157</v>
       </c>
       <c r="V36" t="n">
-        <v>1.132132</v>
+        <v>2.283471</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.751154</v>
+        <v>0.648992</v>
       </c>
       <c r="X36" t="n">
-        <v>4.406902</v>
+        <v>1.763565</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.714306</v>
+        <v>4.166499</v>
       </c>
       <c r="Z36" t="n">
-        <v>-4.451799</v>
+        <v>-5.596201</v>
       </c>
       <c r="AA36" t="n">
-        <v>-6.584889</v>
+        <v>-2.37859</v>
       </c>
       <c r="AB36" t="n">
-        <v>-10.604085</v>
+        <v>-4.521147</v>
       </c>
       <c r="AC36" t="n">
-        <v>-3.650094</v>
+        <v>-1.241019</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B37" t="n">
-        <v>136004</v>
+        <v>131816</v>
       </c>
       <c r="C37" t="n">
-        <v>132.600006</v>
+        <v>128.429993</v>
       </c>
       <c r="D37" t="n">
-        <v>102.769997</v>
+        <v>97.959999</v>
       </c>
       <c r="E37" t="n">
-        <v>354.850006</v>
+        <v>349.799988</v>
       </c>
       <c r="F37" t="n">
-        <v>5.6277</v>
+        <v>5.4332</v>
       </c>
       <c r="G37" t="n">
-        <v>6.2224</v>
+        <v>6.0652</v>
       </c>
       <c r="H37" t="n">
-        <v>5648.399902</v>
+        <v>5762.47998</v>
       </c>
       <c r="I37" t="n">
-        <v>17713.619141</v>
+        <v>18189.169922</v>
       </c>
       <c r="J37" t="n">
-        <v>41563.078125</v>
+        <v>42330.148438</v>
       </c>
       <c r="K37" t="n">
-        <v>2527.600098</v>
+        <v>2659.399902</v>
       </c>
       <c r="L37" t="n">
-        <v>73.550003</v>
+        <v>68.16999800000001</v>
       </c>
       <c r="M37" t="n">
-        <v>78.800003</v>
+        <v>71.769997</v>
       </c>
       <c r="N37" t="n">
-        <v>982</v>
+        <v>1057</v>
       </c>
       <c r="O37" t="n">
-        <v>378</v>
+        <v>424.75</v>
       </c>
       <c r="P37" t="n">
-        <v>6.542788</v>
+        <v>-3.079321</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.901004</v>
+        <v>-3.144806</v>
       </c>
       <c r="R37" t="n">
-        <v>4.335022</v>
+        <v>-4.680352</v>
       </c>
       <c r="S37" t="n">
-        <v>2.056369</v>
+        <v>-1.423142</v>
       </c>
       <c r="T37" t="n">
-        <v>0.295836</v>
+        <v>-3.456118</v>
       </c>
       <c r="U37" t="n">
-        <v>2.519157</v>
+        <v>-2.526362</v>
       </c>
       <c r="V37" t="n">
-        <v>2.283471</v>
+        <v>2.019688</v>
       </c>
       <c r="W37" t="n">
-        <v>0.648992</v>
+        <v>2.684662</v>
       </c>
       <c r="X37" t="n">
-        <v>1.763565</v>
+        <v>1.845557</v>
       </c>
       <c r="Y37" t="n">
-        <v>4.166499</v>
+        <v>5.214425</v>
       </c>
       <c r="Z37" t="n">
-        <v>-5.596201</v>
+        <v>-7.314758</v>
       </c>
       <c r="AA37" t="n">
-        <v>-2.37859</v>
+        <v>-8.921328000000001</v>
       </c>
       <c r="AB37" t="n">
-        <v>-4.521147</v>
+        <v>7.637475</v>
       </c>
       <c r="AC37" t="n">
-        <v>-1.241019</v>
+        <v>12.367725</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B38" t="n">
-        <v>131816</v>
+        <v>129713</v>
       </c>
       <c r="C38" t="n">
-        <v>128.429993</v>
+        <v>126.260002</v>
       </c>
       <c r="D38" t="n">
-        <v>97.959999</v>
+        <v>97.25</v>
       </c>
       <c r="E38" t="n">
-        <v>349.799988</v>
+        <v>368.579987</v>
       </c>
       <c r="F38" t="n">
-        <v>5.4332</v>
+        <v>5.7623</v>
       </c>
       <c r="G38" t="n">
-        <v>6.0652</v>
+        <v>6.2522</v>
       </c>
       <c r="H38" t="n">
-        <v>5762.47998</v>
+        <v>5705.450195</v>
       </c>
       <c r="I38" t="n">
-        <v>18189.169922</v>
+        <v>18095.150391</v>
       </c>
       <c r="J38" t="n">
-        <v>42330.148438</v>
+        <v>41763.460938</v>
       </c>
       <c r="K38" t="n">
-        <v>2659.399902</v>
+        <v>2749.300049</v>
       </c>
       <c r="L38" t="n">
-        <v>68.16999800000001</v>
+        <v>69.260002</v>
       </c>
       <c r="M38" t="n">
-        <v>71.769997</v>
+        <v>73.160004</v>
       </c>
       <c r="N38" t="n">
-        <v>1057</v>
+        <v>982.5</v>
       </c>
       <c r="O38" t="n">
-        <v>424.75</v>
+        <v>410.75</v>
       </c>
       <c r="P38" t="n">
-        <v>-3.079321</v>
+        <v>-1.595406</v>
       </c>
       <c r="Q38" t="n">
-        <v>-3.144806</v>
+        <v>-1.689629</v>
       </c>
       <c r="R38" t="n">
-        <v>-4.680352</v>
+        <v>-0.724785</v>
       </c>
       <c r="S38" t="n">
-        <v>-1.423142</v>
+        <v>5.368782</v>
       </c>
       <c r="T38" t="n">
-        <v>-3.456118</v>
+        <v>6.057206</v>
       </c>
       <c r="U38" t="n">
-        <v>-2.526362</v>
+        <v>3.083168</v>
       </c>
       <c r="V38" t="n">
-        <v>2.019688</v>
+        <v>-0.9896740000000001</v>
       </c>
       <c r="W38" t="n">
-        <v>2.684662</v>
+        <v>-0.516898</v>
       </c>
       <c r="X38" t="n">
-        <v>1.845557</v>
+        <v>-1.338733</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.214425</v>
+        <v>3.380467</v>
       </c>
       <c r="Z38" t="n">
-        <v>-7.314758</v>
+        <v>1.59895</v>
       </c>
       <c r="AA38" t="n">
-        <v>-8.921328000000001</v>
+        <v>1.936752</v>
       </c>
       <c r="AB38" t="n">
-        <v>7.637475</v>
+        <v>-7.04825</v>
       </c>
       <c r="AC38" t="n">
-        <v>12.367725</v>
+        <v>-3.296057</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B39" t="n">
-        <v>129713</v>
+        <v>125668</v>
       </c>
       <c r="C39" t="n">
-        <v>126.260002</v>
+        <v>122.32</v>
       </c>
       <c r="D39" t="n">
-        <v>97.25</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>368.579987</v>
+        <v>402.850006</v>
       </c>
       <c r="F39" t="n">
-        <v>5.7623</v>
+        <v>6.0139</v>
       </c>
       <c r="G39" t="n">
-        <v>6.2522</v>
+        <v>6.345178</v>
       </c>
       <c r="H39" t="n">
-        <v>5705.450195</v>
+        <v>6032.379883</v>
       </c>
       <c r="I39" t="n">
-        <v>18095.150391</v>
+        <v>19218.169922</v>
       </c>
       <c r="J39" t="n">
-        <v>41763.460938</v>
+        <v>44910.648438</v>
       </c>
       <c r="K39" t="n">
-        <v>2749.300049</v>
+        <v>2657</v>
       </c>
       <c r="L39" t="n">
-        <v>69.260002</v>
+        <v>68</v>
       </c>
       <c r="M39" t="n">
-        <v>73.160004</v>
+        <v>72.94000200000001</v>
       </c>
       <c r="N39" t="n">
-        <v>982.5</v>
+        <v>989.5</v>
       </c>
       <c r="O39" t="n">
-        <v>410.75</v>
+        <v>423</v>
       </c>
       <c r="P39" t="n">
-        <v>-1.595406</v>
+        <v>-3.118423</v>
       </c>
       <c r="Q39" t="n">
-        <v>-1.689629</v>
+        <v>-3.120547</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.724785</v>
+        <v>-4.041131</v>
       </c>
       <c r="S39" t="n">
-        <v>5.368782</v>
+        <v>9.297851</v>
       </c>
       <c r="T39" t="n">
-        <v>6.057206</v>
+        <v>4.366308</v>
       </c>
       <c r="U39" t="n">
-        <v>3.083168</v>
+        <v>1.487125</v>
       </c>
       <c r="V39" t="n">
-        <v>-0.9896740000000001</v>
+        <v>5.73013</v>
       </c>
       <c r="W39" t="n">
-        <v>-0.516898</v>
+        <v>6.206191</v>
       </c>
       <c r="X39" t="n">
-        <v>-1.338733</v>
+        <v>7.535744</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.380467</v>
+        <v>-3.35722</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.59895</v>
+        <v>-1.819235</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.936752</v>
+        <v>-0.300712</v>
       </c>
       <c r="AB39" t="n">
-        <v>-7.04825</v>
+        <v>0.712468</v>
       </c>
       <c r="AC39" t="n">
-        <v>-3.296057</v>
+        <v>2.982349</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B40" t="n">
-        <v>125668</v>
+        <v>120283</v>
       </c>
       <c r="C40" t="n">
-        <v>122.32</v>
+        <v>117.269997</v>
       </c>
       <c r="D40" t="n">
-        <v>93.31999999999999</v>
+        <v>85.949997</v>
       </c>
       <c r="E40" t="n">
-        <v>402.850006</v>
+        <v>407.700012</v>
       </c>
       <c r="F40" t="n">
-        <v>6.0139</v>
+        <v>6.1779</v>
       </c>
       <c r="G40" t="n">
-        <v>6.345178</v>
+        <v>6.422608</v>
       </c>
       <c r="H40" t="n">
-        <v>6032.379883</v>
+        <v>5881.629883</v>
       </c>
       <c r="I40" t="n">
-        <v>19218.169922</v>
+        <v>19310.789062</v>
       </c>
       <c r="J40" t="n">
-        <v>44910.648438</v>
+        <v>42544.21875</v>
       </c>
       <c r="K40" t="n">
-        <v>2657</v>
+        <v>2641</v>
       </c>
       <c r="L40" t="n">
-        <v>68</v>
+        <v>71.720001</v>
       </c>
       <c r="M40" t="n">
-        <v>72.94000200000001</v>
+        <v>74.639999</v>
       </c>
       <c r="N40" t="n">
-        <v>989.5</v>
+        <v>998.25</v>
       </c>
       <c r="O40" t="n">
-        <v>423</v>
+        <v>458.5</v>
       </c>
       <c r="P40" t="n">
-        <v>-3.118423</v>
+        <v>-4.2851</v>
       </c>
       <c r="Q40" t="n">
-        <v>-3.120547</v>
+        <v>-4.128518</v>
       </c>
       <c r="R40" t="n">
-        <v>-4.041131</v>
+        <v>-7.89756</v>
       </c>
       <c r="S40" t="n">
-        <v>9.297851</v>
+        <v>1.203924</v>
       </c>
       <c r="T40" t="n">
-        <v>4.366308</v>
+        <v>2.727016</v>
       </c>
       <c r="U40" t="n">
-        <v>1.487125</v>
+        <v>1.220293</v>
       </c>
       <c r="V40" t="n">
-        <v>5.73013</v>
+        <v>-2.499014</v>
       </c>
       <c r="W40" t="n">
-        <v>6.206191</v>
+        <v>0.481935</v>
       </c>
       <c r="X40" t="n">
-        <v>7.535744</v>
+        <v>-5.269195</v>
       </c>
       <c r="Y40" t="n">
-        <v>-3.35722</v>
+        <v>-0.602183</v>
       </c>
       <c r="Z40" t="n">
-        <v>-1.819235</v>
+        <v>5.47059</v>
       </c>
       <c r="AA40" t="n">
-        <v>-0.300712</v>
+        <v>2.330678</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.712468</v>
+        <v>0.884285</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.982349</v>
+        <v>8.392435000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B41" t="n">
-        <v>120283</v>
+        <v>126135</v>
       </c>
       <c r="C41" t="n">
-        <v>117.269997</v>
+        <v>123</v>
       </c>
       <c r="D41" t="n">
-        <v>85.949997</v>
+        <v>91.400002</v>
       </c>
       <c r="E41" t="n">
-        <v>407.700012</v>
+        <v>394.149994</v>
       </c>
       <c r="F41" t="n">
-        <v>6.1779</v>
+        <v>5.8745</v>
       </c>
       <c r="G41" t="n">
-        <v>6.422608</v>
+        <v>6.101281</v>
       </c>
       <c r="H41" t="n">
-        <v>5881.629883</v>
+        <v>6040.529785</v>
       </c>
       <c r="I41" t="n">
-        <v>19310.789062</v>
+        <v>19627.439453</v>
       </c>
       <c r="J41" t="n">
-        <v>42544.21875</v>
+        <v>44544.660156</v>
       </c>
       <c r="K41" t="n">
-        <v>2641</v>
+        <v>2812.5</v>
       </c>
       <c r="L41" t="n">
-        <v>71.720001</v>
+        <v>72.529999</v>
       </c>
       <c r="M41" t="n">
-        <v>74.639999</v>
+        <v>76.760002</v>
       </c>
       <c r="N41" t="n">
-        <v>998.25</v>
+        <v>1042</v>
       </c>
       <c r="O41" t="n">
-        <v>458.5</v>
+        <v>482</v>
       </c>
       <c r="P41" t="n">
-        <v>-4.2851</v>
+        <v>4.865193</v>
       </c>
       <c r="Q41" t="n">
-        <v>-4.128518</v>
+        <v>4.886163</v>
       </c>
       <c r="R41" t="n">
-        <v>-7.89756</v>
+        <v>6.340901</v>
       </c>
       <c r="S41" t="n">
-        <v>1.203924</v>
+        <v>-3.323527</v>
       </c>
       <c r="T41" t="n">
-        <v>2.727016</v>
+        <v>-4.911055</v>
       </c>
       <c r="U41" t="n">
-        <v>1.220293</v>
+        <v>-5.003057</v>
       </c>
       <c r="V41" t="n">
-        <v>-2.499014</v>
+        <v>2.70163</v>
       </c>
       <c r="W41" t="n">
-        <v>0.481935</v>
+        <v>1.639759</v>
       </c>
       <c r="X41" t="n">
-        <v>-5.269195</v>
+        <v>4.702029</v>
       </c>
       <c r="Y41" t="n">
-        <v>-0.602183</v>
+        <v>6.493752</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.47059</v>
+        <v>1.129389</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.330678</v>
+        <v>2.840304</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.884285</v>
+        <v>4.38267</v>
       </c>
       <c r="AC41" t="n">
-        <v>8.392435000000001</v>
+        <v>5.125409</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>126135</v>
+        <v>122799</v>
       </c>
       <c r="C42" t="n">
-        <v>123</v>
+        <v>120.010002</v>
       </c>
       <c r="D42" t="n">
-        <v>91.400002</v>
+        <v>87.599998</v>
       </c>
       <c r="E42" t="n">
-        <v>394.149994</v>
+        <v>392.700012</v>
       </c>
       <c r="F42" t="n">
-        <v>5.8745</v>
+        <v>5.839</v>
       </c>
       <c r="G42" t="n">
-        <v>6.101281</v>
+        <v>6.064281</v>
       </c>
       <c r="H42" t="n">
-        <v>6040.529785</v>
+        <v>5954.5</v>
       </c>
       <c r="I42" t="n">
-        <v>19627.439453</v>
+        <v>18847.279297</v>
       </c>
       <c r="J42" t="n">
-        <v>44544.660156</v>
+        <v>43840.910156</v>
       </c>
       <c r="K42" t="n">
-        <v>2812.5</v>
+        <v>2848.5</v>
       </c>
       <c r="L42" t="n">
-        <v>72.529999</v>
+        <v>69.760002</v>
       </c>
       <c r="M42" t="n">
-        <v>76.760002</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>1042</v>
+        <v>1011.5</v>
       </c>
       <c r="O42" t="n">
-        <v>482</v>
+        <v>453.5</v>
       </c>
       <c r="P42" t="n">
-        <v>4.865193</v>
+        <v>-2.644785</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.886163</v>
+        <v>-2.430893</v>
       </c>
       <c r="R42" t="n">
-        <v>6.340901</v>
+        <v>-4.157553</v>
       </c>
       <c r="S42" t="n">
-        <v>-3.323527</v>
+        <v>-0.367876</v>
       </c>
       <c r="T42" t="n">
-        <v>-4.911055</v>
+        <v>-0.604299</v>
       </c>
       <c r="U42" t="n">
-        <v>-5.003057</v>
+        <v>-0.606433</v>
       </c>
       <c r="V42" t="n">
-        <v>2.70163</v>
+        <v>-1.424209</v>
       </c>
       <c r="W42" t="n">
-        <v>1.639759</v>
+        <v>-3.974844</v>
       </c>
       <c r="X42" t="n">
-        <v>4.702029</v>
+        <v>-1.579875</v>
       </c>
       <c r="Y42" t="n">
-        <v>6.493752</v>
+        <v>1.28</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.129389</v>
+        <v>-3.819105</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.840304</v>
+        <v>-4.66389</v>
       </c>
       <c r="AB42" t="n">
-        <v>4.38267</v>
+        <v>-2.927063</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.125409</v>
+        <v>-5.912863</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B43" t="n">
-        <v>122799</v>
+        <v>130260</v>
       </c>
       <c r="C43" t="n">
-        <v>120.010002</v>
+        <v>127.300003</v>
       </c>
       <c r="D43" t="n">
-        <v>87.599998</v>
+        <v>93.41999800000001</v>
       </c>
       <c r="E43" t="n">
-        <v>392.700012</v>
+        <v>358.700012</v>
       </c>
       <c r="F43" t="n">
-        <v>5.839</v>
+        <v>5.7581</v>
       </c>
       <c r="G43" t="n">
-        <v>6.064281</v>
+        <v>6.22665</v>
       </c>
       <c r="H43" t="n">
-        <v>5954.5</v>
+        <v>5611.850098</v>
       </c>
       <c r="I43" t="n">
-        <v>18847.279297</v>
+        <v>17299.289062</v>
       </c>
       <c r="J43" t="n">
-        <v>43840.910156</v>
+        <v>42001.761719</v>
       </c>
       <c r="K43" t="n">
-        <v>2848.5</v>
+        <v>3122.800049</v>
       </c>
       <c r="L43" t="n">
-        <v>69.760002</v>
+        <v>71.480003</v>
       </c>
       <c r="M43" t="n">
-        <v>73.18000000000001</v>
+        <v>74.739998</v>
       </c>
       <c r="N43" t="n">
-        <v>1011.5</v>
+        <v>1014.75</v>
       </c>
       <c r="O43" t="n">
-        <v>453.5</v>
+        <v>457.25</v>
       </c>
       <c r="P43" t="n">
-        <v>-2.644785</v>
+        <v>6.075782</v>
       </c>
       <c r="Q43" t="n">
-        <v>-2.430893</v>
+        <v>6.074494</v>
       </c>
       <c r="R43" t="n">
-        <v>-4.157553</v>
+        <v>6.643835</v>
       </c>
       <c r="S43" t="n">
-        <v>-0.367876</v>
+        <v>-8.658008000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>-0.604299</v>
+        <v>-1.385514</v>
       </c>
       <c r="U43" t="n">
-        <v>-0.606433</v>
+        <v>2.677469</v>
       </c>
       <c r="V43" t="n">
-        <v>-1.424209</v>
+        <v>-5.75447</v>
       </c>
       <c r="W43" t="n">
-        <v>-3.974844</v>
+        <v>-8.213335000000001</v>
       </c>
       <c r="X43" t="n">
-        <v>-1.579875</v>
+        <v>-4.195051</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.28</v>
+        <v>9.629631</v>
       </c>
       <c r="Z43" t="n">
-        <v>-3.819105</v>
+        <v>2.465598</v>
       </c>
       <c r="AA43" t="n">
-        <v>-4.66389</v>
+        <v>2.131727</v>
       </c>
       <c r="AB43" t="n">
-        <v>-2.927063</v>
+        <v>0.321305</v>
       </c>
       <c r="AC43" t="n">
-        <v>-5.912863</v>
+        <v>0.826902</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B44" t="n">
-        <v>130260</v>
+        <v>135067</v>
       </c>
       <c r="C44" t="n">
-        <v>127.300003</v>
+        <v>131.630005</v>
       </c>
       <c r="D44" t="n">
-        <v>93.41999800000001</v>
+        <v>101.5</v>
       </c>
       <c r="E44" t="n">
-        <v>358.700012</v>
+        <v>354.350006</v>
       </c>
       <c r="F44" t="n">
-        <v>5.7581</v>
+        <v>5.62</v>
       </c>
       <c r="G44" t="n">
-        <v>6.22665</v>
+        <v>6.393862</v>
       </c>
       <c r="H44" t="n">
-        <v>5611.850098</v>
+        <v>5569.060059</v>
       </c>
       <c r="I44" t="n">
-        <v>17299.289062</v>
+        <v>17446.339844</v>
       </c>
       <c r="J44" t="n">
-        <v>42001.761719</v>
+        <v>40669.359375</v>
       </c>
       <c r="K44" t="n">
-        <v>3122.800049</v>
+        <v>3319.100098</v>
       </c>
       <c r="L44" t="n">
-        <v>71.480003</v>
+        <v>58.209999</v>
       </c>
       <c r="M44" t="n">
-        <v>74.739998</v>
+        <v>63.119999</v>
       </c>
       <c r="N44" t="n">
-        <v>1014.75</v>
+        <v>1034.75</v>
       </c>
       <c r="O44" t="n">
-        <v>457.25</v>
+        <v>467.25</v>
       </c>
       <c r="P44" t="n">
-        <v>6.075782</v>
+        <v>3.690312</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.074494</v>
+        <v>3.401415</v>
       </c>
       <c r="R44" t="n">
-        <v>6.643835</v>
+        <v>8.649114000000001</v>
       </c>
       <c r="S44" t="n">
-        <v>-8.658008000000001</v>
+        <v>-1.212714</v>
       </c>
       <c r="T44" t="n">
-        <v>-1.385514</v>
+        <v>-2.398363</v>
       </c>
       <c r="U44" t="n">
-        <v>2.677469</v>
+        <v>2.685417</v>
       </c>
       <c r="V44" t="n">
-        <v>-5.75447</v>
+        <v>-0.762494</v>
       </c>
       <c r="W44" t="n">
-        <v>-8.213335000000001</v>
+        <v>0.850039</v>
       </c>
       <c r="X44" t="n">
-        <v>-4.195051</v>
+        <v>-3.172253</v>
       </c>
       <c r="Y44" t="n">
-        <v>9.629631</v>
+        <v>6.286027</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.465598</v>
+        <v>-18.564639</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.131727</v>
+        <v>-15.547229</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.321305</v>
+        <v>1.970929</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.826902</v>
+        <v>2.186987</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B45" t="n">
-        <v>135067</v>
+        <v>137027</v>
       </c>
       <c r="C45" t="n">
-        <v>131.630005</v>
+        <v>133.990005</v>
       </c>
       <c r="D45" t="n">
-        <v>101.5</v>
+        <v>107.639999</v>
       </c>
       <c r="E45" t="n">
-        <v>354.350006</v>
+        <v>378.799988</v>
       </c>
       <c r="F45" t="n">
-        <v>5.62</v>
+        <v>5.6651</v>
       </c>
       <c r="G45" t="n">
-        <v>6.393862</v>
+        <v>6.43915</v>
       </c>
       <c r="H45" t="n">
-        <v>5569.060059</v>
+        <v>5911.689941</v>
       </c>
       <c r="I45" t="n">
-        <v>17446.339844</v>
+        <v>19113.769531</v>
       </c>
       <c r="J45" t="n">
-        <v>40669.359375</v>
+        <v>42270.070312</v>
       </c>
       <c r="K45" t="n">
-        <v>3319.100098</v>
+        <v>3288.899902</v>
       </c>
       <c r="L45" t="n">
-        <v>58.209999</v>
+        <v>60.790001</v>
       </c>
       <c r="M45" t="n">
-        <v>63.119999</v>
+        <v>63.900002</v>
       </c>
       <c r="N45" t="n">
-        <v>1034.75</v>
+        <v>1041.75</v>
       </c>
       <c r="O45" t="n">
-        <v>467.25</v>
+        <v>444</v>
       </c>
       <c r="P45" t="n">
-        <v>3.690312</v>
+        <v>1.451132</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.401415</v>
+        <v>1.792905</v>
       </c>
       <c r="R45" t="n">
-        <v>8.649114000000001</v>
+        <v>6.04926</v>
       </c>
       <c r="S45" t="n">
-        <v>-1.212714</v>
+        <v>6.899952</v>
       </c>
       <c r="T45" t="n">
-        <v>-2.398363</v>
+        <v>0.802495</v>
       </c>
       <c r="U45" t="n">
-        <v>2.685417</v>
+        <v>0.708306</v>
       </c>
       <c r="V45" t="n">
-        <v>-0.762494</v>
+        <v>6.152383</v>
       </c>
       <c r="W45" t="n">
-        <v>0.850039</v>
+        <v>9.557475999999999</v>
       </c>
       <c r="X45" t="n">
-        <v>-3.172253</v>
+        <v>3.935914</v>
       </c>
       <c r="Y45" t="n">
-        <v>6.286027</v>
+        <v>-0.909891</v>
       </c>
       <c r="Z45" t="n">
-        <v>-18.564639</v>
+        <v>4.432231</v>
       </c>
       <c r="AA45" t="n">
-        <v>-15.547229</v>
+        <v>1.235746</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.970929</v>
+        <v>0.676492</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.186987</v>
+        <v>-4.975923</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B46" t="n">
-        <v>137027</v>
+        <v>138855</v>
       </c>
       <c r="C46" t="n">
-        <v>133.990005</v>
+        <v>135.850006</v>
       </c>
       <c r="D46" t="n">
-        <v>107.639999</v>
+        <v>109.029999</v>
       </c>
       <c r="E46" t="n">
-        <v>378.799988</v>
+        <v>377.850006</v>
       </c>
       <c r="F46" t="n">
-        <v>5.6651</v>
+        <v>5.4784</v>
       </c>
       <c r="G46" t="n">
-        <v>6.43915</v>
+        <v>6.418485</v>
       </c>
       <c r="H46" t="n">
-        <v>5911.689941</v>
+        <v>6204.950195</v>
       </c>
       <c r="I46" t="n">
-        <v>19113.769531</v>
+        <v>20369.730469</v>
       </c>
       <c r="J46" t="n">
-        <v>42270.070312</v>
+        <v>44094.769531</v>
       </c>
       <c r="K46" t="n">
-        <v>3288.899902</v>
+        <v>3307.699951</v>
       </c>
       <c r="L46" t="n">
-        <v>60.790001</v>
+        <v>65.110001</v>
       </c>
       <c r="M46" t="n">
-        <v>63.900002</v>
+        <v>67.610001</v>
       </c>
       <c r="N46" t="n">
-        <v>1041.75</v>
+        <v>1024.25</v>
       </c>
       <c r="O46" t="n">
-        <v>444</v>
+        <v>420.5</v>
       </c>
       <c r="P46" t="n">
-        <v>1.451132</v>
+        <v>1.334044</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.792905</v>
+        <v>1.388164</v>
       </c>
       <c r="R46" t="n">
-        <v>6.04926</v>
+        <v>1.291341</v>
       </c>
       <c r="S46" t="n">
-        <v>6.899952</v>
+        <v>-0.250787</v>
       </c>
       <c r="T46" t="n">
-        <v>0.802495</v>
+        <v>-3.295615</v>
       </c>
       <c r="U46" t="n">
-        <v>0.708306</v>
+        <v>-0.320923</v>
       </c>
       <c r="V46" t="n">
-        <v>6.152383</v>
+        <v>4.960684</v>
       </c>
       <c r="W46" t="n">
-        <v>9.557475999999999</v>
+        <v>6.570975</v>
       </c>
       <c r="X46" t="n">
-        <v>3.935914</v>
+        <v>4.316764</v>
       </c>
       <c r="Y46" t="n">
-        <v>-0.909891</v>
+        <v>0.571621</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.432231</v>
+        <v>7.106431</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.235746</v>
+        <v>5.805945</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.676492</v>
+        <v>-1.679866</v>
       </c>
       <c r="AC46" t="n">
-        <v>-4.975923</v>
+        <v>-5.292793</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B47" t="n">
-        <v>138855</v>
+        <v>133071</v>
       </c>
       <c r="C47" t="n">
-        <v>135.850006</v>
+        <v>129.880005</v>
       </c>
       <c r="D47" t="n">
-        <v>109.029999</v>
+        <v>101.919998</v>
       </c>
       <c r="E47" t="n">
-        <v>377.850006</v>
+        <v>398.01001</v>
       </c>
       <c r="F47" t="n">
-        <v>5.4784</v>
+        <v>5.5754</v>
       </c>
       <c r="G47" t="n">
-        <v>6.418485</v>
+        <v>6.365372</v>
       </c>
       <c r="H47" t="n">
-        <v>6204.950195</v>
+        <v>6339.390137</v>
       </c>
       <c r="I47" t="n">
-        <v>20369.730469</v>
+        <v>21122.449219</v>
       </c>
       <c r="J47" t="n">
-        <v>44094.769531</v>
+        <v>44130.980469</v>
       </c>
       <c r="K47" t="n">
-        <v>3307.699951</v>
+        <v>3293.199951</v>
       </c>
       <c r="L47" t="n">
-        <v>65.110001</v>
+        <v>69.260002</v>
       </c>
       <c r="M47" t="n">
-        <v>67.610001</v>
+        <v>72.529999</v>
       </c>
       <c r="N47" t="n">
-        <v>1024.25</v>
+        <v>961.75</v>
       </c>
       <c r="O47" t="n">
-        <v>420.5</v>
+        <v>394</v>
       </c>
       <c r="P47" t="n">
-        <v>1.334044</v>
+        <v>-4.165496</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.388164</v>
+        <v>-4.394554</v>
       </c>
       <c r="R47" t="n">
-        <v>1.291341</v>
+        <v>-6.521142</v>
       </c>
       <c r="S47" t="n">
-        <v>-0.250787</v>
+        <v>5.335451</v>
       </c>
       <c r="T47" t="n">
-        <v>-3.295615</v>
+        <v>1.770583</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.320923</v>
+        <v>-0.8275</v>
       </c>
       <c r="V47" t="n">
-        <v>4.960684</v>
+        <v>2.166656</v>
       </c>
       <c r="W47" t="n">
-        <v>6.570975</v>
+        <v>3.695281</v>
       </c>
       <c r="X47" t="n">
-        <v>4.316764</v>
+        <v>0.082121</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.571621</v>
+        <v>-0.438371</v>
       </c>
       <c r="Z47" t="n">
-        <v>7.106431</v>
+        <v>6.373831</v>
       </c>
       <c r="AA47" t="n">
-        <v>5.805945</v>
+        <v>7.277027</v>
       </c>
       <c r="AB47" t="n">
-        <v>-1.679866</v>
+        <v>-6.102026</v>
       </c>
       <c r="AC47" t="n">
-        <v>-5.292793</v>
+        <v>-6.302021</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B48" t="n">
-        <v>133071</v>
+        <v>141422</v>
       </c>
       <c r="C48" t="n">
-        <v>129.880005</v>
+        <v>138.5</v>
       </c>
       <c r="D48" t="n">
-        <v>101.919998</v>
+        <v>107.43</v>
       </c>
       <c r="E48" t="n">
-        <v>398.01001</v>
+        <v>393.850006</v>
       </c>
       <c r="F48" t="n">
-        <v>5.5754</v>
+        <v>5.413</v>
       </c>
       <c r="G48" t="n">
-        <v>6.365372</v>
+        <v>6.317119</v>
       </c>
       <c r="H48" t="n">
-        <v>6339.390137</v>
+        <v>6460.259766</v>
       </c>
       <c r="I48" t="n">
-        <v>21122.449219</v>
+        <v>21455.550781</v>
       </c>
       <c r="J48" t="n">
-        <v>44130.980469</v>
+        <v>45544.878906</v>
       </c>
       <c r="K48" t="n">
-        <v>3293.199951</v>
+        <v>3516.100098</v>
       </c>
       <c r="L48" t="n">
-        <v>69.260002</v>
+        <v>64.010002</v>
       </c>
       <c r="M48" t="n">
-        <v>72.529999</v>
+        <v>68.120003</v>
       </c>
       <c r="N48" t="n">
-        <v>961.75</v>
+        <v>1036.75</v>
       </c>
       <c r="O48" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P48" t="n">
-        <v>-4.165496</v>
+        <v>6.275597</v>
       </c>
       <c r="Q48" t="n">
-        <v>-4.394554</v>
+        <v>6.636892</v>
       </c>
       <c r="R48" t="n">
-        <v>-6.521142</v>
+        <v>5.406203</v>
       </c>
       <c r="S48" t="n">
-        <v>5.335451</v>
+        <v>-1.045201</v>
       </c>
       <c r="T48" t="n">
-        <v>1.770583</v>
+        <v>-2.912791</v>
       </c>
       <c r="U48" t="n">
-        <v>-0.8275</v>
+        <v>-0.758056</v>
       </c>
       <c r="V48" t="n">
-        <v>2.166656</v>
+        <v>1.906644</v>
       </c>
       <c r="W48" t="n">
-        <v>3.695281</v>
+        <v>1.577003</v>
       </c>
       <c r="X48" t="n">
-        <v>0.082121</v>
+        <v>3.203868</v>
       </c>
       <c r="Y48" t="n">
-        <v>-0.438371</v>
+        <v>6.768497</v>
       </c>
       <c r="Z48" t="n">
-        <v>6.373831</v>
+        <v>-7.580133</v>
       </c>
       <c r="AA48" t="n">
-        <v>7.277027</v>
+        <v>-6.080237</v>
       </c>
       <c r="AB48" t="n">
-        <v>-6.102026</v>
+        <v>7.798284</v>
       </c>
       <c r="AC48" t="n">
-        <v>-6.302021</v>
+        <v>1.015228</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B49" t="n">
-        <v>141422</v>
+        <v>146237</v>
       </c>
       <c r="C49" t="n">
-        <v>138.5</v>
+        <v>143.240005</v>
       </c>
       <c r="D49" t="n">
-        <v>107.43</v>
+        <v>109.669998</v>
       </c>
       <c r="E49" t="n">
-        <v>393.850006</v>
+        <v>399.799988</v>
       </c>
       <c r="F49" t="n">
-        <v>5.413</v>
+        <v>5.3217</v>
       </c>
       <c r="G49" t="n">
-        <v>6.317119</v>
+        <v>6.238303</v>
       </c>
       <c r="H49" t="n">
-        <v>6460.259766</v>
+        <v>6688.459961</v>
       </c>
       <c r="I49" t="n">
-        <v>21455.550781</v>
+        <v>22660.009766</v>
       </c>
       <c r="J49" t="n">
-        <v>45544.878906</v>
+        <v>46397.890625</v>
       </c>
       <c r="K49" t="n">
-        <v>3516.100098</v>
+        <v>3873.199951</v>
       </c>
       <c r="L49" t="n">
-        <v>64.010002</v>
+        <v>62.369999</v>
       </c>
       <c r="M49" t="n">
-        <v>68.120003</v>
+        <v>67.019997</v>
       </c>
       <c r="N49" t="n">
-        <v>1036.75</v>
+        <v>1001.75</v>
       </c>
       <c r="O49" t="n">
-        <v>398</v>
+        <v>415.5</v>
       </c>
       <c r="P49" t="n">
-        <v>6.275597</v>
+        <v>3.404704</v>
       </c>
       <c r="Q49" t="n">
-        <v>6.636892</v>
+        <v>3.422387</v>
       </c>
       <c r="R49" t="n">
-        <v>5.406203</v>
+        <v>2.085077</v>
       </c>
       <c r="S49" t="n">
-        <v>-1.045201</v>
+        <v>1.510723</v>
       </c>
       <c r="T49" t="n">
-        <v>-2.912791</v>
+        <v>-1.68668</v>
       </c>
       <c r="U49" t="n">
-        <v>-0.758056</v>
+        <v>-1.247656</v>
       </c>
       <c r="V49" t="n">
-        <v>1.906644</v>
+        <v>3.532369</v>
       </c>
       <c r="W49" t="n">
-        <v>1.577003</v>
+        <v>5.613741</v>
       </c>
       <c r="X49" t="n">
-        <v>3.203868</v>
+        <v>1.872904</v>
       </c>
       <c r="Y49" t="n">
-        <v>6.768497</v>
+        <v>10.156134</v>
       </c>
       <c r="Z49" t="n">
-        <v>-7.580133</v>
+        <v>-2.562105</v>
       </c>
       <c r="AA49" t="n">
-        <v>-6.080237</v>
+        <v>-1.614806</v>
       </c>
       <c r="AB49" t="n">
-        <v>7.798284</v>
+        <v>-3.375934</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.015228</v>
+        <v>4.396985</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B50" t="n">
-        <v>146237</v>
+        <v>149540</v>
       </c>
       <c r="C50" t="n">
-        <v>143.240005</v>
+        <v>146.410004</v>
       </c>
       <c r="D50" t="n">
-        <v>109.669998</v>
+        <v>110.059998</v>
       </c>
       <c r="E50" t="n">
-        <v>399.799988</v>
+        <v>413.329987</v>
       </c>
       <c r="F50" t="n">
-        <v>5.3217</v>
+        <v>5.382</v>
       </c>
       <c r="G50" t="n">
-        <v>6.238303</v>
+        <v>6.222775</v>
       </c>
       <c r="H50" t="n">
-        <v>6688.459961</v>
+        <v>6840.200195</v>
       </c>
       <c r="I50" t="n">
-        <v>22660.009766</v>
+        <v>23724.960938</v>
       </c>
       <c r="J50" t="n">
-        <v>46397.890625</v>
+        <v>47562.871094</v>
       </c>
       <c r="K50" t="n">
-        <v>3873.199951</v>
+        <v>3996.5</v>
       </c>
       <c r="L50" t="n">
-        <v>62.369999</v>
+        <v>60.98</v>
       </c>
       <c r="M50" t="n">
-        <v>67.019997</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>1001.75</v>
+        <v>1099.75</v>
       </c>
       <c r="O50" t="n">
-        <v>415.5</v>
+        <v>431.5</v>
       </c>
       <c r="P50" t="n">
-        <v>3.404704</v>
+        <v>2.258662</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.422387</v>
+        <v>2.213068</v>
       </c>
       <c r="R50" t="n">
-        <v>2.085077</v>
+        <v>0.355612</v>
       </c>
       <c r="S50" t="n">
-        <v>1.510723</v>
+        <v>3.384192</v>
       </c>
       <c r="T50" t="n">
-        <v>-1.68668</v>
+        <v>1.133094</v>
       </c>
       <c r="U50" t="n">
-        <v>-1.247656</v>
+        <v>-0.248917</v>
       </c>
       <c r="V50" t="n">
-        <v>3.532369</v>
+        <v>2.268687</v>
       </c>
       <c r="W50" t="n">
-        <v>5.613741</v>
+        <v>4.699694</v>
       </c>
       <c r="X50" t="n">
-        <v>1.872904</v>
+        <v>2.510848</v>
       </c>
       <c r="Y50" t="n">
-        <v>10.156134</v>
+        <v>3.183416</v>
       </c>
       <c r="Z50" t="n">
-        <v>-2.562105</v>
+        <v>-2.228635</v>
       </c>
       <c r="AA50" t="n">
-        <v>-1.614806</v>
+        <v>-2.909575</v>
       </c>
       <c r="AB50" t="n">
-        <v>-3.375934</v>
+        <v>9.78288</v>
       </c>
       <c r="AC50" t="n">
-        <v>4.396985</v>
+        <v>3.850782</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B51" t="n">
-        <v>149540</v>
+        <v>159072</v>
       </c>
       <c r="C51" t="n">
-        <v>146.410004</v>
+        <v>155.850006</v>
       </c>
       <c r="D51" t="n">
-        <v>110.059998</v>
+        <v>116.489998</v>
       </c>
       <c r="E51" t="n">
-        <v>413.329987</v>
+        <v>411.089996</v>
       </c>
       <c r="F51" t="n">
-        <v>5.382</v>
+        <v>5.3554</v>
       </c>
       <c r="G51" t="n">
-        <v>6.222775</v>
+        <v>6.207325</v>
       </c>
       <c r="H51" t="n">
-        <v>6840.200195</v>
+        <v>6849.089844</v>
       </c>
       <c r="I51" t="n">
-        <v>23724.960938</v>
+        <v>23365.689453</v>
       </c>
       <c r="J51" t="n">
-        <v>47562.871094</v>
+        <v>47716.421875</v>
       </c>
       <c r="K51" t="n">
-        <v>3996.5</v>
+        <v>4254.899902</v>
       </c>
       <c r="L51" t="n">
-        <v>60.98</v>
+        <v>58.549999</v>
       </c>
       <c r="M51" t="n">
-        <v>65.06999999999999</v>
+        <v>63.200001</v>
       </c>
       <c r="N51" t="n">
-        <v>1099.75</v>
+        <v>1137.75</v>
       </c>
       <c r="O51" t="n">
-        <v>431.5</v>
+        <v>435.5</v>
       </c>
       <c r="P51" t="n">
-        <v>2.258662</v>
+        <v>6.374214</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.213068</v>
+        <v>6.447649</v>
       </c>
       <c r="R51" t="n">
-        <v>0.355612</v>
+        <v>5.842268</v>
       </c>
       <c r="S51" t="n">
-        <v>3.384192</v>
+        <v>-0.541938</v>
       </c>
       <c r="T51" t="n">
-        <v>1.133094</v>
+        <v>-0.494238</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.248917</v>
+        <v>-0.248282</v>
       </c>
       <c r="V51" t="n">
-        <v>2.268687</v>
+        <v>0.129962</v>
       </c>
       <c r="W51" t="n">
-        <v>4.699694</v>
+        <v>-1.514319</v>
       </c>
       <c r="X51" t="n">
-        <v>2.510848</v>
+        <v>0.322837</v>
       </c>
       <c r="Y51" t="n">
-        <v>3.183416</v>
+        <v>6.465655</v>
       </c>
       <c r="Z51" t="n">
-        <v>-2.228635</v>
+        <v>-3.984914</v>
       </c>
       <c r="AA51" t="n">
-        <v>-2.909575</v>
+        <v>-2.873827</v>
       </c>
       <c r="AB51" t="n">
-        <v>9.78288</v>
+        <v>3.455331</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.850782</v>
+        <v>0.926999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B52" t="n">
-        <v>159072</v>
+        <v>161125</v>
       </c>
       <c r="C52" t="n">
-        <v>155.850006</v>
+        <v>158</v>
       </c>
       <c r="D52" t="n">
-        <v>116.489998</v>
+        <v>112.449997</v>
       </c>
       <c r="E52" t="n">
-        <v>411.089996</v>
+        <v>424.200012</v>
       </c>
       <c r="F52" t="n">
-        <v>5.3554</v>
+        <v>5.4762</v>
       </c>
       <c r="G52" t="n">
-        <v>6.207325</v>
+        <v>6.426735</v>
       </c>
       <c r="H52" t="n">
-        <v>6849.089844</v>
+        <v>6845.5</v>
       </c>
       <c r="I52" t="n">
-        <v>23365.689453</v>
+        <v>23241.990234</v>
       </c>
       <c r="J52" t="n">
-        <v>47716.421875</v>
+        <v>48063.289062</v>
       </c>
       <c r="K52" t="n">
-        <v>4254.899902</v>
+        <v>4341.100098</v>
       </c>
       <c r="L52" t="n">
-        <v>58.549999</v>
+        <v>57.419998</v>
       </c>
       <c r="M52" t="n">
-        <v>63.200001</v>
+        <v>60.849998</v>
       </c>
       <c r="N52" t="n">
-        <v>1137.75</v>
+        <v>1030.5</v>
       </c>
       <c r="O52" t="n">
-        <v>435.5</v>
+        <v>440.25</v>
       </c>
       <c r="P52" t="n">
-        <v>6.374214</v>
+        <v>1.290611</v>
       </c>
       <c r="Q52" t="n">
-        <v>6.447649</v>
+        <v>1.379528</v>
       </c>
       <c r="R52" t="n">
-        <v>5.842268</v>
+        <v>-3.46811</v>
       </c>
       <c r="S52" t="n">
-        <v>-0.541938</v>
+        <v>3.189087</v>
       </c>
       <c r="T52" t="n">
-        <v>-0.494238</v>
+        <v>2.255667</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.248282</v>
+        <v>3.534694</v>
       </c>
       <c r="V52" t="n">
-        <v>0.129962</v>
+        <v>-0.052413</v>
       </c>
       <c r="W52" t="n">
-        <v>-1.514319</v>
+        <v>-0.529405</v>
       </c>
       <c r="X52" t="n">
-        <v>0.322837</v>
+        <v>0.726935</v>
       </c>
       <c r="Y52" t="n">
-        <v>6.465655</v>
+        <v>2.025904</v>
       </c>
       <c r="Z52" t="n">
-        <v>-3.984914</v>
+        <v>-1.929976</v>
       </c>
       <c r="AA52" t="n">
-        <v>-2.873827</v>
+        <v>-3.718358</v>
       </c>
       <c r="AB52" t="n">
-        <v>3.455331</v>
+        <v>-9.426500000000001</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.926999</v>
+        <v>1.0907</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B53" t="n">
-        <v>161125</v>
+        <v>181364</v>
       </c>
       <c r="C53" t="n">
-        <v>158</v>
+        <v>178.199997</v>
       </c>
       <c r="D53" t="n">
-        <v>112.449997</v>
+        <v>123.800003</v>
       </c>
       <c r="E53" t="n">
-        <v>424.200012</v>
+        <v>410.649994</v>
       </c>
       <c r="F53" t="n">
-        <v>5.4762</v>
+        <v>5.1892</v>
       </c>
       <c r="G53" t="n">
-        <v>6.426735</v>
+        <v>6.203474</v>
       </c>
       <c r="H53" t="n">
-        <v>6845.5</v>
+        <v>6939.029785</v>
       </c>
       <c r="I53" t="n">
-        <v>23241.990234</v>
+        <v>23461.820312</v>
       </c>
       <c r="J53" t="n">
-        <v>48063.289062</v>
+        <v>48892.46875</v>
       </c>
       <c r="K53" t="n">
-        <v>4341.100098</v>
+        <v>4745.100098</v>
       </c>
       <c r="L53" t="n">
-        <v>57.419998</v>
+        <v>65.209999</v>
       </c>
       <c r="M53" t="n">
-        <v>60.849998</v>
+        <v>70.69000200000001</v>
       </c>
       <c r="N53" t="n">
-        <v>1030.5</v>
+        <v>1064.25</v>
       </c>
       <c r="O53" t="n">
-        <v>440.25</v>
+        <v>428.25</v>
       </c>
       <c r="P53" t="n">
-        <v>1.290611</v>
+        <v>12.561055</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.379528</v>
+        <v>12.784808</v>
       </c>
       <c r="R53" t="n">
-        <v>-3.46811</v>
+        <v>10.093381</v>
       </c>
       <c r="S53" t="n">
-        <v>3.189087</v>
+        <v>-3.194252</v>
       </c>
       <c r="T53" t="n">
-        <v>2.255667</v>
+        <v>-5.240864</v>
       </c>
       <c r="U53" t="n">
-        <v>3.534694</v>
+        <v>-3.473939</v>
       </c>
       <c r="V53" t="n">
-        <v>-0.052413</v>
+        <v>1.366296</v>
       </c>
       <c r="W53" t="n">
-        <v>-0.529405</v>
+        <v>0.945832</v>
       </c>
       <c r="X53" t="n">
-        <v>0.726935</v>
+        <v>1.725183</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.025904</v>
+        <v>9.306397</v>
       </c>
       <c r="Z53" t="n">
-        <v>-1.929976</v>
+        <v>13.566704</v>
       </c>
       <c r="AA53" t="n">
-        <v>-3.718358</v>
+        <v>16.170919</v>
       </c>
       <c r="AB53" t="n">
-        <v>-9.426500000000001</v>
+        <v>3.275109</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.0907</v>
+        <v>-2.725724</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B54" t="n">
-        <v>181364</v>
+        <v>188787</v>
       </c>
       <c r="C54" t="n">
-        <v>178.199997</v>
+        <v>185.160004</v>
       </c>
       <c r="D54" t="n">
-        <v>123.800003</v>
+        <v>126.379997</v>
       </c>
       <c r="E54" t="n">
-        <v>410.649994</v>
+        <v>396.75</v>
       </c>
       <c r="F54" t="n">
-        <v>5.1892</v>
+        <v>5.1366</v>
       </c>
       <c r="G54" t="n">
-        <v>6.203474</v>
+        <v>6.056935</v>
       </c>
       <c r="H54" t="n">
-        <v>6939.029785</v>
+        <v>6878.879883</v>
       </c>
       <c r="I54" t="n">
-        <v>23461.820312</v>
+        <v>22668.210938</v>
       </c>
       <c r="J54" t="n">
-        <v>48892.46875</v>
+        <v>48977.921875</v>
       </c>
       <c r="K54" t="n">
-        <v>4745.100098</v>
+        <v>5247.899902</v>
       </c>
       <c r="L54" t="n">
-        <v>65.209999</v>
+        <v>67.019997</v>
       </c>
       <c r="M54" t="n">
-        <v>70.69000200000001</v>
+        <v>72.480003</v>
       </c>
       <c r="N54" t="n">
-        <v>1064.25</v>
+        <v>1157.25</v>
       </c>
       <c r="O54" t="n">
-        <v>428.25</v>
+        <v>438.75</v>
       </c>
       <c r="P54" t="n">
-        <v>12.561055</v>
+        <v>4.092874</v>
       </c>
       <c r="Q54" t="n">
-        <v>12.784808</v>
+        <v>3.905728</v>
       </c>
       <c r="R54" t="n">
-        <v>10.093381</v>
+        <v>2.084002</v>
       </c>
       <c r="S54" t="n">
-        <v>-3.194252</v>
+        <v>-3.384876</v>
       </c>
       <c r="T54" t="n">
-        <v>-5.240864</v>
+        <v>-1.013642</v>
       </c>
       <c r="U54" t="n">
-        <v>-3.473939</v>
+        <v>-2.362212</v>
       </c>
       <c r="V54" t="n">
-        <v>1.366296</v>
+        <v>-0.866834</v>
       </c>
       <c r="W54" t="n">
-        <v>0.945832</v>
+        <v>-3.382557</v>
       </c>
       <c r="X54" t="n">
-        <v>1.725183</v>
+        <v>0.174778</v>
       </c>
       <c r="Y54" t="n">
-        <v>9.306397</v>
+        <v>10.59619</v>
       </c>
       <c r="Z54" t="n">
-        <v>13.566704</v>
+        <v>2.775644</v>
       </c>
       <c r="AA54" t="n">
-        <v>16.170919</v>
+        <v>2.532184</v>
       </c>
       <c r="AB54" t="n">
-        <v>3.275109</v>
+        <v>8.738548</v>
       </c>
       <c r="AC54" t="n">
-        <v>-2.725724</v>
+        <v>2.451839</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B55" t="n">
-        <v>188787</v>
+        <v>187462</v>
       </c>
       <c r="C55" t="n">
-        <v>185.160004</v>
+        <v>184.279999</v>
       </c>
       <c r="D55" t="n">
-        <v>126.379997</v>
+        <v>120</v>
       </c>
       <c r="E55" t="n">
-        <v>396.75</v>
+        <v>380.149994</v>
       </c>
       <c r="F55" t="n">
-        <v>5.1366</v>
+        <v>5.264</v>
       </c>
       <c r="G55" t="n">
-        <v>6.056935</v>
+        <v>6.027728</v>
       </c>
       <c r="H55" t="n">
-        <v>6878.879883</v>
+        <v>6528.52002</v>
       </c>
       <c r="I55" t="n">
-        <v>22668.210938</v>
+        <v>21590.630859</v>
       </c>
       <c r="J55" t="n">
-        <v>48977.921875</v>
+        <v>46341.511719</v>
       </c>
       <c r="K55" t="n">
-        <v>5247.899902</v>
+        <v>4647.600098</v>
       </c>
       <c r="L55" t="n">
-        <v>67.019997</v>
+        <v>101.379997</v>
       </c>
       <c r="M55" t="n">
-        <v>72.480003</v>
+        <v>118.349998</v>
       </c>
       <c r="N55" t="n">
-        <v>1157.25</v>
+        <v>1171</v>
       </c>
       <c r="O55" t="n">
-        <v>438.75</v>
+        <v>457.75</v>
       </c>
       <c r="P55" t="n">
-        <v>4.092874</v>
+        <v>-0.7018489999999999</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.905728</v>
+        <v>-0.475267</v>
       </c>
       <c r="R55" t="n">
-        <v>2.084002</v>
+        <v>-5.048265</v>
       </c>
       <c r="S55" t="n">
-        <v>-3.384876</v>
+        <v>-4.183996</v>
       </c>
       <c r="T55" t="n">
-        <v>-1.013642</v>
+        <v>2.480238</v>
       </c>
       <c r="U55" t="n">
-        <v>-2.362212</v>
+        <v>-0.482204</v>
       </c>
       <c r="V55" t="n">
-        <v>-0.866834</v>
+        <v>-5.093269</v>
       </c>
       <c r="W55" t="n">
-        <v>-3.382557</v>
+        <v>-4.753706</v>
       </c>
       <c r="X55" t="n">
-        <v>0.174778</v>
+        <v>-5.382854</v>
       </c>
       <c r="Y55" t="n">
-        <v>10.59619</v>
+        <v>-11.438858</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.775644</v>
+        <v>51.268282</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.532184</v>
+        <v>63.286414</v>
       </c>
       <c r="AB55" t="n">
-        <v>8.738548</v>
+        <v>1.188162</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.451839</v>
+        <v>4.330484</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B56" t="n">
-        <v>187462</v>
+        <v>187318</v>
       </c>
       <c r="C56" t="n">
-        <v>184.279999</v>
+        <v>184.089996</v>
       </c>
       <c r="D56" t="n">
-        <v>120</v>
+        <v>115.760002</v>
       </c>
       <c r="E56" t="n">
-        <v>380.149994</v>
+        <v>402.5</v>
       </c>
       <c r="F56" t="n">
-        <v>5.264</v>
+        <v>5.0175</v>
       </c>
       <c r="G56" t="n">
-        <v>6.027728</v>
+        <v>5.858231</v>
       </c>
       <c r="H56" t="n">
-        <v>6528.52002</v>
+        <v>7209.009766</v>
       </c>
       <c r="I56" t="n">
-        <v>21590.630859</v>
+        <v>24892.310547</v>
       </c>
       <c r="J56" t="n">
-        <v>46341.511719</v>
+        <v>49652.140625</v>
       </c>
       <c r="K56" t="n">
-        <v>4647.600098</v>
+        <v>4629.600098</v>
       </c>
       <c r="L56" t="n">
-        <v>101.379997</v>
+        <v>105.07</v>
       </c>
       <c r="M56" t="n">
-        <v>118.349998</v>
+        <v>114.010002</v>
       </c>
       <c r="N56" t="n">
-        <v>1171</v>
+        <v>1182</v>
       </c>
       <c r="O56" t="n">
-        <v>457.75</v>
+        <v>464.75</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.7018489999999999</v>
+        <v>-0.076816</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.475267</v>
+        <v>-0.103105</v>
       </c>
       <c r="R56" t="n">
-        <v>-5.048265</v>
+        <v>-3.533332</v>
       </c>
       <c r="S56" t="n">
-        <v>-4.183996</v>
+        <v>5.87926</v>
       </c>
       <c r="T56" t="n">
-        <v>2.480238</v>
+        <v>-4.682751</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.482204</v>
+        <v>-2.811955</v>
       </c>
       <c r="V56" t="n">
-        <v>-5.093269</v>
+        <v>10.423339</v>
       </c>
       <c r="W56" t="n">
-        <v>-4.753706</v>
+        <v>15.292187</v>
       </c>
       <c r="X56" t="n">
-        <v>-5.382854</v>
+        <v>7.143981</v>
       </c>
       <c r="Y56" t="n">
-        <v>-11.438858</v>
+        <v>-0.387297</v>
       </c>
       <c r="Z56" t="n">
-        <v>51.268282</v>
+        <v>3.639774</v>
       </c>
       <c r="AA56" t="n">
-        <v>63.286414</v>
+        <v>-3.667086</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.188162</v>
+        <v>0.939368</v>
       </c>
       <c r="AC56" t="n">
-        <v>4.330484</v>
+        <v>1.529219</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B57" t="n">
-        <v>187318</v>
+        <v>173788</v>
       </c>
       <c r="C57" t="n">
-        <v>184.089996</v>
+        <v>170.75</v>
       </c>
       <c r="D57" t="n">
-        <v>115.760002</v>
+        <v>110.989998</v>
       </c>
       <c r="E57" t="n">
-        <v>402.5</v>
+        <v>430.399994</v>
       </c>
       <c r="F57" t="n">
-        <v>5.0175</v>
+        <v>5.0517</v>
       </c>
       <c r="G57" t="n">
-        <v>5.858231</v>
+        <v>5.882353</v>
       </c>
       <c r="H57" t="n">
-        <v>7209.009766</v>
+        <v>7580.060059</v>
       </c>
       <c r="I57" t="n">
-        <v>24892.310547</v>
+        <v>26972.619141</v>
       </c>
       <c r="J57" t="n">
-        <v>49652.140625</v>
+        <v>51032.460938</v>
       </c>
       <c r="K57" t="n">
-        <v>4629.600098</v>
+        <v>4593</v>
       </c>
       <c r="L57" t="n">
-        <v>105.07</v>
+        <v>87.360001</v>
       </c>
       <c r="M57" t="n">
-        <v>114.010002</v>
+        <v>92.050003</v>
       </c>
       <c r="N57" t="n">
-        <v>1182</v>
+        <v>1186.75</v>
       </c>
       <c r="O57" t="n">
-        <v>464.75</v>
+        <v>446.75</v>
       </c>
       <c r="P57" t="n">
-        <v>-0.076816</v>
+        <v>-7.223011</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.103105</v>
+        <v>-7.246454</v>
       </c>
       <c r="R57" t="n">
-        <v>-3.533332</v>
+        <v>-4.120598</v>
       </c>
       <c r="S57" t="n">
-        <v>5.87926</v>
+        <v>6.931676</v>
       </c>
       <c r="T57" t="n">
-        <v>-4.682751</v>
+        <v>0.6816179999999999</v>
       </c>
       <c r="U57" t="n">
-        <v>-2.811955</v>
+        <v>0.411758</v>
       </c>
       <c r="V57" t="n">
-        <v>10.423339</v>
+        <v>5.147036</v>
       </c>
       <c r="W57" t="n">
-        <v>15.292187</v>
+        <v>8.357234</v>
       </c>
       <c r="X57" t="n">
-        <v>7.143981</v>
+        <v>2.779981</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.387297</v>
+        <v>-0.790567</v>
       </c>
       <c r="Z57" t="n">
-        <v>3.639774</v>
+        <v>-16.855429</v>
       </c>
       <c r="AA57" t="n">
-        <v>-3.667086</v>
+        <v>-19.261467</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.939368</v>
+        <v>0.401861</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.529219</v>
+        <v>-3.87305</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B58" t="n">
-        <v>173788</v>
+        <v>172024</v>
       </c>
       <c r="C58" t="n">
-        <v>170.75</v>
+        <v>169.050003</v>
       </c>
       <c r="D58" t="n">
-        <v>110.989998</v>
+        <v>107.980003</v>
       </c>
       <c r="E58" t="n">
-        <v>430.399994</v>
+        <v>435.649994</v>
       </c>
       <c r="F58" t="n">
-        <v>5.0517</v>
+        <v>5.181787</v>
       </c>
       <c r="G58" t="n">
-        <v>5.882353</v>
+        <v>5.91716</v>
       </c>
       <c r="H58" t="n">
-        <v>7580.060059</v>
+        <v>7499.359863</v>
       </c>
       <c r="I58" t="n">
-        <v>26972.619141</v>
+        <v>26213.720703</v>
       </c>
       <c r="J58" t="n">
-        <v>51032.460938</v>
+        <v>52319.199219</v>
       </c>
       <c r="K58" t="n">
-        <v>4593</v>
+        <v>4038.5</v>
       </c>
       <c r="L58" t="n">
-        <v>87.360001</v>
+        <v>69.5</v>
       </c>
       <c r="M58" t="n">
-        <v>92.050003</v>
+        <v>72.91999800000001</v>
       </c>
       <c r="N58" t="n">
-        <v>1186.75</v>
+        <v>1116.75</v>
       </c>
       <c r="O58" t="n">
-        <v>446.75</v>
+        <v>412.75</v>
       </c>
       <c r="P58" t="n">
-        <v>-7.223011</v>
+        <v>-1.01503</v>
       </c>
       <c r="Q58" t="n">
-        <v>-7.246454</v>
+        <v>-0.995606</v>
       </c>
       <c r="R58" t="n">
-        <v>-4.120598</v>
+        <v>-2.711951</v>
       </c>
       <c r="S58" t="n">
-        <v>6.931676</v>
+        <v>1.219796</v>
       </c>
       <c r="T58" t="n">
-        <v>0.6816179999999999</v>
+        <v>2.575111</v>
       </c>
       <c r="U58" t="n">
-        <v>0.411758</v>
+        <v>0.591722</v>
       </c>
       <c r="V58" t="n">
-        <v>5.147036</v>
+        <v>-1.064638</v>
       </c>
       <c r="W58" t="n">
-        <v>8.357234</v>
+        <v>-2.813588</v>
       </c>
       <c r="X58" t="n">
-        <v>2.779981</v>
+        <v>2.521411</v>
       </c>
       <c r="Y58" t="n">
-        <v>-0.790567</v>
+        <v>-12.072719</v>
       </c>
       <c r="Z58" t="n">
-        <v>-16.855429</v>
+        <v>-20.44414</v>
       </c>
       <c r="AA58" t="n">
-        <v>-19.261467</v>
+        <v>-20.782188</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.401861</v>
+        <v>-5.898462</v>
       </c>
       <c r="AC58" t="n">
-        <v>-3.87305</v>
+        <v>-7.61052</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B59" t="n">
-        <v>172024</v>
+        <v>177999</v>
       </c>
       <c r="C59" t="n">
-        <v>169.050003</v>
+        <v>175.020004</v>
       </c>
       <c r="D59" t="n">
-        <v>107.980003</v>
+        <v>107.25</v>
       </c>
       <c r="E59" t="n">
-        <v>435.649994</v>
+        <v>428.390015</v>
       </c>
       <c r="F59" t="n">
-        <v>5.181787</v>
+        <v>5.0781</v>
       </c>
       <c r="G59" t="n">
-        <v>5.91716</v>
+        <v>5.847953</v>
       </c>
       <c r="H59" t="n">
-        <v>7499.359863</v>
+        <v>7489.720215</v>
       </c>
       <c r="I59" t="n">
-        <v>26213.720703</v>
+        <v>25373.849609</v>
       </c>
       <c r="J59" t="n">
-        <v>52319.199219</v>
+        <v>52485.03125</v>
       </c>
       <c r="K59" t="n">
-        <v>4038.5</v>
+        <v>4107</v>
       </c>
       <c r="L59" t="n">
-        <v>69.5</v>
+        <v>84.66999800000001</v>
       </c>
       <c r="M59" t="n">
-        <v>72.91999800000001</v>
+        <v>90.120003</v>
       </c>
       <c r="N59" t="n">
-        <v>1116.75</v>
+        <v>1172</v>
       </c>
       <c r="O59" t="n">
-        <v>412.75</v>
+        <v>440.75</v>
       </c>
       <c r="P59" t="n">
-        <v>-1.01503</v>
+        <v>3.473353</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.995606</v>
+        <v>3.5315</v>
       </c>
       <c r="R59" t="n">
-        <v>-2.711951</v>
+        <v>-0.676054</v>
       </c>
       <c r="S59" t="n">
-        <v>1.219796</v>
+        <v>-1.666471</v>
       </c>
       <c r="T59" t="n">
-        <v>2.575111</v>
+        <v>-2.000986</v>
       </c>
       <c r="U59" t="n">
-        <v>0.591722</v>
+        <v>-1.169601</v>
       </c>
       <c r="V59" t="n">
-        <v>-1.064638</v>
+        <v>-0.12854</v>
       </c>
       <c r="W59" t="n">
-        <v>-2.813588</v>
+        <v>-3.203937</v>
       </c>
       <c r="X59" t="n">
-        <v>2.521411</v>
+        <v>0.316962</v>
       </c>
       <c r="Y59" t="n">
-        <v>-12.072719</v>
+        <v>1.696174</v>
       </c>
       <c r="Z59" t="n">
-        <v>-20.44414</v>
+        <v>21.827335</v>
       </c>
       <c r="AA59" t="n">
-        <v>-20.782188</v>
+        <v>23.5875</v>
       </c>
       <c r="AB59" t="n">
-        <v>-5.898462</v>
+        <v>4.947392</v>
       </c>
       <c r="AC59" t="n">
-        <v>-7.61052</v>
+        <v>6.783767</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B60" t="n">
-        <v>177999</v>
+        <v>177419</v>
       </c>
       <c r="C60" t="n">
-        <v>175.020004</v>
+        <v>174.779999</v>
       </c>
       <c r="D60" t="n">
-        <v>107.25</v>
+        <v>106.129997</v>
       </c>
       <c r="E60" t="n">
-        <v>428.390015</v>
+        <v>449.350006</v>
       </c>
       <c r="F60" t="n">
-        <v>5.0781</v>
+        <v>5.1912</v>
       </c>
       <c r="G60" t="n">
-        <v>5.847953</v>
+        <v>6.009615</v>
       </c>
       <c r="H60" t="n">
-        <v>7489.720215</v>
+        <v>7686.140137</v>
       </c>
       <c r="I60" t="n">
-        <v>25373.849609</v>
+        <v>26370.890625</v>
       </c>
       <c r="J60" t="n">
-        <v>52485.03125</v>
+        <v>53185.898438</v>
       </c>
       <c r="K60" t="n">
-        <v>4107</v>
+        <v>4481.5</v>
       </c>
       <c r="L60" t="n">
-        <v>84.66999800000001</v>
+        <v>85.760002</v>
       </c>
       <c r="M60" t="n">
-        <v>90.120003</v>
+        <v>90.489998</v>
       </c>
       <c r="N60" t="n">
-        <v>1172</v>
+        <v>1275.25</v>
       </c>
       <c r="O60" t="n">
-        <v>440.75</v>
+        <v>515</v>
       </c>
       <c r="P60" t="n">
-        <v>3.473353</v>
+        <v>-0.325845</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.5315</v>
+        <v>-0.13713</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.676054</v>
+        <v>-1.044292</v>
       </c>
       <c r="S60" t="n">
-        <v>-1.666471</v>
+        <v>4.892736</v>
       </c>
       <c r="T60" t="n">
-        <v>-2.000986</v>
+        <v>2.227203</v>
       </c>
       <c r="U60" t="n">
-        <v>-1.169601</v>
+        <v>2.764422</v>
       </c>
       <c r="V60" t="n">
-        <v>-0.12854</v>
+        <v>2.622527</v>
       </c>
       <c r="W60" t="n">
-        <v>-3.203937</v>
+        <v>3.929404</v>
       </c>
       <c r="X60" t="n">
-        <v>0.316962</v>
+        <v>1.335366</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.696174</v>
+        <v>9.118577999999999</v>
       </c>
       <c r="Z60" t="n">
-        <v>21.827335</v>
+        <v>1.287356</v>
       </c>
       <c r="AA60" t="n">
-        <v>23.5875</v>
+        <v>0.410558</v>
       </c>
       <c r="AB60" t="n">
-        <v>4.947392</v>
+        <v>8.809727000000001</v>
       </c>
       <c r="AC60" t="n">
-        <v>6.783767</v>
+        <v>16.846285</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B61" t="n">
-        <v>177419</v>
+        <v>186340</v>
       </c>
       <c r="C61" t="n">
-        <v>174.779999</v>
+        <v>181.050003</v>
       </c>
       <c r="D61" t="n">
-        <v>106.129997</v>
+        <v>109.650002</v>
       </c>
       <c r="E61" t="n">
-        <v>449.350006</v>
+        <v>451.529999</v>
       </c>
       <c r="F61" t="n">
-        <v>5.1912</v>
+        <v>5.2029</v>
       </c>
       <c r="G61" t="n">
-        <v>6.009615</v>
+        <v>5.896226</v>
       </c>
       <c r="H61" t="n">
-        <v>7686.140137</v>
+        <v>7651.540039</v>
       </c>
       <c r="I61" t="n">
-        <v>26370.890625</v>
+        <v>26861.060547</v>
       </c>
       <c r="J61" t="n">
-        <v>53185.898438</v>
+        <v>50906.050781</v>
       </c>
       <c r="K61" t="n">
-        <v>4481.5</v>
+        <v>4186.700195</v>
       </c>
       <c r="L61" t="n">
-        <v>85.760002</v>
+        <v>90.41999800000001</v>
       </c>
       <c r="M61" t="n">
-        <v>90.489998</v>
+        <v>103.529999</v>
       </c>
       <c r="N61" t="n">
-        <v>1275.25</v>
+        <v>1293</v>
       </c>
       <c r="O61" t="n">
-        <v>515</v>
+        <v>500.75</v>
       </c>
       <c r="P61" t="n">
-        <v>-0.325845</v>
+        <v>5.02821</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.13713</v>
+        <v>3.587369</v>
       </c>
       <c r="R61" t="n">
-        <v>-1.044292</v>
+        <v>3.316691</v>
       </c>
       <c r="S61" t="n">
-        <v>4.892736</v>
+        <v>0.485144</v>
       </c>
       <c r="T61" t="n">
-        <v>2.227203</v>
+        <v>0.225384</v>
       </c>
       <c r="U61" t="n">
-        <v>2.764422</v>
+        <v>-1.886793</v>
       </c>
       <c r="V61" t="n">
-        <v>2.622527</v>
+        <v>-0.450162</v>
       </c>
       <c r="W61" t="n">
-        <v>3.929404</v>
+        <v>1.858754</v>
       </c>
       <c r="X61" t="n">
-        <v>1.335366</v>
+        <v>-4.286564</v>
       </c>
       <c r="Y61" t="n">
-        <v>9.118577999999999</v>
+        <v>-6.57815</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.287356</v>
+        <v>5.433764</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.410558</v>
+        <v>14.410433</v>
       </c>
       <c r="AB61" t="n">
-        <v>8.809727000000001</v>
+        <v>1.391884</v>
       </c>
       <c r="AC61" t="n">
-        <v>16.846285</v>
+        <v>-2.76699</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>185892.640625</v>
+        <v>186810.84375</v>
       </c>
       <c r="C62" t="n">
-        <v>183.020004</v>
+        <v>183.960007</v>
       </c>
       <c r="D62" t="n">
-        <v>110.860001</v>
+        <v>112.709999</v>
       </c>
       <c r="E62" t="n">
-        <v>451.519989</v>
+        <v>451.859985</v>
       </c>
       <c r="F62" t="n">
-        <v>5.1838</v>
+        <v>5.2282</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8751</v>
+        <v>5.8715</v>
       </c>
       <c r="H62" t="n">
-        <v>7711.649902</v>
+        <v>7647.740234</v>
       </c>
       <c r="I62" t="n">
-        <v>27062.792969</v>
+        <v>26818.607422</v>
       </c>
       <c r="J62" t="n">
-        <v>51319.070312</v>
+        <v>50836.351562</v>
       </c>
       <c r="K62" t="n">
-        <v>4189.299805</v>
+        <v>4195.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>91.379997</v>
+        <v>91.910004</v>
       </c>
       <c r="M62" t="n">
-        <v>98.83000199999999</v>
+        <v>101.080002</v>
       </c>
       <c r="N62" t="n">
-        <v>1306.5</v>
+        <v>1277.25</v>
       </c>
       <c r="O62" t="n">
-        <v>507.5</v>
+        <v>497.75</v>
       </c>
       <c r="P62" t="n">
-        <v>4.776062</v>
+        <v>0.25268</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.714501</v>
+        <v>1.607293</v>
       </c>
       <c r="R62" t="n">
-        <v>4.456802</v>
+        <v>2.790695</v>
       </c>
       <c r="S62" t="n">
-        <v>0.482916</v>
+        <v>0.07308199999999999</v>
       </c>
       <c r="T62" t="n">
-        <v>-0.14254</v>
+        <v>0.486268</v>
       </c>
       <c r="U62" t="n">
-        <v>-2.238327</v>
+        <v>-0.419352</v>
       </c>
       <c r="V62" t="n">
-        <v>0.331893</v>
+        <v>-0.049661</v>
       </c>
       <c r="W62" t="n">
-        <v>2.623735</v>
+        <v>-0.158047</v>
       </c>
       <c r="X62" t="n">
-        <v>-3.510006</v>
+        <v>-0.136917</v>
       </c>
       <c r="Y62" t="n">
-        <v>-6.520143</v>
+        <v>0.207794</v>
       </c>
       <c r="Z62" t="n">
-        <v>6.553166</v>
+        <v>1.647872</v>
       </c>
       <c r="AA62" t="n">
-        <v>9.216493</v>
+        <v>-2.366461</v>
       </c>
       <c r="AB62" t="n">
-        <v>2.4505</v>
+        <v>-1.218097</v>
       </c>
       <c r="AC62" t="n">
-        <v>-1.456311</v>
+        <v>-0.599101</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5798,13 +5798,13 @@
         <v>186340</v>
       </c>
       <c r="C61" t="n">
-        <v>181.050003</v>
+        <v>184.080002</v>
       </c>
       <c r="D61" t="n">
-        <v>109.650002</v>
+        <v>111.93</v>
       </c>
       <c r="E61" t="n">
-        <v>451.529999</v>
+        <v>447.369995</v>
       </c>
       <c r="F61" t="n">
         <v>5.2029</v>
@@ -5840,13 +5840,13 @@
         <v>5.02821</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.587369</v>
+        <v>5.320977</v>
       </c>
       <c r="R61" t="n">
-        <v>3.316691</v>
+        <v>5.464999</v>
       </c>
       <c r="S61" t="n">
-        <v>0.485144</v>
+        <v>-0.440639</v>
       </c>
       <c r="T61" t="n">
         <v>0.225384</v>
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>186810.84375</v>
+        <v>186864.640625</v>
       </c>
       <c r="C62" t="n">
-        <v>183.960007</v>
+        <v>184.139999</v>
       </c>
       <c r="D62" t="n">
-        <v>112.709999</v>
+        <v>113.480003</v>
       </c>
       <c r="E62" t="n">
-        <v>451.859985</v>
+        <v>454.899994</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2282</v>
+        <v>5.225</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8715</v>
+        <v>5.8793</v>
       </c>
       <c r="H62" t="n">
-        <v>7647.740234</v>
+        <v>7723.790039</v>
       </c>
       <c r="I62" t="n">
-        <v>26818.607422</v>
+        <v>27210.888672</v>
       </c>
       <c r="J62" t="n">
-        <v>50836.351562</v>
+        <v>51103.199219</v>
       </c>
       <c r="K62" t="n">
-        <v>4195.399902</v>
+        <v>4160.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>91.910004</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>101.080002</v>
+        <v>101.379997</v>
       </c>
       <c r="N62" t="n">
-        <v>1277.25</v>
+        <v>1279</v>
       </c>
       <c r="O62" t="n">
-        <v>497.75</v>
+        <v>496.25</v>
       </c>
       <c r="P62" t="n">
-        <v>0.25268</v>
+        <v>0.28155</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.607293</v>
+        <v>0.032593</v>
       </c>
       <c r="R62" t="n">
-        <v>2.790695</v>
+        <v>1.384797</v>
       </c>
       <c r="S62" t="n">
-        <v>0.07308199999999999</v>
+        <v>1.68317</v>
       </c>
       <c r="T62" t="n">
-        <v>0.486268</v>
+        <v>0.424763</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.419352</v>
+        <v>-0.287062</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.049661</v>
+        <v>0.944254</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.158047</v>
+        <v>1.302362</v>
       </c>
       <c r="X62" t="n">
-        <v>-0.136917</v>
+        <v>0.387279</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.207794</v>
+        <v>-0.6281870000000001</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.647872</v>
+        <v>0.442382</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.366461</v>
+        <v>-2.076694</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.218097</v>
+        <v>-1.082753</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.599101</v>
+        <v>-0.898652</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>186864.640625</v>
+        <v>187130.234375</v>
       </c>
       <c r="C62" t="n">
-        <v>184.139999</v>
+        <v>184.320007</v>
       </c>
       <c r="D62" t="n">
-        <v>113.480003</v>
+        <v>113.379997</v>
       </c>
       <c r="E62" t="n">
-        <v>454.899994</v>
+        <v>454.670013</v>
       </c>
       <c r="F62" t="n">
-        <v>5.225</v>
+        <v>5.2234</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8793</v>
+        <v>5.8805</v>
       </c>
       <c r="H62" t="n">
-        <v>7723.790039</v>
+        <v>7725.560059</v>
       </c>
       <c r="I62" t="n">
-        <v>27210.888672</v>
+        <v>27222.126953</v>
       </c>
       <c r="J62" t="n">
-        <v>51103.199219</v>
+        <v>51112.210938</v>
       </c>
       <c r="K62" t="n">
-        <v>4160.399902</v>
+        <v>4155.200195</v>
       </c>
       <c r="L62" t="n">
-        <v>90.81999999999999</v>
+        <v>90.970001</v>
       </c>
       <c r="M62" t="n">
-        <v>101.379997</v>
+        <v>101.400002</v>
       </c>
       <c r="N62" t="n">
-        <v>1279</v>
+        <v>1279.25</v>
       </c>
       <c r="O62" t="n">
-        <v>496.25</v>
+        <v>496.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0.28155</v>
+        <v>0.424082</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.032593</v>
+        <v>0.130381</v>
       </c>
       <c r="R62" t="n">
-        <v>1.384797</v>
+        <v>1.29545</v>
       </c>
       <c r="S62" t="n">
-        <v>1.68317</v>
+        <v>1.631763</v>
       </c>
       <c r="T62" t="n">
-        <v>0.424763</v>
+        <v>0.394015</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.287062</v>
+        <v>-0.266714</v>
       </c>
       <c r="V62" t="n">
-        <v>0.944254</v>
+        <v>0.967387</v>
       </c>
       <c r="W62" t="n">
-        <v>1.302362</v>
+        <v>1.3442</v>
       </c>
       <c r="X62" t="n">
-        <v>0.387279</v>
+        <v>0.404982</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.6281870000000001</v>
+        <v>-0.752383</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.442382</v>
+        <v>0.608276</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.076694</v>
+        <v>-2.057372</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.082753</v>
+        <v>-1.063418</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.898652</v>
+        <v>-0.798802</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>187130.234375</v>
+        <v>192115</v>
       </c>
       <c r="C62" t="n">
-        <v>184.320007</v>
+        <v>184.410004</v>
       </c>
       <c r="D62" t="n">
-        <v>113.379997</v>
+        <v>113.019997</v>
       </c>
       <c r="E62" t="n">
-        <v>454.670013</v>
+        <v>452.079987</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2234</v>
+        <v>5.2223</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8805</v>
+        <v>5.8702</v>
       </c>
       <c r="H62" t="n">
-        <v>7725.560059</v>
+        <v>7722.720215</v>
       </c>
       <c r="I62" t="n">
-        <v>27222.126953</v>
+        <v>27190.859375</v>
       </c>
       <c r="J62" t="n">
-        <v>51112.210938</v>
+        <v>51176.960938</v>
       </c>
       <c r="K62" t="n">
-        <v>4155.200195</v>
+        <v>4162.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>90.970001</v>
+        <v>91.110001</v>
       </c>
       <c r="M62" t="n">
-        <v>101.400002</v>
+        <v>102.25</v>
       </c>
       <c r="N62" t="n">
-        <v>1279.25</v>
+        <v>1278.25</v>
       </c>
       <c r="O62" t="n">
-        <v>496.75</v>
+        <v>497.75</v>
       </c>
       <c r="P62" t="n">
-        <v>0.424082</v>
+        <v>3.099174</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.130381</v>
+        <v>0.179271</v>
       </c>
       <c r="R62" t="n">
-        <v>1.29545</v>
+        <v>0.97382</v>
       </c>
       <c r="S62" t="n">
-        <v>1.631763</v>
+        <v>1.052818</v>
       </c>
       <c r="T62" t="n">
-        <v>0.394015</v>
+        <v>0.372871</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.266714</v>
+        <v>-0.441397</v>
       </c>
       <c r="V62" t="n">
-        <v>0.967387</v>
+        <v>0.930273</v>
       </c>
       <c r="W62" t="n">
-        <v>1.3442</v>
+        <v>1.227795</v>
       </c>
       <c r="X62" t="n">
-        <v>0.404982</v>
+        <v>0.532177</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.752383</v>
+        <v>-0.582807</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.608276</v>
+        <v>0.763108</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.057372</v>
+        <v>-1.236355</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.063418</v>
+        <v>-1.140758</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.798802</v>
+        <v>-0.599101</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5887,13 +5887,13 @@
         <v>192115</v>
       </c>
       <c r="C62" t="n">
-        <v>184.410004</v>
+        <v>190</v>
       </c>
       <c r="D62" t="n">
-        <v>113.019997</v>
+        <v>116.339996</v>
       </c>
       <c r="E62" t="n">
-        <v>452.079987</v>
+        <v>454.700012</v>
       </c>
       <c r="F62" t="n">
         <v>5.2223</v>
@@ -5929,13 +5929,13 @@
         <v>3.099174</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.179271</v>
+        <v>3.215992</v>
       </c>
       <c r="R62" t="n">
-        <v>0.97382</v>
+        <v>3.939959</v>
       </c>
       <c r="S62" t="n">
-        <v>1.052818</v>
+        <v>1.638469</v>
       </c>
       <c r="T62" t="n">
         <v>0.372871</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>192115</v>
+        <v>208982.96875</v>
       </c>
       <c r="C62" t="n">
-        <v>190</v>
+        <v>205.960007</v>
       </c>
       <c r="D62" t="n">
-        <v>116.339996</v>
+        <v>128.25</v>
       </c>
       <c r="E62" t="n">
-        <v>454.700012</v>
+        <v>439.059998</v>
       </c>
       <c r="F62" t="n">
-        <v>5.2223</v>
+        <v>4.9902</v>
       </c>
       <c r="G62" t="n">
-        <v>5.8702</v>
+        <v>5.6059</v>
       </c>
       <c r="H62" t="n">
-        <v>7722.720215</v>
+        <v>7785.040039</v>
       </c>
       <c r="I62" t="n">
-        <v>27190.859375</v>
+        <v>27504.978516</v>
       </c>
       <c r="J62" t="n">
-        <v>51176.960938</v>
+        <v>51352.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4162.299805</v>
+        <v>4167</v>
       </c>
       <c r="L62" t="n">
-        <v>91.110001</v>
+        <v>88.980003</v>
       </c>
       <c r="M62" t="n">
-        <v>102.25</v>
+        <v>100</v>
       </c>
       <c r="N62" t="n">
-        <v>1278.25</v>
+        <v>1281</v>
       </c>
       <c r="O62" t="n">
-        <v>497.75</v>
+        <v>497.5</v>
       </c>
       <c r="P62" t="n">
-        <v>3.099174</v>
+        <v>12.151427</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.215992</v>
+        <v>11.886139</v>
       </c>
       <c r="R62" t="n">
-        <v>3.939959</v>
+        <v>14.580541</v>
       </c>
       <c r="S62" t="n">
-        <v>1.638469</v>
+        <v>-1.857522</v>
       </c>
       <c r="T62" t="n">
-        <v>0.372871</v>
+        <v>-4.088103</v>
       </c>
       <c r="U62" t="n">
-        <v>-0.441397</v>
+        <v>-4.923931</v>
       </c>
       <c r="V62" t="n">
-        <v>0.930273</v>
+        <v>1.744747</v>
       </c>
       <c r="W62" t="n">
-        <v>1.227795</v>
+        <v>2.397217</v>
       </c>
       <c r="X62" t="n">
-        <v>0.532177</v>
+        <v>0.87683</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.582807</v>
+        <v>-0.470542</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.763108</v>
+        <v>-1.592562</v>
       </c>
       <c r="AA62" t="n">
-        <v>-1.236355</v>
+        <v>-3.409639</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.140758</v>
+        <v>-0.928074</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.599101</v>
+        <v>-0.649026</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>208982.96875</v>
+        <v>205427.203125</v>
       </c>
       <c r="C62" t="n">
-        <v>205.960007</v>
+        <v>202.289993</v>
       </c>
       <c r="D62" t="n">
-        <v>128.25</v>
+        <v>128.529999</v>
       </c>
       <c r="E62" t="n">
-        <v>439.059998</v>
+        <v>440.369995</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9902</v>
+        <v>4.9748</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6059</v>
+        <v>5.601</v>
       </c>
       <c r="H62" t="n">
-        <v>7785.040039</v>
+        <v>7834.240234</v>
       </c>
       <c r="I62" t="n">
-        <v>27504.978516</v>
+        <v>27662.966797</v>
       </c>
       <c r="J62" t="n">
-        <v>51352.410156</v>
+        <v>51601.289062</v>
       </c>
       <c r="K62" t="n">
-        <v>4167</v>
+        <v>4191.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>88.980003</v>
+        <v>89.220001</v>
       </c>
       <c r="M62" t="n">
-        <v>100</v>
+        <v>99.75</v>
       </c>
       <c r="N62" t="n">
-        <v>1281</v>
+        <v>1295.75</v>
       </c>
       <c r="O62" t="n">
-        <v>497.5</v>
+        <v>506.5</v>
       </c>
       <c r="P62" t="n">
-        <v>12.151427</v>
+        <v>10.243213</v>
       </c>
       <c r="Q62" t="n">
-        <v>11.886139</v>
+        <v>9.892433</v>
       </c>
       <c r="R62" t="n">
-        <v>14.580541</v>
+        <v>14.830696</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.857522</v>
+        <v>-1.5647</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.088103</v>
+        <v>-4.38409</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.923931</v>
+        <v>-5.007035</v>
       </c>
       <c r="V62" t="n">
-        <v>1.744747</v>
+        <v>2.387757</v>
       </c>
       <c r="W62" t="n">
-        <v>2.397217</v>
+        <v>2.985386</v>
       </c>
       <c r="X62" t="n">
-        <v>0.87683</v>
+        <v>1.365728</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.470542</v>
+        <v>0.109862</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.592562</v>
+        <v>-1.327137</v>
       </c>
       <c r="AA62" t="n">
-        <v>-3.409639</v>
+        <v>-3.651114</v>
       </c>
       <c r="AB62" t="n">
-        <v>-0.928074</v>
+        <v>0.212684</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.649026</v>
+        <v>1.148278</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>205427.203125</v>
+        <v>204957.3125</v>
       </c>
       <c r="C62" t="n">
-        <v>202.289993</v>
+        <v>201.839996</v>
       </c>
       <c r="D62" t="n">
-        <v>128.529999</v>
+        <v>130.240005</v>
       </c>
       <c r="E62" t="n">
-        <v>440.369995</v>
+        <v>439.339996</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9748</v>
+        <v>4.9916</v>
       </c>
       <c r="G62" t="n">
-        <v>5.601</v>
+        <v>5.5874</v>
       </c>
       <c r="H62" t="n">
-        <v>7834.240234</v>
+        <v>7800.709961</v>
       </c>
       <c r="I62" t="n">
-        <v>27662.966797</v>
+        <v>27498.011719</v>
       </c>
       <c r="J62" t="n">
-        <v>51601.289062</v>
+        <v>51213.96875</v>
       </c>
       <c r="K62" t="n">
-        <v>4191.299805</v>
+        <v>4135.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>89.220001</v>
+        <v>88.779999</v>
       </c>
       <c r="M62" t="n">
-        <v>99.75</v>
+        <v>100.699997</v>
       </c>
       <c r="N62" t="n">
-        <v>1295.75</v>
+        <v>1293.5</v>
       </c>
       <c r="O62" t="n">
-        <v>506.5</v>
+        <v>501.25</v>
       </c>
       <c r="P62" t="n">
-        <v>10.243213</v>
+        <v>9.991045</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.892433</v>
+        <v>9.647976</v>
       </c>
       <c r="R62" t="n">
-        <v>14.830696</v>
+        <v>16.358443</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.5647</v>
+        <v>-1.794935</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.38409</v>
+        <v>-4.061195</v>
       </c>
       <c r="U62" t="n">
-        <v>-5.007035</v>
+        <v>-5.237689</v>
       </c>
       <c r="V62" t="n">
-        <v>2.387757</v>
+        <v>1.949541</v>
       </c>
       <c r="W62" t="n">
-        <v>2.985386</v>
+        <v>2.371281</v>
       </c>
       <c r="X62" t="n">
-        <v>1.365728</v>
+        <v>0.6048750000000001</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.109862</v>
+        <v>-1.225316</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.327137</v>
+        <v>-1.813757</v>
       </c>
       <c r="AA62" t="n">
-        <v>-3.651114</v>
+        <v>-2.733509</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.212684</v>
+        <v>0.03867</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.148278</v>
+        <v>0.09984999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>204957.3125</v>
+        <v>205987.65625</v>
       </c>
       <c r="C62" t="n">
-        <v>201.839996</v>
+        <v>202.75</v>
       </c>
       <c r="D62" t="n">
-        <v>130.240005</v>
+        <v>133.270004</v>
       </c>
       <c r="E62" t="n">
-        <v>439.339996</v>
+        <v>438.910004</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9916</v>
+        <v>5.0122</v>
       </c>
       <c r="G62" t="n">
-        <v>5.5874</v>
+        <v>5.6139</v>
       </c>
       <c r="H62" t="n">
-        <v>7800.709961</v>
+        <v>7747.589844</v>
       </c>
       <c r="I62" t="n">
-        <v>27498.011719</v>
+        <v>27173.046875</v>
       </c>
       <c r="J62" t="n">
-        <v>51213.96875</v>
+        <v>51085.648438</v>
       </c>
       <c r="K62" t="n">
-        <v>4135.399902</v>
+        <v>4147.5</v>
       </c>
       <c r="L62" t="n">
-        <v>88.779999</v>
+        <v>91.05999799999999</v>
       </c>
       <c r="M62" t="n">
-        <v>100.699997</v>
+        <v>103.629997</v>
       </c>
       <c r="N62" t="n">
-        <v>1293.5</v>
+        <v>1288</v>
       </c>
       <c r="O62" t="n">
-        <v>501.25</v>
+        <v>500</v>
       </c>
       <c r="P62" t="n">
-        <v>9.991045</v>
+        <v>10.543982</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.647976</v>
+        <v>10.142328</v>
       </c>
       <c r="R62" t="n">
-        <v>16.358443</v>
+        <v>19.065491</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.794935</v>
+        <v>-1.89105</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.061195</v>
+        <v>-3.665265</v>
       </c>
       <c r="U62" t="n">
-        <v>-5.237689</v>
+        <v>-4.788245</v>
       </c>
       <c r="V62" t="n">
-        <v>1.949541</v>
+        <v>1.2553</v>
       </c>
       <c r="W62" t="n">
-        <v>2.371281</v>
+        <v>1.161482</v>
       </c>
       <c r="X62" t="n">
-        <v>0.6048750000000001</v>
+        <v>0.352802</v>
       </c>
       <c r="Y62" t="n">
-        <v>-1.225316</v>
+        <v>-0.936303</v>
       </c>
       <c r="Z62" t="n">
-        <v>-1.813757</v>
+        <v>0.707807</v>
       </c>
       <c r="AA62" t="n">
-        <v>-2.733509</v>
+        <v>0.09658899999999999</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.03867</v>
+        <v>-0.386698</v>
       </c>
       <c r="AC62" t="n">
-        <v>0.09984999999999999</v>
+        <v>-0.149775</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>205987.65625</v>
+        <v>206768.96875</v>
       </c>
       <c r="C62" t="n">
-        <v>202.75</v>
+        <v>203.580002</v>
       </c>
       <c r="D62" t="n">
-        <v>133.270004</v>
+        <v>133.729996</v>
       </c>
       <c r="E62" t="n">
-        <v>438.910004</v>
+        <v>438.649994</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0122</v>
+        <v>5.0001</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6139</v>
+        <v>5.6081</v>
       </c>
       <c r="H62" t="n">
-        <v>7747.589844</v>
+        <v>7758.700195</v>
       </c>
       <c r="I62" t="n">
-        <v>27173.046875</v>
+        <v>27225.183594</v>
       </c>
       <c r="J62" t="n">
-        <v>51085.648438</v>
+        <v>51122.460938</v>
       </c>
       <c r="K62" t="n">
-        <v>4147.5</v>
+        <v>4157.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>91.05999799999999</v>
+        <v>90.800003</v>
       </c>
       <c r="M62" t="n">
-        <v>103.629997</v>
+        <v>103.290001</v>
       </c>
       <c r="N62" t="n">
-        <v>1288</v>
+        <v>1287.75</v>
       </c>
       <c r="O62" t="n">
-        <v>500</v>
+        <v>500.5</v>
       </c>
       <c r="P62" t="n">
-        <v>10.543982</v>
+        <v>10.963276</v>
       </c>
       <c r="Q62" t="n">
-        <v>10.142328</v>
+        <v>10.59322</v>
       </c>
       <c r="R62" t="n">
-        <v>19.065491</v>
+        <v>19.476454</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.89105</v>
+        <v>-1.94917</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.665265</v>
+        <v>-3.897822</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.788245</v>
+        <v>-4.886617</v>
       </c>
       <c r="V62" t="n">
-        <v>1.2553</v>
+        <v>1.400504</v>
       </c>
       <c r="W62" t="n">
-        <v>1.161482</v>
+        <v>1.35558</v>
       </c>
       <c r="X62" t="n">
-        <v>0.352802</v>
+        <v>0.425117</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.936303</v>
+        <v>-0.6879</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.707807</v>
+        <v>0.420266</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.09658899999999999</v>
+        <v>-0.231815</v>
       </c>
       <c r="AB62" t="n">
-        <v>-0.386698</v>
+        <v>-0.406032</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.149775</v>
+        <v>-0.049925</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>206768.96875</v>
+        <v>208674.40625</v>
       </c>
       <c r="C62" t="n">
-        <v>203.580002</v>
+        <v>205.360001</v>
       </c>
       <c r="D62" t="n">
-        <v>133.729996</v>
+        <v>138.789993</v>
       </c>
       <c r="E62" t="n">
-        <v>438.649994</v>
+        <v>439.200012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0001</v>
+        <v>4.9842</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6081</v>
+        <v>5.577</v>
       </c>
       <c r="H62" t="n">
-        <v>7758.700195</v>
+        <v>7807.779785</v>
       </c>
       <c r="I62" t="n">
-        <v>27225.183594</v>
+        <v>27350.091797</v>
       </c>
       <c r="J62" t="n">
-        <v>51122.460938</v>
+        <v>51618.488281</v>
       </c>
       <c r="K62" t="n">
-        <v>4157.899902</v>
+        <v>4210.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>90.800003</v>
+        <v>91.480003</v>
       </c>
       <c r="M62" t="n">
-        <v>103.290001</v>
+        <v>104.099998</v>
       </c>
       <c r="N62" t="n">
-        <v>1287.75</v>
+        <v>1274.5</v>
       </c>
       <c r="O62" t="n">
-        <v>500.5</v>
+        <v>472.5</v>
       </c>
       <c r="P62" t="n">
-        <v>10.963276</v>
+        <v>11.985836</v>
       </c>
       <c r="Q62" t="n">
-        <v>10.59322</v>
+        <v>11.56019</v>
       </c>
       <c r="R62" t="n">
-        <v>19.476454</v>
+        <v>23.997135</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.94917</v>
+        <v>-1.826225</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.897822</v>
+        <v>-4.203424</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.886617</v>
+        <v>-5.41407</v>
       </c>
       <c r="V62" t="n">
-        <v>1.400504</v>
+        <v>2.041939</v>
       </c>
       <c r="W62" t="n">
-        <v>1.35558</v>
+        <v>1.820595</v>
       </c>
       <c r="X62" t="n">
-        <v>0.425117</v>
+        <v>1.399514</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.6879</v>
+        <v>0.578014</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.420266</v>
+        <v>1.172313</v>
       </c>
       <c r="AA62" t="n">
-        <v>-0.231815</v>
+        <v>0.550565</v>
       </c>
       <c r="AB62" t="n">
-        <v>-0.406032</v>
+        <v>-1.430781</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.049925</v>
+        <v>-5.641538</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>208674.40625</v>
+        <v>208473.4375</v>
       </c>
       <c r="C62" t="n">
-        <v>205.360001</v>
+        <v>205.149994</v>
       </c>
       <c r="D62" t="n">
-        <v>138.789993</v>
+        <v>138.770004</v>
       </c>
       <c r="E62" t="n">
-        <v>439.200012</v>
+        <v>439.23999</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9842</v>
+        <v>4.9872</v>
       </c>
       <c r="G62" t="n">
-        <v>5.577</v>
+        <v>5.5779</v>
       </c>
       <c r="H62" t="n">
-        <v>7807.779785</v>
+        <v>7812.879883</v>
       </c>
       <c r="I62" t="n">
-        <v>27350.091797</v>
+        <v>27376.107422</v>
       </c>
       <c r="J62" t="n">
-        <v>51618.488281</v>
+        <v>51627.800781</v>
       </c>
       <c r="K62" t="n">
-        <v>4210.899902</v>
+        <v>4214.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>91.480003</v>
+        <v>91.199997</v>
       </c>
       <c r="M62" t="n">
-        <v>104.099998</v>
+        <v>103.879997</v>
       </c>
       <c r="N62" t="n">
-        <v>1274.5</v>
+        <v>1273</v>
       </c>
       <c r="O62" t="n">
-        <v>472.5</v>
+        <v>470.25</v>
       </c>
       <c r="P62" t="n">
-        <v>11.985836</v>
+        <v>11.877985</v>
       </c>
       <c r="Q62" t="n">
-        <v>11.56019</v>
+        <v>11.446106</v>
       </c>
       <c r="R62" t="n">
-        <v>23.997135</v>
+        <v>23.979276</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.826225</v>
+        <v>-1.817289</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.203424</v>
+        <v>-4.145768</v>
       </c>
       <c r="U62" t="n">
-        <v>-5.41407</v>
+        <v>-5.398809</v>
       </c>
       <c r="V62" t="n">
-        <v>2.041939</v>
+        <v>2.108593</v>
       </c>
       <c r="W62" t="n">
-        <v>1.820595</v>
+        <v>1.917448</v>
       </c>
       <c r="X62" t="n">
-        <v>1.399514</v>
+        <v>1.417808</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.578014</v>
+        <v>0.654451</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.172313</v>
+        <v>0.86264</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.550565</v>
+        <v>0.338065</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.430781</v>
+        <v>-1.54679</v>
       </c>
       <c r="AC62" t="n">
-        <v>-5.641538</v>
+        <v>-6.090864</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>208473.4375</v>
+        <v>209067</v>
       </c>
       <c r="C62" t="n">
-        <v>205.149994</v>
+        <v>203.080002</v>
       </c>
       <c r="D62" t="n">
-        <v>138.770004</v>
+        <v>134.389999</v>
       </c>
       <c r="E62" t="n">
-        <v>439.23999</v>
+        <v>440.350006</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9872</v>
+        <v>4.9772</v>
       </c>
       <c r="G62" t="n">
-        <v>5.5779</v>
+        <v>5.5828</v>
       </c>
       <c r="H62" t="n">
-        <v>7812.879883</v>
+        <v>7811.540039</v>
       </c>
       <c r="I62" t="n">
-        <v>27376.107422</v>
+        <v>27366.169922</v>
       </c>
       <c r="J62" t="n">
-        <v>51627.800781</v>
+        <v>51654.949219</v>
       </c>
       <c r="K62" t="n">
-        <v>4214.100098</v>
+        <v>4216.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>91.199997</v>
+        <v>91.849998</v>
       </c>
       <c r="M62" t="n">
-        <v>103.879997</v>
+        <v>104.720001</v>
       </c>
       <c r="N62" t="n">
-        <v>1273</v>
+        <v>1292</v>
       </c>
       <c r="O62" t="n">
-        <v>470.25</v>
+        <v>479.75</v>
       </c>
       <c r="P62" t="n">
-        <v>11.877985</v>
+        <v>12.196522</v>
       </c>
       <c r="Q62" t="n">
-        <v>11.446106</v>
+        <v>10.321599</v>
       </c>
       <c r="R62" t="n">
-        <v>23.979276</v>
+        <v>20.066112</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.817289</v>
+        <v>-1.569168</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.145768</v>
+        <v>-4.337964</v>
       </c>
       <c r="U62" t="n">
-        <v>-5.398809</v>
+        <v>-5.315706</v>
       </c>
       <c r="V62" t="n">
-        <v>2.108593</v>
+        <v>2.091082</v>
       </c>
       <c r="W62" t="n">
-        <v>1.917448</v>
+        <v>1.880452</v>
       </c>
       <c r="X62" t="n">
-        <v>1.417808</v>
+        <v>1.471138</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.654451</v>
+        <v>0.706991</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.86264</v>
+        <v>1.581509</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.338065</v>
+        <v>1.149428</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.54679</v>
+        <v>-0.07734000000000001</v>
       </c>
       <c r="AC62" t="n">
-        <v>-6.090864</v>
+        <v>-4.193709</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5887,16 +5887,16 @@
         <v>209067</v>
       </c>
       <c r="C62" t="n">
-        <v>203.080002</v>
+        <v>205.550003</v>
       </c>
       <c r="D62" t="n">
-        <v>134.389999</v>
+        <v>139.800003</v>
       </c>
       <c r="E62" t="n">
-        <v>440.350006</v>
+        <v>439.25</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9772</v>
+        <v>4.9918</v>
       </c>
       <c r="G62" t="n">
         <v>5.5828</v>
@@ -5929,16 +5929,16 @@
         <v>12.196522</v>
       </c>
       <c r="Q62" t="n">
-        <v>10.321599</v>
+        <v>11.663408</v>
       </c>
       <c r="R62" t="n">
-        <v>20.066112</v>
+        <v>24.899493</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.569168</v>
+        <v>-1.815051</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.337964</v>
+        <v>-4.057355</v>
       </c>
       <c r="U62" t="n">
         <v>-5.315706</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5896,34 +5896,34 @@
         <v>439.25</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9918</v>
+        <v>4.9863</v>
       </c>
       <c r="G62" t="n">
-        <v>5.5828</v>
+        <v>5.5628</v>
       </c>
       <c r="H62" t="n">
-        <v>7811.540039</v>
+        <v>7801.430176</v>
       </c>
       <c r="I62" t="n">
-        <v>27366.169922</v>
+        <v>27238.013672</v>
       </c>
       <c r="J62" t="n">
-        <v>51654.949219</v>
+        <v>51815.429688</v>
       </c>
       <c r="K62" t="n">
-        <v>4216.299805</v>
+        <v>4188.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>91.849998</v>
+        <v>93.55999799999999</v>
       </c>
       <c r="M62" t="n">
-        <v>104.720001</v>
+        <v>106.470001</v>
       </c>
       <c r="N62" t="n">
-        <v>1292</v>
+        <v>1288.25</v>
       </c>
       <c r="O62" t="n">
-        <v>479.75</v>
+        <v>483.5</v>
       </c>
       <c r="P62" t="n">
         <v>12.196522</v>
@@ -5938,34 +5938,34 @@
         <v>-1.815051</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.057355</v>
+        <v>-4.163062</v>
       </c>
       <c r="U62" t="n">
-        <v>-5.315706</v>
+        <v>-5.654905</v>
       </c>
       <c r="V62" t="n">
-        <v>2.091082</v>
+        <v>1.958954</v>
       </c>
       <c r="W62" t="n">
-        <v>1.880452</v>
+        <v>1.403344</v>
       </c>
       <c r="X62" t="n">
-        <v>1.471138</v>
+        <v>1.786387</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.706991</v>
+        <v>0.040598</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.581509</v>
+        <v>3.472682</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.149428</v>
+        <v>2.839759</v>
       </c>
       <c r="AB62" t="n">
-        <v>-0.07734000000000001</v>
+        <v>-0.367363</v>
       </c>
       <c r="AC62" t="n">
-        <v>-4.193709</v>
+        <v>-3.444833</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5902,22 +5902,22 @@
         <v>5.5628</v>
       </c>
       <c r="H62" t="n">
-        <v>7801.430176</v>
+        <v>7805.220215</v>
       </c>
       <c r="I62" t="n">
-        <v>27238.013672</v>
+        <v>27254.84375</v>
       </c>
       <c r="J62" t="n">
-        <v>51815.429688</v>
+        <v>51821.851562</v>
       </c>
       <c r="K62" t="n">
-        <v>4188.399902</v>
+        <v>4192</v>
       </c>
       <c r="L62" t="n">
-        <v>93.55999799999999</v>
+        <v>93.540001</v>
       </c>
       <c r="M62" t="n">
-        <v>106.470001</v>
+        <v>106.489998</v>
       </c>
       <c r="N62" t="n">
         <v>1288.25</v>
@@ -5944,22 +5944,22 @@
         <v>-5.654905</v>
       </c>
       <c r="V62" t="n">
-        <v>1.958954</v>
+        <v>2.008487</v>
       </c>
       <c r="W62" t="n">
-        <v>1.403344</v>
+        <v>1.466</v>
       </c>
       <c r="X62" t="n">
-        <v>1.786387</v>
+        <v>1.799002</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.040598</v>
+        <v>0.126587</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.472682</v>
+        <v>3.450567</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.839759</v>
+        <v>2.859074</v>
       </c>
       <c r="AB62" t="n">
         <v>-0.367363</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>209067</v>
+        <v>206741.546875</v>
       </c>
       <c r="C62" t="n">
-        <v>205.550003</v>
+        <v>203.5</v>
       </c>
       <c r="D62" t="n">
-        <v>139.800003</v>
+        <v>135.210007</v>
       </c>
       <c r="E62" t="n">
-        <v>439.25</v>
+        <v>441.290009</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9863</v>
+        <v>5.0137</v>
       </c>
       <c r="G62" t="n">
-        <v>5.5628</v>
+        <v>5.6095</v>
       </c>
       <c r="H62" t="n">
-        <v>7805.220215</v>
+        <v>7797.970215</v>
       </c>
       <c r="I62" t="n">
-        <v>27254.84375</v>
+        <v>27187.478516</v>
       </c>
       <c r="J62" t="n">
-        <v>51821.851562</v>
+        <v>51644.039062</v>
       </c>
       <c r="K62" t="n">
-        <v>4192</v>
+        <v>4177.399902</v>
       </c>
       <c r="L62" t="n">
-        <v>93.540001</v>
+        <v>94.290001</v>
       </c>
       <c r="M62" t="n">
-        <v>106.489998</v>
+        <v>105.959999</v>
       </c>
       <c r="N62" t="n">
-        <v>1288.25</v>
+        <v>1284</v>
       </c>
       <c r="O62" t="n">
-        <v>483.5</v>
+        <v>482.5</v>
       </c>
       <c r="P62" t="n">
-        <v>12.196522</v>
+        <v>10.94856</v>
       </c>
       <c r="Q62" t="n">
-        <v>11.663408</v>
+        <v>10.54976</v>
       </c>
       <c r="R62" t="n">
-        <v>24.899493</v>
+        <v>20.798719</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.815051</v>
+        <v>-1.359051</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.163062</v>
+        <v>-3.636432</v>
       </c>
       <c r="U62" t="n">
-        <v>-5.654905</v>
+        <v>-4.862873</v>
       </c>
       <c r="V62" t="n">
-        <v>2.008487</v>
+        <v>1.913735</v>
       </c>
       <c r="W62" t="n">
-        <v>1.466</v>
+        <v>1.215209</v>
       </c>
       <c r="X62" t="n">
-        <v>1.799002</v>
+        <v>1.449706</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.126587</v>
+        <v>-0.222139</v>
       </c>
       <c r="Z62" t="n">
-        <v>3.450567</v>
+        <v>4.28003</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.859074</v>
+        <v>2.347146</v>
       </c>
       <c r="AB62" t="n">
-        <v>-0.367363</v>
+        <v>-0.696056</v>
       </c>
       <c r="AC62" t="n">
-        <v>-3.444833</v>
+        <v>-3.644533</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>206741.546875</v>
+        <v>204498.546875</v>
       </c>
       <c r="C62" t="n">
-        <v>203.5</v>
+        <v>201.429993</v>
       </c>
       <c r="D62" t="n">
-        <v>135.210007</v>
+        <v>131.199997</v>
       </c>
       <c r="E62" t="n">
-        <v>441.290009</v>
+        <v>441.929993</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0137</v>
+        <v>5.0395</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6095</v>
+        <v>5.6045</v>
       </c>
       <c r="H62" t="n">
-        <v>7797.970215</v>
+        <v>7748.819824</v>
       </c>
       <c r="I62" t="n">
-        <v>27187.478516</v>
+        <v>26954.634766</v>
       </c>
       <c r="J62" t="n">
-        <v>51644.039062</v>
+        <v>51627.679688</v>
       </c>
       <c r="K62" t="n">
-        <v>4177.399902</v>
+        <v>4118.200195</v>
       </c>
       <c r="L62" t="n">
-        <v>94.290001</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>105.959999</v>
+        <v>105.910004</v>
       </c>
       <c r="N62" t="n">
-        <v>1284</v>
+        <v>1278</v>
       </c>
       <c r="O62" t="n">
-        <v>482.5</v>
+        <v>480</v>
       </c>
       <c r="P62" t="n">
-        <v>10.94856</v>
+        <v>9.744846000000001</v>
       </c>
       <c r="Q62" t="n">
-        <v>10.54976</v>
+        <v>9.425245</v>
       </c>
       <c r="R62" t="n">
-        <v>20.798719</v>
+        <v>17.216114</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.359051</v>
+        <v>-1.215996</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.636432</v>
+        <v>-3.14055</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.862873</v>
+        <v>-4.947675</v>
       </c>
       <c r="V62" t="n">
-        <v>1.913735</v>
+        <v>1.271375</v>
       </c>
       <c r="W62" t="n">
-        <v>1.215209</v>
+        <v>0.348364</v>
       </c>
       <c r="X62" t="n">
-        <v>1.449706</v>
+        <v>1.41757</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.222139</v>
+        <v>-1.636133</v>
       </c>
       <c r="Z62" t="n">
-        <v>4.28003</v>
+        <v>5.419157</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.347146</v>
+        <v>2.298855</v>
       </c>
       <c r="AB62" t="n">
-        <v>-0.696056</v>
+        <v>-1.160093</v>
       </c>
       <c r="AC62" t="n">
-        <v>-3.644533</v>
+        <v>-4.143784</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>204498.546875</v>
+        <v>204599.5</v>
       </c>
       <c r="C62" t="n">
-        <v>201.429993</v>
+        <v>201.509995</v>
       </c>
       <c r="D62" t="n">
-        <v>131.199997</v>
+        <v>130.940002</v>
       </c>
       <c r="E62" t="n">
-        <v>441.929993</v>
+        <v>441.399994</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0395</v>
+        <v>5.0385</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6045</v>
+        <v>5.607</v>
       </c>
       <c r="H62" t="n">
-        <v>7748.819824</v>
+        <v>7748.359863</v>
       </c>
       <c r="I62" t="n">
-        <v>26954.634766</v>
+        <v>26941.662109</v>
       </c>
       <c r="J62" t="n">
-        <v>51627.679688</v>
+        <v>51619.429688</v>
       </c>
       <c r="K62" t="n">
-        <v>4118.200195</v>
+        <v>4125.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>95.31999999999999</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>105.910004</v>
+        <v>105.650002</v>
       </c>
       <c r="N62" t="n">
-        <v>1278</v>
+        <v>1278.25</v>
       </c>
       <c r="O62" t="n">
-        <v>480</v>
+        <v>479.75</v>
       </c>
       <c r="P62" t="n">
-        <v>9.744846000000001</v>
+        <v>9.799023</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.425245</v>
+        <v>9.468705</v>
       </c>
       <c r="R62" t="n">
-        <v>17.216114</v>
+        <v>16.983831</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.215996</v>
+        <v>-1.334466</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.14055</v>
+        <v>-3.159778</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.947675</v>
+        <v>-4.905274</v>
       </c>
       <c r="V62" t="n">
-        <v>1.271375</v>
+        <v>1.265364</v>
       </c>
       <c r="W62" t="n">
-        <v>0.348364</v>
+        <v>0.300068</v>
       </c>
       <c r="X62" t="n">
-        <v>1.41757</v>
+        <v>1.401364</v>
       </c>
       <c r="Y62" t="n">
-        <v>-1.636133</v>
+        <v>-1.466558</v>
       </c>
       <c r="Z62" t="n">
-        <v>5.419157</v>
+        <v>4.987837</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.298855</v>
+        <v>2.047718</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.160093</v>
+        <v>-1.140758</v>
       </c>
       <c r="AC62" t="n">
-        <v>-4.143784</v>
+        <v>-4.193709</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>204599.5</v>
+        <v>205512.375</v>
       </c>
       <c r="C62" t="n">
-        <v>201.509995</v>
+        <v>202.300003</v>
       </c>
       <c r="D62" t="n">
-        <v>130.940002</v>
+        <v>132.309998</v>
       </c>
       <c r="E62" t="n">
-        <v>441.399994</v>
+        <v>438.640015</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0385</v>
+        <v>5.0463</v>
       </c>
       <c r="G62" t="n">
-        <v>5.607</v>
+        <v>5.6621</v>
       </c>
       <c r="H62" t="n">
-        <v>7748.359863</v>
+        <v>7697.810059</v>
       </c>
       <c r="I62" t="n">
-        <v>26941.662109</v>
+        <v>26452.943359</v>
       </c>
       <c r="J62" t="n">
-        <v>51619.429688</v>
+        <v>51953.851562</v>
       </c>
       <c r="K62" t="n">
-        <v>4125.299805</v>
+        <v>4180.600098</v>
       </c>
       <c r="L62" t="n">
-        <v>94.93000000000001</v>
+        <v>95.040001</v>
       </c>
       <c r="M62" t="n">
-        <v>105.650002</v>
+        <v>105.209999</v>
       </c>
       <c r="N62" t="n">
-        <v>1278.25</v>
+        <v>1274.75</v>
       </c>
       <c r="O62" t="n">
-        <v>479.75</v>
+        <v>480.25</v>
       </c>
       <c r="P62" t="n">
-        <v>9.799023</v>
+        <v>10.288921</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.468705</v>
+        <v>9.897871</v>
       </c>
       <c r="R62" t="n">
-        <v>16.983831</v>
+        <v>18.207806</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.334466</v>
+        <v>-1.951401</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.159778</v>
+        <v>-3.00986</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.905274</v>
+        <v>-3.970779</v>
       </c>
       <c r="V62" t="n">
-        <v>1.265364</v>
+        <v>0.604715</v>
       </c>
       <c r="W62" t="n">
-        <v>0.300068</v>
+        <v>-1.519364</v>
       </c>
       <c r="X62" t="n">
-        <v>1.401364</v>
+        <v>2.058303</v>
       </c>
       <c r="Y62" t="n">
-        <v>-1.466558</v>
+        <v>-0.145702</v>
       </c>
       <c r="Z62" t="n">
-        <v>4.987837</v>
+        <v>5.109492</v>
       </c>
       <c r="AA62" t="n">
-        <v>2.047718</v>
+        <v>1.622718</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.140758</v>
+        <v>-1.411446</v>
       </c>
       <c r="AC62" t="n">
-        <v>-4.193709</v>
+        <v>-4.093859</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>205512.375</v>
+        <v>205726.09375</v>
       </c>
       <c r="C62" t="n">
-        <v>202.300003</v>
+        <v>202.639999</v>
       </c>
       <c r="D62" t="n">
-        <v>132.309998</v>
+        <v>131.389999</v>
       </c>
       <c r="E62" t="n">
-        <v>438.640015</v>
+        <v>443.209991</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0463</v>
+        <v>5.0767</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6621</v>
+        <v>5.7122</v>
       </c>
       <c r="H62" t="n">
-        <v>7697.810059</v>
+        <v>7733.080078</v>
       </c>
       <c r="I62" t="n">
-        <v>26452.943359</v>
+        <v>26499.583984</v>
       </c>
       <c r="J62" t="n">
-        <v>51953.851562</v>
+        <v>52400.160156</v>
       </c>
       <c r="K62" t="n">
-        <v>4180.600098</v>
+        <v>4207.799805</v>
       </c>
       <c r="L62" t="n">
-        <v>95.040001</v>
+        <v>95.589996</v>
       </c>
       <c r="M62" t="n">
-        <v>105.209999</v>
+        <v>105.459999</v>
       </c>
       <c r="N62" t="n">
-        <v>1274.75</v>
+        <v>1253.75</v>
       </c>
       <c r="O62" t="n">
-        <v>480.25</v>
+        <v>473.75</v>
       </c>
       <c r="P62" t="n">
-        <v>10.288921</v>
+        <v>10.403614</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.897871</v>
+        <v>10.082571</v>
       </c>
       <c r="R62" t="n">
-        <v>18.207806</v>
+        <v>17.385865</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.951401</v>
+        <v>-0.92988</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.00986</v>
+        <v>-2.425565</v>
       </c>
       <c r="U62" t="n">
-        <v>-3.970779</v>
+        <v>-3.121077</v>
       </c>
       <c r="V62" t="n">
-        <v>0.604715</v>
+        <v>1.065668</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.519364</v>
+        <v>-1.345727</v>
       </c>
       <c r="X62" t="n">
-        <v>2.058303</v>
+        <v>2.935033</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.145702</v>
+        <v>0.503968</v>
       </c>
       <c r="Z62" t="n">
-        <v>5.109492</v>
+        <v>5.71776</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.622718</v>
+        <v>1.864194</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.411446</v>
+        <v>-3.035576</v>
       </c>
       <c r="AC62" t="n">
-        <v>-4.093859</v>
+        <v>-5.391912</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>205726.09375</v>
+        <v>205430</v>
       </c>
       <c r="C62" t="n">
-        <v>202.639999</v>
+        <v>201.389999</v>
       </c>
       <c r="D62" t="n">
-        <v>131.389999</v>
+        <v>130.830002</v>
       </c>
       <c r="E62" t="n">
-        <v>443.209991</v>
+        <v>444.450012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0767</v>
+        <v>5.0693</v>
       </c>
       <c r="G62" t="n">
-        <v>5.7122</v>
+        <v>5.7053</v>
       </c>
       <c r="H62" t="n">
-        <v>7733.080078</v>
+        <v>7659.439941</v>
       </c>
       <c r="I62" t="n">
-        <v>26499.583984</v>
+        <v>26140.029297</v>
       </c>
       <c r="J62" t="n">
-        <v>52400.160156</v>
+        <v>52002.410156</v>
       </c>
       <c r="K62" t="n">
-        <v>4207.799805</v>
+        <v>4181.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>95.589996</v>
+        <v>101.410004</v>
       </c>
       <c r="M62" t="n">
-        <v>105.459999</v>
+        <v>109.860001</v>
       </c>
       <c r="N62" t="n">
-        <v>1253.75</v>
+        <v>1261.25</v>
       </c>
       <c r="O62" t="n">
-        <v>473.75</v>
+        <v>474.25</v>
       </c>
       <c r="P62" t="n">
-        <v>10.403614</v>
+        <v>10.244714</v>
       </c>
       <c r="Q62" t="n">
-        <v>10.082571</v>
+        <v>9.403518999999999</v>
       </c>
       <c r="R62" t="n">
-        <v>17.385865</v>
+        <v>16.885555</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.92988</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.425565</v>
+        <v>-2.567794</v>
       </c>
       <c r="U62" t="n">
-        <v>-3.121077</v>
+        <v>-3.238106</v>
       </c>
       <c r="V62" t="n">
-        <v>1.065668</v>
+        <v>0.103246</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.345727</v>
+        <v>-2.684299</v>
       </c>
       <c r="X62" t="n">
-        <v>2.935033</v>
+        <v>2.153692</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.503968</v>
+        <v>-0.133759</v>
       </c>
       <c r="Z62" t="n">
-        <v>5.71776</v>
+        <v>12.154397</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.864194</v>
+        <v>6.114172</v>
       </c>
       <c r="AB62" t="n">
-        <v>-3.035576</v>
+        <v>-2.45553</v>
       </c>
       <c r="AC62" t="n">
-        <v>-5.391912</v>
+        <v>-5.292062</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -586,9 +586,7 @@
       <c r="F2" t="n">
         <v>5.6449</v>
       </c>
-      <c r="G2" t="n">
-        <v>6.593</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>4605.379883</v>
       </c>
@@ -647,9 +645,7 @@
       <c r="F3" t="n">
         <v>5.6007</v>
       </c>
-      <c r="G3" t="n">
-        <v>6.3223</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>4567</v>
       </c>
@@ -689,9 +685,7 @@
       <c r="T3" t="n">
         <v>-0.783007</v>
       </c>
-      <c r="U3" t="n">
-        <v>-4.10587</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
         <v>-0.833371</v>
       </c>
@@ -736,9 +730,7 @@
       <c r="F4" t="n">
         <v>5.5702</v>
       </c>
-      <c r="G4" t="n">
-        <v>6.3049</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>4766.180176</v>
       </c>
@@ -778,9 +770,7 @@
       <c r="T4" t="n">
         <v>-0.544574</v>
       </c>
-      <c r="U4" t="n">
-        <v>-0.275213</v>
-      </c>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
         <v>4.361291</v>
       </c>
@@ -825,9 +815,7 @@
       <c r="F5" t="n">
         <v>5.3626</v>
       </c>
-      <c r="G5" t="n">
-        <v>5.9782</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>4515.549805</v>
       </c>
@@ -867,9 +855,7 @@
       <c r="T5" t="n">
         <v>-3.726978</v>
       </c>
-      <c r="U5" t="n">
-        <v>-5.181687</v>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
         <v>-5.258517</v>
       </c>
@@ -914,9 +900,7 @@
       <c r="F6" t="n">
         <v>5.1594</v>
       </c>
-      <c r="G6" t="n">
-        <v>5.814</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>4373.939941</v>
       </c>
@@ -956,9 +940,7 @@
       <c r="T6" t="n">
         <v>-3.789204</v>
       </c>
-      <c r="U6" t="n">
-        <v>-2.746643</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
         <v>-3.136049</v>
       </c>
@@ -1003,9 +985,7 @@
       <c r="F7" t="n">
         <v>4.7697</v>
       </c>
-      <c r="G7" t="n">
-        <v>5.3198</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>4530.410156</v>
       </c>
@@ -1045,9 +1025,7 @@
       <c r="T7" t="n">
         <v>-7.553203</v>
       </c>
-      <c r="U7" t="n">
-        <v>-8.500176</v>
-      </c>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
         <v>3.577329</v>
       </c>
@@ -1092,9 +1070,7 @@
       <c r="F8" t="n">
         <v>4.9378</v>
       </c>
-      <c r="G8" t="n">
-        <v>5.1837</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>4131.930176</v>
       </c>
@@ -1134,9 +1110,7 @@
       <c r="T8" t="n">
         <v>3.524328</v>
       </c>
-      <c r="U8" t="n">
-        <v>-2.558363</v>
-      </c>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
         <v>-8.795671</v>
       </c>
@@ -1181,9 +1155,7 @@
       <c r="F9" t="n">
         <v>4.7524</v>
       </c>
-      <c r="G9" t="n">
-        <v>5.1176</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>4132.149902</v>
       </c>
@@ -1223,9 +1195,7 @@
       <c r="T9" t="n">
         <v>-3.754709</v>
       </c>
-      <c r="U9" t="n">
-        <v>-1.275153</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
         <v>0.005318</v>
       </c>
@@ -1270,9 +1240,7 @@
       <c r="F10" t="n">
         <v>5.1809</v>
       </c>
-      <c r="G10" t="n">
-        <v>5.4098</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>3785.379883</v>
       </c>
@@ -1312,9 +1280,7 @@
       <c r="T10" t="n">
         <v>9.016501</v>
       </c>
-      <c r="U10" t="n">
-        <v>5.709709</v>
-      </c>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
         <v>-8.391999999999999</v>
       </c>
@@ -1359,9 +1325,7 @@
       <c r="F11" t="n">
         <v>5.1827</v>
       </c>
-      <c r="G11" t="n">
-        <v>5.2797</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>4130.290039</v>
       </c>
@@ -1401,9 +1365,7 @@
       <c r="T11" t="n">
         <v>0.034744</v>
       </c>
-      <c r="U11" t="n">
-        <v>-2.404899</v>
-      </c>
+      <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
         <v>9.111639</v>
       </c>
@@ -1448,9 +1410,7 @@
       <c r="F12" t="n">
         <v>5.1219</v>
       </c>
-      <c r="G12" t="n">
-        <v>5.1318</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3955</v>
       </c>
@@ -1490,9 +1450,7 @@
       <c r="T12" t="n">
         <v>-1.173135</v>
       </c>
-      <c r="U12" t="n">
-        <v>-2.801289</v>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
         <v>-4.244013</v>
       </c>
@@ -1537,9 +1495,7 @@
       <c r="F13" t="n">
         <v>5.3962</v>
       </c>
-      <c r="G13" t="n">
-        <v>5.3031</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3585.620117</v>
       </c>
@@ -1579,9 +1535,7 @@
       <c r="T13" t="n">
         <v>5.355436</v>
       </c>
-      <c r="U13" t="n">
-        <v>3.338009</v>
-      </c>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
         <v>-9.339567000000001</v>
       </c>
@@ -1626,9 +1580,7 @@
       <c r="F14" t="n">
         <v>5.2885</v>
       </c>
-      <c r="G14" t="n">
-        <v>5.2737</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3871.97998</v>
       </c>
@@ -1668,9 +1620,7 @@
       <c r="T14" t="n">
         <v>-1.995855</v>
       </c>
-      <c r="U14" t="n">
-        <v>-0.55439</v>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
         <v>7.986341</v>
       </c>
@@ -1715,9 +1665,7 @@
       <c r="F15" t="n">
         <v>5.2682</v>
       </c>
-      <c r="G15" t="n">
-        <v>5.4362</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>4080.110107</v>
       </c>
@@ -1757,9 +1705,7 @@
       <c r="T15" t="n">
         <v>-0.38385</v>
       </c>
-      <c r="U15" t="n">
-        <v>3.081326</v>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
         <v>5.375289</v>
       </c>
@@ -1804,9 +1750,7 @@
       <c r="F16" t="n">
         <v>5.2846</v>
       </c>
-      <c r="G16" t="n">
-        <v>5.633</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>3839.5</v>
       </c>
@@ -1846,9 +1790,7 @@
       <c r="T16" t="n">
         <v>0.311299</v>
       </c>
-      <c r="U16" t="n">
-        <v>3.620171</v>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
         <v>-5.897147</v>
       </c>
@@ -1893,9 +1835,7 @@
       <c r="F17" t="n">
         <v>5.1149</v>
       </c>
-      <c r="G17" t="n">
-        <v>5.5471</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>4076.600098</v>
       </c>
@@ -1935,9 +1875,7 @@
       <c r="T17" t="n">
         <v>-3.211211</v>
       </c>
-      <c r="U17" t="n">
-        <v>-1.524939</v>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
         <v>6.175286</v>
       </c>
@@ -1982,9 +1920,7 @@
       <c r="F18" t="n">
         <v>5.1997</v>
       </c>
-      <c r="G18" t="n">
-        <v>5.514</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>3970.149902</v>
       </c>
@@ -2024,9 +1960,7 @@
       <c r="T18" t="n">
         <v>1.657897</v>
       </c>
-      <c r="U18" t="n">
-        <v>-0.59671</v>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
         <v>-2.611249</v>
       </c>
@@ -2071,9 +2005,7 @@
       <c r="F19" t="n">
         <v>5.0927</v>
       </c>
-      <c r="G19" t="n">
-        <v>5.5518</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>4109.310059</v>
       </c>
@@ -2113,9 +2045,7 @@
       <c r="T19" t="n">
         <v>-2.057809</v>
       </c>
-      <c r="U19" t="n">
-        <v>0.6855250000000001</v>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
         <v>3.505161</v>
       </c>
@@ -2160,9 +2090,7 @@
       <c r="F20" t="n">
         <v>4.9762</v>
       </c>
-      <c r="G20" t="n">
-        <v>5.4883</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>4169.47998</v>
       </c>
@@ -2202,9 +2130,7 @@
       <c r="T20" t="n">
         <v>-2.287586</v>
       </c>
-      <c r="U20" t="n">
-        <v>-1.143772</v>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
         <v>1.464234</v>
       </c>
@@ -2249,9 +2175,7 @@
       <c r="F21" t="n">
         <v>5.0348</v>
       </c>
-      <c r="G21" t="n">
-        <v>5.4012</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>4179.830078</v>
       </c>
@@ -2291,9 +2215,7 @@
       <c r="T21" t="n">
         <v>1.177604</v>
       </c>
-      <c r="U21" t="n">
-        <v>-1.587013</v>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
         <v>0.248235</v>
       </c>
@@ -2338,9 +2260,7 @@
       <c r="F22" t="n">
         <v>4.8556</v>
       </c>
-      <c r="G22" t="n">
-        <v>5.2739</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>4450.379883</v>
       </c>
@@ -2380,9 +2300,7 @@
       <c r="T22" t="n">
         <v>-3.559231</v>
       </c>
-      <c r="U22" t="n">
-        <v>-2.35688</v>
-      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
         <v>6.472746</v>
       </c>
@@ -2427,9 +2345,7 @@
       <c r="F23" t="n">
         <v>4.7233</v>
       </c>
-      <c r="G23" t="n">
-        <v>5.1895</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>4588.959961</v>
       </c>
@@ -2469,9 +2385,7 @@
       <c r="T23" t="n">
         <v>-2.724687</v>
       </c>
-      <c r="U23" t="n">
-        <v>-1.600337</v>
-      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
         <v>3.113893</v>
       </c>
@@ -2516,9 +2430,7 @@
       <c r="F24" t="n">
         <v>4.8884</v>
       </c>
-      <c r="G24" t="n">
-        <v>5.313</v>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>4507.660156</v>
       </c>
@@ -2558,9 +2470,7 @@
       <c r="T24" t="n">
         <v>3.49544</v>
       </c>
-      <c r="U24" t="n">
-        <v>2.379812</v>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
         <v>-1.771639</v>
       </c>
@@ -2605,9 +2515,7 @@
       <c r="F25" t="n">
         <v>5.0328</v>
       </c>
-      <c r="G25" t="n">
-        <v>5.3197</v>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>4288.049805</v>
       </c>
@@ -2647,9 +2555,7 @@
       <c r="T25" t="n">
         <v>2.953934</v>
       </c>
-      <c r="U25" t="n">
-        <v>0.126098</v>
-      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
         <v>-4.871937</v>
       </c>
@@ -2694,9 +2600,7 @@
       <c r="F26" t="n">
         <v>5.0461</v>
       </c>
-      <c r="G26" t="n">
-        <v>5.3537</v>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>4193.799805</v>
       </c>
@@ -2736,9 +2640,7 @@
       <c r="T26" t="n">
         <v>0.264265</v>
       </c>
-      <c r="U26" t="n">
-        <v>0.639141</v>
-      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
         <v>-2.197969</v>
       </c>
@@ -2783,9 +2685,7 @@
       <c r="F27" t="n">
         <v>4.9041</v>
       </c>
-      <c r="G27" t="n">
-        <v>5.3628</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>4567.799805</v>
       </c>
@@ -2825,9 +2725,7 @@
       <c r="T27" t="n">
         <v>-2.814058</v>
       </c>
-      <c r="U27" t="n">
-        <v>0.169975</v>
-      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
         <v>8.917927000000001</v>
       </c>
@@ -2872,9 +2770,7 @@
       <c r="F28" t="n">
         <v>4.8502</v>
       </c>
-      <c r="G28" t="n">
-        <v>5.343</v>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>4769.830078</v>
       </c>
@@ -2914,9 +2810,7 @@
       <c r="T28" t="n">
         <v>-1.099076</v>
       </c>
-      <c r="U28" t="n">
-        <v>-0.369214</v>
-      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
         <v>4.422923</v>
       </c>
@@ -2961,9 +2855,7 @@
       <c r="F29" t="n">
         <v>4.9503</v>
       </c>
-      <c r="G29" t="n">
-        <v>5.3604</v>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>4845.649902</v>
       </c>
@@ -3003,9 +2895,7 @@
       <c r="T29" t="n">
         <v>2.063833</v>
       </c>
-      <c r="U29" t="n">
-        <v>0.325665</v>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
         <v>1.589571</v>
       </c>
@@ -3050,9 +2940,7 @@
       <c r="F30" t="n">
         <v>4.9673</v>
       </c>
-      <c r="G30" t="n">
-        <v>5.381</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>5096.27002</v>
       </c>
@@ -3092,9 +2980,7 @@
       <c r="T30" t="n">
         <v>0.343408</v>
       </c>
-      <c r="U30" t="n">
-        <v>0.384297</v>
-      </c>
+      <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
         <v>5.172064</v>
       </c>
@@ -3139,9 +3025,7 @@
       <c r="F31" t="n">
         <v>5.0141</v>
       </c>
-      <c r="G31" t="n">
-        <v>5.4065</v>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>5254.350098</v>
       </c>
@@ -3181,9 +3065,7 @@
       <c r="T31" t="n">
         <v>0.942164</v>
       </c>
-      <c r="U31" t="n">
-        <v>0.473886</v>
-      </c>
+      <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
         <v>3.101878</v>
       </c>
@@ -3228,9 +3110,7 @@
       <c r="F32" t="n">
         <v>5.117</v>
       </c>
-      <c r="G32" t="n">
-        <v>5.4794</v>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>5035.689941</v>
       </c>
@@ -3270,9 +3150,7 @@
       <c r="T32" t="n">
         <v>2.052213</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.348382</v>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
         <v>-4.161507</v>
       </c>
@@ -3317,9 +3195,7 @@
       <c r="F33" t="n">
         <v>5.2021</v>
       </c>
-      <c r="G33" t="n">
-        <v>5.6311</v>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>5277.509766</v>
       </c>
@@ -3359,9 +3235,7 @@
       <c r="T33" t="n">
         <v>1.663078</v>
       </c>
-      <c r="U33" t="n">
-        <v>2.768552</v>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
         <v>4.802119</v>
       </c>
@@ -3406,9 +3280,7 @@
       <c r="F34" t="n">
         <v>5.5005</v>
       </c>
-      <c r="G34" t="n">
-        <v>5.8909</v>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>5460.47998</v>
       </c>
@@ -3448,9 +3320,7 @@
       <c r="T34" t="n">
         <v>5.736153</v>
       </c>
-      <c r="U34" t="n">
-        <v>4.613663</v>
-      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
         <v>3.46698</v>
       </c>
@@ -3495,9 +3365,7 @@
       <c r="F35" t="n">
         <v>5.6111</v>
       </c>
-      <c r="G35" t="n">
-        <v>6.0695</v>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>5522.299805</v>
       </c>
@@ -3537,9 +3405,7 @@
       <c r="T35" t="n">
         <v>2.010726</v>
       </c>
-      <c r="U35" t="n">
-        <v>3.031792</v>
-      </c>
+      <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
         <v>1.132132</v>
       </c>
@@ -3584,9 +3450,7 @@
       <c r="F36" t="n">
         <v>5.6277</v>
       </c>
-      <c r="G36" t="n">
-        <v>6.2224</v>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>5648.399902</v>
       </c>
@@ -3626,9 +3490,7 @@
       <c r="T36" t="n">
         <v>0.295836</v>
       </c>
-      <c r="U36" t="n">
-        <v>2.519157</v>
-      </c>
+      <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
         <v>2.283471</v>
       </c>
@@ -3673,9 +3535,7 @@
       <c r="F37" t="n">
         <v>5.4332</v>
       </c>
-      <c r="G37" t="n">
-        <v>6.0652</v>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>5762.47998</v>
       </c>
@@ -3715,9 +3575,7 @@
       <c r="T37" t="n">
         <v>-3.456118</v>
       </c>
-      <c r="U37" t="n">
-        <v>-2.526362</v>
-      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
         <v>2.019688</v>
       </c>
@@ -3762,9 +3620,7 @@
       <c r="F38" t="n">
         <v>5.7623</v>
       </c>
-      <c r="G38" t="n">
-        <v>6.2522</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>5705.450195</v>
       </c>
@@ -3804,9 +3660,7 @@
       <c r="T38" t="n">
         <v>6.057206</v>
       </c>
-      <c r="U38" t="n">
-        <v>3.083168</v>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
         <v>-0.9896740000000001</v>
       </c>
@@ -3851,9 +3705,7 @@
       <c r="F39" t="n">
         <v>6.0139</v>
       </c>
-      <c r="G39" t="n">
-        <v>6.345178</v>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>6032.379883</v>
       </c>
@@ -3893,9 +3745,7 @@
       <c r="T39" t="n">
         <v>4.366308</v>
       </c>
-      <c r="U39" t="n">
-        <v>1.487125</v>
-      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
         <v>5.73013</v>
       </c>
@@ -3940,9 +3790,7 @@
       <c r="F40" t="n">
         <v>6.1779</v>
       </c>
-      <c r="G40" t="n">
-        <v>6.422608</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>5881.629883</v>
       </c>
@@ -3982,9 +3830,7 @@
       <c r="T40" t="n">
         <v>2.727016</v>
       </c>
-      <c r="U40" t="n">
-        <v>1.220293</v>
-      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
         <v>-2.499014</v>
       </c>
@@ -4029,9 +3875,7 @@
       <c r="F41" t="n">
         <v>5.8745</v>
       </c>
-      <c r="G41" t="n">
-        <v>6.101281</v>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>6040.529785</v>
       </c>
@@ -4071,9 +3915,7 @@
       <c r="T41" t="n">
         <v>-4.911055</v>
       </c>
-      <c r="U41" t="n">
-        <v>-5.003057</v>
-      </c>
+      <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
         <v>2.70163</v>
       </c>
@@ -4118,9 +3960,7 @@
       <c r="F42" t="n">
         <v>5.839</v>
       </c>
-      <c r="G42" t="n">
-        <v>6.064281</v>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>5954.5</v>
       </c>
@@ -4160,9 +4000,7 @@
       <c r="T42" t="n">
         <v>-0.604299</v>
       </c>
-      <c r="U42" t="n">
-        <v>-0.606433</v>
-      </c>
+      <c r="U42" t="inlineStr"/>
       <c r="V42" t="n">
         <v>-1.424209</v>
       </c>
@@ -4207,9 +4045,7 @@
       <c r="F43" t="n">
         <v>5.7581</v>
       </c>
-      <c r="G43" t="n">
-        <v>6.22665</v>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>5611.850098</v>
       </c>
@@ -4249,9 +4085,7 @@
       <c r="T43" t="n">
         <v>-1.385514</v>
       </c>
-      <c r="U43" t="n">
-        <v>2.677469</v>
-      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
         <v>-5.75447</v>
       </c>
@@ -4296,9 +4130,7 @@
       <c r="F44" t="n">
         <v>5.62</v>
       </c>
-      <c r="G44" t="n">
-        <v>6.393862</v>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>5569.060059</v>
       </c>
@@ -4338,9 +4170,7 @@
       <c r="T44" t="n">
         <v>-2.398363</v>
       </c>
-      <c r="U44" t="n">
-        <v>2.685417</v>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="n">
         <v>-0.762494</v>
       </c>
@@ -4385,9 +4215,7 @@
       <c r="F45" t="n">
         <v>5.6651</v>
       </c>
-      <c r="G45" t="n">
-        <v>6.43915</v>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>5911.689941</v>
       </c>
@@ -4427,9 +4255,7 @@
       <c r="T45" t="n">
         <v>0.802495</v>
       </c>
-      <c r="U45" t="n">
-        <v>0.708306</v>
-      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="n">
         <v>6.152383</v>
       </c>
@@ -4474,9 +4300,7 @@
       <c r="F46" t="n">
         <v>5.4784</v>
       </c>
-      <c r="G46" t="n">
-        <v>6.418485</v>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>6204.950195</v>
       </c>
@@ -4516,9 +4340,7 @@
       <c r="T46" t="n">
         <v>-3.295615</v>
       </c>
-      <c r="U46" t="n">
-        <v>-0.320923</v>
-      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="n">
         <v>4.960684</v>
       </c>
@@ -4563,9 +4385,7 @@
       <c r="F47" t="n">
         <v>5.5754</v>
       </c>
-      <c r="G47" t="n">
-        <v>6.365372</v>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>6339.390137</v>
       </c>
@@ -4605,9 +4425,7 @@
       <c r="T47" t="n">
         <v>1.770583</v>
       </c>
-      <c r="U47" t="n">
-        <v>-0.8275</v>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="n">
         <v>2.166656</v>
       </c>
@@ -4652,9 +4470,7 @@
       <c r="F48" t="n">
         <v>5.413</v>
       </c>
-      <c r="G48" t="n">
-        <v>6.317119</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>6460.259766</v>
       </c>
@@ -4694,9 +4510,7 @@
       <c r="T48" t="n">
         <v>-2.912791</v>
       </c>
-      <c r="U48" t="n">
-        <v>-0.758056</v>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="n">
         <v>1.906644</v>
       </c>
@@ -4741,9 +4555,7 @@
       <c r="F49" t="n">
         <v>5.3217</v>
       </c>
-      <c r="G49" t="n">
-        <v>6.238303</v>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>6688.459961</v>
       </c>
@@ -4783,9 +4595,7 @@
       <c r="T49" t="n">
         <v>-1.68668</v>
       </c>
-      <c r="U49" t="n">
-        <v>-1.247656</v>
-      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="n">
         <v>3.532369</v>
       </c>
@@ -4830,9 +4640,7 @@
       <c r="F50" t="n">
         <v>5.382</v>
       </c>
-      <c r="G50" t="n">
-        <v>6.222775</v>
-      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>6840.200195</v>
       </c>
@@ -4872,9 +4680,7 @@
       <c r="T50" t="n">
         <v>1.133094</v>
       </c>
-      <c r="U50" t="n">
-        <v>-0.248917</v>
-      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="n">
         <v>2.268687</v>
       </c>
@@ -4919,9 +4725,7 @@
       <c r="F51" t="n">
         <v>5.3554</v>
       </c>
-      <c r="G51" t="n">
-        <v>6.207325</v>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>6849.089844</v>
       </c>
@@ -4961,9 +4765,7 @@
       <c r="T51" t="n">
         <v>-0.494238</v>
       </c>
-      <c r="U51" t="n">
-        <v>-0.248282</v>
-      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="n">
         <v>0.129962</v>
       </c>
@@ -5008,9 +4810,7 @@
       <c r="F52" t="n">
         <v>5.4762</v>
       </c>
-      <c r="G52" t="n">
-        <v>6.426735</v>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>6845.5</v>
       </c>
@@ -5050,9 +4850,7 @@
       <c r="T52" t="n">
         <v>2.255667</v>
       </c>
-      <c r="U52" t="n">
-        <v>3.534694</v>
-      </c>
+      <c r="U52" t="inlineStr"/>
       <c r="V52" t="n">
         <v>-0.052413</v>
       </c>
@@ -5097,9 +4895,7 @@
       <c r="F53" t="n">
         <v>5.1892</v>
       </c>
-      <c r="G53" t="n">
-        <v>6.203474</v>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>6939.029785</v>
       </c>
@@ -5139,9 +4935,7 @@
       <c r="T53" t="n">
         <v>-5.240864</v>
       </c>
-      <c r="U53" t="n">
-        <v>-3.473939</v>
-      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="n">
         <v>1.366296</v>
       </c>
@@ -5186,9 +4980,7 @@
       <c r="F54" t="n">
         <v>5.1366</v>
       </c>
-      <c r="G54" t="n">
-        <v>6.056935</v>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>6878.879883</v>
       </c>
@@ -5228,9 +5020,7 @@
       <c r="T54" t="n">
         <v>-1.013642</v>
       </c>
-      <c r="U54" t="n">
-        <v>-2.362212</v>
-      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="n">
         <v>-0.866834</v>
       </c>
@@ -5275,9 +5065,7 @@
       <c r="F55" t="n">
         <v>5.264</v>
       </c>
-      <c r="G55" t="n">
-        <v>6.027728</v>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>6528.52002</v>
       </c>
@@ -5317,9 +5105,7 @@
       <c r="T55" t="n">
         <v>2.480238</v>
       </c>
-      <c r="U55" t="n">
-        <v>-0.482204</v>
-      </c>
+      <c r="U55" t="inlineStr"/>
       <c r="V55" t="n">
         <v>-5.093269</v>
       </c>
@@ -5364,9 +5150,7 @@
       <c r="F56" t="n">
         <v>5.0175</v>
       </c>
-      <c r="G56" t="n">
-        <v>5.858231</v>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>7209.009766</v>
       </c>
@@ -5406,9 +5190,7 @@
       <c r="T56" t="n">
         <v>-4.682751</v>
       </c>
-      <c r="U56" t="n">
-        <v>-2.811955</v>
-      </c>
+      <c r="U56" t="inlineStr"/>
       <c r="V56" t="n">
         <v>10.423339</v>
       </c>
@@ -5453,9 +5235,7 @@
       <c r="F57" t="n">
         <v>5.0517</v>
       </c>
-      <c r="G57" t="n">
-        <v>5.882353</v>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>7580.060059</v>
       </c>
@@ -5495,9 +5275,7 @@
       <c r="T57" t="n">
         <v>0.6816179999999999</v>
       </c>
-      <c r="U57" t="n">
-        <v>0.411758</v>
-      </c>
+      <c r="U57" t="inlineStr"/>
       <c r="V57" t="n">
         <v>5.147036</v>
       </c>
@@ -5542,9 +5320,7 @@
       <c r="F58" t="n">
         <v>5.181787</v>
       </c>
-      <c r="G58" t="n">
-        <v>5.91716</v>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>7499.359863</v>
       </c>
@@ -5584,9 +5360,7 @@
       <c r="T58" t="n">
         <v>2.575111</v>
       </c>
-      <c r="U58" t="n">
-        <v>0.591722</v>
-      </c>
+      <c r="U58" t="inlineStr"/>
       <c r="V58" t="n">
         <v>-1.064638</v>
       </c>
@@ -5631,9 +5405,7 @@
       <c r="F59" t="n">
         <v>5.0781</v>
       </c>
-      <c r="G59" t="n">
-        <v>5.847953</v>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>7489.720215</v>
       </c>
@@ -5673,9 +5445,7 @@
       <c r="T59" t="n">
         <v>-2.000986</v>
       </c>
-      <c r="U59" t="n">
-        <v>-1.169601</v>
-      </c>
+      <c r="U59" t="inlineStr"/>
       <c r="V59" t="n">
         <v>-0.12854</v>
       </c>
@@ -5720,9 +5490,7 @@
       <c r="F60" t="n">
         <v>5.1912</v>
       </c>
-      <c r="G60" t="n">
-        <v>6.009615</v>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>7686.140137</v>
       </c>
@@ -5762,9 +5530,7 @@
       <c r="T60" t="n">
         <v>2.227203</v>
       </c>
-      <c r="U60" t="n">
-        <v>2.764422</v>
-      </c>
+      <c r="U60" t="inlineStr"/>
       <c r="V60" t="n">
         <v>2.622527</v>
       </c>
@@ -5809,9 +5575,7 @@
       <c r="F61" t="n">
         <v>5.2029</v>
       </c>
-      <c r="G61" t="n">
-        <v>5.896226</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>7651.540039</v>
       </c>
@@ -5851,9 +5615,7 @@
       <c r="T61" t="n">
         <v>0.225384</v>
       </c>
-      <c r="U61" t="n">
-        <v>-1.886793</v>
-      </c>
+      <c r="U61" t="inlineStr"/>
       <c r="V61" t="n">
         <v>-0.450162</v>
       </c>
@@ -5887,20 +5649,18 @@
         <v>205430</v>
       </c>
       <c r="C62" t="n">
-        <v>201.389999</v>
+        <v>202.300003</v>
       </c>
       <c r="D62" t="n">
-        <v>130.830002</v>
+        <v>131</v>
       </c>
       <c r="E62" t="n">
-        <v>444.450012</v>
+        <v>438.549988</v>
       </c>
       <c r="F62" t="n">
         <v>5.0693</v>
       </c>
-      <c r="G62" t="n">
-        <v>5.7053</v>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>7659.439941</v>
       </c>
@@ -5914,7 +5674,7 @@
         <v>4181.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>101.410004</v>
+        <v>99.019997</v>
       </c>
       <c r="M62" t="n">
         <v>109.860001</v>
@@ -5929,20 +5689,18 @@
         <v>10.244714</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.403518999999999</v>
+        <v>9.897871</v>
       </c>
       <c r="R62" t="n">
-        <v>16.885555</v>
+        <v>17.037434</v>
       </c>
       <c r="S62" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-1.971524</v>
       </c>
       <c r="T62" t="n">
         <v>-2.567794</v>
       </c>
-      <c r="U62" t="n">
-        <v>-3.238106</v>
-      </c>
+      <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
         <v>0.103246</v>
       </c>
@@ -5956,7 +5714,7 @@
         <v>-0.133759</v>
       </c>
       <c r="Z62" t="n">
-        <v>12.154397</v>
+        <v>9.511169000000001</v>
       </c>
       <c r="AA62" t="n">
         <v>6.114172</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -586,7 +586,9 @@
       <c r="F2" t="n">
         <v>5.6449</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>6.593</v>
+      </c>
       <c r="H2" t="n">
         <v>4605.379883</v>
       </c>
@@ -645,7 +647,9 @@
       <c r="F3" t="n">
         <v>5.6007</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>6.3223</v>
+      </c>
       <c r="H3" t="n">
         <v>4567</v>
       </c>
@@ -685,7 +689,9 @@
       <c r="T3" t="n">
         <v>-0.783007</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>-4.10587</v>
+      </c>
       <c r="V3" t="n">
         <v>-0.833371</v>
       </c>
@@ -730,7 +736,9 @@
       <c r="F4" t="n">
         <v>5.5702</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>6.3049</v>
+      </c>
       <c r="H4" t="n">
         <v>4766.180176</v>
       </c>
@@ -770,7 +778,9 @@
       <c r="T4" t="n">
         <v>-0.544574</v>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="n">
+        <v>-0.275213</v>
+      </c>
       <c r="V4" t="n">
         <v>4.361291</v>
       </c>
@@ -815,7 +825,9 @@
       <c r="F5" t="n">
         <v>5.3626</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>5.9782</v>
+      </c>
       <c r="H5" t="n">
         <v>4515.549805</v>
       </c>
@@ -855,7 +867,9 @@
       <c r="T5" t="n">
         <v>-3.726978</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>-5.181687</v>
+      </c>
       <c r="V5" t="n">
         <v>-5.258517</v>
       </c>
@@ -900,7 +914,9 @@
       <c r="F6" t="n">
         <v>5.1594</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>5.814</v>
+      </c>
       <c r="H6" t="n">
         <v>4373.939941</v>
       </c>
@@ -940,7 +956,9 @@
       <c r="T6" t="n">
         <v>-3.789204</v>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>-2.746643</v>
+      </c>
       <c r="V6" t="n">
         <v>-3.136049</v>
       </c>
@@ -985,7 +1003,9 @@
       <c r="F7" t="n">
         <v>4.7697</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>5.3198</v>
+      </c>
       <c r="H7" t="n">
         <v>4530.410156</v>
       </c>
@@ -1025,7 +1045,9 @@
       <c r="T7" t="n">
         <v>-7.553203</v>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="n">
+        <v>-8.500176</v>
+      </c>
       <c r="V7" t="n">
         <v>3.577329</v>
       </c>
@@ -1070,7 +1092,9 @@
       <c r="F8" t="n">
         <v>4.9378</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>5.1837</v>
+      </c>
       <c r="H8" t="n">
         <v>4131.930176</v>
       </c>
@@ -1110,7 +1134,9 @@
       <c r="T8" t="n">
         <v>3.524328</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>-2.558363</v>
+      </c>
       <c r="V8" t="n">
         <v>-8.795671</v>
       </c>
@@ -1155,7 +1181,9 @@
       <c r="F9" t="n">
         <v>4.7524</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>5.1176</v>
+      </c>
       <c r="H9" t="n">
         <v>4132.149902</v>
       </c>
@@ -1195,7 +1223,9 @@
       <c r="T9" t="n">
         <v>-3.754709</v>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="n">
+        <v>-1.275153</v>
+      </c>
       <c r="V9" t="n">
         <v>0.005318</v>
       </c>
@@ -1240,7 +1270,9 @@
       <c r="F10" t="n">
         <v>5.1809</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>5.4098</v>
+      </c>
       <c r="H10" t="n">
         <v>3785.379883</v>
       </c>
@@ -1280,7 +1312,9 @@
       <c r="T10" t="n">
         <v>9.016501</v>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="n">
+        <v>5.709709</v>
+      </c>
       <c r="V10" t="n">
         <v>-8.391999999999999</v>
       </c>
@@ -1325,7 +1359,9 @@
       <c r="F11" t="n">
         <v>5.1827</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>5.2797</v>
+      </c>
       <c r="H11" t="n">
         <v>4130.290039</v>
       </c>
@@ -1365,7 +1401,9 @@
       <c r="T11" t="n">
         <v>0.034744</v>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="n">
+        <v>-2.404899</v>
+      </c>
       <c r="V11" t="n">
         <v>9.111639</v>
       </c>
@@ -1410,7 +1448,9 @@
       <c r="F12" t="n">
         <v>5.1219</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>5.1318</v>
+      </c>
       <c r="H12" t="n">
         <v>3955</v>
       </c>
@@ -1450,7 +1490,9 @@
       <c r="T12" t="n">
         <v>-1.173135</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>-2.801289</v>
+      </c>
       <c r="V12" t="n">
         <v>-4.244013</v>
       </c>
@@ -1495,7 +1537,9 @@
       <c r="F13" t="n">
         <v>5.3962</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>5.3031</v>
+      </c>
       <c r="H13" t="n">
         <v>3585.620117</v>
       </c>
@@ -1535,7 +1579,9 @@
       <c r="T13" t="n">
         <v>5.355436</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>3.338009</v>
+      </c>
       <c r="V13" t="n">
         <v>-9.339567000000001</v>
       </c>
@@ -1580,7 +1626,9 @@
       <c r="F14" t="n">
         <v>5.2885</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>5.2737</v>
+      </c>
       <c r="H14" t="n">
         <v>3871.97998</v>
       </c>
@@ -1620,7 +1668,9 @@
       <c r="T14" t="n">
         <v>-1.995855</v>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>-0.55439</v>
+      </c>
       <c r="V14" t="n">
         <v>7.986341</v>
       </c>
@@ -1665,7 +1715,9 @@
       <c r="F15" t="n">
         <v>5.2682</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>5.4362</v>
+      </c>
       <c r="H15" t="n">
         <v>4080.110107</v>
       </c>
@@ -1705,7 +1757,9 @@
       <c r="T15" t="n">
         <v>-0.38385</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>3.081326</v>
+      </c>
       <c r="V15" t="n">
         <v>5.375289</v>
       </c>
@@ -1750,7 +1804,9 @@
       <c r="F16" t="n">
         <v>5.2846</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>5.633</v>
+      </c>
       <c r="H16" t="n">
         <v>3839.5</v>
       </c>
@@ -1790,7 +1846,9 @@
       <c r="T16" t="n">
         <v>0.311299</v>
       </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>3.620171</v>
+      </c>
       <c r="V16" t="n">
         <v>-5.897147</v>
       </c>
@@ -1835,7 +1893,9 @@
       <c r="F17" t="n">
         <v>5.1149</v>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>5.5471</v>
+      </c>
       <c r="H17" t="n">
         <v>4076.600098</v>
       </c>
@@ -1875,7 +1935,9 @@
       <c r="T17" t="n">
         <v>-3.211211</v>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="n">
+        <v>-1.524939</v>
+      </c>
       <c r="V17" t="n">
         <v>6.175286</v>
       </c>
@@ -1920,7 +1982,9 @@
       <c r="F18" t="n">
         <v>5.1997</v>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>5.514</v>
+      </c>
       <c r="H18" t="n">
         <v>3970.149902</v>
       </c>
@@ -1960,7 +2024,9 @@
       <c r="T18" t="n">
         <v>1.657897</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>-0.59671</v>
+      </c>
       <c r="V18" t="n">
         <v>-2.611249</v>
       </c>
@@ -2005,7 +2071,9 @@
       <c r="F19" t="n">
         <v>5.0927</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>5.5518</v>
+      </c>
       <c r="H19" t="n">
         <v>4109.310059</v>
       </c>
@@ -2045,7 +2113,9 @@
       <c r="T19" t="n">
         <v>-2.057809</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>0.6855250000000001</v>
+      </c>
       <c r="V19" t="n">
         <v>3.505161</v>
       </c>
@@ -2090,7 +2160,9 @@
       <c r="F20" t="n">
         <v>4.9762</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>5.4883</v>
+      </c>
       <c r="H20" t="n">
         <v>4169.47998</v>
       </c>
@@ -2130,7 +2202,9 @@
       <c r="T20" t="n">
         <v>-2.287586</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>-1.143772</v>
+      </c>
       <c r="V20" t="n">
         <v>1.464234</v>
       </c>
@@ -2175,7 +2249,9 @@
       <c r="F21" t="n">
         <v>5.0348</v>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>5.4012</v>
+      </c>
       <c r="H21" t="n">
         <v>4179.830078</v>
       </c>
@@ -2215,7 +2291,9 @@
       <c r="T21" t="n">
         <v>1.177604</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>-1.587013</v>
+      </c>
       <c r="V21" t="n">
         <v>0.248235</v>
       </c>
@@ -2260,7 +2338,9 @@
       <c r="F22" t="n">
         <v>4.8556</v>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>5.2739</v>
+      </c>
       <c r="H22" t="n">
         <v>4450.379883</v>
       </c>
@@ -2300,7 +2380,9 @@
       <c r="T22" t="n">
         <v>-3.559231</v>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>-2.35688</v>
+      </c>
       <c r="V22" t="n">
         <v>6.472746</v>
       </c>
@@ -2345,7 +2427,9 @@
       <c r="F23" t="n">
         <v>4.7233</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>5.1895</v>
+      </c>
       <c r="H23" t="n">
         <v>4588.959961</v>
       </c>
@@ -2385,7 +2469,9 @@
       <c r="T23" t="n">
         <v>-2.724687</v>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>-1.600337</v>
+      </c>
       <c r="V23" t="n">
         <v>3.113893</v>
       </c>
@@ -2430,7 +2516,9 @@
       <c r="F24" t="n">
         <v>4.8884</v>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>5.313</v>
+      </c>
       <c r="H24" t="n">
         <v>4507.660156</v>
       </c>
@@ -2470,7 +2558,9 @@
       <c r="T24" t="n">
         <v>3.49544</v>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>2.379812</v>
+      </c>
       <c r="V24" t="n">
         <v>-1.771639</v>
       </c>
@@ -2515,7 +2605,9 @@
       <c r="F25" t="n">
         <v>5.0328</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>5.3197</v>
+      </c>
       <c r="H25" t="n">
         <v>4288.049805</v>
       </c>
@@ -2555,7 +2647,9 @@
       <c r="T25" t="n">
         <v>2.953934</v>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>0.126098</v>
+      </c>
       <c r="V25" t="n">
         <v>-4.871937</v>
       </c>
@@ -2600,7 +2694,9 @@
       <c r="F26" t="n">
         <v>5.0461</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>5.3537</v>
+      </c>
       <c r="H26" t="n">
         <v>4193.799805</v>
       </c>
@@ -2640,7 +2736,9 @@
       <c r="T26" t="n">
         <v>0.264265</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>0.639141</v>
+      </c>
       <c r="V26" t="n">
         <v>-2.197969</v>
       </c>
@@ -2685,7 +2783,9 @@
       <c r="F27" t="n">
         <v>4.9041</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>5.3628</v>
+      </c>
       <c r="H27" t="n">
         <v>4567.799805</v>
       </c>
@@ -2725,7 +2825,9 @@
       <c r="T27" t="n">
         <v>-2.814058</v>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>0.169975</v>
+      </c>
       <c r="V27" t="n">
         <v>8.917927000000001</v>
       </c>
@@ -2770,7 +2872,9 @@
       <c r="F28" t="n">
         <v>4.8502</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>5.343</v>
+      </c>
       <c r="H28" t="n">
         <v>4769.830078</v>
       </c>
@@ -2810,7 +2914,9 @@
       <c r="T28" t="n">
         <v>-1.099076</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>-0.369214</v>
+      </c>
       <c r="V28" t="n">
         <v>4.422923</v>
       </c>
@@ -2855,7 +2961,9 @@
       <c r="F29" t="n">
         <v>4.9503</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>5.3604</v>
+      </c>
       <c r="H29" t="n">
         <v>4845.649902</v>
       </c>
@@ -2895,7 +3003,9 @@
       <c r="T29" t="n">
         <v>2.063833</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>0.325665</v>
+      </c>
       <c r="V29" t="n">
         <v>1.589571</v>
       </c>
@@ -2940,7 +3050,9 @@
       <c r="F30" t="n">
         <v>4.9673</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>5.381</v>
+      </c>
       <c r="H30" t="n">
         <v>5096.27002</v>
       </c>
@@ -2980,7 +3092,9 @@
       <c r="T30" t="n">
         <v>0.343408</v>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="n">
+        <v>0.384297</v>
+      </c>
       <c r="V30" t="n">
         <v>5.172064</v>
       </c>
@@ -3025,7 +3139,9 @@
       <c r="F31" t="n">
         <v>5.0141</v>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>5.4065</v>
+      </c>
       <c r="H31" t="n">
         <v>5254.350098</v>
       </c>
@@ -3065,7 +3181,9 @@
       <c r="T31" t="n">
         <v>0.942164</v>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="n">
+        <v>0.473886</v>
+      </c>
       <c r="V31" t="n">
         <v>3.101878</v>
       </c>
@@ -3110,7 +3228,9 @@
       <c r="F32" t="n">
         <v>5.117</v>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>5.4794</v>
+      </c>
       <c r="H32" t="n">
         <v>5035.689941</v>
       </c>
@@ -3150,7 +3270,9 @@
       <c r="T32" t="n">
         <v>2.052213</v>
       </c>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="n">
+        <v>1.348382</v>
+      </c>
       <c r="V32" t="n">
         <v>-4.161507</v>
       </c>
@@ -3195,7 +3317,9 @@
       <c r="F33" t="n">
         <v>5.2021</v>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>5.6311</v>
+      </c>
       <c r="H33" t="n">
         <v>5277.509766</v>
       </c>
@@ -3235,7 +3359,9 @@
       <c r="T33" t="n">
         <v>1.663078</v>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="n">
+        <v>2.768552</v>
+      </c>
       <c r="V33" t="n">
         <v>4.802119</v>
       </c>
@@ -3280,7 +3406,9 @@
       <c r="F34" t="n">
         <v>5.5005</v>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>5.8909</v>
+      </c>
       <c r="H34" t="n">
         <v>5460.47998</v>
       </c>
@@ -3320,7 +3448,9 @@
       <c r="T34" t="n">
         <v>5.736153</v>
       </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" t="n">
+        <v>4.613663</v>
+      </c>
       <c r="V34" t="n">
         <v>3.46698</v>
       </c>
@@ -3365,7 +3495,9 @@
       <c r="F35" t="n">
         <v>5.6111</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>6.0695</v>
+      </c>
       <c r="H35" t="n">
         <v>5522.299805</v>
       </c>
@@ -3405,7 +3537,9 @@
       <c r="T35" t="n">
         <v>2.010726</v>
       </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" t="n">
+        <v>3.031792</v>
+      </c>
       <c r="V35" t="n">
         <v>1.132132</v>
       </c>
@@ -3450,7 +3584,9 @@
       <c r="F36" t="n">
         <v>5.6277</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>6.2224</v>
+      </c>
       <c r="H36" t="n">
         <v>5648.399902</v>
       </c>
@@ -3490,7 +3626,9 @@
       <c r="T36" t="n">
         <v>0.295836</v>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="n">
+        <v>2.519157</v>
+      </c>
       <c r="V36" t="n">
         <v>2.283471</v>
       </c>
@@ -3535,7 +3673,9 @@
       <c r="F37" t="n">
         <v>5.4332</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>6.0652</v>
+      </c>
       <c r="H37" t="n">
         <v>5762.47998</v>
       </c>
@@ -3575,7 +3715,9 @@
       <c r="T37" t="n">
         <v>-3.456118</v>
       </c>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" t="n">
+        <v>-2.526362</v>
+      </c>
       <c r="V37" t="n">
         <v>2.019688</v>
       </c>
@@ -3620,7 +3762,9 @@
       <c r="F38" t="n">
         <v>5.7623</v>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>6.2522</v>
+      </c>
       <c r="H38" t="n">
         <v>5705.450195</v>
       </c>
@@ -3660,7 +3804,9 @@
       <c r="T38" t="n">
         <v>6.057206</v>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="n">
+        <v>3.083168</v>
+      </c>
       <c r="V38" t="n">
         <v>-0.9896740000000001</v>
       </c>
@@ -3705,7 +3851,9 @@
       <c r="F39" t="n">
         <v>6.0139</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>6.345178</v>
+      </c>
       <c r="H39" t="n">
         <v>6032.379883</v>
       </c>
@@ -3745,7 +3893,9 @@
       <c r="T39" t="n">
         <v>4.366308</v>
       </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="n">
+        <v>1.487125</v>
+      </c>
       <c r="V39" t="n">
         <v>5.73013</v>
       </c>
@@ -3790,7 +3940,9 @@
       <c r="F40" t="n">
         <v>6.1779</v>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>6.422608</v>
+      </c>
       <c r="H40" t="n">
         <v>5881.629883</v>
       </c>
@@ -3830,7 +3982,9 @@
       <c r="T40" t="n">
         <v>2.727016</v>
       </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" t="n">
+        <v>1.220293</v>
+      </c>
       <c r="V40" t="n">
         <v>-2.499014</v>
       </c>
@@ -3875,7 +4029,9 @@
       <c r="F41" t="n">
         <v>5.8745</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>6.101281</v>
+      </c>
       <c r="H41" t="n">
         <v>6040.529785</v>
       </c>
@@ -3915,7 +4071,9 @@
       <c r="T41" t="n">
         <v>-4.911055</v>
       </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="n">
+        <v>-5.003057</v>
+      </c>
       <c r="V41" t="n">
         <v>2.70163</v>
       </c>
@@ -3960,7 +4118,9 @@
       <c r="F42" t="n">
         <v>5.839</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>6.064281</v>
+      </c>
       <c r="H42" t="n">
         <v>5954.5</v>
       </c>
@@ -4000,7 +4160,9 @@
       <c r="T42" t="n">
         <v>-0.604299</v>
       </c>
-      <c r="U42" t="inlineStr"/>
+      <c r="U42" t="n">
+        <v>-0.606433</v>
+      </c>
       <c r="V42" t="n">
         <v>-1.424209</v>
       </c>
@@ -4045,7 +4207,9 @@
       <c r="F43" t="n">
         <v>5.7581</v>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>6.22665</v>
+      </c>
       <c r="H43" t="n">
         <v>5611.850098</v>
       </c>
@@ -4085,7 +4249,9 @@
       <c r="T43" t="n">
         <v>-1.385514</v>
       </c>
-      <c r="U43" t="inlineStr"/>
+      <c r="U43" t="n">
+        <v>2.677469</v>
+      </c>
       <c r="V43" t="n">
         <v>-5.75447</v>
       </c>
@@ -4130,7 +4296,9 @@
       <c r="F44" t="n">
         <v>5.62</v>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>6.393862</v>
+      </c>
       <c r="H44" t="n">
         <v>5569.060059</v>
       </c>
@@ -4170,7 +4338,9 @@
       <c r="T44" t="n">
         <v>-2.398363</v>
       </c>
-      <c r="U44" t="inlineStr"/>
+      <c r="U44" t="n">
+        <v>2.685417</v>
+      </c>
       <c r="V44" t="n">
         <v>-0.762494</v>
       </c>
@@ -4215,7 +4385,9 @@
       <c r="F45" t="n">
         <v>5.6651</v>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>6.43915</v>
+      </c>
       <c r="H45" t="n">
         <v>5911.689941</v>
       </c>
@@ -4255,7 +4427,9 @@
       <c r="T45" t="n">
         <v>0.802495</v>
       </c>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v>0.708306</v>
+      </c>
       <c r="V45" t="n">
         <v>6.152383</v>
       </c>
@@ -4300,7 +4474,9 @@
       <c r="F46" t="n">
         <v>5.4784</v>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>6.418485</v>
+      </c>
       <c r="H46" t="n">
         <v>6204.950195</v>
       </c>
@@ -4340,7 +4516,9 @@
       <c r="T46" t="n">
         <v>-3.295615</v>
       </c>
-      <c r="U46" t="inlineStr"/>
+      <c r="U46" t="n">
+        <v>-0.320923</v>
+      </c>
       <c r="V46" t="n">
         <v>4.960684</v>
       </c>
@@ -4385,7 +4563,9 @@
       <c r="F47" t="n">
         <v>5.5754</v>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>6.365372</v>
+      </c>
       <c r="H47" t="n">
         <v>6339.390137</v>
       </c>
@@ -4425,7 +4605,9 @@
       <c r="T47" t="n">
         <v>1.770583</v>
       </c>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="n">
+        <v>-0.8275</v>
+      </c>
       <c r="V47" t="n">
         <v>2.166656</v>
       </c>
@@ -4470,7 +4652,9 @@
       <c r="F48" t="n">
         <v>5.413</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>6.317119</v>
+      </c>
       <c r="H48" t="n">
         <v>6460.259766</v>
       </c>
@@ -4510,7 +4694,9 @@
       <c r="T48" t="n">
         <v>-2.912791</v>
       </c>
-      <c r="U48" t="inlineStr"/>
+      <c r="U48" t="n">
+        <v>-0.758056</v>
+      </c>
       <c r="V48" t="n">
         <v>1.906644</v>
       </c>
@@ -4555,7 +4741,9 @@
       <c r="F49" t="n">
         <v>5.3217</v>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>6.238303</v>
+      </c>
       <c r="H49" t="n">
         <v>6688.459961</v>
       </c>
@@ -4595,7 +4783,9 @@
       <c r="T49" t="n">
         <v>-1.68668</v>
       </c>
-      <c r="U49" t="inlineStr"/>
+      <c r="U49" t="n">
+        <v>-1.247656</v>
+      </c>
       <c r="V49" t="n">
         <v>3.532369</v>
       </c>
@@ -4640,7 +4830,9 @@
       <c r="F50" t="n">
         <v>5.382</v>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>6.222775</v>
+      </c>
       <c r="H50" t="n">
         <v>6840.200195</v>
       </c>
@@ -4680,7 +4872,9 @@
       <c r="T50" t="n">
         <v>1.133094</v>
       </c>
-      <c r="U50" t="inlineStr"/>
+      <c r="U50" t="n">
+        <v>-0.248917</v>
+      </c>
       <c r="V50" t="n">
         <v>2.268687</v>
       </c>
@@ -4725,7 +4919,9 @@
       <c r="F51" t="n">
         <v>5.3554</v>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>6.207325</v>
+      </c>
       <c r="H51" t="n">
         <v>6849.089844</v>
       </c>
@@ -4765,7 +4961,9 @@
       <c r="T51" t="n">
         <v>-0.494238</v>
       </c>
-      <c r="U51" t="inlineStr"/>
+      <c r="U51" t="n">
+        <v>-0.248282</v>
+      </c>
       <c r="V51" t="n">
         <v>0.129962</v>
       </c>
@@ -4810,7 +5008,9 @@
       <c r="F52" t="n">
         <v>5.4762</v>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>6.426735</v>
+      </c>
       <c r="H52" t="n">
         <v>6845.5</v>
       </c>
@@ -4850,7 +5050,9 @@
       <c r="T52" t="n">
         <v>2.255667</v>
       </c>
-      <c r="U52" t="inlineStr"/>
+      <c r="U52" t="n">
+        <v>3.534694</v>
+      </c>
       <c r="V52" t="n">
         <v>-0.052413</v>
       </c>
@@ -4895,7 +5097,9 @@
       <c r="F53" t="n">
         <v>5.1892</v>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>6.203474</v>
+      </c>
       <c r="H53" t="n">
         <v>6939.029785</v>
       </c>
@@ -4935,7 +5139,9 @@
       <c r="T53" t="n">
         <v>-5.240864</v>
       </c>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="n">
+        <v>-3.473939</v>
+      </c>
       <c r="V53" t="n">
         <v>1.366296</v>
       </c>
@@ -4980,7 +5186,9 @@
       <c r="F54" t="n">
         <v>5.1366</v>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>6.056935</v>
+      </c>
       <c r="H54" t="n">
         <v>6878.879883</v>
       </c>
@@ -5020,7 +5228,9 @@
       <c r="T54" t="n">
         <v>-1.013642</v>
       </c>
-      <c r="U54" t="inlineStr"/>
+      <c r="U54" t="n">
+        <v>-2.362212</v>
+      </c>
       <c r="V54" t="n">
         <v>-0.866834</v>
       </c>
@@ -5065,7 +5275,9 @@
       <c r="F55" t="n">
         <v>5.264</v>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>6.027728</v>
+      </c>
       <c r="H55" t="n">
         <v>6528.52002</v>
       </c>
@@ -5105,7 +5317,9 @@
       <c r="T55" t="n">
         <v>2.480238</v>
       </c>
-      <c r="U55" t="inlineStr"/>
+      <c r="U55" t="n">
+        <v>-0.482204</v>
+      </c>
       <c r="V55" t="n">
         <v>-5.093269</v>
       </c>
@@ -5150,7 +5364,9 @@
       <c r="F56" t="n">
         <v>5.0175</v>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>5.858231</v>
+      </c>
       <c r="H56" t="n">
         <v>7209.009766</v>
       </c>
@@ -5190,7 +5406,9 @@
       <c r="T56" t="n">
         <v>-4.682751</v>
       </c>
-      <c r="U56" t="inlineStr"/>
+      <c r="U56" t="n">
+        <v>-2.811955</v>
+      </c>
       <c r="V56" t="n">
         <v>10.423339</v>
       </c>
@@ -5235,7 +5453,9 @@
       <c r="F57" t="n">
         <v>5.0517</v>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>5.882353</v>
+      </c>
       <c r="H57" t="n">
         <v>7580.060059</v>
       </c>
@@ -5275,7 +5495,9 @@
       <c r="T57" t="n">
         <v>0.6816179999999999</v>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="n">
+        <v>0.411758</v>
+      </c>
       <c r="V57" t="n">
         <v>5.147036</v>
       </c>
@@ -5320,7 +5542,9 @@
       <c r="F58" t="n">
         <v>5.181787</v>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>5.91716</v>
+      </c>
       <c r="H58" t="n">
         <v>7499.359863</v>
       </c>
@@ -5360,7 +5584,9 @@
       <c r="T58" t="n">
         <v>2.575111</v>
       </c>
-      <c r="U58" t="inlineStr"/>
+      <c r="U58" t="n">
+        <v>0.591722</v>
+      </c>
       <c r="V58" t="n">
         <v>-1.064638</v>
       </c>
@@ -5405,7 +5631,9 @@
       <c r="F59" t="n">
         <v>5.0781</v>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>5.847953</v>
+      </c>
       <c r="H59" t="n">
         <v>7489.720215</v>
       </c>
@@ -5445,7 +5673,9 @@
       <c r="T59" t="n">
         <v>-2.000986</v>
       </c>
-      <c r="U59" t="inlineStr"/>
+      <c r="U59" t="n">
+        <v>-1.169601</v>
+      </c>
       <c r="V59" t="n">
         <v>-0.12854</v>
       </c>
@@ -5490,7 +5720,9 @@
       <c r="F60" t="n">
         <v>5.1912</v>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>6.009615</v>
+      </c>
       <c r="H60" t="n">
         <v>7686.140137</v>
       </c>
@@ -5530,7 +5762,9 @@
       <c r="T60" t="n">
         <v>2.227203</v>
       </c>
-      <c r="U60" t="inlineStr"/>
+      <c r="U60" t="n">
+        <v>2.764422</v>
+      </c>
       <c r="V60" t="n">
         <v>2.622527</v>
       </c>
@@ -5575,7 +5809,9 @@
       <c r="F61" t="n">
         <v>5.2029</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>5.896226</v>
+      </c>
       <c r="H61" t="n">
         <v>7651.540039</v>
       </c>
@@ -5615,7 +5851,9 @@
       <c r="T61" t="n">
         <v>0.225384</v>
       </c>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>-1.886793</v>
+      </c>
       <c r="V61" t="n">
         <v>-0.450162</v>
       </c>
@@ -5646,84 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>205430</v>
+        <v>204667.15625</v>
       </c>
       <c r="C62" t="n">
-        <v>202.300003</v>
+        <v>201.429993</v>
       </c>
       <c r="D62" t="n">
-        <v>131</v>
+        <v>133.410004</v>
       </c>
       <c r="E62" t="n">
-        <v>438.549988</v>
+        <v>440.230011</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0693</v>
-      </c>
-      <c r="G62" t="inlineStr"/>
+        <v>5.0579</v>
+      </c>
+      <c r="G62" t="n">
+        <v>5.673</v>
+      </c>
       <c r="H62" t="n">
-        <v>7659.439941</v>
+        <v>7708.77002</v>
       </c>
       <c r="I62" t="n">
-        <v>26140.029297</v>
+        <v>26522.501953</v>
       </c>
       <c r="J62" t="n">
-        <v>52002.410156</v>
+        <v>52020.359375</v>
       </c>
       <c r="K62" t="n">
-        <v>4181.100098</v>
+        <v>4161.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>99.019997</v>
+        <v>98.599998</v>
       </c>
       <c r="M62" t="n">
-        <v>109.860001</v>
+        <v>109.400002</v>
       </c>
       <c r="N62" t="n">
-        <v>1261.25</v>
+        <v>1251</v>
       </c>
       <c r="O62" t="n">
-        <v>474.25</v>
+        <v>467.75</v>
       </c>
       <c r="P62" t="n">
-        <v>10.244714</v>
+        <v>9.835331</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.897871</v>
+        <v>9.425245</v>
       </c>
       <c r="R62" t="n">
-        <v>17.037434</v>
+        <v>19.190568</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.971524</v>
+        <v>-1.595991</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.567794</v>
-      </c>
-      <c r="U62" t="inlineStr"/>
+        <v>-2.786907</v>
+      </c>
+      <c r="U62" t="n">
+        <v>-3.785914</v>
+      </c>
       <c r="V62" t="n">
-        <v>0.103246</v>
+        <v>0.747954</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.684299</v>
+        <v>-1.260407</v>
       </c>
       <c r="X62" t="n">
-        <v>2.153692</v>
+        <v>2.188951</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.133759</v>
+        <v>-0.592359</v>
       </c>
       <c r="Z62" t="n">
-        <v>9.511169000000001</v>
+        <v>9.046671999999999</v>
       </c>
       <c r="AA62" t="n">
-        <v>6.114172</v>
+        <v>5.669857</v>
       </c>
       <c r="AB62" t="n">
-        <v>-2.45553</v>
+        <v>-3.24826</v>
       </c>
       <c r="AC62" t="n">
-        <v>-5.292062</v>
+        <v>-6.590115</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>204667.15625</v>
+        <v>207377.765625</v>
       </c>
       <c r="C62" t="n">
-        <v>201.429993</v>
+        <v>204.220001</v>
       </c>
       <c r="D62" t="n">
-        <v>133.410004</v>
+        <v>137.440002</v>
       </c>
       <c r="E62" t="n">
-        <v>440.230011</v>
+        <v>437.529999</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0579</v>
+        <v>5.01</v>
       </c>
       <c r="G62" t="n">
-        <v>5.673</v>
+        <v>5.6383</v>
       </c>
       <c r="H62" t="n">
-        <v>7708.77002</v>
+        <v>7736.75</v>
       </c>
       <c r="I62" t="n">
-        <v>26522.501953</v>
+        <v>26544.773438</v>
       </c>
       <c r="J62" t="n">
-        <v>52020.359375</v>
+        <v>52561.949219</v>
       </c>
       <c r="K62" t="n">
-        <v>4161.899902</v>
+        <v>4169.299805</v>
       </c>
       <c r="L62" t="n">
-        <v>98.599998</v>
+        <v>96.30999799999999</v>
       </c>
       <c r="M62" t="n">
-        <v>109.400002</v>
+        <v>107</v>
       </c>
       <c r="N62" t="n">
-        <v>1251</v>
+        <v>1253.25</v>
       </c>
       <c r="O62" t="n">
-        <v>467.75</v>
+        <v>462.75</v>
       </c>
       <c r="P62" t="n">
-        <v>9.835331</v>
+        <v>11.289989</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.425245</v>
+        <v>10.940895</v>
       </c>
       <c r="R62" t="n">
-        <v>19.190568</v>
+        <v>22.791032</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.595991</v>
+        <v>-2.199521</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.786907</v>
+        <v>-3.707542</v>
       </c>
       <c r="U62" t="n">
-        <v>-3.785914</v>
+        <v>-4.374425</v>
       </c>
       <c r="V62" t="n">
-        <v>0.747954</v>
+        <v>1.113632</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.260407</v>
+        <v>-1.177493</v>
       </c>
       <c r="X62" t="n">
-        <v>2.188951</v>
+        <v>3.252852</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.592359</v>
+        <v>-0.415611</v>
       </c>
       <c r="Z62" t="n">
-        <v>9.046671999999999</v>
+        <v>6.514045</v>
       </c>
       <c r="AA62" t="n">
-        <v>5.669857</v>
+        <v>3.351687</v>
       </c>
       <c r="AB62" t="n">
-        <v>-3.24826</v>
+        <v>-3.074246</v>
       </c>
       <c r="AC62" t="n">
-        <v>-6.590115</v>
+        <v>-7.588617</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>207377.765625</v>
+        <v>207602.875</v>
       </c>
       <c r="C62" t="n">
-        <v>204.220001</v>
+        <v>204.389999</v>
       </c>
       <c r="D62" t="n">
-        <v>137.440002</v>
+        <v>137.669998</v>
       </c>
       <c r="E62" t="n">
-        <v>437.529999</v>
+        <v>438.600006</v>
       </c>
       <c r="F62" t="n">
-        <v>5.01</v>
+        <v>5.023</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6383</v>
+        <v>5.6414</v>
       </c>
       <c r="H62" t="n">
-        <v>7736.75</v>
+        <v>7733.419922</v>
       </c>
       <c r="I62" t="n">
-        <v>26544.773438</v>
+        <v>26607.212891</v>
       </c>
       <c r="J62" t="n">
-        <v>52561.949219</v>
+        <v>52536.589844</v>
       </c>
       <c r="K62" t="n">
-        <v>4169.299805</v>
+        <v>4149.100098</v>
       </c>
       <c r="L62" t="n">
-        <v>96.30999799999999</v>
+        <v>97.800003</v>
       </c>
       <c r="M62" t="n">
-        <v>107</v>
+        <v>109.040001</v>
       </c>
       <c r="N62" t="n">
-        <v>1253.25</v>
+        <v>1238.5</v>
       </c>
       <c r="O62" t="n">
-        <v>462.75</v>
+        <v>456.25</v>
       </c>
       <c r="P62" t="n">
-        <v>11.289989</v>
+        <v>11.410795</v>
       </c>
       <c r="Q62" t="n">
-        <v>10.940895</v>
+        <v>11.033245</v>
       </c>
       <c r="R62" t="n">
-        <v>22.791032</v>
+        <v>22.996514</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.199521</v>
+        <v>-1.960344</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.707542</v>
+        <v>-3.45769</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.374425</v>
+        <v>-4.32185</v>
       </c>
       <c r="V62" t="n">
-        <v>1.113632</v>
+        <v>1.07011</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.177493</v>
+        <v>-0.94504</v>
       </c>
       <c r="X62" t="n">
-        <v>3.252852</v>
+        <v>3.203036</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.415611</v>
+        <v>-0.898084</v>
       </c>
       <c r="Z62" t="n">
-        <v>6.514045</v>
+        <v>8.161917000000001</v>
       </c>
       <c r="AA62" t="n">
-        <v>3.351687</v>
+        <v>5.322131</v>
       </c>
       <c r="AB62" t="n">
-        <v>-3.074246</v>
+        <v>-4.215004</v>
       </c>
       <c r="AC62" t="n">
-        <v>-7.588617</v>
+        <v>-8.886670000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>207602.875</v>
+        <v>203775.984375</v>
       </c>
       <c r="C62" t="n">
-        <v>204.389999</v>
+        <v>200.619995</v>
       </c>
       <c r="D62" t="n">
-        <v>137.669998</v>
+        <v>134.389999</v>
       </c>
       <c r="E62" t="n">
-        <v>438.600006</v>
+        <v>435.700012</v>
       </c>
       <c r="F62" t="n">
-        <v>5.023</v>
+        <v>5.0487</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6414</v>
+        <v>5.6493</v>
       </c>
       <c r="H62" t="n">
-        <v>7733.419922</v>
+        <v>7649.620117</v>
       </c>
       <c r="I62" t="n">
-        <v>26607.212891</v>
+        <v>26096.677734</v>
       </c>
       <c r="J62" t="n">
-        <v>52536.589844</v>
+        <v>52570.058594</v>
       </c>
       <c r="K62" t="n">
-        <v>4149.100098</v>
+        <v>4069.300049</v>
       </c>
       <c r="L62" t="n">
-        <v>97.800003</v>
+        <v>98.410004</v>
       </c>
       <c r="M62" t="n">
-        <v>109.040001</v>
+        <v>111.389999</v>
       </c>
       <c r="N62" t="n">
-        <v>1238.5</v>
+        <v>1263.75</v>
       </c>
       <c r="O62" t="n">
-        <v>456.25</v>
+        <v>459.75</v>
       </c>
       <c r="P62" t="n">
-        <v>11.410795</v>
+        <v>9.357081000000001</v>
       </c>
       <c r="Q62" t="n">
-        <v>11.033245</v>
+        <v>8.98522</v>
       </c>
       <c r="R62" t="n">
-        <v>22.996514</v>
+        <v>20.066112</v>
       </c>
       <c r="S62" t="n">
-        <v>-1.960344</v>
+        <v>-2.608575</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.45769</v>
+        <v>-2.963733</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.32185</v>
+        <v>-4.187862</v>
       </c>
       <c r="V62" t="n">
-        <v>1.07011</v>
+        <v>-0.025092</v>
       </c>
       <c r="W62" t="n">
-        <v>-0.94504</v>
+        <v>-2.845691</v>
       </c>
       <c r="X62" t="n">
-        <v>3.203036</v>
+        <v>3.268782</v>
       </c>
       <c r="Y62" t="n">
-        <v>-0.898084</v>
+        <v>-2.804121</v>
       </c>
       <c r="Z62" t="n">
-        <v>8.161917000000001</v>
+        <v>8.836546999999999</v>
       </c>
       <c r="AA62" t="n">
-        <v>5.322131</v>
+        <v>7.592003</v>
       </c>
       <c r="AB62" t="n">
-        <v>-4.215004</v>
+        <v>-2.262181</v>
       </c>
       <c r="AC62" t="n">
-        <v>-8.886670000000001</v>
+        <v>-8.187718</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>203775.984375</v>
+        <v>203917.265625</v>
       </c>
       <c r="C62" t="n">
-        <v>200.619995</v>
+        <v>200.830002</v>
       </c>
       <c r="D62" t="n">
-        <v>134.389999</v>
+        <v>134.300003</v>
       </c>
       <c r="E62" t="n">
-        <v>435.700012</v>
+        <v>433.559998</v>
       </c>
       <c r="F62" t="n">
-        <v>5.0487</v>
+        <v>5.044</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6493</v>
+        <v>5.6461</v>
       </c>
       <c r="H62" t="n">
-        <v>7649.620117</v>
+        <v>7620.830078</v>
       </c>
       <c r="I62" t="n">
-        <v>26096.677734</v>
+        <v>25972.888672</v>
       </c>
       <c r="J62" t="n">
-        <v>52570.058594</v>
+        <v>52102.460938</v>
       </c>
       <c r="K62" t="n">
-        <v>4069.300049</v>
+        <v>4010.300049</v>
       </c>
       <c r="L62" t="n">
-        <v>98.410004</v>
+        <v>102.190002</v>
       </c>
       <c r="M62" t="n">
-        <v>111.389999</v>
+        <v>111.139999</v>
       </c>
       <c r="N62" t="n">
-        <v>1263.75</v>
+        <v>1271.75</v>
       </c>
       <c r="O62" t="n">
-        <v>459.75</v>
+        <v>457.75</v>
       </c>
       <c r="P62" t="n">
-        <v>9.357081000000001</v>
+        <v>9.4329</v>
       </c>
       <c r="Q62" t="n">
-        <v>8.98522</v>
+        <v>9.099304999999999</v>
       </c>
       <c r="R62" t="n">
-        <v>20.066112</v>
+        <v>19.985708</v>
       </c>
       <c r="S62" t="n">
-        <v>-2.608575</v>
+        <v>-3.08693</v>
       </c>
       <c r="T62" t="n">
-        <v>-2.963733</v>
+        <v>-3.054062</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.187862</v>
+        <v>-4.242135</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.025092</v>
+        <v>-0.401357</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.845691</v>
+        <v>-3.306541</v>
       </c>
       <c r="X62" t="n">
-        <v>3.268782</v>
+        <v>2.350232</v>
       </c>
       <c r="Y62" t="n">
-        <v>-2.804121</v>
+        <v>-4.213346</v>
       </c>
       <c r="Z62" t="n">
-        <v>8.836546999999999</v>
+        <v>13.017037</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.592003</v>
+        <v>7.350527</v>
       </c>
       <c r="AB62" t="n">
-        <v>-2.262181</v>
+        <v>-1.643465</v>
       </c>
       <c r="AC62" t="n">
-        <v>-8.187718</v>
+        <v>-8.587119</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>203917.265625</v>
+        <v>205083</v>
       </c>
       <c r="C62" t="n">
-        <v>200.830002</v>
+        <v>201.690002</v>
       </c>
       <c r="D62" t="n">
-        <v>134.300003</v>
+        <v>137.160004</v>
       </c>
       <c r="E62" t="n">
-        <v>433.559998</v>
+        <v>430</v>
       </c>
       <c r="F62" t="n">
-        <v>5.044</v>
+        <v>4.9964</v>
       </c>
       <c r="G62" t="n">
-        <v>5.6461</v>
+        <v>5.5626</v>
       </c>
       <c r="H62" t="n">
-        <v>7620.830078</v>
+        <v>7623.680176</v>
       </c>
       <c r="I62" t="n">
-        <v>25972.888672</v>
+        <v>25955.339844</v>
       </c>
       <c r="J62" t="n">
-        <v>52102.460938</v>
+        <v>52215.160156</v>
       </c>
       <c r="K62" t="n">
-        <v>4010.300049</v>
+        <v>4007.899902</v>
       </c>
       <c r="L62" t="n">
-        <v>102.190002</v>
+        <v>103.269997</v>
       </c>
       <c r="M62" t="n">
-        <v>111.139999</v>
+        <v>116.720001</v>
       </c>
       <c r="N62" t="n">
-        <v>1271.75</v>
+        <v>1256.5</v>
       </c>
       <c r="O62" t="n">
-        <v>457.75</v>
+        <v>456</v>
       </c>
       <c r="P62" t="n">
-        <v>9.4329</v>
+        <v>10.058495</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.099304999999999</v>
+        <v>9.566492999999999</v>
       </c>
       <c r="R62" t="n">
-        <v>19.985708</v>
+        <v>22.540877</v>
       </c>
       <c r="S62" t="n">
-        <v>-3.08693</v>
+        <v>-3.882691</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.054062</v>
+        <v>-3.968941</v>
       </c>
       <c r="U62" t="n">
-        <v>-4.242135</v>
+        <v>-5.658294</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.401357</v>
+        <v>-0.364108</v>
       </c>
       <c r="W62" t="n">
-        <v>-3.306541</v>
+        <v>-3.371872</v>
       </c>
       <c r="X62" t="n">
-        <v>2.350232</v>
+        <v>2.571618</v>
       </c>
       <c r="Y62" t="n">
-        <v>-4.213346</v>
+        <v>-4.270673</v>
       </c>
       <c r="Z62" t="n">
-        <v>13.017037</v>
+        <v>14.211456</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.350527</v>
+        <v>12.740271</v>
       </c>
       <c r="AB62" t="n">
-        <v>-1.643465</v>
+        <v>-2.822892</v>
       </c>
       <c r="AC62" t="n">
-        <v>-8.587119</v>
+        <v>-8.936595000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5896,7 +5896,7 @@
         <v>430</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9964</v>
+        <v>4.9652</v>
       </c>
       <c r="G62" t="n">
         <v>5.5626</v>
@@ -5917,7 +5917,7 @@
         <v>103.269997</v>
       </c>
       <c r="M62" t="n">
-        <v>116.720001</v>
+        <v>111.699997</v>
       </c>
       <c r="N62" t="n">
         <v>1256.5</v>
@@ -5938,7 +5938,7 @@
         <v>-3.882691</v>
       </c>
       <c r="T62" t="n">
-        <v>-3.968941</v>
+        <v>-4.568606</v>
       </c>
       <c r="U62" t="n">
         <v>-5.658294</v>
@@ -5959,7 +5959,7 @@
         <v>14.211456</v>
       </c>
       <c r="AA62" t="n">
-        <v>12.740271</v>
+        <v>7.891431</v>
       </c>
       <c r="AB62" t="n">
         <v>-2.822892</v>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>205083</v>
+        <v>173958.859375</v>
       </c>
       <c r="C62" t="n">
-        <v>201.690002</v>
+        <v>170.990005</v>
       </c>
       <c r="D62" t="n">
-        <v>137.160004</v>
+        <v>100.959999</v>
       </c>
       <c r="E62" t="n">
-        <v>430</v>
+        <v>471.690002</v>
       </c>
       <c r="F62" t="n">
-        <v>4.9652</v>
+        <v>5.4467</v>
       </c>
       <c r="G62" t="n">
-        <v>5.5626</v>
+        <v>6.0905</v>
       </c>
       <c r="H62" t="n">
-        <v>7623.680176</v>
+        <v>7681.919922</v>
       </c>
       <c r="I62" t="n">
-        <v>25955.339844</v>
+        <v>26216.0625</v>
       </c>
       <c r="J62" t="n">
-        <v>52215.160156</v>
+        <v>52373.011719</v>
       </c>
       <c r="K62" t="n">
-        <v>4007.899902</v>
+        <v>4032.800049</v>
       </c>
       <c r="L62" t="n">
-        <v>103.269997</v>
+        <v>102.870003</v>
       </c>
       <c r="M62" t="n">
-        <v>111.699997</v>
+        <v>111.949997</v>
       </c>
       <c r="N62" t="n">
-        <v>1256.5</v>
+        <v>1248.5</v>
       </c>
       <c r="O62" t="n">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P62" t="n">
-        <v>10.058495</v>
+        <v>-6.644382</v>
       </c>
       <c r="Q62" t="n">
-        <v>9.566492999999999</v>
+        <v>-7.111037</v>
       </c>
       <c r="R62" t="n">
-        <v>22.540877</v>
+        <v>-9.800769000000001</v>
       </c>
       <c r="S62" t="n">
-        <v>-3.882691</v>
+        <v>5.436218</v>
       </c>
       <c r="T62" t="n">
-        <v>-4.568606</v>
+        <v>4.685851</v>
       </c>
       <c r="U62" t="n">
-        <v>-5.658294</v>
+        <v>3.294886</v>
       </c>
       <c r="V62" t="n">
-        <v>-0.364108</v>
+        <v>0.397043</v>
       </c>
       <c r="W62" t="n">
-        <v>-3.371872</v>
+        <v>-2.401238</v>
       </c>
       <c r="X62" t="n">
-        <v>2.571618</v>
+        <v>2.881702</v>
       </c>
       <c r="Y62" t="n">
-        <v>-4.270673</v>
+        <v>-3.675929</v>
       </c>
       <c r="Z62" t="n">
-        <v>14.211456</v>
+        <v>13.769083</v>
       </c>
       <c r="AA62" t="n">
-        <v>7.891431</v>
+        <v>8.132906999999999</v>
       </c>
       <c r="AB62" t="n">
-        <v>-2.822892</v>
+        <v>-3.441609</v>
       </c>
       <c r="AC62" t="n">
-        <v>-8.936595000000001</v>
+        <v>-9.335996</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>173958.859375</v>
+        <v>176027.578125</v>
       </c>
       <c r="C62" t="n">
-        <v>170.990005</v>
+        <v>173.179993</v>
       </c>
       <c r="D62" t="n">
-        <v>100.959999</v>
+        <v>100.730003</v>
       </c>
       <c r="E62" t="n">
-        <v>471.690002</v>
+        <v>465.970001</v>
       </c>
       <c r="F62" t="n">
-        <v>5.4467</v>
+        <v>5.3271</v>
       </c>
       <c r="G62" t="n">
-        <v>6.0905</v>
+        <v>5.9472</v>
       </c>
       <c r="H62" t="n">
-        <v>7681.919922</v>
+        <v>7721.919922</v>
       </c>
       <c r="I62" t="n">
-        <v>26216.0625</v>
+        <v>26448.109375</v>
       </c>
       <c r="J62" t="n">
-        <v>52373.011719</v>
+        <v>52447.628906</v>
       </c>
       <c r="K62" t="n">
-        <v>4032.800049</v>
+        <v>4072.300049</v>
       </c>
       <c r="L62" t="n">
-        <v>102.870003</v>
+        <v>100.040001</v>
       </c>
       <c r="M62" t="n">
-        <v>111.949997</v>
+        <v>109.370003</v>
       </c>
       <c r="N62" t="n">
-        <v>1248.5</v>
+        <v>1249.75</v>
       </c>
       <c r="O62" t="n">
-        <v>454</v>
+        <v>451.5</v>
       </c>
       <c r="P62" t="n">
-        <v>-6.644382</v>
+        <v>-5.534197</v>
       </c>
       <c r="Q62" t="n">
-        <v>-7.111037</v>
+        <v>-5.921343</v>
       </c>
       <c r="R62" t="n">
-        <v>-9.800769000000001</v>
+        <v>-10.006251</v>
       </c>
       <c r="S62" t="n">
-        <v>5.436218</v>
+        <v>4.157634</v>
       </c>
       <c r="T62" t="n">
-        <v>4.685851</v>
+        <v>2.387128</v>
       </c>
       <c r="U62" t="n">
-        <v>3.294886</v>
+        <v>0.864517</v>
       </c>
       <c r="V62" t="n">
-        <v>0.397043</v>
+        <v>0.919813</v>
       </c>
       <c r="W62" t="n">
-        <v>-2.401238</v>
+        <v>-1.53736</v>
       </c>
       <c r="X62" t="n">
-        <v>2.881702</v>
+        <v>3.028281</v>
       </c>
       <c r="Y62" t="n">
-        <v>-3.675929</v>
+        <v>-2.732466</v>
       </c>
       <c r="Z62" t="n">
-        <v>13.769083</v>
+        <v>10.639242</v>
       </c>
       <c r="AA62" t="n">
-        <v>8.132906999999999</v>
+        <v>5.640881</v>
       </c>
       <c r="AB62" t="n">
-        <v>-3.441609</v>
+        <v>-3.344934</v>
       </c>
       <c r="AC62" t="n">
-        <v>-9.335996</v>
+        <v>-9.835247000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5884,88 +5884,88 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>176027.578125</v>
+        <v>171106.125</v>
       </c>
       <c r="C62" t="n">
-        <v>173.179993</v>
+        <v>168.339996</v>
       </c>
       <c r="D62" t="n">
-        <v>100.730003</v>
+        <v>94.989998</v>
       </c>
       <c r="E62" t="n">
-        <v>465.970001</v>
+        <v>469.320007</v>
       </c>
       <c r="F62" t="n">
-        <v>5.3271</v>
+        <v>5.3707</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9472</v>
+        <v>5.9943</v>
       </c>
       <c r="H62" t="n">
-        <v>7721.919922</v>
+        <v>7734.149902</v>
       </c>
       <c r="I62" t="n">
-        <v>26448.109375</v>
+        <v>26453.009766</v>
       </c>
       <c r="J62" t="n">
-        <v>52447.628906</v>
+        <v>52486.179688</v>
       </c>
       <c r="K62" t="n">
-        <v>4072.300049</v>
+        <v>4051.699951</v>
       </c>
       <c r="L62" t="n">
-        <v>100.040001</v>
+        <v>103.459999</v>
       </c>
       <c r="M62" t="n">
-        <v>109.370003</v>
+        <v>112.5</v>
       </c>
       <c r="N62" t="n">
-        <v>1249.75</v>
+        <v>1243</v>
       </c>
       <c r="O62" t="n">
-        <v>451.5</v>
+        <v>451.75</v>
       </c>
       <c r="P62" t="n">
-        <v>-5.534197</v>
+        <v>-8.175311000000001</v>
       </c>
       <c r="Q62" t="n">
-        <v>-5.921343</v>
+        <v>-8.550632999999999</v>
       </c>
       <c r="R62" t="n">
-        <v>-10.006251</v>
+        <v>-15.134461</v>
       </c>
       <c r="S62" t="n">
-        <v>4.157634</v>
+        <v>4.906456</v>
       </c>
       <c r="T62" t="n">
-        <v>2.387128</v>
+        <v>3.225124</v>
       </c>
       <c r="U62" t="n">
-        <v>0.864517</v>
+        <v>1.663334</v>
       </c>
       <c r="V62" t="n">
-        <v>0.919813</v>
+        <v>1.07965</v>
       </c>
       <c r="W62" t="n">
-        <v>-1.53736</v>
+        <v>-1.519116</v>
       </c>
       <c r="X62" t="n">
-        <v>3.028281</v>
+        <v>3.10401</v>
       </c>
       <c r="Y62" t="n">
-        <v>-2.732466</v>
+        <v>-3.224502</v>
       </c>
       <c r="Z62" t="n">
-        <v>10.639242</v>
+        <v>14.421589</v>
       </c>
       <c r="AA62" t="n">
-        <v>5.640881</v>
+        <v>8.664156999999999</v>
       </c>
       <c r="AB62" t="n">
-        <v>-3.344934</v>
+        <v>-3.866976</v>
       </c>
       <c r="AC62" t="n">
-        <v>-9.835247000000001</v>
+        <v>-9.785322000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -592,9 +592,7 @@
       <c r="H2" t="n">
         <v>4605.379883</v>
       </c>
-      <c r="I2" t="n">
-        <v>15498.389648</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
         <v>35819.558594</v>
       </c>
@@ -653,9 +651,7 @@
       <c r="H3" t="n">
         <v>4567</v>
       </c>
-      <c r="I3" t="n">
-        <v>15537.69043</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
         <v>34483.71875</v>
       </c>
@@ -695,9 +691,7 @@
       <c r="V3" t="n">
         <v>-0.833371</v>
       </c>
-      <c r="W3" t="n">
-        <v>0.25358</v>
-      </c>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>-3.729359</v>
       </c>
@@ -742,9 +736,7 @@
       <c r="H4" t="n">
         <v>4766.180176</v>
       </c>
-      <c r="I4" t="n">
-        <v>15644.969727</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>36338.300781</v>
       </c>
@@ -784,9 +776,7 @@
       <c r="V4" t="n">
         <v>4.361291</v>
       </c>
-      <c r="W4" t="n">
-        <v>0.690446</v>
-      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>5.378138</v>
       </c>
@@ -831,9 +821,7 @@
       <c r="H5" t="n">
         <v>4515.549805</v>
       </c>
-      <c r="I5" t="n">
-        <v>14239.879883</v>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>35131.859375</v>
       </c>
@@ -873,9 +861,7 @@
       <c r="V5" t="n">
         <v>-5.258517</v>
       </c>
-      <c r="W5" t="n">
-        <v>-8.981097</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
         <v>-3.320027</v>
       </c>
@@ -920,9 +906,7 @@
       <c r="H6" t="n">
         <v>4373.939941</v>
       </c>
-      <c r="I6" t="n">
-        <v>13751.400391</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>33892.601562</v>
       </c>
@@ -962,9 +946,7 @@
       <c r="V6" t="n">
         <v>-3.136049</v>
       </c>
-      <c r="W6" t="n">
-        <v>-3.430362</v>
-      </c>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>-3.527447</v>
       </c>
@@ -1009,9 +991,7 @@
       <c r="H7" t="n">
         <v>4530.410156</v>
       </c>
-      <c r="I7" t="n">
-        <v>14220.519531</v>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>34678.351562</v>
       </c>
@@ -1051,9 +1031,7 @@
       <c r="V7" t="n">
         <v>3.577329</v>
       </c>
-      <c r="W7" t="n">
-        <v>3.411428</v>
-      </c>
+      <c r="W7" t="inlineStr"/>
       <c r="X7" t="n">
         <v>2.318353</v>
       </c>
@@ -1098,9 +1076,7 @@
       <c r="H8" t="n">
         <v>4131.930176</v>
       </c>
-      <c r="I8" t="n">
-        <v>12334.639648</v>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>32977.210938</v>
       </c>
@@ -1140,9 +1116,7 @@
       <c r="V8" t="n">
         <v>-8.795671</v>
       </c>
-      <c r="W8" t="n">
-        <v>-13.261681</v>
-      </c>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>-4.905483</v>
       </c>
@@ -1187,9 +1161,7 @@
       <c r="H9" t="n">
         <v>4132.149902</v>
       </c>
-      <c r="I9" t="n">
-        <v>12081.389648</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
         <v>32990.121094</v>
       </c>
@@ -1229,9 +1201,7 @@
       <c r="V9" t="n">
         <v>0.005318</v>
       </c>
-      <c r="W9" t="n">
-        <v>-2.053161</v>
-      </c>
+      <c r="W9" t="inlineStr"/>
       <c r="X9" t="n">
         <v>0.039149</v>
       </c>
@@ -1276,9 +1246,7 @@
       <c r="H10" t="n">
         <v>3785.379883</v>
       </c>
-      <c r="I10" t="n">
-        <v>11028.740234</v>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
         <v>30775.429688</v>
       </c>
@@ -1318,9 +1286,7 @@
       <c r="V10" t="n">
         <v>-8.391999999999999</v>
       </c>
-      <c r="W10" t="n">
-        <v>-8.712982999999999</v>
-      </c>
+      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>-6.713196</v>
       </c>
@@ -1365,9 +1331,7 @@
       <c r="H11" t="n">
         <v>4130.290039</v>
       </c>
-      <c r="I11" t="n">
-        <v>12390.69043</v>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
         <v>32845.128906</v>
       </c>
@@ -1407,9 +1371,7 @@
       <c r="V11" t="n">
         <v>9.111639</v>
       </c>
-      <c r="W11" t="n">
-        <v>12.3491</v>
-      </c>
+      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>6.725168</v>
       </c>
@@ -1454,9 +1416,7 @@
       <c r="H12" t="n">
         <v>3955</v>
       </c>
-      <c r="I12" t="n">
-        <v>11816.200195</v>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
         <v>31510.429688</v>
       </c>
@@ -1496,9 +1456,7 @@
       <c r="V12" t="n">
         <v>-4.244013</v>
       </c>
-      <c r="W12" t="n">
-        <v>-4.636467</v>
-      </c>
+      <c r="W12" t="inlineStr"/>
       <c r="X12" t="n">
         <v>-4.063614</v>
       </c>
@@ -1543,9 +1501,7 @@
       <c r="H13" t="n">
         <v>3585.620117</v>
       </c>
-      <c r="I13" t="n">
-        <v>10575.620117</v>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
         <v>28725.509766</v>
       </c>
@@ -1585,9 +1541,7 @@
       <c r="V13" t="n">
         <v>-9.339567000000001</v>
       </c>
-      <c r="W13" t="n">
-        <v>-10.498976</v>
-      </c>
+      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
         <v>-8.838089</v>
       </c>
@@ -1632,9 +1586,7 @@
       <c r="H14" t="n">
         <v>3871.97998</v>
       </c>
-      <c r="I14" t="n">
-        <v>10988.150391</v>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
         <v>32732.949219</v>
       </c>
@@ -1674,9 +1626,7 @@
       <c r="V14" t="n">
         <v>7.986341</v>
       </c>
-      <c r="W14" t="n">
-        <v>3.900767</v>
-      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>13.950804</v>
       </c>
@@ -1721,9 +1671,7 @@
       <c r="H15" t="n">
         <v>4080.110107</v>
       </c>
-      <c r="I15" t="n">
-        <v>11468</v>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
         <v>34589.769531</v>
       </c>
@@ -1763,9 +1711,7 @@
       <c r="V15" t="n">
         <v>5.375289</v>
       </c>
-      <c r="W15" t="n">
-        <v>4.366973</v>
-      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>5.672634</v>
       </c>
@@ -1810,9 +1756,7 @@
       <c r="H16" t="n">
         <v>3839.5</v>
       </c>
-      <c r="I16" t="n">
-        <v>10466.480469</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
         <v>33147.25</v>
       </c>
@@ -1852,9 +1796,7 @@
       <c r="V16" t="n">
         <v>-5.897147</v>
       </c>
-      <c r="W16" t="n">
-        <v>-8.733166000000001</v>
-      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
         <v>-4.170365</v>
       </c>
@@ -1899,9 +1841,7 @@
       <c r="H17" t="n">
         <v>4076.600098</v>
       </c>
-      <c r="I17" t="n">
-        <v>11584.549805</v>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="n">
         <v>34086.039062</v>
       </c>
@@ -1941,9 +1881,7 @@
       <c r="V17" t="n">
         <v>6.175286</v>
       </c>
-      <c r="W17" t="n">
-        <v>10.682381</v>
-      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
         <v>2.832178</v>
       </c>
@@ -1988,9 +1926,7 @@
       <c r="H18" t="n">
         <v>3970.149902</v>
       </c>
-      <c r="I18" t="n">
-        <v>11455.540039</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="n">
         <v>32656.699219</v>
       </c>
@@ -2030,9 +1966,7 @@
       <c r="V18" t="n">
         <v>-2.611249</v>
       </c>
-      <c r="W18" t="n">
-        <v>-1.113636</v>
-      </c>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
         <v>-4.193329</v>
       </c>
@@ -2077,9 +2011,7 @@
       <c r="H19" t="n">
         <v>4109.310059</v>
       </c>
-      <c r="I19" t="n">
-        <v>12221.910156</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
         <v>33274.148438</v>
       </c>
@@ -2119,9 +2051,7 @@
       <c r="V19" t="n">
         <v>3.505161</v>
       </c>
-      <c r="W19" t="n">
-        <v>6.689952</v>
-      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
         <v>1.890728</v>
       </c>
@@ -2166,9 +2096,7 @@
       <c r="H20" t="n">
         <v>4169.47998</v>
       </c>
-      <c r="I20" t="n">
-        <v>12226.580078</v>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
         <v>34098.160156</v>
       </c>
@@ -2208,9 +2136,7 @@
       <c r="V20" t="n">
         <v>1.464234</v>
       </c>
-      <c r="W20" t="n">
-        <v>0.038209</v>
-      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
         <v>2.476432</v>
       </c>
@@ -2255,9 +2181,7 @@
       <c r="H21" t="n">
         <v>4179.830078</v>
       </c>
-      <c r="I21" t="n">
-        <v>12935.290039</v>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
         <v>32908.269531</v>
       </c>
@@ -2297,9 +2221,7 @@
       <c r="V21" t="n">
         <v>0.248235</v>
       </c>
-      <c r="W21" t="n">
-        <v>5.796469</v>
-      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
         <v>-3.489604</v>
       </c>
@@ -2344,9 +2266,7 @@
       <c r="H22" t="n">
         <v>4450.379883</v>
       </c>
-      <c r="I22" t="n">
-        <v>13787.919922</v>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
         <v>34407.601562</v>
       </c>
@@ -2386,9 +2306,7 @@
       <c r="V22" t="n">
         <v>6.472746</v>
       </c>
-      <c r="W22" t="n">
-        <v>6.591502</v>
-      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
         <v>4.556095</v>
       </c>
@@ -2433,9 +2351,7 @@
       <c r="H23" t="n">
         <v>4588.959961</v>
       </c>
-      <c r="I23" t="n">
-        <v>14346.019531</v>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
         <v>35559.53125</v>
       </c>
@@ -2475,9 +2391,7 @@
       <c r="V23" t="n">
         <v>3.113893</v>
       </c>
-      <c r="W23" t="n">
-        <v>4.047743</v>
-      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="n">
         <v>3.347893</v>
       </c>
@@ -2522,9 +2436,7 @@
       <c r="H24" t="n">
         <v>4507.660156</v>
       </c>
-      <c r="I24" t="n">
-        <v>14034.969727</v>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
         <v>34721.910156</v>
       </c>
@@ -2564,9 +2476,7 @@
       <c r="V24" t="n">
         <v>-1.771639</v>
       </c>
-      <c r="W24" t="n">
-        <v>-2.168196</v>
-      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="n">
         <v>-2.355546</v>
       </c>
@@ -2611,9 +2521,7 @@
       <c r="H25" t="n">
         <v>4288.049805</v>
       </c>
-      <c r="I25" t="n">
-        <v>13219.320312</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
         <v>33507.5</v>
       </c>
@@ -2653,9 +2561,7 @@
       <c r="V25" t="n">
         <v>-4.871937</v>
       </c>
-      <c r="W25" t="n">
-        <v>-5.811551</v>
-      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="n">
         <v>-3.497533</v>
       </c>
@@ -2700,9 +2606,7 @@
       <c r="H26" t="n">
         <v>4193.799805</v>
       </c>
-      <c r="I26" t="n">
-        <v>12851.240234</v>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
         <v>33052.871094</v>
       </c>
@@ -2742,9 +2646,7 @@
       <c r="V26" t="n">
         <v>-2.197969</v>
       </c>
-      <c r="W26" t="n">
-        <v>-2.78441</v>
-      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="n">
         <v>-1.356797</v>
       </c>
@@ -2789,9 +2691,7 @@
       <c r="H27" t="n">
         <v>4567.799805</v>
       </c>
-      <c r="I27" t="n">
-        <v>14226.219727</v>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
         <v>35950.890625</v>
       </c>
@@ -2831,9 +2731,7 @@
       <c r="V27" t="n">
         <v>8.917927000000001</v>
       </c>
-      <c r="W27" t="n">
-        <v>10.699197</v>
-      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="n">
         <v>8.76783</v>
       </c>
@@ -2878,9 +2776,7 @@
       <c r="H28" t="n">
         <v>4769.830078</v>
       </c>
-      <c r="I28" t="n">
-        <v>15011.349609</v>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
         <v>37689.539062</v>
       </c>
@@ -2920,9 +2816,7 @@
       <c r="V28" t="n">
         <v>4.422923</v>
       </c>
-      <c r="W28" t="n">
-        <v>5.518893</v>
-      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="n">
         <v>4.836176</v>
       </c>
@@ -2967,9 +2861,7 @@
       <c r="H29" t="n">
         <v>4845.649902</v>
       </c>
-      <c r="I29" t="n">
-        <v>15164.009766</v>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
         <v>38150.300781</v>
       </c>
@@ -3009,9 +2901,7 @@
       <c r="V29" t="n">
         <v>1.589571</v>
       </c>
-      <c r="W29" t="n">
-        <v>1.016965</v>
-      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="n">
         <v>1.222519</v>
       </c>
@@ -3056,9 +2946,7 @@
       <c r="H30" t="n">
         <v>5096.27002</v>
       </c>
-      <c r="I30" t="n">
-        <v>16091.919922</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
         <v>38996.390625</v>
       </c>
@@ -3098,9 +2986,7 @@
       <c r="V30" t="n">
         <v>5.172064</v>
       </c>
-      <c r="W30" t="n">
-        <v>6.119161</v>
-      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="n">
         <v>2.21778</v>
       </c>
@@ -3145,9 +3031,7 @@
       <c r="H31" t="n">
         <v>5254.350098</v>
       </c>
-      <c r="I31" t="n">
-        <v>16379.459961</v>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
         <v>39807.371094</v>
       </c>
@@ -3187,9 +3071,7 @@
       <c r="V31" t="n">
         <v>3.101878</v>
       </c>
-      <c r="W31" t="n">
-        <v>1.78686</v>
-      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="n">
         <v>2.07963</v>
       </c>
@@ -3234,9 +3116,7 @@
       <c r="H32" t="n">
         <v>5035.689941</v>
       </c>
-      <c r="I32" t="n">
-        <v>15657.820312</v>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
         <v>37815.921875</v>
       </c>
@@ -3276,9 +3156,7 @@
       <c r="V32" t="n">
         <v>-4.161507</v>
       </c>
-      <c r="W32" t="n">
-        <v>-4.40576</v>
-      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="n">
         <v>-5.002715</v>
       </c>
@@ -3323,9 +3201,7 @@
       <c r="H33" t="n">
         <v>5277.509766</v>
       </c>
-      <c r="I33" t="n">
-        <v>16735.019531</v>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
         <v>38686.320312</v>
       </c>
@@ -3365,9 +3241,7 @@
       <c r="V33" t="n">
         <v>4.802119</v>
       </c>
-      <c r="W33" t="n">
-        <v>6.879624</v>
-      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="n">
         <v>2.301672</v>
       </c>
@@ -3412,9 +3286,7 @@
       <c r="H34" t="n">
         <v>5460.47998</v>
       </c>
-      <c r="I34" t="n">
-        <v>17732.599609</v>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
         <v>39118.859375</v>
       </c>
@@ -3454,9 +3326,7 @@
       <c r="V34" t="n">
         <v>3.46698</v>
       </c>
-      <c r="W34" t="n">
-        <v>5.961033</v>
-      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="n">
         <v>1.118067</v>
       </c>
@@ -3501,9 +3371,7 @@
       <c r="H35" t="n">
         <v>5522.299805</v>
       </c>
-      <c r="I35" t="n">
-        <v>17599.400391</v>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
         <v>40842.789062</v>
       </c>
@@ -3543,9 +3411,7 @@
       <c r="V35" t="n">
         <v>1.132132</v>
       </c>
-      <c r="W35" t="n">
-        <v>-0.751154</v>
-      </c>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="n">
         <v>4.406902</v>
       </c>
@@ -3590,9 +3456,7 @@
       <c r="H36" t="n">
         <v>5648.399902</v>
       </c>
-      <c r="I36" t="n">
-        <v>17713.619141</v>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
         <v>41563.078125</v>
       </c>
@@ -3632,9 +3496,7 @@
       <c r="V36" t="n">
         <v>2.283471</v>
       </c>
-      <c r="W36" t="n">
-        <v>0.648992</v>
-      </c>
+      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>1.763565</v>
       </c>
@@ -3679,9 +3541,7 @@
       <c r="H37" t="n">
         <v>5762.47998</v>
       </c>
-      <c r="I37" t="n">
-        <v>18189.169922</v>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
         <v>42330.148438</v>
       </c>
@@ -3721,9 +3581,7 @@
       <c r="V37" t="n">
         <v>2.019688</v>
       </c>
-      <c r="W37" t="n">
-        <v>2.684662</v>
-      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>1.845557</v>
       </c>
@@ -3768,9 +3626,7 @@
       <c r="H38" t="n">
         <v>5705.450195</v>
       </c>
-      <c r="I38" t="n">
-        <v>18095.150391</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
         <v>41763.460938</v>
       </c>
@@ -3810,9 +3666,7 @@
       <c r="V38" t="n">
         <v>-0.9896740000000001</v>
       </c>
-      <c r="W38" t="n">
-        <v>-0.516898</v>
-      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
         <v>-1.338733</v>
       </c>
@@ -3857,9 +3711,7 @@
       <c r="H39" t="n">
         <v>6032.379883</v>
       </c>
-      <c r="I39" t="n">
-        <v>19218.169922</v>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="n">
         <v>44910.648438</v>
       </c>
@@ -3899,9 +3751,7 @@
       <c r="V39" t="n">
         <v>5.73013</v>
       </c>
-      <c r="W39" t="n">
-        <v>6.206191</v>
-      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="n">
         <v>7.535744</v>
       </c>
@@ -3946,9 +3796,7 @@
       <c r="H40" t="n">
         <v>5881.629883</v>
       </c>
-      <c r="I40" t="n">
-        <v>19310.789062</v>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
         <v>42544.21875</v>
       </c>
@@ -3988,9 +3836,7 @@
       <c r="V40" t="n">
         <v>-2.499014</v>
       </c>
-      <c r="W40" t="n">
-        <v>0.481935</v>
-      </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>-5.269195</v>
       </c>
@@ -4035,9 +3881,7 @@
       <c r="H41" t="n">
         <v>6040.529785</v>
       </c>
-      <c r="I41" t="n">
-        <v>19627.439453</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="n">
         <v>44544.660156</v>
       </c>
@@ -4077,9 +3921,7 @@
       <c r="V41" t="n">
         <v>2.70163</v>
       </c>
-      <c r="W41" t="n">
-        <v>1.639759</v>
-      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>4.702029</v>
       </c>
@@ -4124,9 +3966,7 @@
       <c r="H42" t="n">
         <v>5954.5</v>
       </c>
-      <c r="I42" t="n">
-        <v>18847.279297</v>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="n">
         <v>43840.910156</v>
       </c>
@@ -4166,9 +4006,7 @@
       <c r="V42" t="n">
         <v>-1.424209</v>
       </c>
-      <c r="W42" t="n">
-        <v>-3.974844</v>
-      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
         <v>-1.579875</v>
       </c>
@@ -4213,9 +4051,7 @@
       <c r="H43" t="n">
         <v>5611.850098</v>
       </c>
-      <c r="I43" t="n">
-        <v>17299.289062</v>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="n">
         <v>42001.761719</v>
       </c>
@@ -4255,9 +4091,7 @@
       <c r="V43" t="n">
         <v>-5.75447</v>
       </c>
-      <c r="W43" t="n">
-        <v>-8.213335000000001</v>
-      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>-4.195051</v>
       </c>
@@ -4302,9 +4136,7 @@
       <c r="H44" t="n">
         <v>5569.060059</v>
       </c>
-      <c r="I44" t="n">
-        <v>17446.339844</v>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="n">
         <v>40669.359375</v>
       </c>
@@ -4344,9 +4176,7 @@
       <c r="V44" t="n">
         <v>-0.762494</v>
       </c>
-      <c r="W44" t="n">
-        <v>0.850039</v>
-      </c>
+      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>-3.172253</v>
       </c>
@@ -4391,9 +4221,7 @@
       <c r="H45" t="n">
         <v>5911.689941</v>
       </c>
-      <c r="I45" t="n">
-        <v>19113.769531</v>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="n">
         <v>42270.070312</v>
       </c>
@@ -4433,9 +4261,7 @@
       <c r="V45" t="n">
         <v>6.152383</v>
       </c>
-      <c r="W45" t="n">
-        <v>9.557475999999999</v>
-      </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
         <v>3.935914</v>
       </c>
@@ -4480,9 +4306,7 @@
       <c r="H46" t="n">
         <v>6204.950195</v>
       </c>
-      <c r="I46" t="n">
-        <v>20369.730469</v>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="n">
         <v>44094.769531</v>
       </c>
@@ -4522,9 +4346,7 @@
       <c r="V46" t="n">
         <v>4.960684</v>
       </c>
-      <c r="W46" t="n">
-        <v>6.570975</v>
-      </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>4.316764</v>
       </c>
@@ -4569,9 +4391,7 @@
       <c r="H47" t="n">
         <v>6339.390137</v>
       </c>
-      <c r="I47" t="n">
-        <v>21122.449219</v>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="n">
         <v>44130.980469</v>
       </c>
@@ -4611,9 +4431,7 @@
       <c r="V47" t="n">
         <v>2.166656</v>
       </c>
-      <c r="W47" t="n">
-        <v>3.695281</v>
-      </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
         <v>0.082121</v>
       </c>
@@ -4658,9 +4476,7 @@
       <c r="H48" t="n">
         <v>6460.259766</v>
       </c>
-      <c r="I48" t="n">
-        <v>21455.550781</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="n">
         <v>45544.878906</v>
       </c>
@@ -4700,9 +4516,7 @@
       <c r="V48" t="n">
         <v>1.906644</v>
       </c>
-      <c r="W48" t="n">
-        <v>1.577003</v>
-      </c>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>3.203868</v>
       </c>
@@ -4747,9 +4561,7 @@
       <c r="H49" t="n">
         <v>6688.459961</v>
       </c>
-      <c r="I49" t="n">
-        <v>22660.009766</v>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="n">
         <v>46397.890625</v>
       </c>
@@ -4789,9 +4601,7 @@
       <c r="V49" t="n">
         <v>3.532369</v>
       </c>
-      <c r="W49" t="n">
-        <v>5.613741</v>
-      </c>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="n">
         <v>1.872904</v>
       </c>
@@ -4836,9 +4646,7 @@
       <c r="H50" t="n">
         <v>6840.200195</v>
       </c>
-      <c r="I50" t="n">
-        <v>23724.960938</v>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
         <v>47562.871094</v>
       </c>
@@ -4878,9 +4686,7 @@
       <c r="V50" t="n">
         <v>2.268687</v>
       </c>
-      <c r="W50" t="n">
-        <v>4.699694</v>
-      </c>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="n">
         <v>2.510848</v>
       </c>
@@ -4925,9 +4731,7 @@
       <c r="H51" t="n">
         <v>6849.089844</v>
       </c>
-      <c r="I51" t="n">
-        <v>23365.689453</v>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="n">
         <v>47716.421875</v>
       </c>
@@ -4967,9 +4771,7 @@
       <c r="V51" t="n">
         <v>0.129962</v>
       </c>
-      <c r="W51" t="n">
-        <v>-1.514319</v>
-      </c>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>0.322837</v>
       </c>
@@ -5014,9 +4816,7 @@
       <c r="H52" t="n">
         <v>6845.5</v>
       </c>
-      <c r="I52" t="n">
-        <v>23241.990234</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="n">
         <v>48063.289062</v>
       </c>
@@ -5056,9 +4856,7 @@
       <c r="V52" t="n">
         <v>-0.052413</v>
       </c>
-      <c r="W52" t="n">
-        <v>-0.529405</v>
-      </c>
+      <c r="W52" t="inlineStr"/>
       <c r="X52" t="n">
         <v>0.726935</v>
       </c>
@@ -5103,9 +4901,7 @@
       <c r="H53" t="n">
         <v>6939.029785</v>
       </c>
-      <c r="I53" t="n">
-        <v>23461.820312</v>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="n">
         <v>48892.46875</v>
       </c>
@@ -5145,9 +4941,7 @@
       <c r="V53" t="n">
         <v>1.366296</v>
       </c>
-      <c r="W53" t="n">
-        <v>0.945832</v>
-      </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="n">
         <v>1.725183</v>
       </c>
@@ -5192,9 +4986,7 @@
       <c r="H54" t="n">
         <v>6878.879883</v>
       </c>
-      <c r="I54" t="n">
-        <v>22668.210938</v>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="n">
         <v>48977.921875</v>
       </c>
@@ -5234,9 +5026,7 @@
       <c r="V54" t="n">
         <v>-0.866834</v>
       </c>
-      <c r="W54" t="n">
-        <v>-3.382557</v>
-      </c>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="n">
         <v>0.174778</v>
       </c>
@@ -5281,9 +5071,7 @@
       <c r="H55" t="n">
         <v>6528.52002</v>
       </c>
-      <c r="I55" t="n">
-        <v>21590.630859</v>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="n">
         <v>46341.511719</v>
       </c>
@@ -5323,9 +5111,7 @@
       <c r="V55" t="n">
         <v>-5.093269</v>
       </c>
-      <c r="W55" t="n">
-        <v>-4.753706</v>
-      </c>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>-5.382854</v>
       </c>
@@ -5370,9 +5156,7 @@
       <c r="H56" t="n">
         <v>7209.009766</v>
       </c>
-      <c r="I56" t="n">
-        <v>24892.310547</v>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="n">
         <v>49652.140625</v>
       </c>
@@ -5412,9 +5196,7 @@
       <c r="V56" t="n">
         <v>10.423339</v>
       </c>
-      <c r="W56" t="n">
-        <v>15.292187</v>
-      </c>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
         <v>7.143981</v>
       </c>
@@ -5459,9 +5241,7 @@
       <c r="H57" t="n">
         <v>7580.060059</v>
       </c>
-      <c r="I57" t="n">
-        <v>26972.619141</v>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="n">
         <v>51032.460938</v>
       </c>
@@ -5501,9 +5281,7 @@
       <c r="V57" t="n">
         <v>5.147036</v>
       </c>
-      <c r="W57" t="n">
-        <v>8.357234</v>
-      </c>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="n">
         <v>2.779981</v>
       </c>
@@ -5548,9 +5326,7 @@
       <c r="H58" t="n">
         <v>7499.359863</v>
       </c>
-      <c r="I58" t="n">
-        <v>26213.720703</v>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="n">
         <v>52319.199219</v>
       </c>
@@ -5590,9 +5366,7 @@
       <c r="V58" t="n">
         <v>-1.064638</v>
       </c>
-      <c r="W58" t="n">
-        <v>-2.813588</v>
-      </c>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="n">
         <v>2.521411</v>
       </c>
@@ -5637,9 +5411,7 @@
       <c r="H59" t="n">
         <v>7489.720215</v>
       </c>
-      <c r="I59" t="n">
-        <v>25373.849609</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>52485.03125</v>
       </c>
@@ -5679,9 +5451,7 @@
       <c r="V59" t="n">
         <v>-0.12854</v>
       </c>
-      <c r="W59" t="n">
-        <v>-3.203937</v>
-      </c>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="n">
         <v>0.316962</v>
       </c>
@@ -5726,9 +5496,7 @@
       <c r="H60" t="n">
         <v>7686.140137</v>
       </c>
-      <c r="I60" t="n">
-        <v>26370.890625</v>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
         <v>53185.898438</v>
       </c>
@@ -5768,9 +5536,7 @@
       <c r="V60" t="n">
         <v>2.622527</v>
       </c>
-      <c r="W60" t="n">
-        <v>3.929404</v>
-      </c>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="n">
         <v>1.335366</v>
       </c>
@@ -5815,9 +5581,7 @@
       <c r="H61" t="n">
         <v>7651.540039</v>
       </c>
-      <c r="I61" t="n">
-        <v>26861.060547</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
         <v>50906.050781</v>
       </c>
@@ -5857,9 +5621,7 @@
       <c r="V61" t="n">
         <v>-0.450162</v>
       </c>
-      <c r="W61" t="n">
-        <v>1.858754</v>
-      </c>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="n">
         <v>-4.286564</v>
       </c>
@@ -5884,88 +5646,84 @@
         <v>46326</v>
       </c>
       <c r="B62" t="n">
-        <v>171106.125</v>
+        <v>169332.734375</v>
       </c>
       <c r="C62" t="n">
-        <v>168.339996</v>
+        <v>166.600006</v>
       </c>
       <c r="D62" t="n">
-        <v>94.989998</v>
+        <v>93.900002</v>
       </c>
       <c r="E62" t="n">
-        <v>469.320007</v>
+        <v>471</v>
       </c>
       <c r="F62" t="n">
-        <v>5.3707</v>
+        <v>5.4112</v>
       </c>
       <c r="G62" t="n">
-        <v>5.9943</v>
+        <v>6.0453</v>
       </c>
       <c r="H62" t="n">
-        <v>7734.149902</v>
-      </c>
-      <c r="I62" t="n">
-        <v>26453.009766</v>
-      </c>
+        <v>7711.899902</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="n">
-        <v>52486.179688</v>
+        <v>52266.71875</v>
       </c>
       <c r="K62" t="n">
-        <v>4051.699951</v>
+        <v>4027.5</v>
       </c>
       <c r="L62" t="n">
-        <v>103.459999</v>
+        <v>100.889999</v>
       </c>
       <c r="M62" t="n">
-        <v>112.5</v>
+        <v>109.889999</v>
       </c>
       <c r="N62" t="n">
-        <v>1243</v>
+        <v>1235.5</v>
       </c>
       <c r="O62" t="n">
-        <v>451.75</v>
+        <v>452.5</v>
       </c>
       <c r="P62" t="n">
-        <v>-8.175311000000001</v>
+        <v>-9.127007000000001</v>
       </c>
       <c r="Q62" t="n">
-        <v>-8.550632999999999</v>
+        <v>-9.495869000000001</v>
       </c>
       <c r="R62" t="n">
-        <v>-15.134461</v>
+        <v>-16.108281</v>
       </c>
       <c r="S62" t="n">
-        <v>4.906456</v>
+        <v>5.281983</v>
       </c>
       <c r="T62" t="n">
-        <v>3.225124</v>
+        <v>4.003539</v>
       </c>
       <c r="U62" t="n">
-        <v>1.663334</v>
+        <v>2.528297</v>
       </c>
       <c r="V62" t="n">
-        <v>1.07965</v>
-      </c>
-      <c r="W62" t="n">
-        <v>-1.519116</v>
-      </c>
+        <v>0.788859</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="n">
-        <v>3.10401</v>
+        <v>2.6729</v>
       </c>
       <c r="Y62" t="n">
-        <v>-3.224502</v>
+        <v>-3.802522</v>
       </c>
       <c r="Z62" t="n">
-        <v>14.421589</v>
+        <v>11.579298</v>
       </c>
       <c r="AA62" t="n">
-        <v>8.664156999999999</v>
+        <v>6.143148</v>
       </c>
       <c r="AB62" t="n">
-        <v>-3.866976</v>
+        <v>-4.447022</v>
       </c>
       <c r="AC62" t="n">
-        <v>-9.785322000000001</v>
+        <v>-9.635547000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,47 +569,49 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44500</v>
+        <v>44530</v>
       </c>
       <c r="B2" t="n">
-        <v>103501</v>
+        <v>101915</v>
       </c>
       <c r="C2" t="n">
-        <v>99.68000000000001</v>
+        <v>98.349998</v>
       </c>
       <c r="D2" t="n">
-        <v>111.199997</v>
+        <v>108.800003</v>
       </c>
       <c r="E2" t="n">
-        <v>283</v>
+        <v>280.549988</v>
       </c>
       <c r="F2" t="n">
-        <v>5.6449</v>
+        <v>5.6007</v>
       </c>
       <c r="G2" t="n">
-        <v>6.593</v>
+        <v>6.3223</v>
       </c>
       <c r="H2" t="n">
-        <v>4605.379883</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>4567</v>
+      </c>
+      <c r="I2" t="n">
+        <v>15537.69043</v>
+      </c>
       <c r="J2" t="n">
-        <v>35819.558594</v>
+        <v>34483.71875</v>
       </c>
       <c r="K2" t="n">
-        <v>1783.900024</v>
+        <v>1773.599976</v>
       </c>
       <c r="L2" t="n">
-        <v>83.56999999999999</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>84.379997</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>1235.75</v>
+        <v>1217.25</v>
       </c>
       <c r="O2" t="n">
-        <v>568.25</v>
+        <v>567</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -628,5102 +630,5253 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44530</v>
+        <v>44561</v>
       </c>
       <c r="B3" t="n">
-        <v>101915</v>
+        <v>104822</v>
       </c>
       <c r="C3" t="n">
-        <v>98.349998</v>
+        <v>100.800003</v>
       </c>
       <c r="D3" t="n">
-        <v>108.800003</v>
+        <v>113.300003</v>
       </c>
       <c r="E3" t="n">
-        <v>280.549988</v>
+        <v>293.559998</v>
       </c>
       <c r="F3" t="n">
-        <v>5.6007</v>
+        <v>5.5702</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3223</v>
+        <v>6.3049</v>
       </c>
       <c r="H3" t="n">
-        <v>4567</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>4766.180176</v>
+      </c>
+      <c r="I3" t="n">
+        <v>15644.969727</v>
+      </c>
       <c r="J3" t="n">
-        <v>34483.71875</v>
+        <v>36338.300781</v>
       </c>
       <c r="K3" t="n">
-        <v>1773.599976</v>
+        <v>1828.599976</v>
       </c>
       <c r="L3" t="n">
-        <v>66.18000000000001</v>
+        <v>75.209999</v>
       </c>
       <c r="M3" t="n">
-        <v>70.56999999999999</v>
+        <v>77.779999</v>
       </c>
       <c r="N3" t="n">
-        <v>1217.25</v>
+        <v>1328.75</v>
       </c>
       <c r="O3" t="n">
-        <v>567</v>
+        <v>593.25</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.532352</v>
+        <v>2.852377</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.334271</v>
+        <v>2.491108</v>
       </c>
       <c r="R3" t="n">
-        <v>-2.158268</v>
+        <v>4.136029</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.865729</v>
+        <v>4.637323</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.783007</v>
+        <v>-0.544574</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.10587</v>
+        <v>-0.275213</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.833371</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>4.361291</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.690446</v>
+      </c>
       <c r="X3" t="n">
-        <v>-3.729359</v>
+        <v>5.378138</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.577389</v>
+        <v>3.101037</v>
       </c>
       <c r="Z3" t="n">
-        <v>-20.808902</v>
+        <v>13.644604</v>
       </c>
       <c r="AA3" t="n">
-        <v>-16.366435</v>
+        <v>10.216805</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1.497067</v>
+        <v>9.159992000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.219974</v>
+        <v>4.62963</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="B4" t="n">
-        <v>104822</v>
+        <v>112388</v>
       </c>
       <c r="C4" t="n">
-        <v>100.800003</v>
+        <v>107.980003</v>
       </c>
       <c r="D4" t="n">
-        <v>113.300003</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>293.559998</v>
+        <v>260.399994</v>
       </c>
       <c r="F4" t="n">
-        <v>5.5702</v>
+        <v>5.3626</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3049</v>
+        <v>5.9782</v>
       </c>
       <c r="H4" t="n">
-        <v>4766.180176</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>4515.549805</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14239.879883</v>
+      </c>
       <c r="J4" t="n">
-        <v>36338.300781</v>
+        <v>35131.859375</v>
       </c>
       <c r="K4" t="n">
-        <v>1828.599976</v>
+        <v>1795</v>
       </c>
       <c r="L4" t="n">
-        <v>75.209999</v>
+        <v>88.150002</v>
       </c>
       <c r="M4" t="n">
-        <v>77.779999</v>
+        <v>91.209999</v>
       </c>
       <c r="N4" t="n">
-        <v>1328.75</v>
+        <v>1490.5</v>
       </c>
       <c r="O4" t="n">
-        <v>593.25</v>
+        <v>626</v>
       </c>
       <c r="P4" t="n">
-        <v>2.852377</v>
+        <v>7.21795</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.491108</v>
+        <v>7.123016</v>
       </c>
       <c r="R4" t="n">
-        <v>4.136029</v>
+        <v>3.265664</v>
       </c>
       <c r="S4" t="n">
-        <v>4.637323</v>
+        <v>-11.295818</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.544574</v>
+        <v>-3.726978</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.275213</v>
+        <v>-5.181687</v>
       </c>
       <c r="V4" t="n">
-        <v>4.361291</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
+        <v>-5.258517</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-8.981097</v>
+      </c>
       <c r="X4" t="n">
-        <v>5.378138</v>
+        <v>-3.320027</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.101037</v>
+        <v>-1.83747</v>
       </c>
       <c r="Z4" t="n">
-        <v>13.644604</v>
+        <v>17.205162</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.216805</v>
+        <v>17.26665</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.159992000000001</v>
+        <v>12.173095</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.62963</v>
+        <v>5.520438</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44592</v>
+        <v>44620</v>
       </c>
       <c r="B5" t="n">
-        <v>112388</v>
+        <v>113142</v>
       </c>
       <c r="C5" t="n">
-        <v>107.980003</v>
+        <v>108.900002</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>111.040001</v>
       </c>
       <c r="E5" t="n">
-        <v>260.399994</v>
+        <v>245.5</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3626</v>
+        <v>5.1594</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9782</v>
+        <v>5.814</v>
       </c>
       <c r="H5" t="n">
-        <v>4515.549805</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>4373.939941</v>
+      </c>
+      <c r="I5" t="n">
+        <v>13751.400391</v>
+      </c>
       <c r="J5" t="n">
-        <v>35131.859375</v>
+        <v>33892.601562</v>
       </c>
       <c r="K5" t="n">
-        <v>1795</v>
+        <v>1900.699951</v>
       </c>
       <c r="L5" t="n">
-        <v>88.150002</v>
+        <v>95.720001</v>
       </c>
       <c r="M5" t="n">
-        <v>91.209999</v>
+        <v>100.989998</v>
       </c>
       <c r="N5" t="n">
-        <v>1490.5</v>
+        <v>1644.25</v>
       </c>
       <c r="O5" t="n">
-        <v>626</v>
+        <v>697.5</v>
       </c>
       <c r="P5" t="n">
-        <v>7.21795</v>
+        <v>0.67089</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.123016</v>
+        <v>0.852008</v>
       </c>
       <c r="R5" t="n">
-        <v>3.265664</v>
+        <v>-5.094016</v>
       </c>
       <c r="S5" t="n">
-        <v>-11.295818</v>
+        <v>-5.721964</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.726978</v>
+        <v>-3.789204</v>
       </c>
       <c r="U5" t="n">
-        <v>-5.181687</v>
+        <v>-2.746643</v>
       </c>
       <c r="V5" t="n">
-        <v>-5.258517</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>-3.136049</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-3.430362</v>
+      </c>
       <c r="X5" t="n">
-        <v>-3.320027</v>
+        <v>-3.527447</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1.83747</v>
+        <v>5.888577</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.205162</v>
+        <v>8.587634</v>
       </c>
       <c r="AA5" t="n">
-        <v>17.26665</v>
+        <v>10.722507</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.173095</v>
+        <v>10.31533</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.520438</v>
+        <v>11.421725</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44620</v>
+        <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>113142</v>
+        <v>119999</v>
       </c>
       <c r="C6" t="n">
-        <v>108.900002</v>
+        <v>115.599998</v>
       </c>
       <c r="D6" t="n">
-        <v>111.040001</v>
+        <v>120.940002</v>
       </c>
       <c r="E6" t="n">
-        <v>245.5</v>
+        <v>235.649994</v>
       </c>
       <c r="F6" t="n">
-        <v>5.1594</v>
+        <v>4.7697</v>
       </c>
       <c r="G6" t="n">
-        <v>5.814</v>
+        <v>5.3198</v>
       </c>
       <c r="H6" t="n">
-        <v>4373.939941</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>4530.410156</v>
+      </c>
+      <c r="I6" t="n">
+        <v>14220.519531</v>
+      </c>
       <c r="J6" t="n">
-        <v>33892.601562</v>
+        <v>34678.351562</v>
       </c>
       <c r="K6" t="n">
-        <v>1900.699951</v>
+        <v>1949.199951</v>
       </c>
       <c r="L6" t="n">
-        <v>95.720001</v>
+        <v>100.279999</v>
       </c>
       <c r="M6" t="n">
-        <v>100.989998</v>
+        <v>107.910004</v>
       </c>
       <c r="N6" t="n">
-        <v>1644.25</v>
+        <v>1618.25</v>
       </c>
       <c r="O6" t="n">
-        <v>697.5</v>
+        <v>748.75</v>
       </c>
       <c r="P6" t="n">
-        <v>0.67089</v>
+        <v>6.060526</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.852008</v>
+        <v>6.152431</v>
       </c>
       <c r="R6" t="n">
-        <v>-5.094016</v>
+        <v>8.915706999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-5.721964</v>
+        <v>-4.012222</v>
       </c>
       <c r="T6" t="n">
-        <v>-3.789204</v>
+        <v>-7.553203</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.746643</v>
+        <v>-8.500176</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.136049</v>
-      </c>
-      <c r="W6" t="inlineStr"/>
+        <v>3.577329</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.411428</v>
+      </c>
       <c r="X6" t="n">
-        <v>-3.527447</v>
+        <v>2.318353</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.888577</v>
+        <v>2.551692</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.587634</v>
+        <v>4.763892</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.722507</v>
+        <v>6.852169</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.31533</v>
+        <v>-1.581268</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.421725</v>
+        <v>7.34767</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44651</v>
+        <v>44681</v>
       </c>
       <c r="B7" t="n">
-        <v>119999</v>
+        <v>107876</v>
       </c>
       <c r="C7" t="n">
-        <v>115.599998</v>
+        <v>103.400002</v>
       </c>
       <c r="D7" t="n">
-        <v>120.940002</v>
+        <v>110.599998</v>
       </c>
       <c r="E7" t="n">
-        <v>235.649994</v>
+        <v>224.100006</v>
       </c>
       <c r="F7" t="n">
-        <v>4.7697</v>
+        <v>4.9378</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3198</v>
+        <v>5.1837</v>
       </c>
       <c r="H7" t="n">
-        <v>4530.410156</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>4131.930176</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12334.639648</v>
+      </c>
       <c r="J7" t="n">
-        <v>34678.351562</v>
+        <v>32977.210938</v>
       </c>
       <c r="K7" t="n">
-        <v>1949.199951</v>
+        <v>1911.699951</v>
       </c>
       <c r="L7" t="n">
-        <v>100.279999</v>
+        <v>104.690002</v>
       </c>
       <c r="M7" t="n">
-        <v>107.910004</v>
+        <v>109.339996</v>
       </c>
       <c r="N7" t="n">
-        <v>1618.25</v>
+        <v>1708.25</v>
       </c>
       <c r="O7" t="n">
-        <v>748.75</v>
+        <v>818.25</v>
       </c>
       <c r="P7" t="n">
-        <v>6.060526</v>
+        <v>-10.102584</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.152431</v>
+        <v>-10.553631</v>
       </c>
       <c r="R7" t="n">
-        <v>8.915706999999999</v>
+        <v>-8.549697</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.012222</v>
+        <v>-4.901332</v>
       </c>
       <c r="T7" t="n">
-        <v>-7.553203</v>
+        <v>3.524328</v>
       </c>
       <c r="U7" t="n">
-        <v>-8.500176</v>
+        <v>-2.558363</v>
       </c>
       <c r="V7" t="n">
-        <v>3.577329</v>
-      </c>
-      <c r="W7" t="inlineStr"/>
+        <v>-8.795671</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-13.261681</v>
+      </c>
       <c r="X7" t="n">
-        <v>2.318353</v>
+        <v>-4.905483</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.551692</v>
+        <v>-1.923866</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.763892</v>
+        <v>4.39769</v>
       </c>
       <c r="AA7" t="n">
-        <v>6.852169</v>
+        <v>1.325172</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.581268</v>
+        <v>5.561563</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.34767</v>
+        <v>9.282137000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44681</v>
+        <v>44712</v>
       </c>
       <c r="B8" t="n">
-        <v>107876</v>
+        <v>111351</v>
       </c>
       <c r="C8" t="n">
-        <v>103.400002</v>
+        <v>107.18</v>
       </c>
       <c r="D8" t="n">
-        <v>110.599998</v>
+        <v>109.300003</v>
       </c>
       <c r="E8" t="n">
-        <v>224.100006</v>
+        <v>214.5</v>
       </c>
       <c r="F8" t="n">
-        <v>4.9378</v>
+        <v>4.7524</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1837</v>
+        <v>5.1176</v>
       </c>
       <c r="H8" t="n">
-        <v>4131.930176</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>4132.149902</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12081.389648</v>
+      </c>
       <c r="J8" t="n">
-        <v>32977.210938</v>
+        <v>32990.121094</v>
       </c>
       <c r="K8" t="n">
-        <v>1911.699951</v>
+        <v>1842.699951</v>
       </c>
       <c r="L8" t="n">
-        <v>104.690002</v>
+        <v>114.669998</v>
       </c>
       <c r="M8" t="n">
-        <v>109.339996</v>
+        <v>122.839996</v>
       </c>
       <c r="N8" t="n">
-        <v>1708.25</v>
+        <v>1683.25</v>
       </c>
       <c r="O8" t="n">
-        <v>818.25</v>
+        <v>753.5</v>
       </c>
       <c r="P8" t="n">
-        <v>-10.102584</v>
+        <v>3.221291</v>
       </c>
       <c r="Q8" t="n">
-        <v>-10.553631</v>
+        <v>3.655705</v>
       </c>
       <c r="R8" t="n">
-        <v>-8.549697</v>
+        <v>-1.175403</v>
       </c>
       <c r="S8" t="n">
-        <v>-4.901332</v>
+        <v>-4.283804</v>
       </c>
       <c r="T8" t="n">
-        <v>3.524328</v>
+        <v>-3.754709</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.558363</v>
+        <v>-1.275153</v>
       </c>
       <c r="V8" t="n">
-        <v>-8.795671</v>
-      </c>
-      <c r="W8" t="inlineStr"/>
+        <v>0.005318</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-2.053161</v>
+      </c>
       <c r="X8" t="n">
-        <v>-4.905483</v>
+        <v>0.039149</v>
       </c>
       <c r="Y8" t="n">
-        <v>-1.923866</v>
+        <v>-3.609353</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.39769</v>
+        <v>9.532902</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.325172</v>
+        <v>12.346809</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.561563</v>
+        <v>-1.463486</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.282137000000001</v>
+        <v>-7.913229</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44712</v>
+        <v>44742</v>
       </c>
       <c r="B9" t="n">
-        <v>111351</v>
+        <v>98542</v>
       </c>
       <c r="C9" t="n">
-        <v>107.18</v>
+        <v>95</v>
       </c>
       <c r="D9" t="n">
-        <v>109.300003</v>
+        <v>91.33000199999999</v>
       </c>
       <c r="E9" t="n">
-        <v>214.5</v>
+        <v>216.699997</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7524</v>
+        <v>5.1809</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1176</v>
+        <v>5.4098</v>
       </c>
       <c r="H9" t="n">
-        <v>4132.149902</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>3785.379883</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11028.740234</v>
+      </c>
       <c r="J9" t="n">
-        <v>32990.121094</v>
+        <v>30775.429688</v>
       </c>
       <c r="K9" t="n">
-        <v>1842.699951</v>
+        <v>1807.300049</v>
       </c>
       <c r="L9" t="n">
-        <v>114.669998</v>
+        <v>105.760002</v>
       </c>
       <c r="M9" t="n">
-        <v>122.839996</v>
+        <v>114.809998</v>
       </c>
       <c r="N9" t="n">
-        <v>1683.25</v>
+        <v>1675</v>
       </c>
       <c r="O9" t="n">
-        <v>753.5</v>
+        <v>743.75</v>
       </c>
       <c r="P9" t="n">
-        <v>3.221291</v>
+        <v>-11.503264</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.655705</v>
+        <v>-11.364061</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.175403</v>
+        <v>-16.440989</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.283804</v>
+        <v>1.02564</v>
       </c>
       <c r="T9" t="n">
-        <v>-3.754709</v>
+        <v>9.016501</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.275153</v>
+        <v>5.709709</v>
       </c>
       <c r="V9" t="n">
-        <v>0.005318</v>
-      </c>
-      <c r="W9" t="inlineStr"/>
+        <v>-8.391999999999999</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-8.712982999999999</v>
+      </c>
       <c r="X9" t="n">
-        <v>0.039149</v>
+        <v>-6.713196</v>
       </c>
       <c r="Y9" t="n">
-        <v>-3.609353</v>
+        <v>-1.921089</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.532902</v>
+        <v>-7.77012</v>
       </c>
       <c r="AA9" t="n">
-        <v>12.346809</v>
+        <v>-6.536958</v>
       </c>
       <c r="AB9" t="n">
-        <v>-1.463486</v>
+        <v>-0.490123</v>
       </c>
       <c r="AC9" t="n">
-        <v>-7.913229</v>
+        <v>-1.293962</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44742</v>
+        <v>44773</v>
       </c>
       <c r="B10" t="n">
-        <v>98542</v>
+        <v>103165</v>
       </c>
       <c r="C10" t="n">
-        <v>95</v>
+        <v>99.300003</v>
       </c>
       <c r="D10" t="n">
-        <v>91.33000199999999</v>
+        <v>95.650002</v>
       </c>
       <c r="E10" t="n">
-        <v>216.699997</v>
+        <v>234.5</v>
       </c>
       <c r="F10" t="n">
-        <v>5.1809</v>
+        <v>5.1827</v>
       </c>
       <c r="G10" t="n">
-        <v>5.4098</v>
+        <v>5.2797</v>
       </c>
       <c r="H10" t="n">
-        <v>3785.379883</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>4130.290039</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12390.69043</v>
+      </c>
       <c r="J10" t="n">
-        <v>30775.429688</v>
+        <v>32845.128906</v>
       </c>
       <c r="K10" t="n">
-        <v>1807.300049</v>
+        <v>1762.900024</v>
       </c>
       <c r="L10" t="n">
-        <v>105.760002</v>
+        <v>98.620003</v>
       </c>
       <c r="M10" t="n">
-        <v>114.809998</v>
+        <v>110.010002</v>
       </c>
       <c r="N10" t="n">
-        <v>1675</v>
+        <v>1637</v>
       </c>
       <c r="O10" t="n">
-        <v>743.75</v>
+        <v>616.25</v>
       </c>
       <c r="P10" t="n">
-        <v>-11.503264</v>
+        <v>4.691401</v>
       </c>
       <c r="Q10" t="n">
-        <v>-11.364061</v>
+        <v>4.526319</v>
       </c>
       <c r="R10" t="n">
-        <v>-16.440989</v>
+        <v>4.730099</v>
       </c>
       <c r="S10" t="n">
-        <v>1.02564</v>
+        <v>8.214122</v>
       </c>
       <c r="T10" t="n">
-        <v>9.016501</v>
+        <v>0.034744</v>
       </c>
       <c r="U10" t="n">
-        <v>5.709709</v>
+        <v>-2.404899</v>
       </c>
       <c r="V10" t="n">
-        <v>-8.391999999999999</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
+        <v>9.111639</v>
+      </c>
+      <c r="W10" t="n">
+        <v>12.3491</v>
+      </c>
       <c r="X10" t="n">
-        <v>-6.713196</v>
+        <v>6.725168</v>
       </c>
       <c r="Y10" t="n">
-        <v>-1.921089</v>
+        <v>-2.456705</v>
       </c>
       <c r="Z10" t="n">
-        <v>-7.77012</v>
+        <v>-6.751134</v>
       </c>
       <c r="AA10" t="n">
-        <v>-6.536958</v>
+        <v>-4.180817</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.490123</v>
+        <v>-2.268657</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.293962</v>
+        <v>-17.142857</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44773</v>
+        <v>44804</v>
       </c>
       <c r="B11" t="n">
-        <v>103165</v>
+        <v>109523</v>
       </c>
       <c r="C11" t="n">
-        <v>99.300003</v>
+        <v>105.830002</v>
       </c>
       <c r="D11" t="n">
-        <v>95.650002</v>
+        <v>106.800003</v>
       </c>
       <c r="E11" t="n">
-        <v>234.5</v>
+        <v>226</v>
       </c>
       <c r="F11" t="n">
-        <v>5.1827</v>
+        <v>5.1219</v>
       </c>
       <c r="G11" t="n">
-        <v>5.2797</v>
+        <v>5.1318</v>
       </c>
       <c r="H11" t="n">
-        <v>4130.290039</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>3955</v>
+      </c>
+      <c r="I11" t="n">
+        <v>11816.200195</v>
+      </c>
       <c r="J11" t="n">
-        <v>32845.128906</v>
+        <v>31510.429688</v>
       </c>
       <c r="K11" t="n">
-        <v>1762.900024</v>
+        <v>1726.199951</v>
       </c>
       <c r="L11" t="n">
-        <v>98.620003</v>
+        <v>89.550003</v>
       </c>
       <c r="M11" t="n">
-        <v>110.010002</v>
+        <v>96.489998</v>
       </c>
       <c r="N11" t="n">
-        <v>1637</v>
+        <v>1507.5</v>
       </c>
       <c r="O11" t="n">
-        <v>616.25</v>
+        <v>673.75</v>
       </c>
       <c r="P11" t="n">
-        <v>4.691401</v>
+        <v>6.162943</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.526319</v>
+        <v>6.576031</v>
       </c>
       <c r="R11" t="n">
-        <v>4.730099</v>
+        <v>11.657085</v>
       </c>
       <c r="S11" t="n">
-        <v>8.214122</v>
+        <v>-3.624733</v>
       </c>
       <c r="T11" t="n">
-        <v>0.034744</v>
+        <v>-1.173135</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.404899</v>
+        <v>-2.801289</v>
       </c>
       <c r="V11" t="n">
-        <v>9.111639</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
+        <v>-4.244013</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-4.636467</v>
+      </c>
       <c r="X11" t="n">
-        <v>6.725168</v>
+        <v>-4.063614</v>
       </c>
       <c r="Y11" t="n">
-        <v>-2.456705</v>
+        <v>-2.081801</v>
       </c>
       <c r="Z11" t="n">
-        <v>-6.751134</v>
+        <v>-9.196916999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>-4.180817</v>
+        <v>-12.289795</v>
       </c>
       <c r="AB11" t="n">
-        <v>-2.268657</v>
+        <v>-7.910812</v>
       </c>
       <c r="AC11" t="n">
-        <v>-17.142857</v>
+        <v>9.330629</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44804</v>
+        <v>44834</v>
       </c>
       <c r="B12" t="n">
-        <v>109523</v>
+        <v>110037</v>
       </c>
       <c r="C12" t="n">
-        <v>105.830002</v>
+        <v>106.459999</v>
       </c>
       <c r="D12" t="n">
-        <v>106.800003</v>
+        <v>105.440002</v>
       </c>
       <c r="E12" t="n">
-        <v>226</v>
+        <v>213.5</v>
       </c>
       <c r="F12" t="n">
-        <v>5.1219</v>
+        <v>5.3962</v>
       </c>
       <c r="G12" t="n">
-        <v>5.1318</v>
+        <v>5.3031</v>
       </c>
       <c r="H12" t="n">
-        <v>3955</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>3585.620117</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10575.620117</v>
+      </c>
       <c r="J12" t="n">
-        <v>31510.429688</v>
+        <v>28725.509766</v>
       </c>
       <c r="K12" t="n">
-        <v>1726.199951</v>
+        <v>1672</v>
       </c>
       <c r="L12" t="n">
-        <v>89.550003</v>
+        <v>79.489998</v>
       </c>
       <c r="M12" t="n">
-        <v>96.489998</v>
+        <v>87.959999</v>
       </c>
       <c r="N12" t="n">
-        <v>1507.5</v>
+        <v>1364.75</v>
       </c>
       <c r="O12" t="n">
-        <v>673.75</v>
+        <v>677.5</v>
       </c>
       <c r="P12" t="n">
-        <v>6.162943</v>
+        <v>0.469308</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.576031</v>
+        <v>0.595292</v>
       </c>
       <c r="R12" t="n">
-        <v>11.657085</v>
+        <v>-1.273409</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.624733</v>
+        <v>-5.530973</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.173135</v>
+        <v>5.355436</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.801289</v>
+        <v>3.338009</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.244013</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
+        <v>-9.339567000000001</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-10.498976</v>
+      </c>
       <c r="X12" t="n">
-        <v>-4.063614</v>
+        <v>-8.838089</v>
       </c>
       <c r="Y12" t="n">
-        <v>-2.081801</v>
+        <v>-3.139842</v>
       </c>
       <c r="Z12" t="n">
-        <v>-9.196916999999999</v>
+        <v>-11.233953</v>
       </c>
       <c r="AA12" t="n">
-        <v>-12.289795</v>
+        <v>-8.840293000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>-7.910812</v>
+        <v>-9.46932</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.330629</v>
+        <v>0.556586</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44834</v>
+        <v>44865</v>
       </c>
       <c r="B13" t="n">
-        <v>110037</v>
+        <v>116037</v>
       </c>
       <c r="C13" t="n">
-        <v>106.459999</v>
+        <v>112.150002</v>
       </c>
       <c r="D13" t="n">
-        <v>105.440002</v>
+        <v>112.5</v>
       </c>
       <c r="E13" t="n">
-        <v>213.5</v>
+        <v>220.240005</v>
       </c>
       <c r="F13" t="n">
-        <v>5.3962</v>
+        <v>5.2885</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3031</v>
+        <v>5.2737</v>
       </c>
       <c r="H13" t="n">
-        <v>3585.620117</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
+        <v>3871.97998</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10988.150391</v>
+      </c>
       <c r="J13" t="n">
-        <v>28725.509766</v>
+        <v>32732.949219</v>
       </c>
       <c r="K13" t="n">
-        <v>1672</v>
+        <v>1640.699951</v>
       </c>
       <c r="L13" t="n">
-        <v>79.489998</v>
+        <v>86.529999</v>
       </c>
       <c r="M13" t="n">
-        <v>87.959999</v>
+        <v>94.83000199999999</v>
       </c>
       <c r="N13" t="n">
-        <v>1364.75</v>
+        <v>1407</v>
       </c>
       <c r="O13" t="n">
-        <v>677.5</v>
+        <v>691.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0.469308</v>
+        <v>5.452711</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.595292</v>
+        <v>5.344733</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.273409</v>
+        <v>6.695749</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.530973</v>
+        <v>3.156911</v>
       </c>
       <c r="T13" t="n">
-        <v>5.355436</v>
+        <v>-1.995855</v>
       </c>
       <c r="U13" t="n">
-        <v>3.338009</v>
+        <v>-0.55439</v>
       </c>
       <c r="V13" t="n">
-        <v>-9.339567000000001</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+        <v>7.986341</v>
+      </c>
+      <c r="W13" t="n">
+        <v>3.900767</v>
+      </c>
       <c r="X13" t="n">
-        <v>-8.838089</v>
+        <v>13.950804</v>
       </c>
       <c r="Y13" t="n">
-        <v>-3.139842</v>
+        <v>-1.872012</v>
       </c>
       <c r="Z13" t="n">
-        <v>-11.233953</v>
+        <v>8.856460999999999</v>
       </c>
       <c r="AA13" t="n">
-        <v>-8.840293000000001</v>
+        <v>7.810372</v>
       </c>
       <c r="AB13" t="n">
-        <v>-9.46932</v>
+        <v>3.095805</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.556586</v>
+        <v>2.066421</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44865</v>
+        <v>44895</v>
       </c>
       <c r="B14" t="n">
-        <v>116037</v>
+        <v>112486</v>
       </c>
       <c r="C14" t="n">
-        <v>112.150002</v>
+        <v>108.580002</v>
       </c>
       <c r="D14" t="n">
-        <v>112.5</v>
+        <v>99.980003</v>
       </c>
       <c r="E14" t="n">
-        <v>220.240005</v>
+        <v>233.25</v>
       </c>
       <c r="F14" t="n">
-        <v>5.2885</v>
+        <v>5.2682</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2737</v>
+        <v>5.4362</v>
       </c>
       <c r="H14" t="n">
-        <v>3871.97998</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>4080.110107</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11468</v>
+      </c>
       <c r="J14" t="n">
-        <v>32732.949219</v>
+        <v>34589.769531</v>
       </c>
       <c r="K14" t="n">
-        <v>1640.699951</v>
+        <v>1746</v>
       </c>
       <c r="L14" t="n">
-        <v>86.529999</v>
+        <v>80.550003</v>
       </c>
       <c r="M14" t="n">
-        <v>94.83000199999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>1407</v>
+        <v>1469.5</v>
       </c>
       <c r="O14" t="n">
-        <v>691.5</v>
+        <v>662</v>
       </c>
       <c r="P14" t="n">
-        <v>5.452711</v>
+        <v>-3.060231</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.344733</v>
+        <v>-3.183236</v>
       </c>
       <c r="R14" t="n">
-        <v>6.695749</v>
+        <v>-11.128886</v>
       </c>
       <c r="S14" t="n">
-        <v>3.156911</v>
+        <v>5.90719</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.995855</v>
+        <v>-0.38385</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.55439</v>
+        <v>3.081326</v>
       </c>
       <c r="V14" t="n">
-        <v>7.986341</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
+        <v>5.375289</v>
+      </c>
+      <c r="W14" t="n">
+        <v>4.366973</v>
+      </c>
       <c r="X14" t="n">
-        <v>13.950804</v>
+        <v>5.672634</v>
       </c>
       <c r="Y14" t="n">
-        <v>-1.872012</v>
+        <v>6.417995</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.856460999999999</v>
+        <v>-6.910893</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.810372</v>
+        <v>-9.912476</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.095805</v>
+        <v>4.442075</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.066421</v>
+        <v>-4.266088</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44895</v>
+        <v>44926</v>
       </c>
       <c r="B15" t="n">
-        <v>112486</v>
+        <v>110031</v>
       </c>
       <c r="C15" t="n">
-        <v>108.580002</v>
+        <v>105.949997</v>
       </c>
       <c r="D15" t="n">
-        <v>99.980003</v>
+        <v>96.519997</v>
       </c>
       <c r="E15" t="n">
-        <v>233.25</v>
+        <v>225</v>
       </c>
       <c r="F15" t="n">
-        <v>5.2682</v>
+        <v>5.2846</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4362</v>
+        <v>5.633</v>
       </c>
       <c r="H15" t="n">
-        <v>4080.110107</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>3839.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10466.480469</v>
+      </c>
       <c r="J15" t="n">
-        <v>34589.769531</v>
+        <v>33147.25</v>
       </c>
       <c r="K15" t="n">
-        <v>1746</v>
+        <v>1826.199951</v>
       </c>
       <c r="L15" t="n">
-        <v>80.550003</v>
+        <v>80.260002</v>
       </c>
       <c r="M15" t="n">
-        <v>85.43000000000001</v>
+        <v>85.910004</v>
       </c>
       <c r="N15" t="n">
-        <v>1469.5</v>
+        <v>1519.25</v>
       </c>
       <c r="O15" t="n">
-        <v>662</v>
+        <v>678.5</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.060231</v>
+        <v>-2.182494</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.183236</v>
+        <v>-2.422182</v>
       </c>
       <c r="R15" t="n">
-        <v>-11.128886</v>
+        <v>-3.460699</v>
       </c>
       <c r="S15" t="n">
-        <v>5.90719</v>
+        <v>-3.536977</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.38385</v>
+        <v>0.311299</v>
       </c>
       <c r="U15" t="n">
-        <v>3.081326</v>
+        <v>3.620171</v>
       </c>
       <c r="V15" t="n">
-        <v>5.375289</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
+        <v>-5.897147</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-8.733166000000001</v>
+      </c>
       <c r="X15" t="n">
-        <v>5.672634</v>
+        <v>-4.170365</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.417995</v>
+        <v>4.593353</v>
       </c>
       <c r="Z15" t="n">
-        <v>-6.910893</v>
+        <v>-0.360026</v>
       </c>
       <c r="AA15" t="n">
-        <v>-9.912476</v>
+        <v>0.561867</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.442075</v>
+        <v>3.385505</v>
       </c>
       <c r="AC15" t="n">
-        <v>-4.266088</v>
+        <v>2.492447</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44926</v>
+        <v>44957</v>
       </c>
       <c r="B16" t="n">
-        <v>110031</v>
+        <v>113532</v>
       </c>
       <c r="C16" t="n">
-        <v>105.949997</v>
+        <v>109.839996</v>
       </c>
       <c r="D16" t="n">
-        <v>96.519997</v>
+        <v>99.44000200000001</v>
       </c>
       <c r="E16" t="n">
-        <v>225</v>
+        <v>228.199997</v>
       </c>
       <c r="F16" t="n">
-        <v>5.2846</v>
+        <v>5.1149</v>
       </c>
       <c r="G16" t="n">
-        <v>5.633</v>
+        <v>5.5471</v>
       </c>
       <c r="H16" t="n">
-        <v>3839.5</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>4076.600098</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11584.549805</v>
+      </c>
       <c r="J16" t="n">
-        <v>33147.25</v>
+        <v>34086.039062</v>
       </c>
       <c r="K16" t="n">
-        <v>1826.199951</v>
+        <v>1929.5</v>
       </c>
       <c r="L16" t="n">
-        <v>80.260002</v>
+        <v>78.870003</v>
       </c>
       <c r="M16" t="n">
-        <v>85.910004</v>
+        <v>84.489998</v>
       </c>
       <c r="N16" t="n">
-        <v>1519.25</v>
+        <v>1538</v>
       </c>
       <c r="O16" t="n">
-        <v>678.5</v>
+        <v>679.75</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.182494</v>
+        <v>3.181831</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.422182</v>
+        <v>3.671543</v>
       </c>
       <c r="R16" t="n">
-        <v>-3.460699</v>
+        <v>3.025286</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.536977</v>
+        <v>1.422221</v>
       </c>
       <c r="T16" t="n">
-        <v>0.311299</v>
+        <v>-3.211211</v>
       </c>
       <c r="U16" t="n">
-        <v>3.620171</v>
+        <v>-1.524939</v>
       </c>
       <c r="V16" t="n">
-        <v>-5.897147</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
+        <v>6.175286</v>
+      </c>
+      <c r="W16" t="n">
+        <v>10.682381</v>
+      </c>
       <c r="X16" t="n">
-        <v>-4.170365</v>
+        <v>2.832178</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.593353</v>
+        <v>5.656557</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0.360026</v>
+        <v>-1.731871</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.561867</v>
+        <v>-1.652899</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.385505</v>
+        <v>1.234162</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.492447</v>
+        <v>0.18423</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44957</v>
+        <v>44985</v>
       </c>
       <c r="B17" t="n">
-        <v>113532</v>
+        <v>104932</v>
       </c>
       <c r="C17" t="n">
-        <v>109.839996</v>
+        <v>101.150002</v>
       </c>
       <c r="D17" t="n">
-        <v>99.44000200000001</v>
+        <v>88.360001</v>
       </c>
       <c r="E17" t="n">
-        <v>228.199997</v>
+        <v>229.300003</v>
       </c>
       <c r="F17" t="n">
-        <v>5.1149</v>
+        <v>5.1997</v>
       </c>
       <c r="G17" t="n">
-        <v>5.5471</v>
+        <v>5.514</v>
       </c>
       <c r="H17" t="n">
-        <v>4076.600098</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>3970.149902</v>
+      </c>
+      <c r="I17" t="n">
+        <v>11455.540039</v>
+      </c>
       <c r="J17" t="n">
-        <v>34086.039062</v>
+        <v>32656.699219</v>
       </c>
       <c r="K17" t="n">
-        <v>1929.5</v>
+        <v>1836.699951</v>
       </c>
       <c r="L17" t="n">
-        <v>78.870003</v>
+        <v>77.050003</v>
       </c>
       <c r="M17" t="n">
-        <v>84.489998</v>
+        <v>83.889999</v>
       </c>
       <c r="N17" t="n">
-        <v>1538</v>
+        <v>1490.5</v>
       </c>
       <c r="O17" t="n">
-        <v>679.75</v>
+        <v>629.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.181831</v>
+        <v>-7.574957</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.671543</v>
+        <v>-7.911503</v>
       </c>
       <c r="R17" t="n">
-        <v>3.025286</v>
+        <v>-11.142399</v>
       </c>
       <c r="S17" t="n">
-        <v>1.422221</v>
+        <v>0.482036</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.211211</v>
+        <v>1.657897</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.524939</v>
+        <v>-0.59671</v>
       </c>
       <c r="V17" t="n">
-        <v>6.175286</v>
-      </c>
-      <c r="W17" t="inlineStr"/>
+        <v>-2.611249</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-1.113636</v>
+      </c>
       <c r="X17" t="n">
-        <v>2.832178</v>
+        <v>-4.193329</v>
       </c>
       <c r="Y17" t="n">
-        <v>5.656557</v>
+        <v>-4.809539</v>
       </c>
       <c r="Z17" t="n">
-        <v>-1.731871</v>
+        <v>-2.307594</v>
       </c>
       <c r="AA17" t="n">
-        <v>-1.652899</v>
+        <v>-0.710141</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.234162</v>
+        <v>-3.088427</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.18423</v>
+        <v>-7.392424</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44985</v>
+        <v>45016</v>
       </c>
       <c r="B18" t="n">
-        <v>104932</v>
+        <v>101882</v>
       </c>
       <c r="C18" t="n">
-        <v>101.150002</v>
+        <v>98.489998</v>
       </c>
       <c r="D18" t="n">
-        <v>88.360001</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>229.300003</v>
+        <v>229.75</v>
       </c>
       <c r="F18" t="n">
-        <v>5.1997</v>
+        <v>5.0927</v>
       </c>
       <c r="G18" t="n">
-        <v>5.514</v>
+        <v>5.5518</v>
       </c>
       <c r="H18" t="n">
-        <v>3970.149902</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>4109.310059</v>
+      </c>
+      <c r="I18" t="n">
+        <v>12221.910156</v>
+      </c>
       <c r="J18" t="n">
-        <v>32656.699219</v>
+        <v>33274.148438</v>
       </c>
       <c r="K18" t="n">
-        <v>1836.699951</v>
+        <v>1969</v>
       </c>
       <c r="L18" t="n">
-        <v>77.050003</v>
+        <v>75.66999800000001</v>
       </c>
       <c r="M18" t="n">
-        <v>83.889999</v>
+        <v>79.769997</v>
       </c>
       <c r="N18" t="n">
-        <v>1490.5</v>
+        <v>1505.5</v>
       </c>
       <c r="O18" t="n">
-        <v>629.5</v>
+        <v>660.5</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.574957</v>
+        <v>-2.906644</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.911503</v>
+        <v>-2.629761</v>
       </c>
       <c r="R18" t="n">
-        <v>-11.142399</v>
+        <v>-0.611137</v>
       </c>
       <c r="S18" t="n">
-        <v>0.482036</v>
+        <v>0.196248</v>
       </c>
       <c r="T18" t="n">
-        <v>1.657897</v>
+        <v>-2.057809</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.59671</v>
+        <v>0.6855250000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.611249</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
+        <v>3.505161</v>
+      </c>
+      <c r="W18" t="n">
+        <v>6.689952</v>
+      </c>
       <c r="X18" t="n">
-        <v>-4.193329</v>
+        <v>1.890728</v>
       </c>
       <c r="Y18" t="n">
-        <v>-4.809539</v>
+        <v>7.203139</v>
       </c>
       <c r="Z18" t="n">
-        <v>-2.307594</v>
+        <v>-1.791051</v>
       </c>
       <c r="AA18" t="n">
-        <v>-0.710141</v>
+        <v>-4.911197</v>
       </c>
       <c r="AB18" t="n">
-        <v>-3.088427</v>
+        <v>1.006374</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.392424</v>
+        <v>4.924543</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45016</v>
+        <v>45046</v>
       </c>
       <c r="B19" t="n">
-        <v>101882</v>
+        <v>104432</v>
       </c>
       <c r="C19" t="n">
-        <v>98.489998</v>
+        <v>100.900002</v>
       </c>
       <c r="D19" t="n">
-        <v>87.81999999999999</v>
+        <v>89</v>
       </c>
       <c r="E19" t="n">
         <v>229.75</v>
       </c>
       <c r="F19" t="n">
-        <v>5.0927</v>
+        <v>4.9762</v>
       </c>
       <c r="G19" t="n">
-        <v>5.5518</v>
+        <v>5.4883</v>
       </c>
       <c r="H19" t="n">
-        <v>4109.310059</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>4169.47998</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12226.580078</v>
+      </c>
       <c r="J19" t="n">
-        <v>33274.148438</v>
+        <v>34098.160156</v>
       </c>
       <c r="K19" t="n">
-        <v>1969</v>
+        <v>1999.099976</v>
       </c>
       <c r="L19" t="n">
-        <v>75.66999800000001</v>
+        <v>76.779999</v>
       </c>
       <c r="M19" t="n">
-        <v>79.769997</v>
+        <v>79.540001</v>
       </c>
       <c r="N19" t="n">
-        <v>1505.5</v>
+        <v>1444.25</v>
       </c>
       <c r="O19" t="n">
-        <v>660.5</v>
+        <v>636</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.906644</v>
+        <v>2.502896</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.629761</v>
+        <v>2.446953</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.611137</v>
+        <v>1.343658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.196248</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.057809</v>
+        <v>-2.287586</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6855250000000001</v>
+        <v>-1.143772</v>
       </c>
       <c r="V19" t="n">
-        <v>3.505161</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
+        <v>1.464234</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.038209</v>
+      </c>
       <c r="X19" t="n">
-        <v>1.890728</v>
+        <v>2.476432</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.203139</v>
+        <v>1.528694</v>
       </c>
       <c r="Z19" t="n">
-        <v>-1.791051</v>
+        <v>1.466897</v>
       </c>
       <c r="AA19" t="n">
-        <v>-4.911197</v>
+        <v>-0.288324</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.006374</v>
+        <v>-4.068416</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.924543</v>
+        <v>-3.709311</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45046</v>
+        <v>45077</v>
       </c>
       <c r="B20" t="n">
-        <v>104432</v>
+        <v>108335</v>
       </c>
       <c r="C20" t="n">
-        <v>100.900002</v>
+        <v>104.839996</v>
       </c>
       <c r="D20" t="n">
-        <v>89</v>
+        <v>100.5</v>
       </c>
       <c r="E20" t="n">
-        <v>229.75</v>
+        <v>233.25</v>
       </c>
       <c r="F20" t="n">
-        <v>4.9762</v>
+        <v>5.0348</v>
       </c>
       <c r="G20" t="n">
-        <v>5.4883</v>
+        <v>5.4012</v>
       </c>
       <c r="H20" t="n">
-        <v>4169.47998</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>4179.830078</v>
+      </c>
+      <c r="I20" t="n">
+        <v>12935.290039</v>
+      </c>
       <c r="J20" t="n">
-        <v>34098.160156</v>
+        <v>32908.269531</v>
       </c>
       <c r="K20" t="n">
-        <v>1999.099976</v>
+        <v>1963.900024</v>
       </c>
       <c r="L20" t="n">
-        <v>76.779999</v>
+        <v>68.089996</v>
       </c>
       <c r="M20" t="n">
-        <v>79.540001</v>
+        <v>72.660004</v>
       </c>
       <c r="N20" t="n">
-        <v>1444.25</v>
+        <v>1299.75</v>
       </c>
       <c r="O20" t="n">
-        <v>636</v>
+        <v>594</v>
       </c>
       <c r="P20" t="n">
-        <v>2.502896</v>
+        <v>3.73736</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.446953</v>
+        <v>3.904851</v>
       </c>
       <c r="R20" t="n">
-        <v>1.343658</v>
+        <v>12.921348</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.523395</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.287586</v>
+        <v>1.177604</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.143772</v>
+        <v>-1.587013</v>
       </c>
       <c r="V20" t="n">
-        <v>1.464234</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
+        <v>0.248235</v>
+      </c>
+      <c r="W20" t="n">
+        <v>5.796469</v>
+      </c>
       <c r="X20" t="n">
-        <v>2.476432</v>
+        <v>-3.489604</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.528694</v>
+        <v>-1.76079</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.466897</v>
+        <v>-11.318055</v>
       </c>
       <c r="AA20" t="n">
-        <v>-0.288324</v>
+        <v>-8.649732</v>
       </c>
       <c r="AB20" t="n">
-        <v>-4.068416</v>
+        <v>-10.005193</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.709311</v>
+        <v>-6.603774</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45077</v>
+        <v>45107</v>
       </c>
       <c r="B21" t="n">
-        <v>108335</v>
+        <v>118087</v>
       </c>
       <c r="C21" t="n">
-        <v>104.839996</v>
+        <v>114.169998</v>
       </c>
       <c r="D21" t="n">
-        <v>100.5</v>
+        <v>109.5</v>
       </c>
       <c r="E21" t="n">
-        <v>233.25</v>
+        <v>235.25</v>
       </c>
       <c r="F21" t="n">
-        <v>5.0348</v>
+        <v>4.8556</v>
       </c>
       <c r="G21" t="n">
-        <v>5.4012</v>
+        <v>5.2739</v>
       </c>
       <c r="H21" t="n">
-        <v>4179.830078</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
+        <v>4450.379883</v>
+      </c>
+      <c r="I21" t="n">
+        <v>13787.919922</v>
+      </c>
       <c r="J21" t="n">
-        <v>32908.269531</v>
+        <v>34407.601562</v>
       </c>
       <c r="K21" t="n">
-        <v>1963.900024</v>
+        <v>1929.400024</v>
       </c>
       <c r="L21" t="n">
-        <v>68.089996</v>
+        <v>70.639999</v>
       </c>
       <c r="M21" t="n">
-        <v>72.660004</v>
+        <v>74.900002</v>
       </c>
       <c r="N21" t="n">
-        <v>1299.75</v>
+        <v>1557.25</v>
       </c>
       <c r="O21" t="n">
-        <v>594</v>
+        <v>554.5</v>
       </c>
       <c r="P21" t="n">
-        <v>3.73736</v>
+        <v>9.001708000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.904851</v>
+        <v>8.899277</v>
       </c>
       <c r="R21" t="n">
-        <v>12.921348</v>
+        <v>8.955223999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>1.523395</v>
+        <v>0.857449</v>
       </c>
       <c r="T21" t="n">
-        <v>1.177604</v>
+        <v>-3.559231</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.587013</v>
+        <v>-2.35688</v>
       </c>
       <c r="V21" t="n">
-        <v>0.248235</v>
-      </c>
-      <c r="W21" t="inlineStr"/>
+        <v>6.472746</v>
+      </c>
+      <c r="W21" t="n">
+        <v>6.591502</v>
+      </c>
       <c r="X21" t="n">
-        <v>-3.489604</v>
+        <v>4.556095</v>
       </c>
       <c r="Y21" t="n">
-        <v>-1.76079</v>
+        <v>-1.756709</v>
       </c>
       <c r="Z21" t="n">
-        <v>-11.318055</v>
+        <v>3.745048</v>
       </c>
       <c r="AA21" t="n">
-        <v>-8.649732</v>
+        <v>3.082849</v>
       </c>
       <c r="AB21" t="n">
-        <v>-10.005193</v>
+        <v>19.811502</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.603774</v>
+        <v>-6.649832</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45107</v>
+        <v>45138</v>
       </c>
       <c r="B22" t="n">
-        <v>118087</v>
+        <v>121943</v>
       </c>
       <c r="C22" t="n">
-        <v>114.169998</v>
+        <v>117.949997</v>
       </c>
       <c r="D22" t="n">
-        <v>109.5</v>
+        <v>112.900002</v>
       </c>
       <c r="E22" t="n">
-        <v>235.25</v>
+        <v>239.820007</v>
       </c>
       <c r="F22" t="n">
-        <v>4.8556</v>
+        <v>4.7233</v>
       </c>
       <c r="G22" t="n">
-        <v>5.2739</v>
+        <v>5.1895</v>
       </c>
       <c r="H22" t="n">
-        <v>4450.379883</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>4588.959961</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14346.019531</v>
+      </c>
       <c r="J22" t="n">
-        <v>34407.601562</v>
+        <v>35559.53125</v>
       </c>
       <c r="K22" t="n">
-        <v>1929.400024</v>
+        <v>1970.5</v>
       </c>
       <c r="L22" t="n">
-        <v>70.639999</v>
+        <v>81.800003</v>
       </c>
       <c r="M22" t="n">
-        <v>74.900002</v>
+        <v>85.55999799999999</v>
       </c>
       <c r="N22" t="n">
-        <v>1557.25</v>
+        <v>1445.75</v>
       </c>
       <c r="O22" t="n">
-        <v>554.5</v>
+        <v>504</v>
       </c>
       <c r="P22" t="n">
-        <v>9.001708000000001</v>
+        <v>3.265389</v>
       </c>
       <c r="Q22" t="n">
-        <v>8.899277</v>
+        <v>3.310851</v>
       </c>
       <c r="R22" t="n">
-        <v>8.955223999999999</v>
+        <v>3.105024</v>
       </c>
       <c r="S22" t="n">
-        <v>0.857449</v>
+        <v>1.942617</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.559231</v>
+        <v>-2.724687</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.35688</v>
+        <v>-1.600337</v>
       </c>
       <c r="V22" t="n">
-        <v>6.472746</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
+        <v>3.113893</v>
+      </c>
+      <c r="W22" t="n">
+        <v>4.047743</v>
+      </c>
       <c r="X22" t="n">
-        <v>4.556095</v>
+        <v>3.347893</v>
       </c>
       <c r="Y22" t="n">
-        <v>-1.756709</v>
+        <v>2.130195</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.745048</v>
+        <v>15.79842</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.082849</v>
+        <v>14.232304</v>
       </c>
       <c r="AB22" t="n">
-        <v>19.811502</v>
+        <v>-7.160058</v>
       </c>
       <c r="AC22" t="n">
-        <v>-6.649832</v>
+        <v>-9.107303999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45138</v>
+        <v>45169</v>
       </c>
       <c r="B23" t="n">
-        <v>121943</v>
+        <v>115742</v>
       </c>
       <c r="C23" t="n">
-        <v>117.949997</v>
+        <v>112.309998</v>
       </c>
       <c r="D23" t="n">
-        <v>112.900002</v>
+        <v>104.199997</v>
       </c>
       <c r="E23" t="n">
-        <v>239.820007</v>
+        <v>247.649994</v>
       </c>
       <c r="F23" t="n">
-        <v>4.7233</v>
+        <v>4.8884</v>
       </c>
       <c r="G23" t="n">
-        <v>5.1895</v>
+        <v>5.313</v>
       </c>
       <c r="H23" t="n">
-        <v>4588.959961</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>4507.660156</v>
+      </c>
+      <c r="I23" t="n">
+        <v>14034.969727</v>
+      </c>
       <c r="J23" t="n">
-        <v>35559.53125</v>
+        <v>34721.910156</v>
       </c>
       <c r="K23" t="n">
-        <v>1970.5</v>
+        <v>1965.900024</v>
       </c>
       <c r="L23" t="n">
-        <v>81.800003</v>
+        <v>83.629997</v>
       </c>
       <c r="M23" t="n">
-        <v>85.55999799999999</v>
+        <v>86.860001</v>
       </c>
       <c r="N23" t="n">
-        <v>1445.75</v>
+        <v>1360</v>
       </c>
       <c r="O23" t="n">
-        <v>504</v>
+        <v>461</v>
       </c>
       <c r="P23" t="n">
-        <v>3.265389</v>
+        <v>-5.085163</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.310851</v>
+        <v>-4.781687</v>
       </c>
       <c r="R23" t="n">
-        <v>3.105024</v>
+        <v>-7.705938</v>
       </c>
       <c r="S23" t="n">
-        <v>1.942617</v>
+        <v>3.264943</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.724687</v>
+        <v>3.49544</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.600337</v>
+        <v>2.379812</v>
       </c>
       <c r="V23" t="n">
-        <v>3.113893</v>
-      </c>
-      <c r="W23" t="inlineStr"/>
+        <v>-1.771639</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-2.168196</v>
+      </c>
       <c r="X23" t="n">
-        <v>3.347893</v>
+        <v>-2.355546</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.130195</v>
+        <v>-0.233442</v>
       </c>
       <c r="Z23" t="n">
-        <v>15.79842</v>
+        <v>2.237157</v>
       </c>
       <c r="AA23" t="n">
-        <v>14.232304</v>
+        <v>1.519405</v>
       </c>
       <c r="AB23" t="n">
-        <v>-7.160058</v>
+        <v>-5.931178</v>
       </c>
       <c r="AC23" t="n">
-        <v>-9.107303999999999</v>
+        <v>-8.531746</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45169</v>
+        <v>45199</v>
       </c>
       <c r="B24" t="n">
-        <v>115742</v>
+        <v>116565</v>
       </c>
       <c r="C24" t="n">
-        <v>112.309998</v>
+        <v>113.150002</v>
       </c>
       <c r="D24" t="n">
-        <v>104.199997</v>
+        <v>101.639999</v>
       </c>
       <c r="E24" t="n">
-        <v>247.649994</v>
+        <v>238.789993</v>
       </c>
       <c r="F24" t="n">
-        <v>4.8884</v>
+        <v>5.0328</v>
       </c>
       <c r="G24" t="n">
-        <v>5.313</v>
+        <v>5.3197</v>
       </c>
       <c r="H24" t="n">
-        <v>4507.660156</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>4288.049805</v>
+      </c>
+      <c r="I24" t="n">
+        <v>13219.320312</v>
+      </c>
       <c r="J24" t="n">
-        <v>34721.910156</v>
+        <v>33507.5</v>
       </c>
       <c r="K24" t="n">
-        <v>1965.900024</v>
+        <v>1866.099976</v>
       </c>
       <c r="L24" t="n">
-        <v>83.629997</v>
+        <v>90.790001</v>
       </c>
       <c r="M24" t="n">
-        <v>86.860001</v>
+        <v>95.30999799999999</v>
       </c>
       <c r="N24" t="n">
-        <v>1360</v>
+        <v>1275</v>
       </c>
       <c r="O24" t="n">
-        <v>461</v>
+        <v>476.75</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.085163</v>
+        <v>0.711064</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.781687</v>
+        <v>0.747933</v>
       </c>
       <c r="R24" t="n">
-        <v>-7.705938</v>
+        <v>-2.456812</v>
       </c>
       <c r="S24" t="n">
-        <v>3.264943</v>
+        <v>-3.57763</v>
       </c>
       <c r="T24" t="n">
-        <v>3.49544</v>
+        <v>2.953934</v>
       </c>
       <c r="U24" t="n">
-        <v>2.379812</v>
+        <v>0.126098</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.771639</v>
-      </c>
-      <c r="W24" t="inlineStr"/>
+        <v>-4.871937</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-5.811551</v>
+      </c>
       <c r="X24" t="n">
-        <v>-2.355546</v>
+        <v>-3.497533</v>
       </c>
       <c r="Y24" t="n">
-        <v>-0.233442</v>
+        <v>-5.076558</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.237157</v>
+        <v>8.561526000000001</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.519405</v>
+        <v>9.728294999999999</v>
       </c>
       <c r="AB24" t="n">
-        <v>-5.931178</v>
+        <v>-6.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>-8.531746</v>
+        <v>3.416486</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45199</v>
+        <v>45230</v>
       </c>
       <c r="B25" t="n">
-        <v>116565</v>
+        <v>113144</v>
       </c>
       <c r="C25" t="n">
-        <v>113.150002</v>
+        <v>109.620003</v>
       </c>
       <c r="D25" t="n">
-        <v>101.639999</v>
+        <v>94.199997</v>
       </c>
       <c r="E25" t="n">
-        <v>238.789993</v>
+        <v>234</v>
       </c>
       <c r="F25" t="n">
-        <v>5.0328</v>
+        <v>5.0461</v>
       </c>
       <c r="G25" t="n">
-        <v>5.3197</v>
+        <v>5.3537</v>
       </c>
       <c r="H25" t="n">
-        <v>4288.049805</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>4193.799805</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12851.240234</v>
+      </c>
       <c r="J25" t="n">
-        <v>33507.5</v>
+        <v>33052.871094</v>
       </c>
       <c r="K25" t="n">
-        <v>1866.099976</v>
+        <v>1994.300049</v>
       </c>
       <c r="L25" t="n">
-        <v>90.790001</v>
+        <v>81.019997</v>
       </c>
       <c r="M25" t="n">
-        <v>95.30999799999999</v>
+        <v>87.410004</v>
       </c>
       <c r="N25" t="n">
-        <v>1275</v>
+        <v>1287</v>
       </c>
       <c r="O25" t="n">
-        <v>476.75</v>
+        <v>478.75</v>
       </c>
       <c r="P25" t="n">
-        <v>0.711064</v>
+        <v>-2.934843</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.747933</v>
+        <v>-3.119751</v>
       </c>
       <c r="R25" t="n">
-        <v>-2.456812</v>
+        <v>-7.319955</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.57763</v>
+        <v>-2.005944</v>
       </c>
       <c r="T25" t="n">
-        <v>2.953934</v>
+        <v>0.264265</v>
       </c>
       <c r="U25" t="n">
-        <v>0.126098</v>
+        <v>0.639141</v>
       </c>
       <c r="V25" t="n">
-        <v>-4.871937</v>
-      </c>
-      <c r="W25" t="inlineStr"/>
+        <v>-2.197969</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-2.78441</v>
+      </c>
       <c r="X25" t="n">
-        <v>-3.497533</v>
+        <v>-1.356797</v>
       </c>
       <c r="Y25" t="n">
-        <v>-5.076558</v>
+        <v>6.869947</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.561526000000001</v>
+        <v>-10.761102</v>
       </c>
       <c r="AA25" t="n">
-        <v>9.728294999999999</v>
+        <v>-8.288736</v>
       </c>
       <c r="AB25" t="n">
-        <v>-6.25</v>
+        <v>0.941176</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.416486</v>
+        <v>0.419507</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45230</v>
+        <v>45260</v>
       </c>
       <c r="B26" t="n">
-        <v>113144</v>
+        <v>127331</v>
       </c>
       <c r="C26" t="n">
-        <v>109.620003</v>
+        <v>123.57</v>
       </c>
       <c r="D26" t="n">
-        <v>94.199997</v>
+        <v>106.349998</v>
       </c>
       <c r="E26" t="n">
-        <v>234</v>
+        <v>249.699997</v>
       </c>
       <c r="F26" t="n">
-        <v>5.0461</v>
+        <v>4.9041</v>
       </c>
       <c r="G26" t="n">
-        <v>5.3537</v>
+        <v>5.3628</v>
       </c>
       <c r="H26" t="n">
-        <v>4193.799805</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>4567.799805</v>
+      </c>
+      <c r="I26" t="n">
+        <v>14226.219727</v>
+      </c>
       <c r="J26" t="n">
-        <v>33052.871094</v>
+        <v>35950.890625</v>
       </c>
       <c r="K26" t="n">
-        <v>1994.300049</v>
+        <v>2038.099976</v>
       </c>
       <c r="L26" t="n">
-        <v>81.019997</v>
+        <v>75.959999</v>
       </c>
       <c r="M26" t="n">
-        <v>87.410004</v>
+        <v>82.83000199999999</v>
       </c>
       <c r="N26" t="n">
-        <v>1287</v>
+        <v>1342.75</v>
       </c>
       <c r="O26" t="n">
-        <v>478.75</v>
+        <v>461.75</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.934843</v>
+        <v>12.538888</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.119751</v>
+        <v>12.725777</v>
       </c>
       <c r="R26" t="n">
-        <v>-7.319955</v>
+        <v>12.898091</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.005944</v>
+        <v>6.7094</v>
       </c>
       <c r="T26" t="n">
-        <v>0.264265</v>
+        <v>-2.814058</v>
       </c>
       <c r="U26" t="n">
-        <v>0.639141</v>
+        <v>0.169975</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.197969</v>
-      </c>
-      <c r="W26" t="inlineStr"/>
+        <v>8.917927000000001</v>
+      </c>
+      <c r="W26" t="n">
+        <v>10.699197</v>
+      </c>
       <c r="X26" t="n">
-        <v>-1.356797</v>
+        <v>8.76783</v>
       </c>
       <c r="Y26" t="n">
-        <v>6.869947</v>
+        <v>2.196256</v>
       </c>
       <c r="Z26" t="n">
-        <v>-10.761102</v>
+        <v>-6.245369</v>
       </c>
       <c r="AA26" t="n">
-        <v>-8.288736</v>
+        <v>-5.239677</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.941176</v>
+        <v>4.331779</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.419507</v>
+        <v>-3.550914</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45260</v>
+        <v>45291</v>
       </c>
       <c r="B27" t="n">
-        <v>127331</v>
+        <v>134185</v>
       </c>
       <c r="C27" t="n">
-        <v>123.57</v>
+        <v>130.389999</v>
       </c>
       <c r="D27" t="n">
-        <v>106.349998</v>
+        <v>113.199997</v>
       </c>
       <c r="E27" t="n">
-        <v>249.699997</v>
+        <v>257.609985</v>
       </c>
       <c r="F27" t="n">
-        <v>4.9041</v>
+        <v>4.8502</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3628</v>
+        <v>5.343</v>
       </c>
       <c r="H27" t="n">
-        <v>4567.799805</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>4769.830078</v>
+      </c>
+      <c r="I27" t="n">
+        <v>15011.349609</v>
+      </c>
       <c r="J27" t="n">
-        <v>35950.890625</v>
+        <v>37689.539062</v>
       </c>
       <c r="K27" t="n">
-        <v>2038.099976</v>
+        <v>2071.800049</v>
       </c>
       <c r="L27" t="n">
-        <v>75.959999</v>
+        <v>71.650002</v>
       </c>
       <c r="M27" t="n">
-        <v>82.83000199999999</v>
+        <v>77.040001</v>
       </c>
       <c r="N27" t="n">
-        <v>1342.75</v>
+        <v>1293.5</v>
       </c>
       <c r="O27" t="n">
-        <v>461.75</v>
+        <v>471.25</v>
       </c>
       <c r="P27" t="n">
-        <v>12.538888</v>
+        <v>5.382821</v>
       </c>
       <c r="Q27" t="n">
-        <v>12.725777</v>
+        <v>5.519139</v>
       </c>
       <c r="R27" t="n">
-        <v>12.898091</v>
+        <v>6.440995</v>
       </c>
       <c r="S27" t="n">
-        <v>6.7094</v>
+        <v>3.167797</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.814058</v>
+        <v>-1.099076</v>
       </c>
       <c r="U27" t="n">
-        <v>0.169975</v>
+        <v>-0.369214</v>
       </c>
       <c r="V27" t="n">
-        <v>8.917927000000001</v>
-      </c>
-      <c r="W27" t="inlineStr"/>
+        <v>4.422923</v>
+      </c>
+      <c r="W27" t="n">
+        <v>5.518893</v>
+      </c>
       <c r="X27" t="n">
-        <v>8.76783</v>
+        <v>4.836176</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.196256</v>
+        <v>1.653504</v>
       </c>
       <c r="Z27" t="n">
-        <v>-6.245369</v>
+        <v>-5.674036</v>
       </c>
       <c r="AA27" t="n">
-        <v>-5.239677</v>
+        <v>-6.990222</v>
       </c>
       <c r="AB27" t="n">
-        <v>4.331779</v>
+        <v>-3.667846</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.550914</v>
+        <v>2.05739</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45291</v>
+        <v>45322</v>
       </c>
       <c r="B28" t="n">
-        <v>134185</v>
+        <v>127752</v>
       </c>
       <c r="C28" t="n">
-        <v>130.389999</v>
+        <v>123.949997</v>
       </c>
       <c r="D28" t="n">
-        <v>113.199997</v>
+        <v>106.370003</v>
       </c>
       <c r="E28" t="n">
-        <v>257.609985</v>
+        <v>266.619995</v>
       </c>
       <c r="F28" t="n">
-        <v>4.8502</v>
+        <v>4.9503</v>
       </c>
       <c r="G28" t="n">
-        <v>5.343</v>
+        <v>5.3604</v>
       </c>
       <c r="H28" t="n">
-        <v>4769.830078</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>4845.649902</v>
+      </c>
+      <c r="I28" t="n">
+        <v>15164.009766</v>
+      </c>
       <c r="J28" t="n">
-        <v>37689.539062</v>
+        <v>38150.300781</v>
       </c>
       <c r="K28" t="n">
-        <v>2071.800049</v>
+        <v>2048.399902</v>
       </c>
       <c r="L28" t="n">
-        <v>71.650002</v>
+        <v>75.849998</v>
       </c>
       <c r="M28" t="n">
-        <v>77.040001</v>
+        <v>81.709999</v>
       </c>
       <c r="N28" t="n">
-        <v>1293.5</v>
+        <v>1222.25</v>
       </c>
       <c r="O28" t="n">
-        <v>471.25</v>
+        <v>448.25</v>
       </c>
       <c r="P28" t="n">
-        <v>5.382821</v>
+        <v>-4.794128</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.519139</v>
+        <v>-4.939031</v>
       </c>
       <c r="R28" t="n">
-        <v>6.440995</v>
+        <v>-6.033564</v>
       </c>
       <c r="S28" t="n">
-        <v>3.167797</v>
+        <v>3.497539</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.099076</v>
+        <v>2.063833</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.369214</v>
+        <v>0.325665</v>
       </c>
       <c r="V28" t="n">
-        <v>4.422923</v>
-      </c>
-      <c r="W28" t="inlineStr"/>
+        <v>1.589571</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.016965</v>
+      </c>
       <c r="X28" t="n">
-        <v>4.836176</v>
+        <v>1.222519</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.653504</v>
+        <v>-1.12946</v>
       </c>
       <c r="Z28" t="n">
-        <v>-5.674036</v>
+        <v>5.861824</v>
       </c>
       <c r="AA28" t="n">
-        <v>-6.990222</v>
+        <v>6.061784</v>
       </c>
       <c r="AB28" t="n">
-        <v>-3.667846</v>
+        <v>-5.508311</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.05739</v>
+        <v>-4.880637</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45322</v>
+        <v>45351</v>
       </c>
       <c r="B29" t="n">
-        <v>127752</v>
+        <v>129020</v>
       </c>
       <c r="C29" t="n">
-        <v>123.949997</v>
+        <v>125.25</v>
       </c>
       <c r="D29" t="n">
-        <v>106.370003</v>
+        <v>106.5</v>
       </c>
       <c r="E29" t="n">
-        <v>266.619995</v>
+        <v>281.100006</v>
       </c>
       <c r="F29" t="n">
-        <v>4.9503</v>
+        <v>4.9673</v>
       </c>
       <c r="G29" t="n">
-        <v>5.3604</v>
+        <v>5.381</v>
       </c>
       <c r="H29" t="n">
-        <v>4845.649902</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>5096.27002</v>
+      </c>
+      <c r="I29" t="n">
+        <v>16091.919922</v>
+      </c>
       <c r="J29" t="n">
-        <v>38150.300781</v>
+        <v>38996.390625</v>
       </c>
       <c r="K29" t="n">
-        <v>2048.399902</v>
+        <v>2054.699951</v>
       </c>
       <c r="L29" t="n">
-        <v>75.849998</v>
+        <v>78.260002</v>
       </c>
       <c r="M29" t="n">
-        <v>81.709999</v>
+        <v>83.620003</v>
       </c>
       <c r="N29" t="n">
-        <v>1222.25</v>
+        <v>1128.25</v>
       </c>
       <c r="O29" t="n">
-        <v>448.25</v>
+        <v>415.75</v>
       </c>
       <c r="P29" t="n">
-        <v>-4.794128</v>
+        <v>0.992548</v>
       </c>
       <c r="Q29" t="n">
-        <v>-4.939031</v>
+        <v>1.048812</v>
       </c>
       <c r="R29" t="n">
-        <v>-6.033564</v>
+        <v>0.122212</v>
       </c>
       <c r="S29" t="n">
-        <v>3.497539</v>
+        <v>5.430955</v>
       </c>
       <c r="T29" t="n">
-        <v>2.063833</v>
+        <v>0.343408</v>
       </c>
       <c r="U29" t="n">
-        <v>0.325665</v>
+        <v>0.384297</v>
       </c>
       <c r="V29" t="n">
-        <v>1.589571</v>
-      </c>
-      <c r="W29" t="inlineStr"/>
+        <v>5.172064</v>
+      </c>
+      <c r="W29" t="n">
+        <v>6.119161</v>
+      </c>
       <c r="X29" t="n">
-        <v>1.222519</v>
+        <v>2.21778</v>
       </c>
       <c r="Y29" t="n">
-        <v>-1.12946</v>
+        <v>0.30756</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.861824</v>
+        <v>3.177329</v>
       </c>
       <c r="AA29" t="n">
-        <v>6.061784</v>
+        <v>2.33754</v>
       </c>
       <c r="AB29" t="n">
-        <v>-5.508311</v>
+        <v>-7.690734</v>
       </c>
       <c r="AC29" t="n">
-        <v>-4.880637</v>
+        <v>-7.250418</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45351</v>
+        <v>45382</v>
       </c>
       <c r="B30" t="n">
-        <v>129020</v>
+        <v>128106</v>
       </c>
       <c r="C30" t="n">
-        <v>125.25</v>
+        <v>124.330002</v>
       </c>
       <c r="D30" t="n">
-        <v>106.5</v>
+        <v>109</v>
       </c>
       <c r="E30" t="n">
-        <v>281.100006</v>
+        <v>292.600006</v>
       </c>
       <c r="F30" t="n">
-        <v>4.9673</v>
+        <v>5.0141</v>
       </c>
       <c r="G30" t="n">
-        <v>5.381</v>
+        <v>5.4065</v>
       </c>
       <c r="H30" t="n">
-        <v>5096.27002</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>5254.350098</v>
+      </c>
+      <c r="I30" t="n">
+        <v>16379.459961</v>
+      </c>
       <c r="J30" t="n">
-        <v>38996.390625</v>
+        <v>39807.371094</v>
       </c>
       <c r="K30" t="n">
-        <v>2054.699951</v>
+        <v>2217.399902</v>
       </c>
       <c r="L30" t="n">
-        <v>78.260002</v>
+        <v>83.16999800000001</v>
       </c>
       <c r="M30" t="n">
-        <v>83.620003</v>
+        <v>87.480003</v>
       </c>
       <c r="N30" t="n">
-        <v>1128.25</v>
+        <v>1191.5</v>
       </c>
       <c r="O30" t="n">
-        <v>415.75</v>
+        <v>442</v>
       </c>
       <c r="P30" t="n">
-        <v>0.992548</v>
+        <v>-0.708417</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.048812</v>
+        <v>-0.734529</v>
       </c>
       <c r="R30" t="n">
-        <v>0.122212</v>
+        <v>2.347418</v>
       </c>
       <c r="S30" t="n">
-        <v>5.430955</v>
+        <v>4.091071</v>
       </c>
       <c r="T30" t="n">
-        <v>0.343408</v>
+        <v>0.942164</v>
       </c>
       <c r="U30" t="n">
-        <v>0.384297</v>
+        <v>0.473886</v>
       </c>
       <c r="V30" t="n">
-        <v>5.172064</v>
-      </c>
-      <c r="W30" t="inlineStr"/>
+        <v>3.101878</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.78686</v>
+      </c>
       <c r="X30" t="n">
-        <v>2.21778</v>
+        <v>2.07963</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.30756</v>
+        <v>7.918429</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.177329</v>
+        <v>6.273953</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.33754</v>
+        <v>4.616121</v>
       </c>
       <c r="AB30" t="n">
-        <v>-7.690734</v>
+        <v>5.606027</v>
       </c>
       <c r="AC30" t="n">
-        <v>-7.250418</v>
+        <v>6.313891</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45382</v>
+        <v>45412</v>
       </c>
       <c r="B31" t="n">
-        <v>128106</v>
+        <v>125924</v>
       </c>
       <c r="C31" t="n">
-        <v>124.330002</v>
+        <v>122.379997</v>
       </c>
       <c r="D31" t="n">
-        <v>109</v>
+        <v>100.5</v>
       </c>
       <c r="E31" t="n">
-        <v>292.600006</v>
+        <v>291</v>
       </c>
       <c r="F31" t="n">
-        <v>5.0141</v>
+        <v>5.117</v>
       </c>
       <c r="G31" t="n">
-        <v>5.4065</v>
+        <v>5.4794</v>
       </c>
       <c r="H31" t="n">
-        <v>5254.350098</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>5035.689941</v>
+      </c>
+      <c r="I31" t="n">
+        <v>15657.820312</v>
+      </c>
       <c r="J31" t="n">
-        <v>39807.371094</v>
+        <v>37815.921875</v>
       </c>
       <c r="K31" t="n">
-        <v>2217.399902</v>
+        <v>2302.899902</v>
       </c>
       <c r="L31" t="n">
-        <v>83.16999800000001</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>87.480003</v>
+        <v>87.860001</v>
       </c>
       <c r="N31" t="n">
-        <v>1191.5</v>
+        <v>1145.5</v>
       </c>
       <c r="O31" t="n">
-        <v>442</v>
+        <v>439.5</v>
       </c>
       <c r="P31" t="n">
-        <v>-0.708417</v>
+        <v>-1.703277</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.734529</v>
+        <v>-1.56841</v>
       </c>
       <c r="R31" t="n">
-        <v>2.347418</v>
+        <v>-7.798165</v>
       </c>
       <c r="S31" t="n">
-        <v>4.091071</v>
+        <v>-0.546824</v>
       </c>
       <c r="T31" t="n">
-        <v>0.942164</v>
+        <v>2.052213</v>
       </c>
       <c r="U31" t="n">
-        <v>0.473886</v>
+        <v>1.348382</v>
       </c>
       <c r="V31" t="n">
-        <v>3.101878</v>
-      </c>
-      <c r="W31" t="inlineStr"/>
+        <v>-4.161507</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-4.40576</v>
+      </c>
       <c r="X31" t="n">
-        <v>2.07963</v>
+        <v>-5.002715</v>
       </c>
       <c r="Y31" t="n">
-        <v>7.918429</v>
+        <v>3.855867</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.273953</v>
+        <v>-1.49092</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.616121</v>
+        <v>0.434382</v>
       </c>
       <c r="AB31" t="n">
-        <v>5.606027</v>
+        <v>-3.86068</v>
       </c>
       <c r="AC31" t="n">
-        <v>6.313891</v>
+        <v>-0.565611</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45412</v>
+        <v>45443</v>
       </c>
       <c r="B32" t="n">
-        <v>125924</v>
+        <v>122098</v>
       </c>
       <c r="C32" t="n">
-        <v>122.379997</v>
+        <v>118.660004</v>
       </c>
       <c r="D32" t="n">
-        <v>100.5</v>
+        <v>96.870003</v>
       </c>
       <c r="E32" t="n">
-        <v>291</v>
+        <v>308.200012</v>
       </c>
       <c r="F32" t="n">
-        <v>5.117</v>
+        <v>5.2021</v>
       </c>
       <c r="G32" t="n">
-        <v>5.4794</v>
+        <v>5.6311</v>
       </c>
       <c r="H32" t="n">
-        <v>5035.689941</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>5277.509766</v>
+      </c>
+      <c r="I32" t="n">
+        <v>16735.019531</v>
+      </c>
       <c r="J32" t="n">
-        <v>37815.921875</v>
+        <v>38686.320312</v>
       </c>
       <c r="K32" t="n">
-        <v>2302.899902</v>
+        <v>2322.899902</v>
       </c>
       <c r="L32" t="n">
-        <v>81.93000000000001</v>
+        <v>76.989998</v>
       </c>
       <c r="M32" t="n">
-        <v>87.860001</v>
+        <v>81.620003</v>
       </c>
       <c r="N32" t="n">
-        <v>1145.5</v>
+        <v>1205</v>
       </c>
       <c r="O32" t="n">
-        <v>439.5</v>
+        <v>446.25</v>
       </c>
       <c r="P32" t="n">
-        <v>-1.703277</v>
+        <v>-3.038341</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.56841</v>
+        <v>-3.039707</v>
       </c>
       <c r="R32" t="n">
-        <v>-7.798165</v>
+        <v>-3.611938</v>
       </c>
       <c r="S32" t="n">
-        <v>-0.546824</v>
+        <v>5.910657</v>
       </c>
       <c r="T32" t="n">
-        <v>2.052213</v>
+        <v>1.663078</v>
       </c>
       <c r="U32" t="n">
-        <v>1.348382</v>
+        <v>2.768552</v>
       </c>
       <c r="V32" t="n">
-        <v>-4.161507</v>
-      </c>
-      <c r="W32" t="inlineStr"/>
+        <v>4.802119</v>
+      </c>
+      <c r="W32" t="n">
+        <v>6.879624</v>
+      </c>
       <c r="X32" t="n">
-        <v>-5.002715</v>
+        <v>2.301672</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.855867</v>
+        <v>0.86847</v>
       </c>
       <c r="Z32" t="n">
-        <v>-1.49092</v>
+        <v>-6.02954</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.434382</v>
+        <v>-7.102206</v>
       </c>
       <c r="AB32" t="n">
-        <v>-3.86068</v>
+        <v>5.194238</v>
       </c>
       <c r="AC32" t="n">
-        <v>-0.565611</v>
+        <v>1.535836</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45443</v>
+        <v>45473</v>
       </c>
       <c r="B33" t="n">
-        <v>122098</v>
+        <v>123907</v>
       </c>
       <c r="C33" t="n">
-        <v>118.660004</v>
+        <v>120.379997</v>
       </c>
       <c r="D33" t="n">
-        <v>96.870003</v>
+        <v>96.449997</v>
       </c>
       <c r="E33" t="n">
-        <v>308.200012</v>
+        <v>339.829987</v>
       </c>
       <c r="F33" t="n">
-        <v>5.2021</v>
+        <v>5.5005</v>
       </c>
       <c r="G33" t="n">
-        <v>5.6311</v>
+        <v>5.8909</v>
       </c>
       <c r="H33" t="n">
-        <v>5277.509766</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>5460.47998</v>
+      </c>
+      <c r="I33" t="n">
+        <v>17732.599609</v>
+      </c>
       <c r="J33" t="n">
-        <v>38686.320312</v>
+        <v>39118.859375</v>
       </c>
       <c r="K33" t="n">
-        <v>2322.899902</v>
+        <v>2339.600098</v>
       </c>
       <c r="L33" t="n">
-        <v>76.989998</v>
+        <v>81.540001</v>
       </c>
       <c r="M33" t="n">
-        <v>81.620003</v>
+        <v>86.410004</v>
       </c>
       <c r="N33" t="n">
-        <v>1205</v>
+        <v>1150.5</v>
       </c>
       <c r="O33" t="n">
-        <v>446.25</v>
+        <v>397.25</v>
       </c>
       <c r="P33" t="n">
-        <v>-3.038341</v>
+        <v>1.481597</v>
       </c>
       <c r="Q33" t="n">
-        <v>-3.039707</v>
+        <v>1.449514</v>
       </c>
       <c r="R33" t="n">
-        <v>-3.611938</v>
+        <v>-0.433577</v>
       </c>
       <c r="S33" t="n">
-        <v>5.910657</v>
+        <v>10.262808</v>
       </c>
       <c r="T33" t="n">
-        <v>1.663078</v>
+        <v>5.736153</v>
       </c>
       <c r="U33" t="n">
-        <v>2.768552</v>
+        <v>4.613663</v>
       </c>
       <c r="V33" t="n">
-        <v>4.802119</v>
-      </c>
-      <c r="W33" t="inlineStr"/>
+        <v>3.46698</v>
+      </c>
+      <c r="W33" t="n">
+        <v>5.961033</v>
+      </c>
       <c r="X33" t="n">
-        <v>2.301672</v>
+        <v>1.118067</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.86847</v>
+        <v>0.718937</v>
       </c>
       <c r="Z33" t="n">
-        <v>-6.02954</v>
+        <v>5.909863</v>
       </c>
       <c r="AA33" t="n">
-        <v>-7.102206</v>
+        <v>5.868661</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.194238</v>
+        <v>-4.522822</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.535836</v>
+        <v>-10.980392</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45473</v>
+        <v>45504</v>
       </c>
       <c r="B34" t="n">
-        <v>123907</v>
+        <v>127652</v>
       </c>
       <c r="C34" t="n">
-        <v>120.379997</v>
+        <v>124.040001</v>
       </c>
       <c r="D34" t="n">
-        <v>96.449997</v>
+        <v>98.5</v>
       </c>
       <c r="E34" t="n">
-        <v>339.829987</v>
+        <v>347.700012</v>
       </c>
       <c r="F34" t="n">
-        <v>5.5005</v>
+        <v>5.6111</v>
       </c>
       <c r="G34" t="n">
-        <v>5.8909</v>
+        <v>6.0695</v>
       </c>
       <c r="H34" t="n">
-        <v>5460.47998</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>5522.299805</v>
+      </c>
+      <c r="I34" t="n">
+        <v>17599.400391</v>
+      </c>
       <c r="J34" t="n">
-        <v>39118.859375</v>
+        <v>40842.789062</v>
       </c>
       <c r="K34" t="n">
-        <v>2339.600098</v>
+        <v>2426.5</v>
       </c>
       <c r="L34" t="n">
-        <v>81.540001</v>
+        <v>77.910004</v>
       </c>
       <c r="M34" t="n">
-        <v>86.410004</v>
+        <v>80.720001</v>
       </c>
       <c r="N34" t="n">
-        <v>1150.5</v>
+        <v>1028.5</v>
       </c>
       <c r="O34" t="n">
-        <v>397.25</v>
+        <v>382.75</v>
       </c>
       <c r="P34" t="n">
-        <v>1.481597</v>
+        <v>3.022428</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.449514</v>
+        <v>3.040375</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.433577</v>
+        <v>2.125457</v>
       </c>
       <c r="S34" t="n">
-        <v>10.262808</v>
+        <v>2.315871</v>
       </c>
       <c r="T34" t="n">
-        <v>5.736153</v>
+        <v>2.010726</v>
       </c>
       <c r="U34" t="n">
-        <v>4.613663</v>
+        <v>3.031792</v>
       </c>
       <c r="V34" t="n">
-        <v>3.46698</v>
-      </c>
-      <c r="W34" t="inlineStr"/>
+        <v>1.132132</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-0.751154</v>
+      </c>
       <c r="X34" t="n">
-        <v>1.118067</v>
+        <v>4.406902</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.718937</v>
+        <v>3.714306</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.909863</v>
+        <v>-4.451799</v>
       </c>
       <c r="AA34" t="n">
-        <v>5.868661</v>
+        <v>-6.584889</v>
       </c>
       <c r="AB34" t="n">
-        <v>-4.522822</v>
+        <v>-10.604085</v>
       </c>
       <c r="AC34" t="n">
-        <v>-10.980392</v>
+        <v>-3.650094</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45504</v>
+        <v>45535</v>
       </c>
       <c r="B35" t="n">
-        <v>127652</v>
+        <v>136004</v>
       </c>
       <c r="C35" t="n">
-        <v>124.040001</v>
+        <v>132.600006</v>
       </c>
       <c r="D35" t="n">
-        <v>98.5</v>
+        <v>102.769997</v>
       </c>
       <c r="E35" t="n">
-        <v>347.700012</v>
+        <v>354.850006</v>
       </c>
       <c r="F35" t="n">
-        <v>5.6111</v>
+        <v>5.6277</v>
       </c>
       <c r="G35" t="n">
-        <v>6.0695</v>
+        <v>6.2224</v>
       </c>
       <c r="H35" t="n">
-        <v>5522.299805</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>5648.399902</v>
+      </c>
+      <c r="I35" t="n">
+        <v>17713.619141</v>
+      </c>
       <c r="J35" t="n">
-        <v>40842.789062</v>
+        <v>41563.078125</v>
       </c>
       <c r="K35" t="n">
-        <v>2426.5</v>
+        <v>2527.600098</v>
       </c>
       <c r="L35" t="n">
-        <v>77.910004</v>
+        <v>73.550003</v>
       </c>
       <c r="M35" t="n">
-        <v>80.720001</v>
+        <v>78.800003</v>
       </c>
       <c r="N35" t="n">
-        <v>1028.5</v>
+        <v>982</v>
       </c>
       <c r="O35" t="n">
-        <v>382.75</v>
+        <v>378</v>
       </c>
       <c r="P35" t="n">
-        <v>3.022428</v>
+        <v>6.542788</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.040375</v>
+        <v>6.901004</v>
       </c>
       <c r="R35" t="n">
-        <v>2.125457</v>
+        <v>4.335022</v>
       </c>
       <c r="S35" t="n">
-        <v>2.315871</v>
+        <v>2.056369</v>
       </c>
       <c r="T35" t="n">
-        <v>2.010726</v>
+        <v>0.295836</v>
       </c>
       <c r="U35" t="n">
-        <v>3.031792</v>
+        <v>2.519157</v>
       </c>
       <c r="V35" t="n">
-        <v>1.132132</v>
-      </c>
-      <c r="W35" t="inlineStr"/>
+        <v>2.283471</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.648992</v>
+      </c>
       <c r="X35" t="n">
-        <v>4.406902</v>
+        <v>1.763565</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.714306</v>
+        <v>4.166499</v>
       </c>
       <c r="Z35" t="n">
-        <v>-4.451799</v>
+        <v>-5.596201</v>
       </c>
       <c r="AA35" t="n">
-        <v>-6.584889</v>
+        <v>-2.37859</v>
       </c>
       <c r="AB35" t="n">
-        <v>-10.604085</v>
+        <v>-4.521147</v>
       </c>
       <c r="AC35" t="n">
-        <v>-3.650094</v>
+        <v>-1.241019</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45535</v>
+        <v>45565</v>
       </c>
       <c r="B36" t="n">
-        <v>136004</v>
+        <v>131816</v>
       </c>
       <c r="C36" t="n">
-        <v>132.600006</v>
+        <v>128.429993</v>
       </c>
       <c r="D36" t="n">
-        <v>102.769997</v>
+        <v>97.959999</v>
       </c>
       <c r="E36" t="n">
-        <v>354.850006</v>
+        <v>349.799988</v>
       </c>
       <c r="F36" t="n">
-        <v>5.6277</v>
+        <v>5.4332</v>
       </c>
       <c r="G36" t="n">
-        <v>6.2224</v>
+        <v>6.0652</v>
       </c>
       <c r="H36" t="n">
-        <v>5648.399902</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+        <v>5762.47998</v>
+      </c>
+      <c r="I36" t="n">
+        <v>18189.169922</v>
+      </c>
       <c r="J36" t="n">
-        <v>41563.078125</v>
+        <v>42330.148438</v>
       </c>
       <c r="K36" t="n">
-        <v>2527.600098</v>
+        <v>2659.399902</v>
       </c>
       <c r="L36" t="n">
-        <v>73.550003</v>
+        <v>68.16999800000001</v>
       </c>
       <c r="M36" t="n">
-        <v>78.800003</v>
+        <v>71.769997</v>
       </c>
       <c r="N36" t="n">
-        <v>982</v>
+        <v>1057</v>
       </c>
       <c r="O36" t="n">
-        <v>378</v>
+        <v>424.75</v>
       </c>
       <c r="P36" t="n">
-        <v>6.542788</v>
+        <v>-3.079321</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.901004</v>
+        <v>-3.144806</v>
       </c>
       <c r="R36" t="n">
-        <v>4.335022</v>
+        <v>-4.680352</v>
       </c>
       <c r="S36" t="n">
-        <v>2.056369</v>
+        <v>-1.423142</v>
       </c>
       <c r="T36" t="n">
-        <v>0.295836</v>
+        <v>-3.456118</v>
       </c>
       <c r="U36" t="n">
-        <v>2.519157</v>
+        <v>-2.526362</v>
       </c>
       <c r="V36" t="n">
-        <v>2.283471</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
+        <v>2.019688</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.684662</v>
+      </c>
       <c r="X36" t="n">
-        <v>1.763565</v>
+        <v>1.845557</v>
       </c>
       <c r="Y36" t="n">
-        <v>4.166499</v>
+        <v>5.214425</v>
       </c>
       <c r="Z36" t="n">
-        <v>-5.596201</v>
+        <v>-7.314758</v>
       </c>
       <c r="AA36" t="n">
-        <v>-2.37859</v>
+        <v>-8.921328000000001</v>
       </c>
       <c r="AB36" t="n">
-        <v>-4.521147</v>
+        <v>7.637475</v>
       </c>
       <c r="AC36" t="n">
-        <v>-1.241019</v>
+        <v>12.367725</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="B37" t="n">
-        <v>131816</v>
+        <v>129713</v>
       </c>
       <c r="C37" t="n">
-        <v>128.429993</v>
+        <v>126.260002</v>
       </c>
       <c r="D37" t="n">
-        <v>97.959999</v>
+        <v>97.25</v>
       </c>
       <c r="E37" t="n">
-        <v>349.799988</v>
+        <v>368.579987</v>
       </c>
       <c r="F37" t="n">
-        <v>5.4332</v>
+        <v>5.7623</v>
       </c>
       <c r="G37" t="n">
-        <v>6.0652</v>
+        <v>6.2522</v>
       </c>
       <c r="H37" t="n">
-        <v>5762.47998</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
+        <v>5705.450195</v>
+      </c>
+      <c r="I37" t="n">
+        <v>18095.150391</v>
+      </c>
       <c r="J37" t="n">
-        <v>42330.148438</v>
+        <v>41763.460938</v>
       </c>
       <c r="K37" t="n">
-        <v>2659.399902</v>
+        <v>2749.300049</v>
       </c>
       <c r="L37" t="n">
-        <v>68.16999800000001</v>
+        <v>69.260002</v>
       </c>
       <c r="M37" t="n">
-        <v>71.769997</v>
+        <v>73.160004</v>
       </c>
       <c r="N37" t="n">
-        <v>1057</v>
+        <v>982.5</v>
       </c>
       <c r="O37" t="n">
-        <v>424.75</v>
+        <v>410.75</v>
       </c>
       <c r="P37" t="n">
-        <v>-3.079321</v>
+        <v>-1.595406</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.144806</v>
+        <v>-1.689629</v>
       </c>
       <c r="R37" t="n">
-        <v>-4.680352</v>
+        <v>-0.724785</v>
       </c>
       <c r="S37" t="n">
-        <v>-1.423142</v>
+        <v>5.368782</v>
       </c>
       <c r="T37" t="n">
-        <v>-3.456118</v>
+        <v>6.057206</v>
       </c>
       <c r="U37" t="n">
-        <v>-2.526362</v>
+        <v>3.083168</v>
       </c>
       <c r="V37" t="n">
-        <v>2.019688</v>
-      </c>
-      <c r="W37" t="inlineStr"/>
+        <v>-0.9896740000000001</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-0.516898</v>
+      </c>
       <c r="X37" t="n">
-        <v>1.845557</v>
+        <v>-1.338733</v>
       </c>
       <c r="Y37" t="n">
-        <v>5.214425</v>
+        <v>3.380467</v>
       </c>
       <c r="Z37" t="n">
-        <v>-7.314758</v>
+        <v>1.59895</v>
       </c>
       <c r="AA37" t="n">
-        <v>-8.921328000000001</v>
+        <v>1.936752</v>
       </c>
       <c r="AB37" t="n">
-        <v>7.637475</v>
+        <v>-7.04825</v>
       </c>
       <c r="AC37" t="n">
-        <v>12.367725</v>
+        <v>-3.296057</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45596</v>
+        <v>45626</v>
       </c>
       <c r="B38" t="n">
-        <v>129713</v>
+        <v>125668</v>
       </c>
       <c r="C38" t="n">
-        <v>126.260002</v>
+        <v>122.32</v>
       </c>
       <c r="D38" t="n">
-        <v>97.25</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>368.579987</v>
+        <v>402.850006</v>
       </c>
       <c r="F38" t="n">
-        <v>5.7623</v>
+        <v>6.0139</v>
       </c>
       <c r="G38" t="n">
-        <v>6.2522</v>
+        <v>6.345178</v>
       </c>
       <c r="H38" t="n">
-        <v>5705.450195</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>6032.379883</v>
+      </c>
+      <c r="I38" t="n">
+        <v>19218.169922</v>
+      </c>
       <c r="J38" t="n">
-        <v>41763.460938</v>
+        <v>44910.648438</v>
       </c>
       <c r="K38" t="n">
-        <v>2749.300049</v>
+        <v>2657</v>
       </c>
       <c r="L38" t="n">
-        <v>69.260002</v>
+        <v>68</v>
       </c>
       <c r="M38" t="n">
-        <v>73.160004</v>
+        <v>72.94000200000001</v>
       </c>
       <c r="N38" t="n">
-        <v>982.5</v>
+        <v>989.5</v>
       </c>
       <c r="O38" t="n">
-        <v>410.75</v>
+        <v>423</v>
       </c>
       <c r="P38" t="n">
-        <v>-1.595406</v>
+        <v>-3.118423</v>
       </c>
       <c r="Q38" t="n">
-        <v>-1.689629</v>
+        <v>-3.120547</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.724785</v>
+        <v>-4.041131</v>
       </c>
       <c r="S38" t="n">
-        <v>5.368782</v>
+        <v>9.297851</v>
       </c>
       <c r="T38" t="n">
-        <v>6.057206</v>
+        <v>4.366308</v>
       </c>
       <c r="U38" t="n">
-        <v>3.083168</v>
+        <v>1.487125</v>
       </c>
       <c r="V38" t="n">
-        <v>-0.9896740000000001</v>
-      </c>
-      <c r="W38" t="inlineStr"/>
+        <v>5.73013</v>
+      </c>
+      <c r="W38" t="n">
+        <v>6.206191</v>
+      </c>
       <c r="X38" t="n">
-        <v>-1.338733</v>
+        <v>7.535744</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.380467</v>
+        <v>-3.35722</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.59895</v>
+        <v>-1.819235</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.936752</v>
+        <v>-0.300712</v>
       </c>
       <c r="AB38" t="n">
-        <v>-7.04825</v>
+        <v>0.712468</v>
       </c>
       <c r="AC38" t="n">
-        <v>-3.296057</v>
+        <v>2.982349</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45626</v>
+        <v>45657</v>
       </c>
       <c r="B39" t="n">
-        <v>125668</v>
+        <v>120283</v>
       </c>
       <c r="C39" t="n">
-        <v>122.32</v>
+        <v>117.269997</v>
       </c>
       <c r="D39" t="n">
-        <v>93.31999999999999</v>
+        <v>85.949997</v>
       </c>
       <c r="E39" t="n">
-        <v>402.850006</v>
+        <v>407.700012</v>
       </c>
       <c r="F39" t="n">
-        <v>6.0139</v>
+        <v>6.1779</v>
       </c>
       <c r="G39" t="n">
-        <v>6.345178</v>
+        <v>6.422608</v>
       </c>
       <c r="H39" t="n">
-        <v>6032.379883</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>5881.629883</v>
+      </c>
+      <c r="I39" t="n">
+        <v>19310.789062</v>
+      </c>
       <c r="J39" t="n">
-        <v>44910.648438</v>
+        <v>42544.21875</v>
       </c>
       <c r="K39" t="n">
-        <v>2657</v>
+        <v>2641</v>
       </c>
       <c r="L39" t="n">
-        <v>68</v>
+        <v>71.720001</v>
       </c>
       <c r="M39" t="n">
-        <v>72.94000200000001</v>
+        <v>74.639999</v>
       </c>
       <c r="N39" t="n">
-        <v>989.5</v>
+        <v>998.25</v>
       </c>
       <c r="O39" t="n">
-        <v>423</v>
+        <v>458.5</v>
       </c>
       <c r="P39" t="n">
-        <v>-3.118423</v>
+        <v>-4.2851</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3.120547</v>
+        <v>-4.128518</v>
       </c>
       <c r="R39" t="n">
-        <v>-4.041131</v>
+        <v>-7.89756</v>
       </c>
       <c r="S39" t="n">
-        <v>9.297851</v>
+        <v>1.203924</v>
       </c>
       <c r="T39" t="n">
-        <v>4.366308</v>
+        <v>2.727016</v>
       </c>
       <c r="U39" t="n">
-        <v>1.487125</v>
+        <v>1.220293</v>
       </c>
       <c r="V39" t="n">
-        <v>5.73013</v>
-      </c>
-      <c r="W39" t="inlineStr"/>
+        <v>-2.499014</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.481935</v>
+      </c>
       <c r="X39" t="n">
-        <v>7.535744</v>
+        <v>-5.269195</v>
       </c>
       <c r="Y39" t="n">
-        <v>-3.35722</v>
+        <v>-0.602183</v>
       </c>
       <c r="Z39" t="n">
-        <v>-1.819235</v>
+        <v>5.47059</v>
       </c>
       <c r="AA39" t="n">
-        <v>-0.300712</v>
+        <v>2.330678</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.712468</v>
+        <v>0.884285</v>
       </c>
       <c r="AC39" t="n">
-        <v>2.982349</v>
+        <v>8.392435000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45657</v>
+        <v>45688</v>
       </c>
       <c r="B40" t="n">
-        <v>120283</v>
+        <v>126135</v>
       </c>
       <c r="C40" t="n">
-        <v>117.269997</v>
+        <v>123</v>
       </c>
       <c r="D40" t="n">
-        <v>85.949997</v>
+        <v>91.400002</v>
       </c>
       <c r="E40" t="n">
-        <v>407.700012</v>
+        <v>394.149994</v>
       </c>
       <c r="F40" t="n">
-        <v>6.1779</v>
+        <v>5.8745</v>
       </c>
       <c r="G40" t="n">
-        <v>6.422608</v>
+        <v>6.101281</v>
       </c>
       <c r="H40" t="n">
-        <v>5881.629883</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>6040.529785</v>
+      </c>
+      <c r="I40" t="n">
+        <v>19627.439453</v>
+      </c>
       <c r="J40" t="n">
-        <v>42544.21875</v>
+        <v>44544.660156</v>
       </c>
       <c r="K40" t="n">
-        <v>2641</v>
+        <v>2812.5</v>
       </c>
       <c r="L40" t="n">
-        <v>71.720001</v>
+        <v>72.529999</v>
       </c>
       <c r="M40" t="n">
-        <v>74.639999</v>
+        <v>76.760002</v>
       </c>
       <c r="N40" t="n">
-        <v>998.25</v>
+        <v>1042</v>
       </c>
       <c r="O40" t="n">
-        <v>458.5</v>
+        <v>482</v>
       </c>
       <c r="P40" t="n">
-        <v>-4.2851</v>
+        <v>4.865193</v>
       </c>
       <c r="Q40" t="n">
-        <v>-4.128518</v>
+        <v>4.886163</v>
       </c>
       <c r="R40" t="n">
-        <v>-7.89756</v>
+        <v>6.340901</v>
       </c>
       <c r="S40" t="n">
-        <v>1.203924</v>
+        <v>-3.323527</v>
       </c>
       <c r="T40" t="n">
-        <v>2.727016</v>
+        <v>-4.911055</v>
       </c>
       <c r="U40" t="n">
-        <v>1.220293</v>
+        <v>-5.003057</v>
       </c>
       <c r="V40" t="n">
-        <v>-2.499014</v>
-      </c>
-      <c r="W40" t="inlineStr"/>
+        <v>2.70163</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.639759</v>
+      </c>
       <c r="X40" t="n">
-        <v>-5.269195</v>
+        <v>4.702029</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.602183</v>
+        <v>6.493752</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.47059</v>
+        <v>1.129389</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.330678</v>
+        <v>2.840304</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.884285</v>
+        <v>4.38267</v>
       </c>
       <c r="AC40" t="n">
-        <v>8.392435000000001</v>
+        <v>5.125409</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45688</v>
+        <v>45716</v>
       </c>
       <c r="B41" t="n">
-        <v>126135</v>
+        <v>122799</v>
       </c>
       <c r="C41" t="n">
-        <v>123</v>
+        <v>120.010002</v>
       </c>
       <c r="D41" t="n">
-        <v>91.400002</v>
+        <v>87.599998</v>
       </c>
       <c r="E41" t="n">
-        <v>394.149994</v>
+        <v>392.700012</v>
       </c>
       <c r="F41" t="n">
-        <v>5.8745</v>
+        <v>5.839</v>
       </c>
       <c r="G41" t="n">
-        <v>6.101281</v>
+        <v>6.064281</v>
       </c>
       <c r="H41" t="n">
-        <v>6040.529785</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>5954.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>18847.279297</v>
+      </c>
       <c r="J41" t="n">
-        <v>44544.660156</v>
+        <v>43840.910156</v>
       </c>
       <c r="K41" t="n">
-        <v>2812.5</v>
+        <v>2848.5</v>
       </c>
       <c r="L41" t="n">
-        <v>72.529999</v>
+        <v>69.760002</v>
       </c>
       <c r="M41" t="n">
-        <v>76.760002</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>1042</v>
+        <v>1011.5</v>
       </c>
       <c r="O41" t="n">
-        <v>482</v>
+        <v>453.5</v>
       </c>
       <c r="P41" t="n">
-        <v>4.865193</v>
+        <v>-2.644785</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.886163</v>
+        <v>-2.430893</v>
       </c>
       <c r="R41" t="n">
-        <v>6.340901</v>
+        <v>-4.157553</v>
       </c>
       <c r="S41" t="n">
-        <v>-3.323527</v>
+        <v>-0.367876</v>
       </c>
       <c r="T41" t="n">
-        <v>-4.911055</v>
+        <v>-0.604299</v>
       </c>
       <c r="U41" t="n">
-        <v>-5.003057</v>
+        <v>-0.606433</v>
       </c>
       <c r="V41" t="n">
-        <v>2.70163</v>
-      </c>
-      <c r="W41" t="inlineStr"/>
+        <v>-1.424209</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-3.974844</v>
+      </c>
       <c r="X41" t="n">
-        <v>4.702029</v>
+        <v>-1.579875</v>
       </c>
       <c r="Y41" t="n">
-        <v>6.493752</v>
+        <v>1.28</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.129389</v>
+        <v>-3.819105</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.840304</v>
+        <v>-4.66389</v>
       </c>
       <c r="AB41" t="n">
-        <v>4.38267</v>
+        <v>-2.927063</v>
       </c>
       <c r="AC41" t="n">
-        <v>5.125409</v>
+        <v>-5.912863</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="B42" t="n">
-        <v>122799</v>
+        <v>130260</v>
       </c>
       <c r="C42" t="n">
-        <v>120.010002</v>
+        <v>127.300003</v>
       </c>
       <c r="D42" t="n">
-        <v>87.599998</v>
+        <v>93.41999800000001</v>
       </c>
       <c r="E42" t="n">
-        <v>392.700012</v>
+        <v>358.700012</v>
       </c>
       <c r="F42" t="n">
-        <v>5.839</v>
+        <v>5.7581</v>
       </c>
       <c r="G42" t="n">
-        <v>6.064281</v>
+        <v>6.22665</v>
       </c>
       <c r="H42" t="n">
-        <v>5954.5</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>5611.850098</v>
+      </c>
+      <c r="I42" t="n">
+        <v>17299.289062</v>
+      </c>
       <c r="J42" t="n">
-        <v>43840.910156</v>
+        <v>42001.761719</v>
       </c>
       <c r="K42" t="n">
-        <v>2848.5</v>
+        <v>3122.800049</v>
       </c>
       <c r="L42" t="n">
-        <v>69.760002</v>
+        <v>71.480003</v>
       </c>
       <c r="M42" t="n">
-        <v>73.18000000000001</v>
+        <v>74.739998</v>
       </c>
       <c r="N42" t="n">
-        <v>1011.5</v>
+        <v>1014.75</v>
       </c>
       <c r="O42" t="n">
-        <v>453.5</v>
+        <v>457.25</v>
       </c>
       <c r="P42" t="n">
-        <v>-2.644785</v>
+        <v>6.075782</v>
       </c>
       <c r="Q42" t="n">
-        <v>-2.430893</v>
+        <v>6.074494</v>
       </c>
       <c r="R42" t="n">
-        <v>-4.157553</v>
+        <v>6.643835</v>
       </c>
       <c r="S42" t="n">
-        <v>-0.367876</v>
+        <v>-8.658008000000001</v>
       </c>
       <c r="T42" t="n">
-        <v>-0.604299</v>
+        <v>-1.385514</v>
       </c>
       <c r="U42" t="n">
-        <v>-0.606433</v>
+        <v>2.677469</v>
       </c>
       <c r="V42" t="n">
-        <v>-1.424209</v>
-      </c>
-      <c r="W42" t="inlineStr"/>
+        <v>-5.75447</v>
+      </c>
+      <c r="W42" t="n">
+        <v>-8.213335000000001</v>
+      </c>
       <c r="X42" t="n">
-        <v>-1.579875</v>
+        <v>-4.195051</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.28</v>
+        <v>9.629631</v>
       </c>
       <c r="Z42" t="n">
-        <v>-3.819105</v>
+        <v>2.465598</v>
       </c>
       <c r="AA42" t="n">
-        <v>-4.66389</v>
+        <v>2.131727</v>
       </c>
       <c r="AB42" t="n">
-        <v>-2.927063</v>
+        <v>0.321305</v>
       </c>
       <c r="AC42" t="n">
-        <v>-5.912863</v>
+        <v>0.826902</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="B43" t="n">
-        <v>130260</v>
+        <v>135067</v>
       </c>
       <c r="C43" t="n">
-        <v>127.300003</v>
+        <v>131.630005</v>
       </c>
       <c r="D43" t="n">
-        <v>93.41999800000001</v>
+        <v>101.5</v>
       </c>
       <c r="E43" t="n">
-        <v>358.700012</v>
+        <v>354.350006</v>
       </c>
       <c r="F43" t="n">
-        <v>5.7581</v>
+        <v>5.62</v>
       </c>
       <c r="G43" t="n">
-        <v>6.22665</v>
+        <v>6.393862</v>
       </c>
       <c r="H43" t="n">
-        <v>5611.850098</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
+        <v>5569.060059</v>
+      </c>
+      <c r="I43" t="n">
+        <v>17446.339844</v>
+      </c>
       <c r="J43" t="n">
-        <v>42001.761719</v>
+        <v>40669.359375</v>
       </c>
       <c r="K43" t="n">
-        <v>3122.800049</v>
+        <v>3319.100098</v>
       </c>
       <c r="L43" t="n">
-        <v>71.480003</v>
+        <v>58.209999</v>
       </c>
       <c r="M43" t="n">
-        <v>74.739998</v>
+        <v>63.119999</v>
       </c>
       <c r="N43" t="n">
-        <v>1014.75</v>
+        <v>1034.75</v>
       </c>
       <c r="O43" t="n">
-        <v>457.25</v>
+        <v>467.25</v>
       </c>
       <c r="P43" t="n">
-        <v>6.075782</v>
+        <v>3.690312</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.074494</v>
+        <v>3.401415</v>
       </c>
       <c r="R43" t="n">
-        <v>6.643835</v>
+        <v>8.649114000000001</v>
       </c>
       <c r="S43" t="n">
-        <v>-8.658008000000001</v>
+        <v>-1.212714</v>
       </c>
       <c r="T43" t="n">
-        <v>-1.385514</v>
+        <v>-2.398363</v>
       </c>
       <c r="U43" t="n">
-        <v>2.677469</v>
+        <v>2.685417</v>
       </c>
       <c r="V43" t="n">
-        <v>-5.75447</v>
-      </c>
-      <c r="W43" t="inlineStr"/>
+        <v>-0.762494</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.850039</v>
+      </c>
       <c r="X43" t="n">
-        <v>-4.195051</v>
+        <v>-3.172253</v>
       </c>
       <c r="Y43" t="n">
-        <v>9.629631</v>
+        <v>6.286027</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.465598</v>
+        <v>-18.564639</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.131727</v>
+        <v>-15.547229</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.321305</v>
+        <v>1.970929</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.826902</v>
+        <v>2.186987</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45777</v>
+        <v>45808</v>
       </c>
       <c r="B44" t="n">
-        <v>135067</v>
+        <v>137027</v>
       </c>
       <c r="C44" t="n">
-        <v>131.630005</v>
+        <v>133.990005</v>
       </c>
       <c r="D44" t="n">
-        <v>101.5</v>
+        <v>107.639999</v>
       </c>
       <c r="E44" t="n">
-        <v>354.350006</v>
+        <v>378.799988</v>
       </c>
       <c r="F44" t="n">
-        <v>5.62</v>
+        <v>5.6651</v>
       </c>
       <c r="G44" t="n">
-        <v>6.393862</v>
+        <v>6.43915</v>
       </c>
       <c r="H44" t="n">
-        <v>5569.060059</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
+        <v>5911.689941</v>
+      </c>
+      <c r="I44" t="n">
+        <v>19113.769531</v>
+      </c>
       <c r="J44" t="n">
-        <v>40669.359375</v>
+        <v>42270.070312</v>
       </c>
       <c r="K44" t="n">
-        <v>3319.100098</v>
+        <v>3288.899902</v>
       </c>
       <c r="L44" t="n">
-        <v>58.209999</v>
+        <v>60.790001</v>
       </c>
       <c r="M44" t="n">
-        <v>63.119999</v>
+        <v>63.900002</v>
       </c>
       <c r="N44" t="n">
-        <v>1034.75</v>
+        <v>1041.75</v>
       </c>
       <c r="O44" t="n">
-        <v>467.25</v>
+        <v>444</v>
       </c>
       <c r="P44" t="n">
-        <v>3.690312</v>
+        <v>1.451132</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.401415</v>
+        <v>1.792905</v>
       </c>
       <c r="R44" t="n">
-        <v>8.649114000000001</v>
+        <v>6.04926</v>
       </c>
       <c r="S44" t="n">
-        <v>-1.212714</v>
+        <v>6.899952</v>
       </c>
       <c r="T44" t="n">
-        <v>-2.398363</v>
+        <v>0.802495</v>
       </c>
       <c r="U44" t="n">
-        <v>2.685417</v>
+        <v>0.708306</v>
       </c>
       <c r="V44" t="n">
-        <v>-0.762494</v>
-      </c>
-      <c r="W44" t="inlineStr"/>
+        <v>6.152383</v>
+      </c>
+      <c r="W44" t="n">
+        <v>9.557475999999999</v>
+      </c>
       <c r="X44" t="n">
-        <v>-3.172253</v>
+        <v>3.935914</v>
       </c>
       <c r="Y44" t="n">
-        <v>6.286027</v>
+        <v>-0.909891</v>
       </c>
       <c r="Z44" t="n">
-        <v>-18.564639</v>
+        <v>4.432231</v>
       </c>
       <c r="AA44" t="n">
-        <v>-15.547229</v>
+        <v>1.235746</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.970929</v>
+        <v>0.676492</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.186987</v>
+        <v>-4.975923</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45808</v>
+        <v>45838</v>
       </c>
       <c r="B45" t="n">
-        <v>137027</v>
+        <v>138855</v>
       </c>
       <c r="C45" t="n">
-        <v>133.990005</v>
+        <v>135.850006</v>
       </c>
       <c r="D45" t="n">
-        <v>107.639999</v>
+        <v>109.029999</v>
       </c>
       <c r="E45" t="n">
-        <v>378.799988</v>
+        <v>377.850006</v>
       </c>
       <c r="F45" t="n">
-        <v>5.6651</v>
+        <v>5.4784</v>
       </c>
       <c r="G45" t="n">
-        <v>6.43915</v>
+        <v>6.418485</v>
       </c>
       <c r="H45" t="n">
-        <v>5911.689941</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
+        <v>6204.950195</v>
+      </c>
+      <c r="I45" t="n">
+        <v>20369.730469</v>
+      </c>
       <c r="J45" t="n">
-        <v>42270.070312</v>
+        <v>44094.769531</v>
       </c>
       <c r="K45" t="n">
-        <v>3288.899902</v>
+        <v>3307.699951</v>
       </c>
       <c r="L45" t="n">
-        <v>60.790001</v>
+        <v>65.110001</v>
       </c>
       <c r="M45" t="n">
-        <v>63.900002</v>
+        <v>67.610001</v>
       </c>
       <c r="N45" t="n">
-        <v>1041.75</v>
+        <v>1024.25</v>
       </c>
       <c r="O45" t="n">
-        <v>444</v>
+        <v>420.5</v>
       </c>
       <c r="P45" t="n">
-        <v>1.451132</v>
+        <v>1.334044</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.792905</v>
+        <v>1.388164</v>
       </c>
       <c r="R45" t="n">
-        <v>6.04926</v>
+        <v>1.291341</v>
       </c>
       <c r="S45" t="n">
-        <v>6.899952</v>
+        <v>-0.250787</v>
       </c>
       <c r="T45" t="n">
-        <v>0.802495</v>
+        <v>-3.295615</v>
       </c>
       <c r="U45" t="n">
-        <v>0.708306</v>
+        <v>-0.320923</v>
       </c>
       <c r="V45" t="n">
-        <v>6.152383</v>
-      </c>
-      <c r="W45" t="inlineStr"/>
+        <v>4.960684</v>
+      </c>
+      <c r="W45" t="n">
+        <v>6.570975</v>
+      </c>
       <c r="X45" t="n">
-        <v>3.935914</v>
+        <v>4.316764</v>
       </c>
       <c r="Y45" t="n">
-        <v>-0.909891</v>
+        <v>0.571621</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.432231</v>
+        <v>7.106431</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.235746</v>
+        <v>5.805945</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.676492</v>
+        <v>-1.679866</v>
       </c>
       <c r="AC45" t="n">
-        <v>-4.975923</v>
+        <v>-5.292793</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45838</v>
+        <v>45869</v>
       </c>
       <c r="B46" t="n">
-        <v>138855</v>
+        <v>133071</v>
       </c>
       <c r="C46" t="n">
-        <v>135.850006</v>
+        <v>129.880005</v>
       </c>
       <c r="D46" t="n">
-        <v>109.029999</v>
+        <v>101.919998</v>
       </c>
       <c r="E46" t="n">
-        <v>377.850006</v>
+        <v>398.01001</v>
       </c>
       <c r="F46" t="n">
-        <v>5.4784</v>
+        <v>5.5754</v>
       </c>
       <c r="G46" t="n">
-        <v>6.418485</v>
+        <v>6.365372</v>
       </c>
       <c r="H46" t="n">
-        <v>6204.950195</v>
-      </c>
-      <c r="I46" t="inlineStr"/>
+        <v>6339.390137</v>
+      </c>
+      <c r="I46" t="n">
+        <v>21122.449219</v>
+      </c>
       <c r="J46" t="n">
-        <v>44094.769531</v>
+        <v>44130.980469</v>
       </c>
       <c r="K46" t="n">
-        <v>3307.699951</v>
+        <v>3293.199951</v>
       </c>
       <c r="L46" t="n">
-        <v>65.110001</v>
+        <v>69.260002</v>
       </c>
       <c r="M46" t="n">
-        <v>67.610001</v>
+        <v>72.529999</v>
       </c>
       <c r="N46" t="n">
-        <v>1024.25</v>
+        <v>961.75</v>
       </c>
       <c r="O46" t="n">
-        <v>420.5</v>
+        <v>394</v>
       </c>
       <c r="P46" t="n">
-        <v>1.334044</v>
+        <v>-4.165496</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.388164</v>
+        <v>-4.394554</v>
       </c>
       <c r="R46" t="n">
-        <v>1.291341</v>
+        <v>-6.521142</v>
       </c>
       <c r="S46" t="n">
-        <v>-0.250787</v>
+        <v>5.335451</v>
       </c>
       <c r="T46" t="n">
-        <v>-3.295615</v>
+        <v>1.770583</v>
       </c>
       <c r="U46" t="n">
-        <v>-0.320923</v>
+        <v>-0.8275</v>
       </c>
       <c r="V46" t="n">
-        <v>4.960684</v>
-      </c>
-      <c r="W46" t="inlineStr"/>
+        <v>2.166656</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.695281</v>
+      </c>
       <c r="X46" t="n">
-        <v>4.316764</v>
+        <v>0.082121</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.571621</v>
+        <v>-0.438371</v>
       </c>
       <c r="Z46" t="n">
-        <v>7.106431</v>
+        <v>6.373831</v>
       </c>
       <c r="AA46" t="n">
-        <v>5.805945</v>
+        <v>7.277027</v>
       </c>
       <c r="AB46" t="n">
-        <v>-1.679866</v>
+        <v>-6.102026</v>
       </c>
       <c r="AC46" t="n">
-        <v>-5.292793</v>
+        <v>-6.302021</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45869</v>
+        <v>45900</v>
       </c>
       <c r="B47" t="n">
-        <v>133071</v>
+        <v>141422</v>
       </c>
       <c r="C47" t="n">
-        <v>129.880005</v>
+        <v>138.5</v>
       </c>
       <c r="D47" t="n">
-        <v>101.919998</v>
+        <v>107.43</v>
       </c>
       <c r="E47" t="n">
-        <v>398.01001</v>
+        <v>393.850006</v>
       </c>
       <c r="F47" t="n">
-        <v>5.5754</v>
+        <v>5.413</v>
       </c>
       <c r="G47" t="n">
-        <v>6.365372</v>
+        <v>6.317119</v>
       </c>
       <c r="H47" t="n">
-        <v>6339.390137</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
+        <v>6460.259766</v>
+      </c>
+      <c r="I47" t="n">
+        <v>21455.550781</v>
+      </c>
       <c r="J47" t="n">
-        <v>44130.980469</v>
+        <v>45544.878906</v>
       </c>
       <c r="K47" t="n">
-        <v>3293.199951</v>
+        <v>3516.100098</v>
       </c>
       <c r="L47" t="n">
-        <v>69.260002</v>
+        <v>64.010002</v>
       </c>
       <c r="M47" t="n">
-        <v>72.529999</v>
+        <v>68.120003</v>
       </c>
       <c r="N47" t="n">
-        <v>961.75</v>
+        <v>1036.75</v>
       </c>
       <c r="O47" t="n">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="P47" t="n">
-        <v>-4.165496</v>
+        <v>6.275597</v>
       </c>
       <c r="Q47" t="n">
-        <v>-4.394554</v>
+        <v>6.636892</v>
       </c>
       <c r="R47" t="n">
-        <v>-6.521142</v>
+        <v>5.406203</v>
       </c>
       <c r="S47" t="n">
-        <v>5.335451</v>
+        <v>-1.045201</v>
       </c>
       <c r="T47" t="n">
-        <v>1.770583</v>
+        <v>-2.912791</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.8275</v>
+        <v>-0.758056</v>
       </c>
       <c r="V47" t="n">
-        <v>2.166656</v>
-      </c>
-      <c r="W47" t="inlineStr"/>
+        <v>1.906644</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.577003</v>
+      </c>
       <c r="X47" t="n">
-        <v>0.082121</v>
+        <v>3.203868</v>
       </c>
       <c r="Y47" t="n">
-        <v>-0.438371</v>
+        <v>6.768497</v>
       </c>
       <c r="Z47" t="n">
-        <v>6.373831</v>
+        <v>-7.580133</v>
       </c>
       <c r="AA47" t="n">
-        <v>7.277027</v>
+        <v>-6.080237</v>
       </c>
       <c r="AB47" t="n">
-        <v>-6.102026</v>
+        <v>7.798284</v>
       </c>
       <c r="AC47" t="n">
-        <v>-6.302021</v>
+        <v>1.015228</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45900</v>
+        <v>45930</v>
       </c>
       <c r="B48" t="n">
-        <v>141422</v>
+        <v>146237</v>
       </c>
       <c r="C48" t="n">
-        <v>138.5</v>
+        <v>143.240005</v>
       </c>
       <c r="D48" t="n">
-        <v>107.43</v>
+        <v>109.669998</v>
       </c>
       <c r="E48" t="n">
-        <v>393.850006</v>
+        <v>399.799988</v>
       </c>
       <c r="F48" t="n">
-        <v>5.413</v>
+        <v>5.3217</v>
       </c>
       <c r="G48" t="n">
-        <v>6.317119</v>
+        <v>6.238303</v>
       </c>
       <c r="H48" t="n">
-        <v>6460.259766</v>
-      </c>
-      <c r="I48" t="inlineStr"/>
+        <v>6688.459961</v>
+      </c>
+      <c r="I48" t="n">
+        <v>22660.009766</v>
+      </c>
       <c r="J48" t="n">
-        <v>45544.878906</v>
+        <v>46397.890625</v>
       </c>
       <c r="K48" t="n">
-        <v>3516.100098</v>
+        <v>3873.199951</v>
       </c>
       <c r="L48" t="n">
-        <v>64.010002</v>
+        <v>62.369999</v>
       </c>
       <c r="M48" t="n">
-        <v>68.120003</v>
+        <v>67.019997</v>
       </c>
       <c r="N48" t="n">
-        <v>1036.75</v>
+        <v>1001.75</v>
       </c>
       <c r="O48" t="n">
-        <v>398</v>
+        <v>415.5</v>
       </c>
       <c r="P48" t="n">
-        <v>6.275597</v>
+        <v>3.404704</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.636892</v>
+        <v>3.422387</v>
       </c>
       <c r="R48" t="n">
-        <v>5.406203</v>
+        <v>2.085077</v>
       </c>
       <c r="S48" t="n">
-        <v>-1.045201</v>
+        <v>1.510723</v>
       </c>
       <c r="T48" t="n">
-        <v>-2.912791</v>
+        <v>-1.68668</v>
       </c>
       <c r="U48" t="n">
-        <v>-0.758056</v>
+        <v>-1.247656</v>
       </c>
       <c r="V48" t="n">
-        <v>1.906644</v>
-      </c>
-      <c r="W48" t="inlineStr"/>
+        <v>3.532369</v>
+      </c>
+      <c r="W48" t="n">
+        <v>5.613741</v>
+      </c>
       <c r="X48" t="n">
-        <v>3.203868</v>
+        <v>1.872904</v>
       </c>
       <c r="Y48" t="n">
-        <v>6.768497</v>
+        <v>10.156134</v>
       </c>
       <c r="Z48" t="n">
-        <v>-7.580133</v>
+        <v>-2.562105</v>
       </c>
       <c r="AA48" t="n">
-        <v>-6.080237</v>
+        <v>-1.614806</v>
       </c>
       <c r="AB48" t="n">
-        <v>7.798284</v>
+        <v>-3.375934</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.015228</v>
+        <v>4.396985</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45930</v>
+        <v>45961</v>
       </c>
       <c r="B49" t="n">
-        <v>146237</v>
+        <v>149540</v>
       </c>
       <c r="C49" t="n">
-        <v>143.240005</v>
+        <v>146.410004</v>
       </c>
       <c r="D49" t="n">
-        <v>109.669998</v>
+        <v>110.059998</v>
       </c>
       <c r="E49" t="n">
-        <v>399.799988</v>
+        <v>413.329987</v>
       </c>
       <c r="F49" t="n">
-        <v>5.3217</v>
+        <v>5.382</v>
       </c>
       <c r="G49" t="n">
-        <v>6.238303</v>
+        <v>6.222775</v>
       </c>
       <c r="H49" t="n">
-        <v>6688.459961</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
+        <v>6840.200195</v>
+      </c>
+      <c r="I49" t="n">
+        <v>23724.960938</v>
+      </c>
       <c r="J49" t="n">
-        <v>46397.890625</v>
+        <v>47562.871094</v>
       </c>
       <c r="K49" t="n">
-        <v>3873.199951</v>
+        <v>3996.5</v>
       </c>
       <c r="L49" t="n">
-        <v>62.369999</v>
+        <v>60.98</v>
       </c>
       <c r="M49" t="n">
-        <v>67.019997</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>1001.75</v>
+        <v>1099.75</v>
       </c>
       <c r="O49" t="n">
-        <v>415.5</v>
+        <v>431.5</v>
       </c>
       <c r="P49" t="n">
-        <v>3.404704</v>
+        <v>2.258662</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.422387</v>
+        <v>2.213068</v>
       </c>
       <c r="R49" t="n">
-        <v>2.085077</v>
+        <v>0.355612</v>
       </c>
       <c r="S49" t="n">
-        <v>1.510723</v>
+        <v>3.384192</v>
       </c>
       <c r="T49" t="n">
-        <v>-1.68668</v>
+        <v>1.133094</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.247656</v>
+        <v>-0.248917</v>
       </c>
       <c r="V49" t="n">
-        <v>3.532369</v>
-      </c>
-      <c r="W49" t="inlineStr"/>
+        <v>2.268687</v>
+      </c>
+      <c r="W49" t="n">
+        <v>4.699694</v>
+      </c>
       <c r="X49" t="n">
-        <v>1.872904</v>
+        <v>2.510848</v>
       </c>
       <c r="Y49" t="n">
-        <v>10.156134</v>
+        <v>3.183416</v>
       </c>
       <c r="Z49" t="n">
-        <v>-2.562105</v>
+        <v>-2.228635</v>
       </c>
       <c r="AA49" t="n">
-        <v>-1.614806</v>
+        <v>-2.909575</v>
       </c>
       <c r="AB49" t="n">
-        <v>-3.375934</v>
+        <v>9.78288</v>
       </c>
       <c r="AC49" t="n">
-        <v>4.396985</v>
+        <v>3.850782</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45961</v>
+        <v>45991</v>
       </c>
       <c r="B50" t="n">
-        <v>149540</v>
+        <v>159072</v>
       </c>
       <c r="C50" t="n">
-        <v>146.410004</v>
+        <v>155.850006</v>
       </c>
       <c r="D50" t="n">
-        <v>110.059998</v>
+        <v>116.489998</v>
       </c>
       <c r="E50" t="n">
-        <v>413.329987</v>
+        <v>411.089996</v>
       </c>
       <c r="F50" t="n">
-        <v>5.382</v>
+        <v>5.3554</v>
       </c>
       <c r="G50" t="n">
-        <v>6.222775</v>
+        <v>6.207325</v>
       </c>
       <c r="H50" t="n">
-        <v>6840.200195</v>
-      </c>
-      <c r="I50" t="inlineStr"/>
+        <v>6849.089844</v>
+      </c>
+      <c r="I50" t="n">
+        <v>23365.689453</v>
+      </c>
       <c r="J50" t="n">
-        <v>47562.871094</v>
+        <v>47716.421875</v>
       </c>
       <c r="K50" t="n">
-        <v>3996.5</v>
+        <v>4254.899902</v>
       </c>
       <c r="L50" t="n">
-        <v>60.98</v>
+        <v>58.549999</v>
       </c>
       <c r="M50" t="n">
-        <v>65.06999999999999</v>
+        <v>63.200001</v>
       </c>
       <c r="N50" t="n">
-        <v>1099.75</v>
+        <v>1137.75</v>
       </c>
       <c r="O50" t="n">
-        <v>431.5</v>
+        <v>435.5</v>
       </c>
       <c r="P50" t="n">
-        <v>2.258662</v>
+        <v>6.374214</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.213068</v>
+        <v>6.447649</v>
       </c>
       <c r="R50" t="n">
-        <v>0.355612</v>
+        <v>5.842268</v>
       </c>
       <c r="S50" t="n">
-        <v>3.384192</v>
+        <v>-0.541938</v>
       </c>
       <c r="T50" t="n">
-        <v>1.133094</v>
+        <v>-0.494238</v>
       </c>
       <c r="U50" t="n">
-        <v>-0.248917</v>
+        <v>-0.248282</v>
       </c>
       <c r="V50" t="n">
-        <v>2.268687</v>
-      </c>
-      <c r="W50" t="inlineStr"/>
+        <v>0.129962</v>
+      </c>
+      <c r="W50" t="n">
+        <v>-1.514319</v>
+      </c>
       <c r="X50" t="n">
-        <v>2.510848</v>
+        <v>0.322837</v>
       </c>
       <c r="Y50" t="n">
-        <v>3.183416</v>
+        <v>6.465655</v>
       </c>
       <c r="Z50" t="n">
-        <v>-2.228635</v>
+        <v>-3.984914</v>
       </c>
       <c r="AA50" t="n">
-        <v>-2.909575</v>
+        <v>-2.873827</v>
       </c>
       <c r="AB50" t="n">
-        <v>9.78288</v>
+        <v>3.455331</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.850782</v>
+        <v>0.926999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45991</v>
+        <v>46022</v>
       </c>
       <c r="B51" t="n">
-        <v>159072</v>
+        <v>161125</v>
       </c>
       <c r="C51" t="n">
-        <v>155.850006</v>
+        <v>158</v>
       </c>
       <c r="D51" t="n">
-        <v>116.489998</v>
+        <v>112.449997</v>
       </c>
       <c r="E51" t="n">
-        <v>411.089996</v>
+        <v>424.200012</v>
       </c>
       <c r="F51" t="n">
-        <v>5.3554</v>
+        <v>5.4762</v>
       </c>
       <c r="G51" t="n">
-        <v>6.207325</v>
+        <v>6.426735</v>
       </c>
       <c r="H51" t="n">
-        <v>6849.089844</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
+        <v>6845.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>23241.990234</v>
+      </c>
       <c r="J51" t="n">
-        <v>47716.421875</v>
+        <v>48063.289062</v>
       </c>
       <c r="K51" t="n">
-        <v>4254.899902</v>
+        <v>4341.100098</v>
       </c>
       <c r="L51" t="n">
-        <v>58.549999</v>
+        <v>57.419998</v>
       </c>
       <c r="M51" t="n">
-        <v>63.200001</v>
+        <v>60.849998</v>
       </c>
       <c r="N51" t="n">
-        <v>1137.75</v>
+        <v>1030.5</v>
       </c>
       <c r="O51" t="n">
-        <v>435.5</v>
+        <v>440.25</v>
       </c>
       <c r="P51" t="n">
-        <v>6.374214</v>
+        <v>1.290611</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.447649</v>
+        <v>1.379528</v>
       </c>
       <c r="R51" t="n">
-        <v>5.842268</v>
+        <v>-3.46811</v>
       </c>
       <c r="S51" t="n">
-        <v>-0.541938</v>
+        <v>3.189087</v>
       </c>
       <c r="T51" t="n">
-        <v>-0.494238</v>
+        <v>2.255667</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.248282</v>
+        <v>3.534694</v>
       </c>
       <c r="V51" t="n">
-        <v>0.129962</v>
-      </c>
-      <c r="W51" t="inlineStr"/>
+        <v>-0.052413</v>
+      </c>
+      <c r="W51" t="n">
+        <v>-0.529405</v>
+      </c>
       <c r="X51" t="n">
-        <v>0.322837</v>
+        <v>0.726935</v>
       </c>
       <c r="Y51" t="n">
-        <v>6.465655</v>
+        <v>2.025904</v>
       </c>
       <c r="Z51" t="n">
-        <v>-3.984914</v>
+        <v>-1.929976</v>
       </c>
       <c r="AA51" t="n">
-        <v>-2.873827</v>
+        <v>-3.718358</v>
       </c>
       <c r="AB51" t="n">
-        <v>3.455331</v>
+        <v>-9.426500000000001</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.926999</v>
+        <v>1.0907</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="B52" t="n">
-        <v>161125</v>
+        <v>181364</v>
       </c>
       <c r="C52" t="n">
-        <v>158</v>
+        <v>178.199997</v>
       </c>
       <c r="D52" t="n">
-        <v>112.449997</v>
+        <v>123.800003</v>
       </c>
       <c r="E52" t="n">
-        <v>424.200012</v>
+        <v>410.649994</v>
       </c>
       <c r="F52" t="n">
-        <v>5.4762</v>
+        <v>5.1892</v>
       </c>
       <c r="G52" t="n">
-        <v>6.426735</v>
+        <v>6.203474</v>
       </c>
       <c r="H52" t="n">
-        <v>6845.5</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
+        <v>6939.029785</v>
+      </c>
+      <c r="I52" t="n">
+        <v>23461.820312</v>
+      </c>
       <c r="J52" t="n">
-        <v>48063.289062</v>
+        <v>48892.46875</v>
       </c>
       <c r="K52" t="n">
-        <v>4341.100098</v>
+        <v>4745.100098</v>
       </c>
       <c r="L52" t="n">
-        <v>57.419998</v>
+        <v>65.209999</v>
       </c>
       <c r="M52" t="n">
-        <v>60.849998</v>
+        <v>70.69000200000001</v>
       </c>
       <c r="N52" t="n">
-        <v>1030.5</v>
+        <v>1064.25</v>
       </c>
       <c r="O52" t="n">
-        <v>440.25</v>
+        <v>428.25</v>
       </c>
       <c r="P52" t="n">
-        <v>1.290611</v>
+        <v>12.561055</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.379528</v>
+        <v>12.784808</v>
       </c>
       <c r="R52" t="n">
-        <v>-3.46811</v>
+        <v>10.093381</v>
       </c>
       <c r="S52" t="n">
-        <v>3.189087</v>
+        <v>-3.194252</v>
       </c>
       <c r="T52" t="n">
-        <v>2.255667</v>
+        <v>-5.240864</v>
       </c>
       <c r="U52" t="n">
-        <v>3.534694</v>
+        <v>-3.473939</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.052413</v>
-      </c>
-      <c r="W52" t="inlineStr"/>
+        <v>1.366296</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.945832</v>
+      </c>
       <c r="X52" t="n">
-        <v>0.726935</v>
+        <v>1.725183</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.025904</v>
+        <v>9.306397</v>
       </c>
       <c r="Z52" t="n">
-        <v>-1.929976</v>
+        <v>13.566704</v>
       </c>
       <c r="AA52" t="n">
-        <v>-3.718358</v>
+        <v>16.170919</v>
       </c>
       <c r="AB52" t="n">
-        <v>-9.426500000000001</v>
+        <v>3.275109</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.0907</v>
+        <v>-2.725724</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="B53" t="n">
-        <v>181364</v>
+        <v>188787</v>
       </c>
       <c r="C53" t="n">
-        <v>178.199997</v>
+        <v>185.160004</v>
       </c>
       <c r="D53" t="n">
-        <v>123.800003</v>
+        <v>126.379997</v>
       </c>
       <c r="E53" t="n">
-        <v>410.649994</v>
+        <v>396.75</v>
       </c>
       <c r="F53" t="n">
-        <v>5.1892</v>
+        <v>5.1366</v>
       </c>
       <c r="G53" t="n">
-        <v>6.203474</v>
+        <v>6.056935</v>
       </c>
       <c r="H53" t="n">
-        <v>6939.029785</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
+        <v>6878.879883</v>
+      </c>
+      <c r="I53" t="n">
+        <v>22668.210938</v>
+      </c>
       <c r="J53" t="n">
-        <v>48892.46875</v>
+        <v>48977.921875</v>
       </c>
       <c r="K53" t="n">
-        <v>4745.100098</v>
+        <v>5247.899902</v>
       </c>
       <c r="L53" t="n">
-        <v>65.209999</v>
+        <v>67.019997</v>
       </c>
       <c r="M53" t="n">
-        <v>70.69000200000001</v>
+        <v>72.480003</v>
       </c>
       <c r="N53" t="n">
-        <v>1064.25</v>
+        <v>1157.25</v>
       </c>
       <c r="O53" t="n">
-        <v>428.25</v>
+        <v>438.75</v>
       </c>
       <c r="P53" t="n">
-        <v>12.561055</v>
+        <v>4.092874</v>
       </c>
       <c r="Q53" t="n">
-        <v>12.784808</v>
+        <v>3.905728</v>
       </c>
       <c r="R53" t="n">
-        <v>10.093381</v>
+        <v>2.084002</v>
       </c>
       <c r="S53" t="n">
-        <v>-3.194252</v>
+        <v>-3.384876</v>
       </c>
       <c r="T53" t="n">
-        <v>-5.240864</v>
+        <v>-1.013642</v>
       </c>
       <c r="U53" t="n">
-        <v>-3.473939</v>
+        <v>-2.362212</v>
       </c>
       <c r="V53" t="n">
-        <v>1.366296</v>
-      </c>
-      <c r="W53" t="inlineStr"/>
+        <v>-0.866834</v>
+      </c>
+      <c r="W53" t="n">
+        <v>-3.382557</v>
+      </c>
       <c r="X53" t="n">
-        <v>1.725183</v>
+        <v>0.174778</v>
       </c>
       <c r="Y53" t="n">
-        <v>9.306397</v>
+        <v>10.59619</v>
       </c>
       <c r="Z53" t="n">
-        <v>13.566704</v>
+        <v>2.775644</v>
       </c>
       <c r="AA53" t="n">
-        <v>16.170919</v>
+        <v>2.532184</v>
       </c>
       <c r="AB53" t="n">
-        <v>3.275109</v>
+        <v>8.738548</v>
       </c>
       <c r="AC53" t="n">
-        <v>-2.725724</v>
+        <v>2.451839</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>46081</v>
+        <v>46112</v>
       </c>
       <c r="B54" t="n">
-        <v>188787</v>
+        <v>187462</v>
       </c>
       <c r="C54" t="n">
-        <v>185.160004</v>
+        <v>184.279999</v>
       </c>
       <c r="D54" t="n">
-        <v>126.379997</v>
+        <v>120</v>
       </c>
       <c r="E54" t="n">
-        <v>396.75</v>
+        <v>380.149994</v>
       </c>
       <c r="F54" t="n">
-        <v>5.1366</v>
+        <v>5.264</v>
       </c>
       <c r="G54" t="n">
-        <v>6.056935</v>
+        <v>6.027728</v>
       </c>
       <c r="H54" t="n">
-        <v>6878.879883</v>
-      </c>
-      <c r="I54" t="inlineStr"/>
+        <v>6528.52002</v>
+      </c>
+      <c r="I54" t="n">
+        <v>21590.630859</v>
+      </c>
       <c r="J54" t="n">
-        <v>48977.921875</v>
+        <v>46341.511719</v>
       </c>
       <c r="K54" t="n">
-        <v>5247.899902</v>
+        <v>4647.600098</v>
       </c>
       <c r="L54" t="n">
-        <v>67.019997</v>
+        <v>101.379997</v>
       </c>
       <c r="M54" t="n">
-        <v>72.480003</v>
+        <v>118.349998</v>
       </c>
       <c r="N54" t="n">
-        <v>1157.25</v>
+        <v>1171</v>
       </c>
       <c r="O54" t="n">
-        <v>438.75</v>
+        <v>457.75</v>
       </c>
       <c r="P54" t="n">
-        <v>4.092874</v>
+        <v>-0.7018489999999999</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.905728</v>
+        <v>-0.475267</v>
       </c>
       <c r="R54" t="n">
-        <v>2.084002</v>
+        <v>-5.048265</v>
       </c>
       <c r="S54" t="n">
-        <v>-3.384876</v>
+        <v>-4.183996</v>
       </c>
       <c r="T54" t="n">
-        <v>-1.013642</v>
+        <v>2.480238</v>
       </c>
       <c r="U54" t="n">
-        <v>-2.362212</v>
+        <v>-0.482204</v>
       </c>
       <c r="V54" t="n">
-        <v>-0.866834</v>
-      </c>
-      <c r="W54" t="inlineStr"/>
+        <v>-5.093269</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-4.753706</v>
+      </c>
       <c r="X54" t="n">
-        <v>0.174778</v>
+        <v>-5.382854</v>
       </c>
       <c r="Y54" t="n">
-        <v>10.59619</v>
+        <v>-11.438858</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.775644</v>
+        <v>51.268282</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.532184</v>
+        <v>63.286414</v>
       </c>
       <c r="AB54" t="n">
-        <v>8.738548</v>
+        <v>1.188162</v>
       </c>
       <c r="AC54" t="n">
-        <v>2.451839</v>
+        <v>4.330484</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>46112</v>
+        <v>46142</v>
       </c>
       <c r="B55" t="n">
-        <v>187462</v>
+        <v>187318</v>
       </c>
       <c r="C55" t="n">
-        <v>184.279999</v>
+        <v>184.089996</v>
       </c>
       <c r="D55" t="n">
-        <v>120</v>
+        <v>115.760002</v>
       </c>
       <c r="E55" t="n">
-        <v>380.149994</v>
+        <v>402.5</v>
       </c>
       <c r="F55" t="n">
-        <v>5.264</v>
+        <v>5.0175</v>
       </c>
       <c r="G55" t="n">
-        <v>6.027728</v>
+        <v>5.858231</v>
       </c>
       <c r="H55" t="n">
-        <v>6528.52002</v>
-      </c>
-      <c r="I55" t="inlineStr"/>
+        <v>7209.009766</v>
+      </c>
+      <c r="I55" t="n">
+        <v>24892.310547</v>
+      </c>
       <c r="J55" t="n">
-        <v>46341.511719</v>
+        <v>49652.140625</v>
       </c>
       <c r="K55" t="n">
-        <v>4647.600098</v>
+        <v>4629.600098</v>
       </c>
       <c r="L55" t="n">
-        <v>101.379997</v>
+        <v>105.07</v>
       </c>
       <c r="M55" t="n">
-        <v>118.349998</v>
+        <v>114.010002</v>
       </c>
       <c r="N55" t="n">
-        <v>1171</v>
+        <v>1182</v>
       </c>
       <c r="O55" t="n">
-        <v>457.75</v>
+        <v>464.75</v>
       </c>
       <c r="P55" t="n">
-        <v>-0.7018489999999999</v>
+        <v>-0.076816</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.475267</v>
+        <v>-0.103105</v>
       </c>
       <c r="R55" t="n">
-        <v>-5.048265</v>
+        <v>-3.533332</v>
       </c>
       <c r="S55" t="n">
-        <v>-4.183996</v>
+        <v>5.87926</v>
       </c>
       <c r="T55" t="n">
-        <v>2.480238</v>
+        <v>-4.682751</v>
       </c>
       <c r="U55" t="n">
-        <v>-0.482204</v>
+        <v>-2.811955</v>
       </c>
       <c r="V55" t="n">
-        <v>-5.093269</v>
-      </c>
-      <c r="W55" t="inlineStr"/>
+        <v>10.423339</v>
+      </c>
+      <c r="W55" t="n">
+        <v>15.292187</v>
+      </c>
       <c r="X55" t="n">
-        <v>-5.382854</v>
+        <v>7.143981</v>
       </c>
       <c r="Y55" t="n">
-        <v>-11.438858</v>
+        <v>-0.387297</v>
       </c>
       <c r="Z55" t="n">
-        <v>51.268282</v>
+        <v>3.639774</v>
       </c>
       <c r="AA55" t="n">
-        <v>63.286414</v>
+        <v>-3.667086</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.188162</v>
+        <v>0.939368</v>
       </c>
       <c r="AC55" t="n">
-        <v>4.330484</v>
+        <v>1.529219</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>46142</v>
+        <v>46173</v>
       </c>
       <c r="B56" t="n">
-        <v>187318</v>
+        <v>173788</v>
       </c>
       <c r="C56" t="n">
-        <v>184.089996</v>
+        <v>170.75</v>
       </c>
       <c r="D56" t="n">
-        <v>115.760002</v>
+        <v>110.989998</v>
       </c>
       <c r="E56" t="n">
-        <v>402.5</v>
+        <v>430.399994</v>
       </c>
       <c r="F56" t="n">
-        <v>5.0175</v>
+        <v>5.0517</v>
       </c>
       <c r="G56" t="n">
-        <v>5.858231</v>
+        <v>5.882353</v>
       </c>
       <c r="H56" t="n">
-        <v>7209.009766</v>
-      </c>
-      <c r="I56" t="inlineStr"/>
+        <v>7580.060059</v>
+      </c>
+      <c r="I56" t="n">
+        <v>26972.619141</v>
+      </c>
       <c r="J56" t="n">
-        <v>49652.140625</v>
+        <v>51032.460938</v>
       </c>
       <c r="K56" t="n">
-        <v>4629.600098</v>
+        <v>4593</v>
       </c>
       <c r="L56" t="n">
-        <v>105.07</v>
+        <v>87.360001</v>
       </c>
       <c r="M56" t="n">
-        <v>114.010002</v>
+        <v>92.050003</v>
       </c>
       <c r="N56" t="n">
-        <v>1182</v>
+        <v>1186.75</v>
       </c>
       <c r="O56" t="n">
-        <v>464.75</v>
+        <v>446.75</v>
       </c>
       <c r="P56" t="n">
-        <v>-0.076816</v>
+        <v>-7.223011</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.103105</v>
+        <v>-7.246454</v>
       </c>
       <c r="R56" t="n">
-        <v>-3.533332</v>
+        <v>-4.120598</v>
       </c>
       <c r="S56" t="n">
-        <v>5.87926</v>
+        <v>6.931676</v>
       </c>
       <c r="T56" t="n">
-        <v>-4.682751</v>
+        <v>0.6816179999999999</v>
       </c>
       <c r="U56" t="n">
-        <v>-2.811955</v>
+        <v>0.411758</v>
       </c>
       <c r="V56" t="n">
-        <v>10.423339</v>
-      </c>
-      <c r="W56" t="inlineStr"/>
+        <v>5.147036</v>
+      </c>
+      <c r="W56" t="n">
+        <v>8.357234</v>
+      </c>
       <c r="X56" t="n">
-        <v>7.143981</v>
+        <v>2.779981</v>
       </c>
       <c r="Y56" t="n">
-        <v>-0.387297</v>
+        <v>-0.790567</v>
       </c>
       <c r="Z56" t="n">
-        <v>3.639774</v>
+        <v>-16.855429</v>
       </c>
       <c r="AA56" t="n">
-        <v>-3.667086</v>
+        <v>-19.261467</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.939368</v>
+        <v>0.401861</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.529219</v>
+        <v>-3.87305</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>46173</v>
+        <v>46203</v>
       </c>
       <c r="B57" t="n">
-        <v>173788</v>
+        <v>172024</v>
       </c>
       <c r="C57" t="n">
-        <v>170.75</v>
+        <v>169.050003</v>
       </c>
       <c r="D57" t="n">
-        <v>110.989998</v>
+        <v>107.980003</v>
       </c>
       <c r="E57" t="n">
-        <v>430.399994</v>
+        <v>435.649994</v>
       </c>
       <c r="F57" t="n">
-        <v>5.0517</v>
+        <v>5.181787</v>
       </c>
       <c r="G57" t="n">
-        <v>5.882353</v>
+        <v>5.91716</v>
       </c>
       <c r="H57" t="n">
-        <v>7580.060059</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
+        <v>7499.359863</v>
+      </c>
+      <c r="I57" t="n">
+        <v>26213.720703</v>
+      </c>
       <c r="J57" t="n">
-        <v>51032.460938</v>
+        <v>52319.199219</v>
       </c>
       <c r="K57" t="n">
-        <v>4593</v>
+        <v>4038.5</v>
       </c>
       <c r="L57" t="n">
-        <v>87.360001</v>
+        <v>69.5</v>
       </c>
       <c r="M57" t="n">
-        <v>92.050003</v>
+        <v>72.91999800000001</v>
       </c>
       <c r="N57" t="n">
-        <v>1186.75</v>
+        <v>1116.75</v>
       </c>
       <c r="O57" t="n">
-        <v>446.75</v>
+        <v>412.75</v>
       </c>
       <c r="P57" t="n">
-        <v>-7.223011</v>
+        <v>-1.01503</v>
       </c>
       <c r="Q57" t="n">
-        <v>-7.246454</v>
+        <v>-0.995606</v>
       </c>
       <c r="R57" t="n">
-        <v>-4.120598</v>
+        <v>-2.711951</v>
       </c>
       <c r="S57" t="n">
-        <v>6.931676</v>
+        <v>1.219796</v>
       </c>
       <c r="T57" t="n">
-        <v>0.6816179999999999</v>
+        <v>2.575111</v>
       </c>
       <c r="U57" t="n">
-        <v>0.411758</v>
+        <v>0.591722</v>
       </c>
       <c r="V57" t="n">
-        <v>5.147036</v>
-      </c>
-      <c r="W57" t="inlineStr"/>
+        <v>-1.064638</v>
+      </c>
+      <c r="W57" t="n">
+        <v>-2.813588</v>
+      </c>
       <c r="X57" t="n">
-        <v>2.779981</v>
+        <v>2.521411</v>
       </c>
       <c r="Y57" t="n">
-        <v>-0.790567</v>
+        <v>-12.072719</v>
       </c>
       <c r="Z57" t="n">
-        <v>-16.855429</v>
+        <v>-20.44414</v>
       </c>
       <c r="AA57" t="n">
-        <v>-19.261467</v>
+        <v>-20.782188</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.401861</v>
+        <v>-5.898462</v>
       </c>
       <c r="AC57" t="n">
-        <v>-3.87305</v>
+        <v>-7.61052</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
-        <v>172024</v>
+        <v>177999</v>
       </c>
       <c r="C58" t="n">
-        <v>169.050003</v>
+        <v>175.020004</v>
       </c>
       <c r="D58" t="n">
-        <v>107.980003</v>
+        <v>107.25</v>
       </c>
       <c r="E58" t="n">
-        <v>435.649994</v>
+        <v>428.390015</v>
       </c>
       <c r="F58" t="n">
-        <v>5.181787</v>
+        <v>5.0781</v>
       </c>
       <c r="G58" t="n">
-        <v>5.91716</v>
+        <v>5.847953</v>
       </c>
       <c r="H58" t="n">
-        <v>7499.359863</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
+        <v>7489.720215</v>
+      </c>
+      <c r="I58" t="n">
+        <v>25373.849609</v>
+      </c>
       <c r="J58" t="n">
-        <v>52319.199219</v>
+        <v>52485.03125</v>
       </c>
       <c r="K58" t="n">
-        <v>4038.5</v>
+        <v>4107</v>
       </c>
       <c r="L58" t="n">
-        <v>69.5</v>
+        <v>84.66999800000001</v>
       </c>
       <c r="M58" t="n">
-        <v>72.91999800000001</v>
+        <v>90.120003</v>
       </c>
       <c r="N58" t="n">
-        <v>1116.75</v>
+        <v>1172</v>
       </c>
       <c r="O58" t="n">
-        <v>412.75</v>
+        <v>440.75</v>
       </c>
       <c r="P58" t="n">
-        <v>-1.01503</v>
+        <v>3.473353</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.995606</v>
+        <v>3.5315</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.711951</v>
+        <v>-0.676054</v>
       </c>
       <c r="S58" t="n">
-        <v>1.219796</v>
+        <v>-1.666471</v>
       </c>
       <c r="T58" t="n">
-        <v>2.575111</v>
+        <v>-2.000986</v>
       </c>
       <c r="U58" t="n">
-        <v>0.591722</v>
+        <v>-1.169601</v>
       </c>
       <c r="V58" t="n">
-        <v>-1.064638</v>
-      </c>
-      <c r="W58" t="inlineStr"/>
+        <v>-0.12854</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-3.203937</v>
+      </c>
       <c r="X58" t="n">
-        <v>2.521411</v>
+        <v>0.316962</v>
       </c>
       <c r="Y58" t="n">
-        <v>-12.072719</v>
+        <v>1.696174</v>
       </c>
       <c r="Z58" t="n">
-        <v>-20.44414</v>
+        <v>21.827335</v>
       </c>
       <c r="AA58" t="n">
-        <v>-20.782188</v>
+        <v>23.5875</v>
       </c>
       <c r="AB58" t="n">
-        <v>-5.898462</v>
+        <v>4.947392</v>
       </c>
       <c r="AC58" t="n">
-        <v>-7.61052</v>
+        <v>6.783767</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="B59" t="n">
-        <v>177999</v>
+        <v>177419</v>
       </c>
       <c r="C59" t="n">
-        <v>175.020004</v>
+        <v>174.779999</v>
       </c>
       <c r="D59" t="n">
-        <v>107.25</v>
+        <v>106.129997</v>
       </c>
       <c r="E59" t="n">
-        <v>428.390015</v>
+        <v>449.350006</v>
       </c>
       <c r="F59" t="n">
-        <v>5.0781</v>
+        <v>5.1912</v>
       </c>
       <c r="G59" t="n">
-        <v>5.847953</v>
+        <v>6.009615</v>
       </c>
       <c r="H59" t="n">
-        <v>7489.720215</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
+        <v>7686.140137</v>
+      </c>
+      <c r="I59" t="n">
+        <v>26370.890625</v>
+      </c>
       <c r="J59" t="n">
-        <v>52485.03125</v>
+        <v>53185.898438</v>
       </c>
       <c r="K59" t="n">
-        <v>4107</v>
+        <v>4481.5</v>
       </c>
       <c r="L59" t="n">
-        <v>84.66999800000001</v>
+        <v>85.760002</v>
       </c>
       <c r="M59" t="n">
-        <v>90.120003</v>
+        <v>90.489998</v>
       </c>
       <c r="N59" t="n">
-        <v>1172</v>
+        <v>1275.25</v>
       </c>
       <c r="O59" t="n">
-        <v>440.75</v>
+        <v>515</v>
       </c>
       <c r="P59" t="n">
-        <v>3.473353</v>
+        <v>-0.325845</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.5315</v>
+        <v>-0.13713</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.676054</v>
+        <v>-1.044292</v>
       </c>
       <c r="S59" t="n">
-        <v>-1.666471</v>
+        <v>4.892736</v>
       </c>
       <c r="T59" t="n">
-        <v>-2.000986</v>
+        <v>2.227203</v>
       </c>
       <c r="U59" t="n">
-        <v>-1.169601</v>
+        <v>2.764422</v>
       </c>
       <c r="V59" t="n">
-        <v>-0.12854</v>
-      </c>
-      <c r="W59" t="inlineStr"/>
+        <v>2.622527</v>
+      </c>
+      <c r="W59" t="n">
+        <v>3.929404</v>
+      </c>
       <c r="X59" t="n">
-        <v>0.316962</v>
+        <v>1.335366</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.696174</v>
+        <v>9.118577999999999</v>
       </c>
       <c r="Z59" t="n">
-        <v>21.827335</v>
+        <v>1.287356</v>
       </c>
       <c r="AA59" t="n">
-        <v>23.5875</v>
+        <v>0.410558</v>
       </c>
       <c r="AB59" t="n">
-        <v>4.947392</v>
+        <v>8.809727000000001</v>
       </c>
       <c r="AC59" t="n">
-        <v>6.783767</v>
+        <v>16.846285</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>46265</v>
+        <v>46295</v>
       </c>
       <c r="B60" t="n">
-        <v>177419</v>
+        <v>186340</v>
       </c>
       <c r="C60" t="n">
-        <v>174.779999</v>
+        <v>184.080002</v>
       </c>
       <c r="D60" t="n">
-        <v>106.129997</v>
+        <v>111.93</v>
       </c>
       <c r="E60" t="n">
-        <v>449.350006</v>
+        <v>447.369995</v>
       </c>
       <c r="F60" t="n">
-        <v>5.1912</v>
+        <v>5.2029</v>
       </c>
       <c r="G60" t="n">
-        <v>6.009615</v>
+        <v>5.896226</v>
       </c>
       <c r="H60" t="n">
-        <v>7686.140137</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
+        <v>7651.540039</v>
+      </c>
+      <c r="I60" t="n">
+        <v>26861.060547</v>
+      </c>
       <c r="J60" t="n">
-        <v>53185.898438</v>
+        <v>50906.050781</v>
       </c>
       <c r="K60" t="n">
-        <v>4481.5</v>
+        <v>4186.700195</v>
       </c>
       <c r="L60" t="n">
-        <v>85.760002</v>
+        <v>90.41999800000001</v>
       </c>
       <c r="M60" t="n">
-        <v>90.489998</v>
+        <v>103.529999</v>
       </c>
       <c r="N60" t="n">
-        <v>1275.25</v>
+        <v>1293</v>
       </c>
       <c r="O60" t="n">
-        <v>515</v>
+        <v>500.75</v>
       </c>
       <c r="P60" t="n">
-        <v>-0.325845</v>
+        <v>5.02821</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.13713</v>
+        <v>5.320977</v>
       </c>
       <c r="R60" t="n">
-        <v>-1.044292</v>
+        <v>5.464999</v>
       </c>
       <c r="S60" t="n">
-        <v>4.892736</v>
+        <v>-0.440639</v>
       </c>
       <c r="T60" t="n">
-        <v>2.227203</v>
+        <v>0.225384</v>
       </c>
       <c r="U60" t="n">
-        <v>2.764422</v>
+        <v>-1.886793</v>
       </c>
       <c r="V60" t="n">
-        <v>2.622527</v>
-      </c>
-      <c r="W60" t="inlineStr"/>
+        <v>-0.450162</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1.858754</v>
+      </c>
       <c r="X60" t="n">
-        <v>1.335366</v>
+        <v>-4.286564</v>
       </c>
       <c r="Y60" t="n">
-        <v>9.118577999999999</v>
+        <v>-6.57815</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.287356</v>
+        <v>5.433764</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.410558</v>
+        <v>14.410433</v>
       </c>
       <c r="AB60" t="n">
-        <v>8.809727000000001</v>
+        <v>1.391884</v>
       </c>
       <c r="AC60" t="n">
-        <v>16.846285</v>
+        <v>-2.76699</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>186340</v>
+        <v>168219.609375</v>
       </c>
       <c r="C61" t="n">
-        <v>184.080002</v>
+        <v>165.490005</v>
       </c>
       <c r="D61" t="n">
-        <v>111.93</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>447.369995</v>
+        <v>465.75</v>
       </c>
       <c r="F61" t="n">
-        <v>5.2029</v>
+        <v>5.4297</v>
       </c>
       <c r="G61" t="n">
-        <v>5.896226</v>
+        <v>6.0641</v>
       </c>
       <c r="H61" t="n">
-        <v>7651.540039</v>
-      </c>
-      <c r="I61" t="inlineStr"/>
+        <v>7594.609863</v>
+      </c>
+      <c r="I61" t="n">
+        <v>25479.597656</v>
+      </c>
       <c r="J61" t="n">
-        <v>50906.050781</v>
+        <v>51957.371094</v>
       </c>
       <c r="K61" t="n">
-        <v>4186.700195</v>
+        <v>3906</v>
       </c>
       <c r="L61" t="n">
-        <v>90.41999800000001</v>
+        <v>104.360001</v>
       </c>
       <c r="M61" t="n">
-        <v>103.529999</v>
+        <v>113.879997</v>
       </c>
       <c r="N61" t="n">
-        <v>1293</v>
+        <v>1235.25</v>
       </c>
       <c r="O61" t="n">
-        <v>500.75</v>
+        <v>447.75</v>
       </c>
       <c r="P61" t="n">
-        <v>5.02821</v>
+        <v>-9.72437</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.320977</v>
+        <v>-10.098868</v>
       </c>
       <c r="R61" t="n">
-        <v>5.464999</v>
+        <v>-17.966587</v>
       </c>
       <c r="S61" t="n">
-        <v>-0.440639</v>
+        <v>4.108457</v>
       </c>
       <c r="T61" t="n">
-        <v>0.225384</v>
+        <v>4.359107</v>
       </c>
       <c r="U61" t="n">
-        <v>-1.886793</v>
+        <v>2.847141</v>
       </c>
       <c r="V61" t="n">
-        <v>-0.450162</v>
-      </c>
-      <c r="W61" t="inlineStr"/>
+        <v>-0.744036</v>
+      </c>
+      <c r="W61" t="n">
+        <v>-5.142995</v>
+      </c>
       <c r="X61" t="n">
-        <v>-4.286564</v>
+        <v>2.065217</v>
       </c>
       <c r="Y61" t="n">
-        <v>-6.57815</v>
+        <v>-6.704569</v>
       </c>
       <c r="Z61" t="n">
-        <v>5.433764</v>
+        <v>15.416946</v>
       </c>
       <c r="AA61" t="n">
-        <v>14.410433</v>
+        <v>9.997101000000001</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.391884</v>
+        <v>-4.466357</v>
       </c>
       <c r="AC61" t="n">
-        <v>-2.76699</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>46326</v>
-      </c>
-      <c r="B62" t="n">
-        <v>169332.734375</v>
-      </c>
-      <c r="C62" t="n">
-        <v>166.600006</v>
-      </c>
-      <c r="D62" t="n">
-        <v>93.900002</v>
-      </c>
-      <c r="E62" t="n">
-        <v>471</v>
-      </c>
-      <c r="F62" t="n">
-        <v>5.4112</v>
-      </c>
-      <c r="G62" t="n">
-        <v>6.0453</v>
-      </c>
-      <c r="H62" t="n">
-        <v>7711.899902</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
-        <v>52266.71875</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4027.5</v>
-      </c>
-      <c r="L62" t="n">
-        <v>100.889999</v>
-      </c>
-      <c r="M62" t="n">
-        <v>109.889999</v>
-      </c>
-      <c r="N62" t="n">
-        <v>1235.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>452.5</v>
-      </c>
-      <c r="P62" t="n">
-        <v>-9.127007000000001</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>-9.495869000000001</v>
-      </c>
-      <c r="R62" t="n">
-        <v>-16.108281</v>
-      </c>
-      <c r="S62" t="n">
-        <v>5.281983</v>
-      </c>
-      <c r="T62" t="n">
-        <v>4.003539</v>
-      </c>
-      <c r="U62" t="n">
-        <v>2.528297</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0.788859</v>
-      </c>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="n">
-        <v>2.6729</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>-3.802522</v>
-      </c>
-      <c r="Z62" t="n">
-        <v>11.579298</v>
-      </c>
-      <c r="AA62" t="n">
-        <v>6.143148</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>-4.447022</v>
-      </c>
-      <c r="AC62" t="n">
-        <v>-9.635547000000001</v>
+        <v>-10.584124</v>
       </c>
     </row>
   </sheetData>

--- a/data/final/yahoo/base_yahoo_mensal_larga.xlsx
+++ b/data/final/yahoo/base_yahoo_mensal_larga.xlsx
@@ -5795,85 +5795,85 @@
         <v>46326</v>
       </c>
       <c r="B61" t="n">
-        <v>168219.609375</v>
+        <v>167922</v>
       </c>
       <c r="C61" t="n">
-        <v>165.490005</v>
+        <v>165.399994</v>
       </c>
       <c r="D61" t="n">
-        <v>91.81999999999999</v>
+        <v>92.150002</v>
       </c>
       <c r="E61" t="n">
-        <v>465.75</v>
+        <v>466.5</v>
       </c>
       <c r="F61" t="n">
-        <v>5.4297</v>
+        <v>5.3848</v>
       </c>
       <c r="G61" t="n">
-        <v>6.0641</v>
+        <v>6.0193</v>
       </c>
       <c r="H61" t="n">
-        <v>7594.609863</v>
+        <v>7580.069824</v>
       </c>
       <c r="I61" t="n">
-        <v>25479.597656</v>
+        <v>25437</v>
       </c>
       <c r="J61" t="n">
-        <v>51957.371094</v>
+        <v>51770.308594</v>
       </c>
       <c r="K61" t="n">
-        <v>3906</v>
+        <v>3898.899902</v>
       </c>
       <c r="L61" t="n">
-        <v>104.360001</v>
+        <v>104.120003</v>
       </c>
       <c r="M61" t="n">
-        <v>113.879997</v>
+        <v>117.639999</v>
       </c>
       <c r="N61" t="n">
-        <v>1235.25</v>
+        <v>1222.25</v>
       </c>
       <c r="O61" t="n">
         <v>447.75</v>
       </c>
       <c r="P61" t="n">
-        <v>-9.72437</v>
+        <v>-9.884083</v>
       </c>
       <c r="Q61" t="n">
-        <v>-10.098868</v>
+        <v>-10.147766</v>
       </c>
       <c r="R61" t="n">
-        <v>-17.966587</v>
+        <v>-17.671758</v>
       </c>
       <c r="S61" t="n">
-        <v>4.108457</v>
+        <v>4.276104</v>
       </c>
       <c r="T61" t="n">
-        <v>4.359107</v>
+        <v>3.496128</v>
       </c>
       <c r="U61" t="n">
-        <v>2.847141</v>
+        <v>2.087336</v>
       </c>
       <c r="V61" t="n">
-        <v>-0.744036</v>
+        <v>-0.934063</v>
       </c>
       <c r="W61" t="n">
-        <v>-5.142995</v>
+        <v>-5.30158</v>
       </c>
       <c r="X61" t="n">
-        <v>2.065217</v>
+        <v>1.697751</v>
       </c>
       <c r="Y61" t="n">
-        <v>-6.704569</v>
+        <v>-6.874156</v>
       </c>
       <c r="Z61" t="n">
-        <v>15.416946</v>
+        <v>15.151521</v>
       </c>
       <c r="AA61" t="n">
-        <v>9.997101000000001</v>
+        <v>13.628901</v>
       </c>
       <c r="AB61" t="n">
-        <v>-4.466357</v>
+        <v>-5.471771</v>
       </c>
       <c r="AC61" t="n">
         <v>-10.584124</v>
